--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25320" windowHeight="8145" firstSheet="3" activeTab="9"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25320" windowHeight="8145" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Расчёт колличества бетона " sheetId="2" r:id="rId1"/>
@@ -438,7 +438,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="943" uniqueCount="613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="619">
   <si>
     <t>№ п/п</t>
   </si>
@@ -2437,6 +2437,24 @@
   </si>
   <si>
     <t>Etimat</t>
+  </si>
+  <si>
+    <t>шина нулевая "стойка" 6x9 мм 12 групп на din рейку ekf - 1шт.</t>
+  </si>
+  <si>
+    <t>шина нулевая 6x9 мм 14 групп на din рейку ekf - 1шт.</t>
+  </si>
+  <si>
+    <t>din рейка 30 см оцинкованная 2 шт</t>
+  </si>
+  <si>
+    <t>шина соединительная 3 полюса 63А 12 мод ekf - 1шт</t>
+  </si>
+  <si>
+    <t>держатель для коронок bi-metal 32-152мм dorn pro</t>
+  </si>
+  <si>
+    <t>коронка bi-metal 8% по металлу/дереву 73мм dorn  pro</t>
   </si>
 </sst>
 </file>
@@ -2759,22 +2777,7 @@
   </cellStyles>
   <dxfs count="35">
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
@@ -2830,7 +2833,22 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
@@ -2909,14 +2927,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F323" totalsRowCount="1">
-  <autoFilter ref="B5:F322"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F343" totalsRowCount="1">
+  <autoFilter ref="B5:F342"/>
   <tableColumns count="5">
     <tableColumn id="1" name="№ п/п"/>
     <tableColumn id="2" name="Наименование "/>
-    <tableColumn id="3" name="Цена (руб)" totalsRowFunction="sum" dataDxfId="34" totalsRowDxfId="14"/>
+    <tableColumn id="3" name="Цена (руб)" totalsRowFunction="sum" dataDxfId="34" totalsRowDxfId="1"/>
     <tableColumn id="4" name="Примечание"/>
-    <tableColumn id="5" name="дата" dataDxfId="33" totalsRowDxfId="13"/>
+    <tableColumn id="5" name="дата" dataDxfId="33" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3050,15 +3068,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Таблица2" displayName="Таблица2" ref="A4:F28" totalsRowCount="1">
   <autoFilter ref="A4:F27"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="№ п/п" totalsRowLabel="Итого:" totalsRowDxfId="12"/>
-    <tableColumn id="2" name="Тип" totalsRowDxfId="11"/>
-    <tableColumn id="3" name="Количество (М3/шт)" totalsRowDxfId="10"/>
-    <tableColumn id="4" name="Цена  (м3 или штук)" dataDxfId="32" totalsRowDxfId="9"/>
-    <tableColumn id="5" name="Сумма" totalsRowFunction="custom" dataDxfId="31" totalsRowDxfId="8">
+    <tableColumn id="1" name="№ п/п" totalsRowLabel="Итого:" totalsRowDxfId="7"/>
+    <tableColumn id="2" name="Тип" totalsRowDxfId="6"/>
+    <tableColumn id="3" name="Количество (М3/шт)" totalsRowDxfId="5"/>
+    <tableColumn id="4" name="Цена  (м3 или штук)" dataDxfId="32" totalsRowDxfId="4"/>
+    <tableColumn id="5" name="Сумма" totalsRowFunction="custom" dataDxfId="31" totalsRowDxfId="3">
       <calculatedColumnFormula>Таблица2[[#This Row],[Цена  (м3 или штук)]]*Таблица2[[#This Row],[Количество (М3/шт)]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(E5:E27)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" name="Примечание" totalsRowDxfId="7"/>
+    <tableColumn id="6" name="Примечание" totalsRowDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3069,13 +3087,13 @@
   <autoFilter ref="E22:L35"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Комплектующие\Магазины"/>
-    <tableColumn id="2" name=" Legrand" dataDxfId="6"/>
-    <tableColumn id="6" name="Dekraft" dataDxfId="5"/>
-    <tableColumn id="7" name="EKF" dataDxfId="4"/>
-    <tableColumn id="8" name="TDM electric" dataDxfId="3"/>
-    <tableColumn id="9" name="IEK" dataDxfId="2"/>
-    <tableColumn id="10" name="Спец 800вт" dataDxfId="1"/>
-    <tableColumn id="11" name="Etimat" dataDxfId="0"/>
+    <tableColumn id="2" name=" Legrand" dataDxfId="14"/>
+    <tableColumn id="6" name="Dekraft" dataDxfId="13"/>
+    <tableColumn id="7" name="EKF" dataDxfId="12"/>
+    <tableColumn id="8" name="TDM electric" dataDxfId="11"/>
+    <tableColumn id="9" name="IEK" dataDxfId="10"/>
+    <tableColumn id="10" name="Спец 800вт" dataDxfId="9"/>
+    <tableColumn id="11" name="Etimat" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4143,7 +4161,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:F323"/>
+  <dimension ref="B3:F343"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="72.5703125" customWidth="1"/>
@@ -9167,27 +9185,149 @@
       </c>
     </row>
     <row r="319" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D319" s="7"/>
-      <c r="F319" s="9"/>
+      <c r="C319" t="s">
+        <v>613</v>
+      </c>
+      <c r="D319" s="7">
+        <v>125</v>
+      </c>
+      <c r="F319" s="9">
+        <v>46073</v>
+      </c>
     </row>
     <row r="320" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D320" s="7"/>
-      <c r="F320" s="9"/>
-    </row>
-    <row r="321" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D321" s="7"/>
-      <c r="F321" s="9"/>
-    </row>
-    <row r="322" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D322" s="7"/>
-      <c r="F322" s="9"/>
-    </row>
-    <row r="323" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="C320" t="s">
+        <v>614</v>
+      </c>
+      <c r="D320" s="7">
+        <v>209</v>
+      </c>
+      <c r="F320" s="9">
+        <v>46073</v>
+      </c>
+    </row>
+    <row r="321" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C321" t="s">
+        <v>615</v>
+      </c>
+      <c r="D321" s="7">
+        <v>138</v>
+      </c>
+      <c r="F321" s="9">
+        <v>46073</v>
+      </c>
+    </row>
+    <row r="322" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C322" t="s">
+        <v>616</v>
+      </c>
+      <c r="D322" s="7">
+        <v>539</v>
+      </c>
+      <c r="F322" s="9">
+        <v>46073</v>
+      </c>
+    </row>
+    <row r="323" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C323" t="s">
+        <v>617</v>
+      </c>
       <c r="D323" s="7">
+        <v>479</v>
+      </c>
+      <c r="F323" s="9">
+        <v>46075</v>
+      </c>
+    </row>
+    <row r="324" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C324" t="s">
+        <v>618</v>
+      </c>
+      <c r="D324" s="7">
+        <v>839</v>
+      </c>
+      <c r="F324" s="9">
+        <v>46075</v>
+      </c>
+    </row>
+    <row r="325" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D325" s="7"/>
+      <c r="F325" s="9"/>
+    </row>
+    <row r="326" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D326" s="7"/>
+      <c r="F326" s="9"/>
+    </row>
+    <row r="327" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D327" s="7"/>
+      <c r="F327" s="9"/>
+    </row>
+    <row r="328" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D328" s="7"/>
+      <c r="F328" s="9"/>
+    </row>
+    <row r="329" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D329" s="7"/>
+      <c r="F329" s="9"/>
+    </row>
+    <row r="330" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D330" s="7"/>
+      <c r="F330" s="9"/>
+    </row>
+    <row r="331" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D331" s="7"/>
+      <c r="F331" s="9"/>
+    </row>
+    <row r="332" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D332" s="7"/>
+      <c r="F332" s="9"/>
+    </row>
+    <row r="333" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D333" s="7"/>
+      <c r="F333" s="9"/>
+    </row>
+    <row r="334" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D334" s="7"/>
+      <c r="F334" s="9"/>
+    </row>
+    <row r="335" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D335" s="7"/>
+      <c r="F335" s="9"/>
+    </row>
+    <row r="336" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D336" s="7"/>
+      <c r="F336" s="9"/>
+    </row>
+    <row r="337" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D337" s="7"/>
+      <c r="F337" s="9"/>
+    </row>
+    <row r="338" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D338" s="7"/>
+      <c r="F338" s="9"/>
+    </row>
+    <row r="339" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D339" s="7"/>
+      <c r="F339" s="9"/>
+    </row>
+    <row r="340" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D340" s="7"/>
+      <c r="F340" s="9"/>
+    </row>
+    <row r="341" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D341" s="7"/>
+      <c r="F341" s="9"/>
+    </row>
+    <row r="342" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D342" s="7"/>
+      <c r="F342" s="9"/>
+    </row>
+    <row r="343" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D343" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>3986173.8900000011</v>
-      </c>
-      <c r="F323" s="9"/>
+        <v>3988502.8900000011</v>
+      </c>
+      <c r="F343" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -438,7 +438,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="626">
   <si>
     <t>№ п/п</t>
   </si>
@@ -2455,6 +2455,27 @@
   </si>
   <si>
     <t>коронка bi-metal 8% по металлу/дереву 73мм dorn  pro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">вибратор для бетона deko 1500 Вт с булавой 1.5 м </t>
+  </si>
+  <si>
+    <t>Электрон 34 ящик ЩМП 05 ip54 металлический</t>
+  </si>
+  <si>
+    <t>Розетка EKF трёхфазная пятипроводная 32A 380В</t>
+  </si>
+  <si>
+    <t>автоматический выключатель dekraft c20a 4 полюсный</t>
+  </si>
+  <si>
+    <t>Розетка на din рейку iek 16A 250В</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>wildberries</t>
   </si>
 </sst>
 </file>
@@ -9191,6 +9212,9 @@
       <c r="D319" s="7">
         <v>125</v>
       </c>
+      <c r="E319" t="s">
+        <v>173</v>
+      </c>
       <c r="F319" s="9">
         <v>46073</v>
       </c>
@@ -9202,99 +9226,167 @@
       <c r="D320" s="7">
         <v>209</v>
       </c>
+      <c r="E320" t="s">
+        <v>173</v>
+      </c>
       <c r="F320" s="9">
         <v>46073</v>
       </c>
     </row>
-    <row r="321" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="321" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C321" t="s">
         <v>615</v>
       </c>
       <c r="D321" s="7">
         <v>138</v>
       </c>
+      <c r="E321" t="s">
+        <v>173</v>
+      </c>
       <c r="F321" s="9">
         <v>46073</v>
       </c>
     </row>
-    <row r="322" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="322" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C322" t="s">
         <v>616</v>
       </c>
       <c r="D322" s="7">
         <v>539</v>
       </c>
+      <c r="E322" t="s">
+        <v>173</v>
+      </c>
       <c r="F322" s="9">
         <v>46073</v>
       </c>
     </row>
-    <row r="323" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="323" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C323" t="s">
         <v>617</v>
       </c>
       <c r="D323" s="7">
         <v>479</v>
       </c>
+      <c r="E323" t="s">
+        <v>173</v>
+      </c>
       <c r="F323" s="9">
         <v>46075</v>
       </c>
     </row>
-    <row r="324" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="324" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C324" t="s">
         <v>618</v>
       </c>
       <c r="D324" s="7">
         <v>839</v>
       </c>
+      <c r="E324" t="s">
+        <v>173</v>
+      </c>
       <c r="F324" s="9">
         <v>46075</v>
       </c>
     </row>
-    <row r="325" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D325" s="7"/>
-      <c r="F325" s="9"/>
-    </row>
-    <row r="326" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D326" s="7"/>
-      <c r="F326" s="9"/>
-    </row>
-    <row r="327" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D327" s="7"/>
-      <c r="F327" s="9"/>
-    </row>
-    <row r="328" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D328" s="7"/>
-      <c r="F328" s="9"/>
-    </row>
-    <row r="329" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D329" s="7"/>
-      <c r="F329" s="9"/>
-    </row>
-    <row r="330" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C325" t="s">
+        <v>619</v>
+      </c>
+      <c r="D325" s="7">
+        <v>2471</v>
+      </c>
+      <c r="E325" t="s">
+        <v>625</v>
+      </c>
+      <c r="F325" s="9">
+        <v>46071</v>
+      </c>
+    </row>
+    <row r="326" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C326" t="s">
+        <v>620</v>
+      </c>
+      <c r="D326" s="7">
+        <v>3700</v>
+      </c>
+      <c r="E326" t="s">
+        <v>625</v>
+      </c>
+      <c r="F326" s="9">
+        <v>46071</v>
+      </c>
+    </row>
+    <row r="327" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C327" t="s">
+        <v>621</v>
+      </c>
+      <c r="D327" s="7">
+        <v>473</v>
+      </c>
+      <c r="E327" t="s">
+        <v>625</v>
+      </c>
+      <c r="F327" s="9">
+        <v>46071</v>
+      </c>
+    </row>
+    <row r="328" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C328" t="s">
+        <v>622</v>
+      </c>
+      <c r="D328" s="7">
+        <v>2040</v>
+      </c>
+      <c r="E328" t="s">
+        <v>625</v>
+      </c>
+      <c r="F328" s="9">
+        <v>46070</v>
+      </c>
+    </row>
+    <row r="329" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B329" t="s">
+        <v>624</v>
+      </c>
+      <c r="C329" t="s">
+        <v>623</v>
+      </c>
+      <c r="D329" s="7">
+        <v>348</v>
+      </c>
+      <c r="E329" t="s">
+        <v>625</v>
+      </c>
+      <c r="F329" s="9">
+        <v>46070</v>
+      </c>
+    </row>
+    <row r="330" spans="2:6" x14ac:dyDescent="0.25">
       <c r="D330" s="7"/>
       <c r="F330" s="9"/>
     </row>
-    <row r="331" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="331" spans="2:6" x14ac:dyDescent="0.25">
       <c r="D331" s="7"/>
       <c r="F331" s="9"/>
     </row>
-    <row r="332" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="332" spans="2:6" x14ac:dyDescent="0.25">
       <c r="D332" s="7"/>
       <c r="F332" s="9"/>
     </row>
-    <row r="333" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="333" spans="2:6" x14ac:dyDescent="0.25">
       <c r="D333" s="7"/>
       <c r="F333" s="9"/>
     </row>
-    <row r="334" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="334" spans="2:6" x14ac:dyDescent="0.25">
       <c r="D334" s="7"/>
       <c r="F334" s="9"/>
     </row>
-    <row r="335" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="335" spans="2:6" x14ac:dyDescent="0.25">
       <c r="D335" s="7"/>
       <c r="F335" s="9"/>
     </row>
-    <row r="336" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:6" x14ac:dyDescent="0.25">
       <c r="D336" s="7"/>
       <c r="F336" s="9"/>
     </row>
@@ -9325,7 +9417,7 @@
     <row r="343" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D343" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>3988502.8900000011</v>
+        <v>3997534.8900000011</v>
       </c>
       <c r="F343" s="9"/>
     </row>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -438,7 +438,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="627">
   <si>
     <t>№ п/п</t>
   </si>
@@ -2476,6 +2476,9 @@
   </si>
   <si>
     <t>wildberries</t>
+  </si>
+  <si>
+    <t>Фен строительный DEKO 2000 Вт</t>
   </si>
 </sst>
 </file>
@@ -9363,8 +9366,18 @@
       </c>
     </row>
     <row r="330" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D330" s="7"/>
-      <c r="F330" s="9"/>
+      <c r="C330" t="s">
+        <v>626</v>
+      </c>
+      <c r="D330" s="7">
+        <v>988</v>
+      </c>
+      <c r="E330" t="s">
+        <v>625</v>
+      </c>
+      <c r="F330" s="9">
+        <v>46084</v>
+      </c>
     </row>
     <row r="331" spans="2:6" x14ac:dyDescent="0.25">
       <c r="D331" s="7"/>
@@ -9417,7 +9430,7 @@
     <row r="343" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D343" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>3997534.8900000011</v>
+        <v>3998522.8900000011</v>
       </c>
       <c r="F343" s="9"/>
     </row>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25320" windowHeight="8145" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25320" windowHeight="8145" firstSheet="4" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="Расчёт колличества бетона " sheetId="2" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="Высоты" sheetId="7" r:id="rId8"/>
     <sheet name="Розетки и освещение" sheetId="12" r:id="rId9"/>
     <sheet name="сравнение цен на 13_02_26" sheetId="13" r:id="rId10"/>
+    <sheet name="котельная и вентиляция" sheetId="14" r:id="rId11"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
@@ -438,7 +439,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="627">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="651">
   <si>
     <t>№ п/п</t>
   </si>
@@ -2480,6 +2481,450 @@
   <si>
     <t>Фен строительный DEKO 2000 Вт</t>
   </si>
+  <si>
+    <r>
+      <t>Для котла </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t>Fondital Victoria Compact CTFS 24 AF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t> при объеме котельной </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t>18 м³</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t> рекомендуемый внутренний диаметр вентканала составляет </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t>150 мм</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t> (или прямоугольное сечение эквивалентной площади 177 см²). </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Поскольку модель </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t>CTFS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t> (аббревиатура </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t>Camera Turbo Forzata Stagna</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t>) оснащена </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t>закрытой камерой сгорания</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t> и принудительным дымоудалением, расчет вентиляции упрощается: вам не нужно закладывать дополнительный приток воздуха на горение газа в саму трубу вытяжки, так как котел берет его с улицы через коаксиальный дымоход. </t>
+    </r>
+  </si>
+  <si>
+    <t>Обоснование расчета</t>
+  </si>
+  <si>
+    <r>
+      <t>Согласно нормативам (СП 402.1325800.2018), для газовых котельных обязателен </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t>трехкратный воздухообмен</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t> в час. </t>
+    </r>
+  </si>
+  <si>
+    <t>АО «Газпром газораспределение Петрозаводск +1</t>
+  </si>
+  <si>
+    <r>
+      <t>Необходимый объем вытяжки:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t> 18 м³ × 3 = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t>54 м³/час</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Скорость воздуха:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t> При естественной вентиляции расчетная скорость составляет ~1 м/с.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Требуемая площадь сечения:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t> Для пропуска 54 м³/ч при такой скорости необходимо сечение около </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t>150 см²</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Подбор диаметра:</t>
+  </si>
+  <si>
+    <r>
+      <t>Труба </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t>Ø125 мм</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t> имеет площадь ~122 см² (этого может быть недостаточно при низком атмосферном давлении или малой высоте трубы).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Труба </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t>Ø150 мм</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t> имеет площадь ~176 см², что полностью перекрывает норматив и является стандартом для таких помещений. </t>
+    </r>
+  </si>
+  <si>
+    <t>xn--11-6kca3c6bt.xn--p1ai +1</t>
+  </si>
+  <si>
+    <t>Требования к исполнению</t>
+  </si>
+  <si>
+    <r>
+      <t>1. Материал:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t> Канал должен быть выполнен из негорючих материалов (оцинкованная сталь, нержавейка). Использование пластика (ПВХ) запрещено.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. Расположение:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t> Вытяжное отверстие должно находиться в верхней зоне помещения (не ниже 30 см от потолка).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3. Приток:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t> Для работы вытяжки необходим приток воздуха (например, подрез в нижней части двери площадью не менее 0,02 м² или приточный клапан). </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Для раздельной системы дымоудаления (раздельного дымохода) газового котла Fondital Victoria Compact CTFS 24 AF требуются две трубы диаметром </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t>80 мм</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t> каждая — одна для дымоудаления, другая для забора воздуха. Это стандартное решение для турбированных моделей, обеспечивающее эффективный отвод продуктов сгорания. </t>
+    </r>
+  </si>
+  <si>
+    <t>www.allb.ru +1</t>
+  </si>
+  <si>
+    <t>Ключевые особенности:</t>
+  </si>
+  <si>
+    <r>
+      <t>Диаметр труб:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t> 80/80 мм.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Тип системы:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t> Раздельная (воздуховод и дымоход идут отдельно).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Тип котла:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t> Закрытая камера сгорания (CTFS), турбированный. </t>
+    </r>
+  </si>
+  <si>
+    <t>ТеплоВсем +2</t>
+  </si>
+  <si>
+    <t>Использование труб диаметром 80 мм позволяет оптимизировать работу системы дымоудаления и обеспечить безопасную эксплуатацию котла.</t>
+  </si>
 </sst>
 </file>
 
@@ -2489,7 +2934,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2679,6 +3124,50 @@
       <name val="Tahoma"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0A0A0A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF0A0A0A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF56595E"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF0A0A0A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="15"/>
+      <color rgb="FF0A0A0A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF545D7E"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -2722,7 +3211,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2794,18 +3283,39 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="35">
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
-    </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
@@ -2855,6 +3365,12 @@
         <top/>
         <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
@@ -2950,15 +3466,272 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2049" name="img-lLixaYSIE4q3wPAPwPSOkA4_1" descr="x2dom.ru"/>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="609600" y="5581650"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>304800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2050" name="img-lLixaYSIE4q3wPAPwPSOkA4_2" descr="ГК Новые технологии"/>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="609600" y="10972800"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2051" name="img-lLixaYSIE4q3wPAPwPSOkA4_3" descr="АО «Газпром газораспределение Петрозаводск"/>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="609600" y="16411575"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2052" name="img-lLixaYSIE4q3wPAPwPSOkA4_4" descr="xn--11-6kca3c6bt.xn--p1ai"/>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="609600" y="37928550"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2053" name="img-5baxadmXD42RwPAP1fTFqAo_1" descr="www.allb.ru"/>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="7048500" y="1238250"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2054" name="img-5baxadmXD42RwPAP1fTFqAo_2" descr="ТеплоВсем"/>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="7048500" y="6172200"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F343" totalsRowCount="1">
   <autoFilter ref="B5:F342"/>
   <tableColumns count="5">
     <tableColumn id="1" name="№ п/п"/>
     <tableColumn id="2" name="Наименование "/>
-    <tableColumn id="3" name="Цена (руб)" totalsRowFunction="sum" dataDxfId="34" totalsRowDxfId="1"/>
+    <tableColumn id="3" name="Цена (руб)" totalsRowFunction="sum" dataDxfId="34" totalsRowDxfId="7"/>
     <tableColumn id="4" name="Примечание"/>
-    <tableColumn id="5" name="дата" dataDxfId="33" totalsRowDxfId="0"/>
+    <tableColumn id="5" name="дата" dataDxfId="33" totalsRowDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3092,15 +3865,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Таблица2" displayName="Таблица2" ref="A4:F28" totalsRowCount="1">
   <autoFilter ref="A4:F27"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="№ п/п" totalsRowLabel="Итого:" totalsRowDxfId="7"/>
-    <tableColumn id="2" name="Тип" totalsRowDxfId="6"/>
-    <tableColumn id="3" name="Количество (М3/шт)" totalsRowDxfId="5"/>
-    <tableColumn id="4" name="Цена  (м3 или штук)" dataDxfId="32" totalsRowDxfId="4"/>
-    <tableColumn id="5" name="Сумма" totalsRowFunction="custom" dataDxfId="31" totalsRowDxfId="3">
+    <tableColumn id="1" name="№ п/п" totalsRowLabel="Итого:" totalsRowDxfId="5"/>
+    <tableColumn id="2" name="Тип" totalsRowDxfId="4"/>
+    <tableColumn id="3" name="Количество (М3/шт)" totalsRowDxfId="3"/>
+    <tableColumn id="4" name="Цена  (м3 или штук)" dataDxfId="32" totalsRowDxfId="2"/>
+    <tableColumn id="5" name="Сумма" totalsRowFunction="custom" dataDxfId="31" totalsRowDxfId="1">
       <calculatedColumnFormula>Таблица2[[#This Row],[Цена  (м3 или штук)]]*Таблица2[[#This Row],[Количество (М3/шт)]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(E5:E27)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" name="Примечание" totalsRowDxfId="2"/>
+    <tableColumn id="6" name="Примечание" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4183,6 +4956,132 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B3:F20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="69.140625" customWidth="1"/>
+    <col min="6" max="6" width="72.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:6" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="43" t="s">
+        <v>627</v>
+      </c>
+      <c r="F3" s="43" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="44"/>
+      <c r="F4" s="49" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" ht="129.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="43" t="s">
+        <v>628</v>
+      </c>
+      <c r="F5" s="50" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" ht="77.25" x14ac:dyDescent="0.25">
+      <c r="B6" s="44"/>
+      <c r="F6" s="46" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="45" t="s">
+        <v>629</v>
+      </c>
+      <c r="F7" s="46" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" ht="122.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="43" t="s">
+        <v>630</v>
+      </c>
+      <c r="F8" s="46" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B9" s="44" t="s">
+        <v>631</v>
+      </c>
+      <c r="F9" s="51" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="46" t="s">
+        <v>632</v>
+      </c>
+      <c r="F10" s="43" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="46" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" ht="336.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="46" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B13" s="46" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="47" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" ht="133.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="47" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B16" s="48" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="45" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" ht="161.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="46" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" ht="105.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="46" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" ht="144" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="46" t="s">
+        <v>642</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:F343"/>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25320" windowHeight="8145" firstSheet="4" activeTab="10"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25320" windowHeight="8145" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Расчёт колличества бетона " sheetId="2" r:id="rId1"/>
@@ -439,7 +439,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="651">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1018" uniqueCount="664">
   <si>
     <t>№ п/п</t>
   </si>
@@ -2924,6 +2924,45 @@
   </si>
   <si>
     <t>Использование труб диаметром 80 мм позволяет оптимизировать работу системы дымоудаления и обеспечить безопасную эксплуатацию котла.</t>
+  </si>
+  <si>
+    <t>Доставка блоков 150 аэроблок - 5 паллет</t>
+  </si>
+  <si>
+    <t>Кримпер для обжима наконечников</t>
+  </si>
+  <si>
+    <t>Выключатель нагрузки IEK</t>
+  </si>
+  <si>
+    <t>автоматический выключатель IEK c25 3 полюсный</t>
+  </si>
+  <si>
+    <t>автоматический выключатель 4 полюса 25а</t>
+  </si>
+  <si>
+    <t> Кабель твёрдый круглый негорючий низкотоксичный ВВГ-нг LSLTx 3x2,5 ГОС - 1 метр</t>
+  </si>
+  <si>
+    <t>Уголок монтажный усиленный 90х90х65х1,8мм - 10 шт (1 шт - 45р)</t>
+  </si>
+  <si>
+    <t>Перчатки полиэстер с полиуретановым обливом, 10/XL, черн, Sado Plus - 2 пары</t>
+  </si>
+  <si>
+    <t>Гвозди оцинк. 4,0х120мм 1кг</t>
+  </si>
+  <si>
+    <t> Гвозди оцинк. 5,0х150мм 1кг</t>
+  </si>
+  <si>
+    <t>Шпилька рез. М8х1000мм. - 2 шт</t>
+  </si>
+  <si>
+    <t>Шайба DIN9021 кузовная оцинк. М12 10шт</t>
+  </si>
+  <si>
+    <t>Сверло по дереву балочное 8х460, 6-гранный хвостовик</t>
   </si>
 </sst>
 </file>
@@ -3317,6 +3356,12 @@
   </cellStyles>
   <dxfs count="35">
     <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -3365,12 +3410,6 @@
         <top/>
         <bottom/>
       </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
@@ -3724,14 +3763,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F343" totalsRowCount="1">
-  <autoFilter ref="B5:F342"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F351" totalsRowCount="1">
+  <autoFilter ref="B5:F350"/>
   <tableColumns count="5">
     <tableColumn id="1" name="№ п/п"/>
     <tableColumn id="2" name="Наименование "/>
-    <tableColumn id="3" name="Цена (руб)" totalsRowFunction="sum" dataDxfId="34" totalsRowDxfId="7"/>
+    <tableColumn id="3" name="Цена (руб)" totalsRowFunction="sum" dataDxfId="34" totalsRowDxfId="1"/>
     <tableColumn id="4" name="Примечание"/>
-    <tableColumn id="5" name="дата" dataDxfId="33" totalsRowDxfId="6"/>
+    <tableColumn id="5" name="дата" dataDxfId="33" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3865,15 +3904,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Таблица2" displayName="Таблица2" ref="A4:F28" totalsRowCount="1">
   <autoFilter ref="A4:F27"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="№ п/п" totalsRowLabel="Итого:" totalsRowDxfId="5"/>
-    <tableColumn id="2" name="Тип" totalsRowDxfId="4"/>
-    <tableColumn id="3" name="Количество (М3/шт)" totalsRowDxfId="3"/>
-    <tableColumn id="4" name="Цена  (м3 или штук)" dataDxfId="32" totalsRowDxfId="2"/>
-    <tableColumn id="5" name="Сумма" totalsRowFunction="custom" dataDxfId="31" totalsRowDxfId="1">
+    <tableColumn id="1" name="№ п/п" totalsRowLabel="Итого:" totalsRowDxfId="7"/>
+    <tableColumn id="2" name="Тип" totalsRowDxfId="6"/>
+    <tableColumn id="3" name="Количество (М3/шт)" totalsRowDxfId="5"/>
+    <tableColumn id="4" name="Цена  (м3 или штук)" dataDxfId="32" totalsRowDxfId="4"/>
+    <tableColumn id="5" name="Сумма" totalsRowFunction="custom" dataDxfId="31" totalsRowDxfId="3">
       <calculatedColumnFormula>Таблица2[[#This Row],[Цена  (м3 или штук)]]*Таблица2[[#This Row],[Количество (М3/шт)]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(E5:E27)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" name="Примечание" totalsRowDxfId="0"/>
+    <tableColumn id="6" name="Примечание" totalsRowDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4987,7 +5026,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="77.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B6" s="44"/>
       <c r="F6" s="46" t="s">
         <v>646</v>
@@ -5030,12 +5069,12 @@
         <v>633</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="336.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B12" s="46" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B13" s="46" t="s">
         <v>635</v>
       </c>
@@ -5084,10 +5123,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:F343"/>
+  <dimension ref="B3:F351"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="72.5703125" customWidth="1"/>
+    <col min="3" max="3" width="79" customWidth="1"/>
     <col min="4" max="4" width="22.5703125" customWidth="1"/>
     <col min="5" max="5" width="80.85546875" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
@@ -10279,59 +10318,221 @@
       </c>
     </row>
     <row r="331" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D331" s="7"/>
-      <c r="F331" s="9"/>
+      <c r="C331" t="s">
+        <v>651</v>
+      </c>
+      <c r="D331" s="7">
+        <v>8000</v>
+      </c>
+      <c r="E331" t="s">
+        <v>272</v>
+      </c>
+      <c r="F331" s="9">
+        <v>46098</v>
+      </c>
     </row>
     <row r="332" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D332" s="7"/>
-      <c r="F332" s="9"/>
+      <c r="C332" t="s">
+        <v>652</v>
+      </c>
+      <c r="D332" s="7">
+        <v>1215</v>
+      </c>
+      <c r="E332" t="s">
+        <v>625</v>
+      </c>
+      <c r="F332" s="9">
+        <v>46085</v>
+      </c>
     </row>
     <row r="333" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D333" s="7"/>
-      <c r="F333" s="9"/>
+      <c r="C333" t="s">
+        <v>653</v>
+      </c>
+      <c r="D333" s="7">
+        <v>3275</v>
+      </c>
+      <c r="E333" t="s">
+        <v>625</v>
+      </c>
+      <c r="F333" s="9">
+        <v>46085</v>
+      </c>
     </row>
     <row r="334" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D334" s="7"/>
-      <c r="F334" s="9"/>
+      <c r="C334" t="s">
+        <v>654</v>
+      </c>
+      <c r="D334" s="7">
+        <v>677</v>
+      </c>
+      <c r="E334" t="s">
+        <v>625</v>
+      </c>
+      <c r="F334" s="9">
+        <v>46080</v>
+      </c>
     </row>
     <row r="335" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D335" s="7"/>
-      <c r="F335" s="9"/>
+      <c r="C335" t="s">
+        <v>655</v>
+      </c>
+      <c r="D335" s="7">
+        <v>1123</v>
+      </c>
+      <c r="E335" t="s">
+        <v>625</v>
+      </c>
+      <c r="F335" s="9">
+        <v>46079</v>
+      </c>
     </row>
     <row r="336" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D336" s="7"/>
-      <c r="F336" s="9"/>
-    </row>
-    <row r="337" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D337" s="7"/>
-      <c r="F337" s="9"/>
-    </row>
-    <row r="338" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D338" s="7"/>
-      <c r="F338" s="9"/>
-    </row>
-    <row r="339" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D339" s="7"/>
-      <c r="F339" s="9"/>
-    </row>
-    <row r="340" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D340" s="7"/>
-      <c r="F340" s="9"/>
-    </row>
-    <row r="341" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D341" s="7"/>
-      <c r="F341" s="9"/>
-    </row>
-    <row r="342" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D342" s="7"/>
-      <c r="F342" s="9"/>
-    </row>
-    <row r="343" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="C336" s="18" t="s">
+        <v>656</v>
+      </c>
+      <c r="D336" s="7">
+        <v>127.78</v>
+      </c>
+      <c r="E336" t="s">
+        <v>173</v>
+      </c>
+      <c r="F336" s="9">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="337" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C337" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="D337" s="7">
+        <v>450</v>
+      </c>
+      <c r="E337" t="s">
+        <v>173</v>
+      </c>
+      <c r="F337" s="9">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="338" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C338" s="18" t="s">
+        <v>658</v>
+      </c>
+      <c r="D338" s="7">
+        <v>182</v>
+      </c>
+      <c r="E338" t="s">
+        <v>173</v>
+      </c>
+      <c r="F338" s="9">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="339" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C339" s="18" t="s">
+        <v>659</v>
+      </c>
+      <c r="D339" s="7">
+        <v>228.89</v>
+      </c>
+      <c r="E339" t="s">
+        <v>173</v>
+      </c>
+      <c r="F339" s="9">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="340" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C340" s="18" t="s">
+        <v>660</v>
+      </c>
+      <c r="D340" s="7">
+        <v>228.89</v>
+      </c>
+      <c r="E340" t="s">
+        <v>173</v>
+      </c>
+      <c r="F340" s="9">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="341" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C341" s="18" t="s">
+        <v>661</v>
+      </c>
+      <c r="D341" s="7">
+        <v>102</v>
+      </c>
+      <c r="E341" t="s">
+        <v>173</v>
+      </c>
+      <c r="F341" s="9">
+        <v>46101</v>
+      </c>
+    </row>
+    <row r="342" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C342" s="18" t="s">
+        <v>662</v>
+      </c>
+      <c r="D342" s="7">
+        <v>116.15</v>
+      </c>
+      <c r="E342" t="s">
+        <v>173</v>
+      </c>
+      <c r="F342" s="9">
+        <v>46101</v>
+      </c>
+    </row>
+    <row r="343" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C343" s="18" t="s">
+        <v>663</v>
+      </c>
       <c r="D343" s="7">
+        <v>224.2</v>
+      </c>
+      <c r="E343" t="s">
+        <v>173</v>
+      </c>
+      <c r="F343" s="9">
+        <v>46101</v>
+      </c>
+    </row>
+    <row r="344" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D344" s="7"/>
+      <c r="F344" s="9"/>
+    </row>
+    <row r="345" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D345" s="7"/>
+      <c r="F345" s="9"/>
+    </row>
+    <row r="346" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D346" s="7"/>
+      <c r="F346" s="9"/>
+    </row>
+    <row r="347" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D347" s="7"/>
+      <c r="F347" s="9"/>
+    </row>
+    <row r="348" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D348" s="7"/>
+      <c r="F348" s="9"/>
+    </row>
+    <row r="349" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D349" s="7"/>
+      <c r="F349" s="9"/>
+    </row>
+    <row r="350" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D350" s="7"/>
+      <c r="F350" s="9"/>
+    </row>
+    <row r="351" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D351" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>3998522.8900000011</v>
-      </c>
-      <c r="F343" s="9"/>
+        <v>4014472.8000000012</v>
+      </c>
+      <c r="F351" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -439,7 +439,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1018" uniqueCount="664">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="668">
   <si>
     <t>№ п/п</t>
   </si>
@@ -2963,6 +2963,18 @@
   </si>
   <si>
     <t>Сверло по дереву балочное 8х460, 6-гранный хвостовик</t>
+  </si>
+  <si>
+    <t>ООО СИТ - покупка метал труб прямоуг сечения</t>
+  </si>
+  <si>
+    <t>40х20х1.5х6000 мм труб прямоуг + резка</t>
+  </si>
+  <si>
+    <t>уголки+шурупы</t>
+  </si>
+  <si>
+    <t>уголки + шурупы</t>
   </si>
 </sst>
 </file>
@@ -10500,16 +10512,46 @@
       </c>
     </row>
     <row r="344" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D344" s="7"/>
-      <c r="F344" s="9"/>
+      <c r="C344" t="s">
+        <v>665</v>
+      </c>
+      <c r="D344" s="7">
+        <v>845</v>
+      </c>
+      <c r="E344" t="s">
+        <v>664</v>
+      </c>
+      <c r="F344" s="9">
+        <v>46105</v>
+      </c>
     </row>
     <row r="345" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D345" s="7"/>
-      <c r="F345" s="9"/>
+      <c r="C345" t="s">
+        <v>666</v>
+      </c>
+      <c r="D345" s="7">
+        <v>898</v>
+      </c>
+      <c r="E345" t="s">
+        <v>159</v>
+      </c>
+      <c r="F345" s="9">
+        <v>46105</v>
+      </c>
     </row>
     <row r="346" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D346" s="7"/>
-      <c r="F346" s="9"/>
+      <c r="C346" t="s">
+        <v>667</v>
+      </c>
+      <c r="D346" s="7">
+        <v>444</v>
+      </c>
+      <c r="E346" t="s">
+        <v>173</v>
+      </c>
+      <c r="F346" s="9">
+        <v>46106</v>
+      </c>
     </row>
     <row r="347" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D347" s="7"/>
@@ -10530,7 +10572,7 @@
     <row r="351" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D351" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>4014472.8000000012</v>
+        <v>4016659.8000000012</v>
       </c>
       <c r="F351" s="9"/>
     </row>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -439,7 +439,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="668">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="671">
   <si>
     <t>№ п/п</t>
   </si>
@@ -2975,6 +2975,15 @@
   </si>
   <si>
     <t>уголки + шурупы</t>
+  </si>
+  <si>
+    <t>саморез с шайбой по дереву 3,8х45мм 50 шт</t>
+  </si>
+  <si>
+    <t>уголок монтажный усиленный 90х90х65х1.8 мм 2 шт</t>
+  </si>
+  <si>
+    <t>уголок монтажный усиленный 60х60х45х1.8 мм 17 шт</t>
   </si>
 </sst>
 </file>
@@ -3775,8 +3784,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F351" totalsRowCount="1">
-  <autoFilter ref="B5:F350"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F354" totalsRowCount="1">
+  <autoFilter ref="B5:F353"/>
   <tableColumns count="5">
     <tableColumn id="1" name="№ п/п"/>
     <tableColumn id="2" name="Наименование "/>
@@ -5135,7 +5144,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:F351"/>
+  <dimension ref="B3:F354"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="79" customWidth="1"/>
@@ -10554,27 +10563,69 @@
       </c>
     </row>
     <row r="347" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D347" s="7"/>
-      <c r="F347" s="9"/>
+      <c r="C347" t="s">
+        <v>668</v>
+      </c>
+      <c r="D347" s="7">
+        <v>179</v>
+      </c>
+      <c r="E347" t="s">
+        <v>173</v>
+      </c>
+      <c r="F347" s="9">
+        <v>46107</v>
+      </c>
     </row>
     <row r="348" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D348" s="7"/>
-      <c r="F348" s="9"/>
+      <c r="C348" t="s">
+        <v>669</v>
+      </c>
+      <c r="D348" s="7">
+        <v>98</v>
+      </c>
+      <c r="E348" t="s">
+        <v>173</v>
+      </c>
+      <c r="F348" s="9">
+        <v>46107</v>
+      </c>
     </row>
     <row r="349" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D349" s="7"/>
-      <c r="F349" s="9"/>
+      <c r="C349" t="s">
+        <v>670</v>
+      </c>
+      <c r="D349" s="7">
+        <v>374</v>
+      </c>
+      <c r="E349" t="s">
+        <v>173</v>
+      </c>
+      <c r="F349" s="9">
+        <v>46107</v>
+      </c>
     </row>
     <row r="350" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D350" s="7"/>
       <c r="F350" s="9"/>
     </row>
     <row r="351" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D351" s="7">
+      <c r="D351" s="7"/>
+      <c r="F351" s="9"/>
+    </row>
+    <row r="352" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D352" s="7"/>
+      <c r="F352" s="9"/>
+    </row>
+    <row r="353" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D353" s="7"/>
+      <c r="F353" s="9"/>
+    </row>
+    <row r="354" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D354" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>4016659.8000000012</v>
-      </c>
-      <c r="F351" s="9"/>
+        <v>4017310.8000000012</v>
+      </c>
+      <c r="F354" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -439,7 +439,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1032" uniqueCount="672">
   <si>
     <t>№ п/п</t>
   </si>
@@ -2984,6 +2984,9 @@
   </si>
   <si>
     <t>уголок монтажный усиленный 60х60х45х1.8 мм 17 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">шпилька м8 1 метр + конструк саморезы 140 мм </t>
   </si>
 </sst>
 </file>
@@ -10605,8 +10608,18 @@
       </c>
     </row>
     <row r="350" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D350" s="7"/>
-      <c r="F350" s="9"/>
+      <c r="C350" t="s">
+        <v>671</v>
+      </c>
+      <c r="D350" s="7">
+        <v>271</v>
+      </c>
+      <c r="E350" t="s">
+        <v>173</v>
+      </c>
+      <c r="F350" s="9">
+        <v>46110</v>
+      </c>
     </row>
     <row r="351" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D351" s="7"/>
@@ -10623,7 +10636,7 @@
     <row r="354" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D354" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>4017310.8000000012</v>
+        <v>4017581.8000000012</v>
       </c>
       <c r="F354" s="9"/>
     </row>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -439,7 +439,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1032" uniqueCount="672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1042" uniqueCount="676">
   <si>
     <t>№ п/п</t>
   </si>
@@ -2987,6 +2987,18 @@
   </si>
   <si>
     <t xml:space="preserve">шпилька м8 1 метр + конструк саморезы 140 мм </t>
+  </si>
+  <si>
+    <t>шпилька м8 1000мм 1 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">уголок монтажный усиленный 60х60х45х1.8 мм 50 шт </t>
+  </si>
+  <si>
+    <t>гвозди строительные 4х120 мм 4 кг</t>
+  </si>
+  <si>
+    <t>саморез с пресшайбой по дереву 3.8 х 45 50 шт 2 упак</t>
   </si>
 </sst>
 </file>
@@ -3787,8 +3799,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F354" totalsRowCount="1">
-  <autoFilter ref="B5:F353"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F363" totalsRowCount="1">
+  <autoFilter ref="B5:F362"/>
   <tableColumns count="5">
     <tableColumn id="1" name="№ п/п"/>
     <tableColumn id="2" name="Наименование "/>
@@ -5147,7 +5159,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:F354"/>
+  <dimension ref="B3:F363"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="79" customWidth="1"/>
@@ -10622,23 +10634,109 @@
       </c>
     </row>
     <row r="351" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D351" s="7"/>
-      <c r="F351" s="9"/>
+      <c r="C351" t="s">
+        <v>672</v>
+      </c>
+      <c r="D351" s="7">
+        <v>57</v>
+      </c>
+      <c r="E351" t="s">
+        <v>173</v>
+      </c>
+      <c r="F351" s="9">
+        <v>46113</v>
+      </c>
     </row>
     <row r="352" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D352" s="7"/>
-      <c r="F352" s="9"/>
-    </row>
-    <row r="353" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D353" s="7"/>
-      <c r="F353" s="9"/>
-    </row>
-    <row r="354" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="C352" t="s">
+        <v>673</v>
+      </c>
+      <c r="D352" s="7">
+        <v>1100</v>
+      </c>
+      <c r="E352" t="s">
+        <v>173</v>
+      </c>
+      <c r="F352" s="9">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="353" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C353" t="s">
+        <v>674</v>
+      </c>
+      <c r="D353" s="7">
+        <v>756</v>
+      </c>
+      <c r="E353" t="s">
+        <v>173</v>
+      </c>
+      <c r="F353" s="9">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="354" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C354" t="s">
+        <v>675</v>
+      </c>
       <c r="D354" s="7">
+        <v>358</v>
+      </c>
+      <c r="E354" t="s">
+        <v>173</v>
+      </c>
+      <c r="F354" s="9">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="355" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C355" t="s">
+        <v>187</v>
+      </c>
+      <c r="D355" s="7">
+        <v>79</v>
+      </c>
+      <c r="E355" t="s">
+        <v>173</v>
+      </c>
+      <c r="F355" s="9">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="356" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D356" s="7"/>
+      <c r="F356" s="9"/>
+    </row>
+    <row r="357" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D357" s="7"/>
+      <c r="F357" s="9"/>
+    </row>
+    <row r="358" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D358" s="7"/>
+      <c r="F358" s="9"/>
+    </row>
+    <row r="359" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D359" s="7"/>
+      <c r="F359" s="9"/>
+    </row>
+    <row r="360" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D360" s="7"/>
+      <c r="F360" s="9"/>
+    </row>
+    <row r="361" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D361" s="7"/>
+      <c r="F361" s="9"/>
+    </row>
+    <row r="362" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D362" s="7"/>
+      <c r="F362" s="9"/>
+    </row>
+    <row r="363" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D363" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>4017581.8000000012</v>
-      </c>
-      <c r="F354" s="9"/>
+        <v>4019931.8000000012</v>
+      </c>
+      <c r="F363" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -439,7 +439,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1042" uniqueCount="676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="677">
   <si>
     <t>№ п/п</t>
   </si>
@@ -2999,6 +2999,9 @@
   </si>
   <si>
     <t>саморез с пресшайбой по дереву 3.8 х 45 50 шт 2 упак</t>
+  </si>
+  <si>
+    <t>ООО «Региональная кадастровая компания» +7 963 350-70-61 info@rkk39.ru www.rkk39.ru 236022, г. Калининград, ул. Г. Димитрова, д. 3, пом. 2</t>
   </si>
 </sst>
 </file>
@@ -10704,8 +10707,18 @@
       </c>
     </row>
     <row r="356" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D356" s="7"/>
-      <c r="F356" s="9"/>
+      <c r="C356" t="s">
+        <v>44</v>
+      </c>
+      <c r="D356" s="7">
+        <v>4000</v>
+      </c>
+      <c r="E356" t="s">
+        <v>676</v>
+      </c>
+      <c r="F356" s="9">
+        <v>46113</v>
+      </c>
     </row>
     <row r="357" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D357" s="7"/>
@@ -10734,7 +10747,7 @@
     <row r="363" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D363" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>4019931.8000000012</v>
+        <v>4023931.8000000012</v>
       </c>
       <c r="F363" s="9"/>
     </row>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -439,7 +439,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="677">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="682">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3003,6 +3003,21 @@
   <si>
     <t>ООО «Региональная кадастровая компания» +7 963 350-70-61 info@rkk39.ru www.rkk39.ru 236022, г. Калининград, ул. Г. Димитрова, д. 3, пом. 2</t>
   </si>
+  <si>
+    <t> База стройматериалов «БСМ» -бауцентр</t>
+  </si>
+  <si>
+    <t>Кабель круглый бронированный АПвБШп 4х16 - 22 м x 279 ₽</t>
+  </si>
+  <si>
+    <t>Кабель круглый негорючий малодымный ВВГнг(А)-LS 5х10 ГОСТ - 10 м x 889 ₽</t>
+  </si>
+  <si>
+    <t>Пленка паро-гидроизоляционная Изоспан D усиленная 90 г/м2 70 м2 - 4 рул x 4 490 ₽</t>
+  </si>
+  <si>
+    <t>Цемент ЦЕМ II/В-Ш 42,5Н Heidelberg 25 кг - 1 шт x 529 ₽</t>
+  </si>
 </sst>
 </file>
 
@@ -3012,7 +3027,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
   </numFmts>
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="32" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3246,6 +3261,21 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF2C2D2E"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF2C2D2E"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -3289,7 +3319,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3388,6 +3418,9 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -5162,13 +5195,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:F363"/>
+  <dimension ref="B3:I363"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="79" customWidth="1"/>
+    <col min="3" max="3" width="85.28515625" customWidth="1"/>
     <col min="4" max="4" width="22.5703125" customWidth="1"/>
     <col min="5" max="5" width="80.85546875" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="9" max="9" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
@@ -10664,7 +10698,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="353" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="353" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C353" t="s">
         <v>674</v>
       </c>
@@ -10678,7 +10712,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="354" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="354" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C354" t="s">
         <v>675</v>
       </c>
@@ -10692,7 +10726,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="355" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="355" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C355" t="s">
         <v>187</v>
       </c>
@@ -10706,7 +10740,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="356" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="356" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C356" t="s">
         <v>44</v>
       </c>
@@ -10720,34 +10754,75 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="357" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D357" s="7"/>
-      <c r="F357" s="9"/>
-    </row>
-    <row r="358" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D358" s="7"/>
-      <c r="F358" s="9"/>
-    </row>
-    <row r="359" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D359" s="7"/>
-      <c r="F359" s="9"/>
-    </row>
-    <row r="360" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D360" s="7"/>
-      <c r="F360" s="9"/>
-    </row>
-    <row r="361" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="357" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C357" s="54" t="s">
+        <v>678</v>
+      </c>
+      <c r="D357" s="7">
+        <v>6138</v>
+      </c>
+      <c r="E357" s="52" t="s">
+        <v>677</v>
+      </c>
+      <c r="F357" s="9">
+        <v>46119</v>
+      </c>
+      <c r="I357" s="7"/>
+    </row>
+    <row r="358" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C358" s="54" t="s">
+        <v>679</v>
+      </c>
+      <c r="D358" s="7">
+        <v>8890</v>
+      </c>
+      <c r="E358" s="52" t="s">
+        <v>677</v>
+      </c>
+      <c r="F358" s="9">
+        <v>46119</v>
+      </c>
+    </row>
+    <row r="359" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C359" s="54" t="s">
+        <v>680</v>
+      </c>
+      <c r="D359" s="7">
+        <v>17960</v>
+      </c>
+      <c r="E359" s="52" t="s">
+        <v>677</v>
+      </c>
+      <c r="F359" s="9">
+        <v>46119</v>
+      </c>
+    </row>
+    <row r="360" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C360" s="53" t="s">
+        <v>681</v>
+      </c>
+      <c r="D360" s="7">
+        <v>529</v>
+      </c>
+      <c r="E360" s="52" t="s">
+        <v>677</v>
+      </c>
+      <c r="F360" s="9">
+        <v>46119</v>
+      </c>
+    </row>
+    <row r="361" spans="3:9" x14ac:dyDescent="0.25">
       <c r="D361" s="7"/>
       <c r="F361" s="9"/>
     </row>
-    <row r="362" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="362" spans="3:9" x14ac:dyDescent="0.25">
       <c r="D362" s="7"/>
       <c r="F362" s="9"/>
     </row>
-    <row r="363" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="363" spans="3:9" x14ac:dyDescent="0.25">
       <c r="D363" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>4023931.8000000012</v>
+        <v>4057448.8000000012</v>
       </c>
       <c r="F363" s="9"/>
     </row>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Building\6-131\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zip\develop\my_home\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
     <sheet name="сравнение цен на 13_02_26" sheetId="13" r:id="rId10"/>
     <sheet name="котельная и вентиляция" sheetId="14" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -439,7 +439,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="690">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3018,11 +3018,35 @@
   <si>
     <t>Цемент ЦЕМ II/В-Ш 42,5Н Heidelberg 25 кг - 1 шт x 529 ₽</t>
   </si>
+  <si>
+    <t>трубка термоусадочная клеевая сттк 55\16  1м-546,11р 2 шт</t>
+  </si>
+  <si>
+    <t>трубка термоусадочная тту 10\5 1м 16,49р</t>
+  </si>
+  <si>
+    <t>труба гофрированная двухслойная электрокор флекс 61 х 3м</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Мегаполис-балтика </t>
+  </si>
+  <si>
+    <t>электрический провод ПуГВнг(а)-LS 1x10 на отрез 246х3м</t>
+  </si>
+  <si>
+    <t>наконечник гильза ншви2 6-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">шпагат пп 100м </t>
+  </si>
+  <si>
+    <t>респиратор ffp1 форм с клапаном юлия</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
@@ -3835,8 +3859,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F363" totalsRowCount="1">
-  <autoFilter ref="B5:F362"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F373" totalsRowCount="1">
+  <autoFilter ref="B5:F372"/>
   <tableColumns count="5">
     <tableColumn id="1" name="№ п/п"/>
     <tableColumn id="2" name="Наименование "/>
@@ -5195,7 +5219,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:I363"/>
+  <dimension ref="B3:I373"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="85.28515625" customWidth="1"/>
@@ -10812,19 +10836,129 @@
       </c>
     </row>
     <row r="361" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="D361" s="7"/>
-      <c r="F361" s="9"/>
+      <c r="C361" t="s">
+        <v>682</v>
+      </c>
+      <c r="D361" s="7">
+        <v>1092.22</v>
+      </c>
+      <c r="E361" t="s">
+        <v>685</v>
+      </c>
+      <c r="F361" s="9">
+        <v>46123</v>
+      </c>
     </row>
     <row r="362" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="D362" s="7"/>
-      <c r="F362" s="9"/>
+      <c r="C362" t="s">
+        <v>683</v>
+      </c>
+      <c r="D362" s="7">
+        <v>16.489999999999998</v>
+      </c>
+      <c r="E362" t="s">
+        <v>685</v>
+      </c>
+      <c r="F362" s="9">
+        <v>46123</v>
+      </c>
     </row>
     <row r="363" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C363" t="s">
+        <v>684</v>
+      </c>
       <c r="D363" s="7">
+        <v>183</v>
+      </c>
+      <c r="E363" t="s">
+        <v>685</v>
+      </c>
+      <c r="F363" s="9">
+        <v>46123</v>
+      </c>
+    </row>
+    <row r="364" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C364" t="s">
+        <v>686</v>
+      </c>
+      <c r="D364" s="7">
+        <v>792</v>
+      </c>
+      <c r="E364" t="s">
+        <v>500</v>
+      </c>
+      <c r="F364" s="9">
+        <v>46124</v>
+      </c>
+    </row>
+    <row r="365" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C365" t="s">
+        <v>687</v>
+      </c>
+      <c r="D365" s="7">
+        <v>136</v>
+      </c>
+      <c r="E365" t="s">
+        <v>500</v>
+      </c>
+      <c r="F365" s="9">
+        <v>46124</v>
+      </c>
+    </row>
+    <row r="366" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C366" t="s">
+        <v>688</v>
+      </c>
+      <c r="D366" s="7">
+        <v>101</v>
+      </c>
+      <c r="E366" t="s">
+        <v>500</v>
+      </c>
+      <c r="F366" s="9">
+        <v>46124</v>
+      </c>
+    </row>
+    <row r="367" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C367" t="s">
+        <v>689</v>
+      </c>
+      <c r="D367" s="7">
+        <v>72</v>
+      </c>
+      <c r="E367" t="s">
+        <v>500</v>
+      </c>
+      <c r="F367" s="9">
+        <v>46124</v>
+      </c>
+    </row>
+    <row r="368" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D368" s="7"/>
+      <c r="F368" s="9"/>
+    </row>
+    <row r="369" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D369" s="7"/>
+      <c r="F369" s="9"/>
+    </row>
+    <row r="370" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D370" s="7"/>
+      <c r="F370" s="9"/>
+    </row>
+    <row r="371" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D371" s="7"/>
+      <c r="F371" s="9"/>
+    </row>
+    <row r="372" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D372" s="7"/>
+      <c r="F372" s="9"/>
+    </row>
+    <row r="373" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D373" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>4057448.8000000012</v>
-      </c>
-      <c r="F363" s="9"/>
+        <v>4059841.5100000016</v>
+      </c>
+      <c r="F373" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25320" windowHeight="8145" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25320" windowHeight="8145" firstSheet="5" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="Расчёт колличества бетона " sheetId="2" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="Розетки и освещение" sheetId="12" r:id="rId9"/>
     <sheet name="сравнение цен на 13_02_26" sheetId="13" r:id="rId10"/>
     <sheet name="котельная и вентиляция" sheetId="14" r:id="rId11"/>
+    <sheet name="дерево заказ на 18 апр 2026" sheetId="15" r:id="rId12"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
@@ -439,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="690">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="706">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3041,6 +3042,54 @@
   </si>
   <si>
     <t>респиратор ffp1 форм с клапаном юлия</t>
+  </si>
+  <si>
+    <t>ншви2 10мм2</t>
+  </si>
+  <si>
+    <t>сигнальная лента</t>
+  </si>
+  <si>
+    <t>Сечение (мм)</t>
+  </si>
+  <si>
+    <t>50х200х6000</t>
+  </si>
+  <si>
+    <t>50х150х6000</t>
+  </si>
+  <si>
+    <t>перемычки</t>
+  </si>
+  <si>
+    <t>50х50</t>
+  </si>
+  <si>
+    <t>310 м.п</t>
+  </si>
+  <si>
+    <t>контробрешётка</t>
+  </si>
+  <si>
+    <t>25х100</t>
+  </si>
+  <si>
+    <t>530 м.п</t>
+  </si>
+  <si>
+    <t>количество (шт - м.п)</t>
+  </si>
+  <si>
+    <t>120 м.п</t>
+  </si>
+  <si>
+    <t>ветровая доска - 120/6 = 20 шт</t>
+  </si>
+  <si>
+    <t>обрешётка 530/6 = 89 шт</t>
+  </si>
+  <si>
+    <t>стропило не достающее</t>
   </si>
 </sst>
 </file>
@@ -3452,12 +3501,6 @@
   </cellStyles>
   <dxfs count="35">
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -3506,6 +3549,12 @@
         <top/>
         <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
@@ -3864,9 +3913,9 @@
   <tableColumns count="5">
     <tableColumn id="1" name="№ п/п"/>
     <tableColumn id="2" name="Наименование "/>
-    <tableColumn id="3" name="Цена (руб)" totalsRowFunction="sum" dataDxfId="34" totalsRowDxfId="1"/>
+    <tableColumn id="3" name="Цена (руб)" totalsRowFunction="sum" dataDxfId="34" totalsRowDxfId="7"/>
     <tableColumn id="4" name="Примечание"/>
-    <tableColumn id="5" name="дата" dataDxfId="33" totalsRowDxfId="0"/>
+    <tableColumn id="5" name="дата" dataDxfId="33" totalsRowDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4000,15 +4049,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Таблица2" displayName="Таблица2" ref="A4:F28" totalsRowCount="1">
   <autoFilter ref="A4:F27"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="№ п/п" totalsRowLabel="Итого:" totalsRowDxfId="7"/>
-    <tableColumn id="2" name="Тип" totalsRowDxfId="6"/>
-    <tableColumn id="3" name="Количество (М3/шт)" totalsRowDxfId="5"/>
-    <tableColumn id="4" name="Цена  (м3 или штук)" dataDxfId="32" totalsRowDxfId="4"/>
-    <tableColumn id="5" name="Сумма" totalsRowFunction="custom" dataDxfId="31" totalsRowDxfId="3">
+    <tableColumn id="1" name="№ п/п" totalsRowLabel="Итого:" totalsRowDxfId="5"/>
+    <tableColumn id="2" name="Тип" totalsRowDxfId="4"/>
+    <tableColumn id="3" name="Количество (М3/шт)" totalsRowDxfId="3"/>
+    <tableColumn id="4" name="Цена  (м3 или штук)" dataDxfId="32" totalsRowDxfId="2"/>
+    <tableColumn id="5" name="Сумма" totalsRowFunction="custom" dataDxfId="31" totalsRowDxfId="1">
       <calculatedColumnFormula>Таблица2[[#This Row],[Цена  (м3 или штук)]]*Таблица2[[#This Row],[Количество (М3/шт)]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(E5:E27)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" name="Примечание" totalsRowDxfId="2"/>
+    <tableColumn id="6" name="Примечание" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4028,6 +4077,18 @@
     <tableColumn id="11" name="Etimat" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Таблица11" displayName="Таблица11" ref="B3:D8" totalsRowShown="0">
+  <autoFilter ref="B3:D8"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="Сечение (мм)"/>
+    <tableColumn id="2" name="количество (шт - м.п)"/>
+    <tableColumn id="3" name="примечание"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -5217,6 +5278,90 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B3:D8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="22.28515625" customWidth="1"/>
+    <col min="3" max="3" width="22.5703125" customWidth="1"/>
+    <col min="4" max="4" width="55.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>692</v>
+      </c>
+      <c r="C3" t="s">
+        <v>701</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>693</v>
+      </c>
+      <c r="C4">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>694</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>696</v>
+      </c>
+      <c r="C6" t="s">
+        <v>697</v>
+      </c>
+      <c r="D6" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>699</v>
+      </c>
+      <c r="C7" t="s">
+        <v>700</v>
+      </c>
+      <c r="D7" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>699</v>
+      </c>
+      <c r="C8" t="s">
+        <v>702</v>
+      </c>
+      <c r="D8" t="s">
+        <v>703</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:I373"/>
@@ -10934,29 +11079,49 @@
       </c>
     </row>
     <row r="368" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="D368" s="7"/>
-      <c r="F368" s="9"/>
-    </row>
-    <row r="369" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D369" s="7"/>
-      <c r="F369" s="9"/>
-    </row>
-    <row r="370" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="C368" t="s">
+        <v>690</v>
+      </c>
+      <c r="D368" s="7">
+        <v>164</v>
+      </c>
+      <c r="E368" t="s">
+        <v>500</v>
+      </c>
+      <c r="F368" s="9">
+        <v>46127</v>
+      </c>
+    </row>
+    <row r="369" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C369" t="s">
+        <v>691</v>
+      </c>
+      <c r="D369" s="7">
+        <v>162</v>
+      </c>
+      <c r="E369" t="s">
+        <v>500</v>
+      </c>
+      <c r="F369" s="9">
+        <v>46127</v>
+      </c>
+    </row>
+    <row r="370" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D370" s="7"/>
       <c r="F370" s="9"/>
     </row>
-    <row r="371" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="371" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D371" s="7"/>
       <c r="F371" s="9"/>
     </row>
-    <row r="372" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="372" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D372" s="7"/>
       <c r="F372" s="9"/>
     </row>
-    <row r="373" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="373" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D373" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>4059841.5100000016</v>
+        <v>4060167.5100000016</v>
       </c>
       <c r="F373" s="9"/>
     </row>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="713">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3068,9 +3068,6 @@
     <t>310 м.п</t>
   </si>
   <si>
-    <t>контробрешётка</t>
-  </si>
-  <si>
     <t>25х100</t>
   </si>
   <si>
@@ -3090,6 +3087,30 @@
   </si>
   <si>
     <t>стропило не достающее</t>
+  </si>
+  <si>
+    <t>25х100х6000</t>
+  </si>
+  <si>
+    <t>размеры</t>
+  </si>
+  <si>
+    <t>количество</t>
+  </si>
+  <si>
+    <t>цена на м3</t>
+  </si>
+  <si>
+    <t>объём</t>
+  </si>
+  <si>
+    <t>сумма (руб)</t>
+  </si>
+  <si>
+    <t>50х50х3000</t>
+  </si>
+  <si>
+    <t>контробрешётка 310/3 = 104 щт</t>
   </si>
 </sst>
 </file>
@@ -4092,6 +4113,20 @@
 </table>
 </file>
 
+<file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Таблица12" displayName="Таблица12" ref="B14:F19" totalsRowShown="0">
+  <autoFilter ref="B14:F19"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="размеры"/>
+    <tableColumn id="2" name="количество"/>
+    <tableColumn id="3" name="цена на м3"/>
+    <tableColumn id="4" name="объём"/>
+    <tableColumn id="5" name="сумма (руб)"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Таблица1" displayName="Таблица1" ref="B2:D9" totalsRowShown="0">
   <autoFilter ref="B2:D9"/>
@@ -5280,26 +5315,28 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:D8"/>
+  <dimension ref="B3:F19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="22.28515625" customWidth="1"/>
     <col min="3" max="3" width="22.5703125" customWidth="1"/>
-    <col min="4" max="4" width="55.140625" customWidth="1"/>
+    <col min="4" max="4" width="37.140625" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="6" max="6" width="21.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>692</v>
       </c>
       <c r="C3" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>693</v>
       </c>
@@ -5307,10 +5344,10 @@
         <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>694</v>
       </c>
@@ -5321,7 +5358,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>696</v>
       </c>
@@ -5329,35 +5366,135 @@
         <v>697</v>
       </c>
       <c r="D6" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
         <v>698</v>
       </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>699</v>
       </c>
-      <c r="C7" t="s">
-        <v>700</v>
-      </c>
       <c r="D7" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="C8" t="s">
+        <v>701</v>
+      </c>
+      <c r="D8" t="s">
         <v>702</v>
       </c>
-      <c r="D8" t="s">
-        <v>703</v>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>706</v>
+      </c>
+      <c r="C14" t="s">
+        <v>707</v>
+      </c>
+      <c r="D14" t="s">
+        <v>708</v>
+      </c>
+      <c r="E14" t="s">
+        <v>709</v>
+      </c>
+      <c r="F14" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>705</v>
+      </c>
+      <c r="C15">
+        <v>109</v>
+      </c>
+      <c r="D15">
+        <v>26000</v>
+      </c>
+      <c r="E15">
+        <v>1.635</v>
+      </c>
+      <c r="F15">
+        <v>42510</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>693</v>
+      </c>
+      <c r="C16">
+        <v>25</v>
+      </c>
+      <c r="D16">
+        <v>26000</v>
+      </c>
+      <c r="E16">
+        <v>1.5</v>
+      </c>
+      <c r="F16">
+        <v>39000</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>694</v>
+      </c>
+      <c r="C17">
+        <v>3</v>
+      </c>
+      <c r="D17">
+        <v>26000</v>
+      </c>
+      <c r="E17">
+        <v>0.13500000000000001</v>
+      </c>
+      <c r="F17">
+        <v>3510</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>711</v>
+      </c>
+      <c r="C18">
+        <v>104</v>
+      </c>
+      <c r="D18">
+        <v>26000</v>
+      </c>
+      <c r="E18">
+        <v>0.78</v>
+      </c>
+      <c r="F18">
+        <v>20280</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B19" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19">
+        <f>SUM(E15:E18)</f>
+        <v>4.05</v>
+      </c>
+      <c r="F19">
+        <f>SUM(F15:F18)</f>
+        <v>105300</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="2">
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25320" windowHeight="8145" firstSheet="5" activeTab="11"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25320" windowHeight="8145" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Расчёт колличества бетона " sheetId="2" r:id="rId1"/>
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="713">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1106" uniqueCount="719">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3111,6 +3111,24 @@
   </si>
   <si>
     <t>контробрешётка 310/3 = 104 щт</t>
+  </si>
+  <si>
+    <t>доска 25х100х6000 - 109 шт  - 26000 р\м3</t>
+  </si>
+  <si>
+    <t>доска 50х200х6000 - 25 шт - 26000 р\м3</t>
+  </si>
+  <si>
+    <t>доска 50х150х6000 - 3 шт - 26000 р\м3</t>
+  </si>
+  <si>
+    <t>брус 50х50х3000 - 104 шт - 26000 р\м3</t>
+  </si>
+  <si>
+    <t>Сергей с авито</t>
+  </si>
+  <si>
+    <t>доставка досок манипулятором jac n90</t>
   </si>
 </sst>
 </file>
@@ -3522,6 +3540,12 @@
   </cellStyles>
   <dxfs count="35">
     <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -3570,12 +3594,6 @@
         <top/>
         <bottom/>
       </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
@@ -3929,14 +3947,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F373" totalsRowCount="1">
-  <autoFilter ref="B5:F372"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F386" totalsRowCount="1">
+  <autoFilter ref="B5:F385"/>
   <tableColumns count="5">
     <tableColumn id="1" name="№ п/п"/>
     <tableColumn id="2" name="Наименование "/>
-    <tableColumn id="3" name="Цена (руб)" totalsRowFunction="sum" dataDxfId="34" totalsRowDxfId="7"/>
+    <tableColumn id="3" name="Цена (руб)" totalsRowFunction="sum" dataDxfId="34" totalsRowDxfId="1"/>
     <tableColumn id="4" name="Примечание"/>
-    <tableColumn id="5" name="дата" dataDxfId="33" totalsRowDxfId="6"/>
+    <tableColumn id="5" name="дата" dataDxfId="33" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4070,15 +4088,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Таблица2" displayName="Таблица2" ref="A4:F28" totalsRowCount="1">
   <autoFilter ref="A4:F27"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="№ п/п" totalsRowLabel="Итого:" totalsRowDxfId="5"/>
-    <tableColumn id="2" name="Тип" totalsRowDxfId="4"/>
-    <tableColumn id="3" name="Количество (М3/шт)" totalsRowDxfId="3"/>
-    <tableColumn id="4" name="Цена  (м3 или штук)" dataDxfId="32" totalsRowDxfId="2"/>
-    <tableColumn id="5" name="Сумма" totalsRowFunction="custom" dataDxfId="31" totalsRowDxfId="1">
+    <tableColumn id="1" name="№ п/п" totalsRowLabel="Итого:" totalsRowDxfId="7"/>
+    <tableColumn id="2" name="Тип" totalsRowDxfId="6"/>
+    <tableColumn id="3" name="Количество (М3/шт)" totalsRowDxfId="5"/>
+    <tableColumn id="4" name="Цена  (м3 или штук)" dataDxfId="32" totalsRowDxfId="4"/>
+    <tableColumn id="5" name="Сумма" totalsRowFunction="custom" dataDxfId="31" totalsRowDxfId="3">
       <calculatedColumnFormula>Таблица2[[#This Row],[Цена  (м3 или штук)]]*Таблица2[[#This Row],[Количество (М3/шт)]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(E5:E27)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" name="Примечание" totalsRowDxfId="0"/>
+    <tableColumn id="6" name="Примечание" totalsRowDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5501,7 +5519,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:I373"/>
+  <dimension ref="B3:I386"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="85.28515625" customWidth="1"/>
@@ -11244,23 +11262,125 @@
       </c>
     </row>
     <row r="370" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D370" s="7"/>
-      <c r="F370" s="9"/>
+      <c r="C370" t="s">
+        <v>713</v>
+      </c>
+      <c r="D370" s="7">
+        <v>42510</v>
+      </c>
+      <c r="E370" t="s">
+        <v>470</v>
+      </c>
+      <c r="F370" s="9">
+        <v>46132</v>
+      </c>
     </row>
     <row r="371" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D371" s="7"/>
-      <c r="F371" s="9"/>
+      <c r="C371" t="s">
+        <v>714</v>
+      </c>
+      <c r="D371" s="7">
+        <v>39000</v>
+      </c>
+      <c r="E371" t="s">
+        <v>470</v>
+      </c>
+      <c r="F371" s="9">
+        <v>46132</v>
+      </c>
     </row>
     <row r="372" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D372" s="7"/>
-      <c r="F372" s="9"/>
+      <c r="C372" t="s">
+        <v>715</v>
+      </c>
+      <c r="D372" s="7">
+        <v>3510</v>
+      </c>
+      <c r="E372" t="s">
+        <v>470</v>
+      </c>
+      <c r="F372" s="9">
+        <v>46132</v>
+      </c>
     </row>
     <row r="373" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C373" t="s">
+        <v>716</v>
+      </c>
       <c r="D373" s="7">
+        <v>20280</v>
+      </c>
+      <c r="E373" t="s">
+        <v>470</v>
+      </c>
+      <c r="F373" s="9">
+        <v>46132</v>
+      </c>
+    </row>
+    <row r="374" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C374" t="s">
+        <v>718</v>
+      </c>
+      <c r="D374" s="7">
+        <v>6000</v>
+      </c>
+      <c r="E374" t="s">
+        <v>717</v>
+      </c>
+      <c r="F374" s="9">
+        <v>46132</v>
+      </c>
+    </row>
+    <row r="375" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D375" s="7"/>
+      <c r="F375" s="9"/>
+    </row>
+    <row r="376" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D376" s="7"/>
+      <c r="F376" s="9"/>
+    </row>
+    <row r="377" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D377" s="7"/>
+      <c r="F377" s="9"/>
+    </row>
+    <row r="378" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D378" s="7"/>
+      <c r="F378" s="9"/>
+    </row>
+    <row r="379" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D379" s="7"/>
+      <c r="F379" s="9"/>
+    </row>
+    <row r="380" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D380" s="7"/>
+      <c r="F380" s="9"/>
+    </row>
+    <row r="381" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D381" s="7"/>
+      <c r="F381" s="9"/>
+    </row>
+    <row r="382" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D382" s="7"/>
+      <c r="F382" s="9"/>
+    </row>
+    <row r="383" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D383" s="7"/>
+      <c r="F383" s="9"/>
+    </row>
+    <row r="384" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D384" s="7"/>
+      <c r="F384" s="9"/>
+    </row>
+    <row r="385" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D385" s="7"/>
+      <c r="F385" s="9"/>
+    </row>
+    <row r="386" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D386" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>4060167.5100000016</v>
-      </c>
-      <c r="F373" s="9"/>
+        <v>4171467.5100000016</v>
+      </c>
+      <c r="F386" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zip\develop\my_home\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Building\6-131\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -25,7 +25,7 @@
     <sheet name="котельная и вентиляция" sheetId="14" r:id="rId11"/>
     <sheet name="дерево заказ на 18 апр 2026" sheetId="15" r:id="rId12"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1106" uniqueCount="719">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="725">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3130,11 +3130,29 @@
   <si>
     <t>доставка досок манипулятором jac n90</t>
   </si>
+  <si>
+    <t>ПНД 32 гладкая 64.99 р х 4 метра</t>
+  </si>
+  <si>
+    <t>труба 50 гофрированная двухслойная электрокор флекс 61 х 3м</t>
+  </si>
+  <si>
+    <t>лента прямая (стальная перфорированная) lp 20x0,70-0,80мм 5 метров</t>
+  </si>
+  <si>
+    <t>труба термоусаживаемая клеевая сттк (3-4:1) 55\16мм 1м -546,11р 2 метра</t>
+  </si>
+  <si>
+    <t>диск отрезной 125х1,6мм диск по металлу DORN 2 шт</t>
+  </si>
+  <si>
+    <t>уголок монтажный усиленный 60х60х45х1.8мм - 16 шт</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
@@ -11332,36 +11350,116 @@
       </c>
     </row>
     <row r="375" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D375" s="7"/>
-      <c r="F375" s="9"/>
+      <c r="C375" t="s">
+        <v>719</v>
+      </c>
+      <c r="D375" s="7">
+        <v>259.95999999999998</v>
+      </c>
+      <c r="E375" t="s">
+        <v>211</v>
+      </c>
+      <c r="F375" s="9">
+        <v>46138</v>
+      </c>
     </row>
     <row r="376" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D376" s="7"/>
-      <c r="F376" s="9"/>
+      <c r="C376" t="s">
+        <v>720</v>
+      </c>
+      <c r="D376" s="7">
+        <v>183</v>
+      </c>
+      <c r="E376" t="s">
+        <v>211</v>
+      </c>
+      <c r="F376" s="9">
+        <v>46138</v>
+      </c>
     </row>
     <row r="377" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D377" s="7"/>
-      <c r="F377" s="9"/>
+      <c r="C377" t="s">
+        <v>721</v>
+      </c>
+      <c r="D377" s="7">
+        <v>251.23</v>
+      </c>
+      <c r="E377" t="s">
+        <v>211</v>
+      </c>
+      <c r="F377" s="9">
+        <v>46138</v>
+      </c>
     </row>
     <row r="378" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D378" s="7"/>
-      <c r="F378" s="9"/>
+      <c r="C378" t="s">
+        <v>722</v>
+      </c>
+      <c r="D378" s="7">
+        <v>1092.22</v>
+      </c>
+      <c r="E378" t="s">
+        <v>211</v>
+      </c>
+      <c r="F378" s="9">
+        <v>46138</v>
+      </c>
     </row>
     <row r="379" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D379" s="7"/>
-      <c r="F379" s="9"/>
+      <c r="C379" t="s">
+        <v>658</v>
+      </c>
+      <c r="D379" s="7">
+        <v>182.22</v>
+      </c>
+      <c r="E379" t="s">
+        <v>173</v>
+      </c>
+      <c r="F379" s="9">
+        <v>46138</v>
+      </c>
     </row>
     <row r="380" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D380" s="7"/>
-      <c r="F380" s="9"/>
+      <c r="C380" t="s">
+        <v>528</v>
+      </c>
+      <c r="D380" s="7">
+        <v>46.02</v>
+      </c>
+      <c r="E380" t="s">
+        <v>173</v>
+      </c>
+      <c r="F380" s="9">
+        <v>46138</v>
+      </c>
     </row>
     <row r="381" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D381" s="7"/>
-      <c r="F381" s="9"/>
+      <c r="C381" t="s">
+        <v>723</v>
+      </c>
+      <c r="D381" s="7">
+        <v>108.6</v>
+      </c>
+      <c r="E381" t="s">
+        <v>173</v>
+      </c>
+      <c r="F381" s="9">
+        <v>46138</v>
+      </c>
     </row>
     <row r="382" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D382" s="7"/>
-      <c r="F382" s="9"/>
+      <c r="C382" t="s">
+        <v>724</v>
+      </c>
+      <c r="D382" s="7">
+        <v>323.95999999999998</v>
+      </c>
+      <c r="E382" t="s">
+        <v>173</v>
+      </c>
+      <c r="F382" s="9">
+        <v>46138</v>
+      </c>
     </row>
     <row r="383" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D383" s="7"/>
@@ -11378,7 +11476,7 @@
     <row r="386" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D386" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>4171467.5100000016</v>
+        <v>4173914.7200000021</v>
       </c>
       <c r="F386" s="9"/>
     </row>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="725">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="733">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3147,6 +3147,30 @@
   </si>
   <si>
     <t>уголок монтажный усиленный 60х60х45х1.8мм - 16 шт</t>
+  </si>
+  <si>
+    <t>Электроцентр, ИП Савельев</t>
+  </si>
+  <si>
+    <t>провод ПуГВнг(А)LS 1x10 чёрный 1 метр</t>
+  </si>
+  <si>
+    <t>провод ПуГВнг(А)LS 1x6 красный 1 метр</t>
+  </si>
+  <si>
+    <t>наконечник НШВИ 10-12 (20шт\упак) IEK</t>
+  </si>
+  <si>
+    <t>наконечник НШВИ 6-12 (20шт\упак) IEK</t>
+  </si>
+  <si>
+    <t>Гвозди оцинк 3х80 1кг 2 упак х 240р</t>
+  </si>
+  <si>
+    <t>гвозди строительные 4х120 мм 1 кг</t>
+  </si>
+  <si>
+    <t>Гвозди строительные 3,5х90мм 1 кг, 3 упак х 182.47р</t>
   </si>
 </sst>
 </file>
@@ -3965,8 +3989,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F386" totalsRowCount="1">
-  <autoFilter ref="B5:F385"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F397" totalsRowCount="1">
+  <autoFilter ref="B5:F396"/>
   <tableColumns count="5">
     <tableColumn id="1" name="№ п/п"/>
     <tableColumn id="2" name="Наименование "/>
@@ -5537,7 +5561,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:I386"/>
+  <dimension ref="B3:I397"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="85.28515625" customWidth="1"/>
@@ -11462,23 +11486,137 @@
       </c>
     </row>
     <row r="383" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D383" s="7"/>
-      <c r="F383" s="9"/>
+      <c r="C383" t="s">
+        <v>726</v>
+      </c>
+      <c r="D383" s="7">
+        <v>175</v>
+      </c>
+      <c r="E383" t="s">
+        <v>725</v>
+      </c>
+      <c r="F383" s="9">
+        <v>46139</v>
+      </c>
     </row>
     <row r="384" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D384" s="7"/>
-      <c r="F384" s="9"/>
-    </row>
-    <row r="385" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D385" s="7"/>
-      <c r="F385" s="9"/>
-    </row>
-    <row r="386" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="C384" t="s">
+        <v>727</v>
+      </c>
+      <c r="D384" s="7">
+        <v>109</v>
+      </c>
+      <c r="E384" t="s">
+        <v>725</v>
+      </c>
+      <c r="F384" s="9">
+        <v>46139</v>
+      </c>
+    </row>
+    <row r="385" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C385" t="s">
+        <v>728</v>
+      </c>
+      <c r="D385" s="7">
+        <v>171</v>
+      </c>
+      <c r="E385" t="s">
+        <v>725</v>
+      </c>
+      <c r="F385" s="9">
+        <v>46139</v>
+      </c>
+    </row>
+    <row r="386" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C386" t="s">
+        <v>729</v>
+      </c>
       <c r="D386" s="7">
+        <v>196</v>
+      </c>
+      <c r="E386" t="s">
+        <v>725</v>
+      </c>
+      <c r="F386" s="9">
+        <v>46139</v>
+      </c>
+    </row>
+    <row r="387" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C387" t="s">
+        <v>730</v>
+      </c>
+      <c r="D387" s="7">
+        <v>480.8</v>
+      </c>
+      <c r="E387" t="s">
+        <v>173</v>
+      </c>
+      <c r="F387" s="9">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="388" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C388" t="s">
+        <v>731</v>
+      </c>
+      <c r="D388" s="7">
+        <v>182.47</v>
+      </c>
+      <c r="E388" t="s">
+        <v>173</v>
+      </c>
+      <c r="F388" s="9">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="389" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C389" t="s">
+        <v>732</v>
+      </c>
+      <c r="D389" s="7">
+        <v>547.41</v>
+      </c>
+      <c r="E389" t="s">
+        <v>173</v>
+      </c>
+      <c r="F389" s="9">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="390" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D390" s="7"/>
+      <c r="F390" s="9"/>
+    </row>
+    <row r="391" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D391" s="7"/>
+      <c r="F391" s="9"/>
+    </row>
+    <row r="392" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D392" s="7"/>
+      <c r="F392" s="9"/>
+    </row>
+    <row r="393" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D393" s="7"/>
+      <c r="F393" s="9"/>
+    </row>
+    <row r="394" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D394" s="7"/>
+      <c r="F394" s="9"/>
+    </row>
+    <row r="395" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D395" s="7"/>
+      <c r="F395" s="9"/>
+    </row>
+    <row r="396" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D396" s="7"/>
+      <c r="F396" s="9"/>
+    </row>
+    <row r="397" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D397" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>4173914.7200000021</v>
-      </c>
-      <c r="F386" s="9"/>
+        <v>4175776.4000000022</v>
+      </c>
+      <c r="F397" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Building\6-131\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zip\develop\my_home\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -25,7 +25,7 @@
     <sheet name="котельная и вентиляция" sheetId="14" r:id="rId11"/>
     <sheet name="дерево заказ на 18 апр 2026" sheetId="15" r:id="rId12"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="733">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="738">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3172,11 +3172,26 @@
   <si>
     <t>Гвозди строительные 3,5х90мм 1 кг, 3 упак х 182.47р</t>
   </si>
+  <si>
+    <t>доска 50х200х6000 - 19 шт - 26000 р\м3</t>
+  </si>
+  <si>
+    <t>объём - 1,14 м3 ИП Лыков</t>
+  </si>
+  <si>
+    <t>40х50х6000 - 5 шт - 26000р\м3</t>
+  </si>
+  <si>
+    <t>объём - 0,06 м3 ИП Лыков</t>
+  </si>
+  <si>
+    <t>доставка досок</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
@@ -11584,16 +11599,46 @@
       </c>
     </row>
     <row r="390" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D390" s="7"/>
-      <c r="F390" s="9"/>
+      <c r="C390" t="s">
+        <v>733</v>
+      </c>
+      <c r="D390" s="7">
+        <v>29640</v>
+      </c>
+      <c r="E390" t="s">
+        <v>734</v>
+      </c>
+      <c r="F390" s="9">
+        <v>46147</v>
+      </c>
     </row>
     <row r="391" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D391" s="7"/>
-      <c r="F391" s="9"/>
+      <c r="C391" t="s">
+        <v>735</v>
+      </c>
+      <c r="D391" s="7">
+        <v>1560</v>
+      </c>
+      <c r="E391" t="s">
+        <v>736</v>
+      </c>
+      <c r="F391" s="9">
+        <v>46147</v>
+      </c>
     </row>
     <row r="392" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D392" s="7"/>
-      <c r="F392" s="9"/>
+      <c r="C392" t="s">
+        <v>737</v>
+      </c>
+      <c r="D392" s="7">
+        <v>3000</v>
+      </c>
+      <c r="E392" t="s">
+        <v>119</v>
+      </c>
+      <c r="F392" s="9">
+        <v>46147</v>
+      </c>
     </row>
     <row r="393" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D393" s="7"/>
@@ -11614,7 +11659,7 @@
     <row r="397" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D397" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>4175776.4000000022</v>
+        <v>4209976.4000000022</v>
       </c>
       <c r="F397" s="9"/>
     </row>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="738">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1150" uniqueCount="742">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3186,6 +3186,18 @@
   </si>
   <si>
     <t>доставка досок</t>
+  </si>
+  <si>
+    <t xml:space="preserve">уголок монтажный 60х80х80х2.5мм </t>
+  </si>
+  <si>
+    <t>Опора бруса раскрытая OBR R 51х105х1,8мм 1 шт</t>
+  </si>
+  <si>
+    <t>Шуруп конструкционный, для дерева, полусфера, TORX 30 6,0x100мм. 4 шт</t>
+  </si>
+  <si>
+    <t>Гвозди оцинк 4х100 1кг 1 упак х 207.31р</t>
   </si>
 </sst>
 </file>
@@ -4004,8 +4016,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F397" totalsRowCount="1">
-  <autoFilter ref="B5:F396"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F404" totalsRowCount="1">
+  <autoFilter ref="B5:F403"/>
   <tableColumns count="5">
     <tableColumn id="1" name="№ п/п"/>
     <tableColumn id="2" name="Наименование "/>
@@ -5576,7 +5588,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:I397"/>
+  <dimension ref="B3:I404"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="85.28515625" customWidth="1"/>
@@ -11641,27 +11653,95 @@
       </c>
     </row>
     <row r="393" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D393" s="7"/>
-      <c r="F393" s="9"/>
+      <c r="C393" t="s">
+        <v>738</v>
+      </c>
+      <c r="D393" s="7">
+        <v>57.94</v>
+      </c>
+      <c r="E393" t="s">
+        <v>173</v>
+      </c>
+      <c r="F393" s="9">
+        <v>46149</v>
+      </c>
     </row>
     <row r="394" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D394" s="7"/>
-      <c r="F394" s="9"/>
+      <c r="C394" t="s">
+        <v>739</v>
+      </c>
+      <c r="D394" s="7">
+        <v>98.67</v>
+      </c>
+      <c r="E394" t="s">
+        <v>173</v>
+      </c>
+      <c r="F394" s="9">
+        <v>46149</v>
+      </c>
     </row>
     <row r="395" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D395" s="7"/>
-      <c r="F395" s="9"/>
+      <c r="C395" t="s">
+        <v>740</v>
+      </c>
+      <c r="D395" s="7">
+        <v>152.08000000000001</v>
+      </c>
+      <c r="E395" t="s">
+        <v>173</v>
+      </c>
+      <c r="F395" s="9">
+        <v>46149</v>
+      </c>
     </row>
     <row r="396" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D396" s="7"/>
-      <c r="F396" s="9"/>
+      <c r="C396" t="s">
+        <v>741</v>
+      </c>
+      <c r="D396" s="7">
+        <v>207.31</v>
+      </c>
+      <c r="E396" t="s">
+        <v>173</v>
+      </c>
+      <c r="F396" s="9">
+        <v>46149</v>
+      </c>
     </row>
     <row r="397" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D397" s="7">
+      <c r="D397" s="7"/>
+      <c r="F397" s="9"/>
+    </row>
+    <row r="398" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D398" s="7"/>
+      <c r="F398" s="9"/>
+    </row>
+    <row r="399" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D399" s="7"/>
+      <c r="F399" s="9"/>
+    </row>
+    <row r="400" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D400" s="7"/>
+      <c r="F400" s="9"/>
+    </row>
+    <row r="401" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D401" s="7"/>
+      <c r="F401" s="9"/>
+    </row>
+    <row r="402" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D402" s="7"/>
+      <c r="F402" s="9"/>
+    </row>
+    <row r="403" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D403" s="7"/>
+      <c r="F403" s="9"/>
+    </row>
+    <row r="404" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D404" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>4209976.4000000022</v>
-      </c>
-      <c r="F397" s="9"/>
+        <v>4210492.4000000022</v>
+      </c>
+      <c r="F404" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zip\develop\my_home\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Building\6-131\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -25,7 +25,7 @@
     <sheet name="котельная и вентиляция" sheetId="14" r:id="rId11"/>
     <sheet name="дерево заказ на 18 апр 2026" sheetId="15" r:id="rId12"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1150" uniqueCount="742">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="764">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3199,11 +3199,77 @@
   <si>
     <t>Гвозди оцинк 4х100 1кг 1 упак х 207.31р</t>
   </si>
+  <si>
+    <t> Гидроизоляция отсечная ТЕХНОНИКОЛЬ 0,2х20м</t>
+  </si>
+  <si>
+    <t>Пескобетон М 300 (25кг) 4 мешка</t>
+  </si>
+  <si>
+    <t>Уголок монтажный 90х90х40х1,8мм 7х34р</t>
+  </si>
+  <si>
+    <t>Блок вентиляционный керамзитобетонный VB 20х20х40 U 2 CAN - 33 шт</t>
+  </si>
+  <si>
+    <t>Блок вентиляционный керамзитобетонный VB 20х30х20 1 CAN</t>
+  </si>
+  <si>
+    <t>Скобы каленые тип 53, 10мм, 1000шт, Miles 5х178.17</t>
+  </si>
+  <si>
+    <t>Гвозди строительные 4х120мм 5кг 2 X 785.34</t>
+  </si>
+  <si>
+    <t>Клей для блока Klester ZM 22 (25кг) 7 мешков</t>
+  </si>
+  <si>
+    <t>Гвозди строительные 4х100мм 5кг х2</t>
+  </si>
+  <si>
+    <t>5 литров антисептик для обработки древесины</t>
+  </si>
+  <si>
+    <t>Мурат</t>
+  </si>
+  <si>
+    <t>Перчатки полиэстер с полиуретановым обливом, 10/XL, черн, Sado Plus 4x69р</t>
+  </si>
+  <si>
+    <t>Перчатки нейлон с нитриловым обливом, 10/XL, сер, Sado Plus 2пары</t>
+  </si>
+  <si>
+    <t>Брусок нестроганый 50x50x3000 мм хвоя ФГИС ЛК 22 шт х 377р</t>
+  </si>
+  <si>
+    <t>Шпатель зубчатый Интек 10108-150-010 150 мм, нержавеющая сталь, зуб 10x10 мм</t>
+  </si>
+  <si>
+    <t>ЛеманаПРО</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Зонт для дымохода из нерж стали 0.6мм d=80 </t>
+  </si>
+  <si>
+    <t>сборник конденсата для дымохода из нерж стали d=80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">тройник для дымохода из нерж стали d=80мм </t>
+  </si>
+  <si>
+    <t>герметик для каминов силикатный titan professional черный 280мл</t>
+  </si>
+  <si>
+    <t>труба для дымохода из нерж стали 0.6мм d=80 L=1m 960,30р х 4шт</t>
+  </si>
+  <si>
+    <t>хомут метал 75 (21/2*) с шурупом 96.03р х 2шт</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
@@ -4016,8 +4082,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F404" totalsRowCount="1">
-  <autoFilter ref="B5:F403"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F429" totalsRowCount="1">
+  <autoFilter ref="B5:F428"/>
   <tableColumns count="5">
     <tableColumn id="1" name="№ п/п"/>
     <tableColumn id="2" name="Наименование "/>
@@ -5588,7 +5654,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:I404"/>
+  <dimension ref="B3:I429"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="85.28515625" customWidth="1"/>
@@ -11709,39 +11775,359 @@
       </c>
     </row>
     <row r="397" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D397" s="7"/>
-      <c r="F397" s="9"/>
+      <c r="C397" s="18" t="s">
+        <v>742</v>
+      </c>
+      <c r="D397" s="7">
+        <v>899</v>
+      </c>
+      <c r="E397" t="s">
+        <v>173</v>
+      </c>
+      <c r="F397" s="9">
+        <v>46164</v>
+      </c>
     </row>
     <row r="398" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D398" s="7"/>
-      <c r="F398" s="9"/>
+      <c r="C398" t="s">
+        <v>743</v>
+      </c>
+      <c r="D398" s="7">
+        <v>1196</v>
+      </c>
+      <c r="E398" t="s">
+        <v>173</v>
+      </c>
+      <c r="F398" s="9">
+        <v>46164</v>
+      </c>
     </row>
     <row r="399" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D399" s="7"/>
-      <c r="F399" s="9"/>
+      <c r="C399" s="18" t="s">
+        <v>744</v>
+      </c>
+      <c r="D399" s="7">
+        <v>238</v>
+      </c>
+      <c r="E399" t="s">
+        <v>173</v>
+      </c>
+      <c r="F399" s="9">
+        <v>46164</v>
+      </c>
     </row>
     <row r="400" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D400" s="7"/>
-      <c r="F400" s="9"/>
-    </row>
-    <row r="401" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D401" s="7"/>
-      <c r="F401" s="9"/>
-    </row>
-    <row r="402" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D402" s="7"/>
-      <c r="F402" s="9"/>
-    </row>
-    <row r="403" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D403" s="7"/>
-      <c r="F403" s="9"/>
-    </row>
-    <row r="404" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="C400" t="s">
+        <v>745</v>
+      </c>
+      <c r="D400" s="7">
+        <v>9164.33</v>
+      </c>
+      <c r="E400" t="s">
+        <v>173</v>
+      </c>
+      <c r="F400" s="9">
+        <v>46164</v>
+      </c>
+    </row>
+    <row r="401" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C401" t="s">
+        <v>746</v>
+      </c>
+      <c r="D401" s="7">
+        <v>8507.39</v>
+      </c>
+      <c r="E401" t="s">
+        <v>173</v>
+      </c>
+      <c r="F401" s="9">
+        <v>46164</v>
+      </c>
+    </row>
+    <row r="402" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C402" t="s">
+        <v>747</v>
+      </c>
+      <c r="D402" s="7">
+        <v>890.85</v>
+      </c>
+      <c r="E402" t="s">
+        <v>173</v>
+      </c>
+      <c r="F402" s="9">
+        <v>46164</v>
+      </c>
+    </row>
+    <row r="403" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C403" s="18" t="s">
+        <v>748</v>
+      </c>
+      <c r="D403" s="7">
+        <v>1570.68</v>
+      </c>
+      <c r="E403" t="s">
+        <v>173</v>
+      </c>
+      <c r="F403" s="9">
+        <v>46164</v>
+      </c>
+    </row>
+    <row r="404" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C404" s="18" t="s">
+        <v>749</v>
+      </c>
       <c r="D404" s="7">
+        <v>2780.06</v>
+      </c>
+      <c r="E404" t="s">
+        <v>173</v>
+      </c>
+      <c r="F404" s="9">
+        <v>46164</v>
+      </c>
+    </row>
+    <row r="405" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C405" t="s">
+        <v>750</v>
+      </c>
+      <c r="D405" s="7">
+        <v>1570.7</v>
+      </c>
+      <c r="E405" t="s">
+        <v>173</v>
+      </c>
+      <c r="F405" s="9">
+        <v>46164</v>
+      </c>
+    </row>
+    <row r="406" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C406" s="18" t="s">
+        <v>429</v>
+      </c>
+      <c r="D406" s="7">
+        <v>2030</v>
+      </c>
+      <c r="E406" t="s">
+        <v>173</v>
+      </c>
+      <c r="F406" s="9">
+        <v>46164</v>
+      </c>
+    </row>
+    <row r="407" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C407" t="s">
+        <v>751</v>
+      </c>
+      <c r="D407" s="7">
+        <v>1900</v>
+      </c>
+      <c r="E407" t="s">
+        <v>752</v>
+      </c>
+      <c r="F407" s="9">
+        <v>46164</v>
+      </c>
+    </row>
+    <row r="408" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C408" s="18" t="s">
+        <v>753</v>
+      </c>
+      <c r="D408" s="7">
+        <v>277.24</v>
+      </c>
+      <c r="E408" t="s">
+        <v>173</v>
+      </c>
+      <c r="F408" s="9">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="409" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C409" s="18" t="s">
+        <v>754</v>
+      </c>
+      <c r="D409" s="7">
+        <v>110.62</v>
+      </c>
+      <c r="E409" t="s">
+        <v>173</v>
+      </c>
+      <c r="F409" s="9">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="410" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C410" t="s">
+        <v>755</v>
+      </c>
+      <c r="D410" s="7">
+        <v>7414</v>
+      </c>
+      <c r="E410" t="s">
+        <v>757</v>
+      </c>
+      <c r="F410" s="9">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="411" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C411" t="s">
+        <v>756</v>
+      </c>
+      <c r="D411" s="7">
+        <v>81</v>
+      </c>
+      <c r="E411" t="s">
+        <v>757</v>
+      </c>
+      <c r="F411" s="9">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="412" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C412" t="s">
+        <v>209</v>
+      </c>
+      <c r="D412" s="7">
+        <v>670</v>
+      </c>
+      <c r="E412" t="s">
+        <v>757</v>
+      </c>
+      <c r="F412" s="9">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="413" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C413" t="s">
+        <v>758</v>
+      </c>
+      <c r="D413" s="7">
+        <v>548.04999999999995</v>
+      </c>
+      <c r="E413" t="s">
+        <v>211</v>
+      </c>
+      <c r="F413" s="9">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="414" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C414" t="s">
+        <v>759</v>
+      </c>
+      <c r="D414" s="7">
+        <v>703.25</v>
+      </c>
+      <c r="E414" t="s">
+        <v>211</v>
+      </c>
+      <c r="F414" s="9">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="415" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C415" t="s">
+        <v>760</v>
+      </c>
+      <c r="D415" s="7">
+        <v>960.3</v>
+      </c>
+      <c r="E415" t="s">
+        <v>211</v>
+      </c>
+      <c r="F415" s="9">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="416" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C416" t="s">
+        <v>761</v>
+      </c>
+      <c r="D416" s="7">
+        <v>348.23</v>
+      </c>
+      <c r="E416" t="s">
+        <v>211</v>
+      </c>
+      <c r="F416" s="9">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="417" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C417" t="s">
+        <v>762</v>
+      </c>
+      <c r="D417" s="7">
+        <v>3841.2</v>
+      </c>
+      <c r="E417" t="s">
+        <v>211</v>
+      </c>
+      <c r="F417" s="9">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="418" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C418" t="s">
+        <v>763</v>
+      </c>
+      <c r="D418" s="7">
+        <v>192.06</v>
+      </c>
+      <c r="E418" t="s">
+        <v>211</v>
+      </c>
+      <c r="F418" s="9">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="419" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D419" s="7"/>
+      <c r="F419" s="9"/>
+    </row>
+    <row r="420" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D420" s="7"/>
+      <c r="F420" s="9"/>
+    </row>
+    <row r="421" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D421" s="7"/>
+      <c r="F421" s="9"/>
+    </row>
+    <row r="422" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D422" s="7"/>
+      <c r="F422" s="9"/>
+    </row>
+    <row r="423" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D423" s="7"/>
+      <c r="F423" s="9"/>
+    </row>
+    <row r="424" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D424" s="7"/>
+      <c r="F424" s="9"/>
+    </row>
+    <row r="425" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D425" s="7"/>
+      <c r="F425" s="9"/>
+    </row>
+    <row r="426" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D426" s="7"/>
+      <c r="F426" s="9"/>
+    </row>
+    <row r="427" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D427" s="7"/>
+      <c r="F427" s="9"/>
+    </row>
+    <row r="428" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D428" s="7"/>
+      <c r="F428" s="9"/>
+    </row>
+    <row r="429" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D429" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>4210492.4000000022</v>
-      </c>
-      <c r="F404" s="9"/>
+        <v>4256385.3600000013</v>
+      </c>
+      <c r="F429" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Building\6-131\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Building\my_home\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="764">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1214" uniqueCount="774">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3264,6 +3264,36 @@
   </si>
   <si>
     <t>хомут метал 75 (21/2*) с шурупом 96.03р х 2шт</t>
+  </si>
+  <si>
+    <t>уголок монтажный 90х90х40х1,8мм 43х27.99р</t>
+  </si>
+  <si>
+    <t>Гвозди строительные 4х120мм 5 кг</t>
+  </si>
+  <si>
+    <t>саморез по дереву 4,2х65мм 250 шт</t>
+  </si>
+  <si>
+    <t>клей для блока KLESTER zm22 25 кг</t>
+  </si>
+  <si>
+    <t>ЦПС м150 25 кг</t>
+  </si>
+  <si>
+    <t>Канал круглый 100 мм х 1,5 м 10ВП1,5 ERA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Заглушка D100 PDP пластик ERA </t>
+  </si>
+  <si>
+    <t>соединитель круглых каналов D100vv 10СКП ERA 96,47x2шт</t>
+  </si>
+  <si>
+    <t>тройник D100мм 10 тп ERA</t>
+  </si>
+  <si>
+    <t>канал круглый 0.5м 100мм 188,10х2</t>
   </si>
 </sst>
 </file>
@@ -4082,8 +4112,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F429" totalsRowCount="1">
-  <autoFilter ref="B5:F428"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F434" totalsRowCount="1">
+  <autoFilter ref="B5:F433"/>
   <tableColumns count="5">
     <tableColumn id="1" name="№ п/п"/>
     <tableColumn id="2" name="Наименование "/>
@@ -5654,7 +5684,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:I429"/>
+  <dimension ref="B3:I434"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="85.28515625" customWidth="1"/>
@@ -12083,51 +12113,171 @@
       </c>
     </row>
     <row r="419" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D419" s="7"/>
-      <c r="F419" s="9"/>
+      <c r="C419" t="s">
+        <v>764</v>
+      </c>
+      <c r="D419" s="7">
+        <v>1203.43</v>
+      </c>
+      <c r="E419" t="s">
+        <v>173</v>
+      </c>
+      <c r="F419" s="9">
+        <v>46168</v>
+      </c>
     </row>
     <row r="420" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D420" s="7"/>
-      <c r="F420" s="9"/>
+      <c r="C420" t="s">
+        <v>765</v>
+      </c>
+      <c r="D420" s="7">
+        <v>649.45000000000005</v>
+      </c>
+      <c r="E420" t="s">
+        <v>173</v>
+      </c>
+      <c r="F420" s="9">
+        <v>46168</v>
+      </c>
     </row>
     <row r="421" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D421" s="7"/>
-      <c r="F421" s="9"/>
+      <c r="C421" t="s">
+        <v>766</v>
+      </c>
+      <c r="D421" s="7">
+        <v>246.12</v>
+      </c>
+      <c r="E421" t="s">
+        <v>173</v>
+      </c>
+      <c r="F421" s="9">
+        <v>46168</v>
+      </c>
     </row>
     <row r="422" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D422" s="7"/>
-      <c r="F422" s="9"/>
+      <c r="C422" t="s">
+        <v>767</v>
+      </c>
+      <c r="D422" s="7">
+        <v>384.89</v>
+      </c>
+      <c r="E422" t="s">
+        <v>173</v>
+      </c>
+      <c r="F422" s="9">
+        <v>46169</v>
+      </c>
     </row>
     <row r="423" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D423" s="7"/>
-      <c r="F423" s="9"/>
+      <c r="C423" t="s">
+        <v>768</v>
+      </c>
+      <c r="D423" s="7">
+        <v>257.56</v>
+      </c>
+      <c r="E423" t="s">
+        <v>173</v>
+      </c>
+      <c r="F423" s="9">
+        <v>46169</v>
+      </c>
     </row>
     <row r="424" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D424" s="7"/>
-      <c r="F424" s="9"/>
+      <c r="C424" t="s">
+        <v>769</v>
+      </c>
+      <c r="D424" s="7">
+        <v>622.17999999999995</v>
+      </c>
+      <c r="E424" t="s">
+        <v>173</v>
+      </c>
+      <c r="F424" s="9">
+        <v>46169</v>
+      </c>
     </row>
     <row r="425" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D425" s="7"/>
-      <c r="F425" s="9"/>
+      <c r="C425" t="s">
+        <v>770</v>
+      </c>
+      <c r="D425" s="7">
+        <v>120.58</v>
+      </c>
+      <c r="E425" t="s">
+        <v>173</v>
+      </c>
+      <c r="F425" s="9">
+        <v>46169</v>
+      </c>
     </row>
     <row r="426" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D426" s="7"/>
-      <c r="F426" s="9"/>
+      <c r="C426" t="s">
+        <v>771</v>
+      </c>
+      <c r="D426" s="7">
+        <v>192.94</v>
+      </c>
+      <c r="E426" t="s">
+        <v>173</v>
+      </c>
+      <c r="F426" s="9">
+        <v>46169</v>
+      </c>
     </row>
     <row r="427" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D427" s="7"/>
-      <c r="F427" s="9"/>
+      <c r="C427" t="s">
+        <v>772</v>
+      </c>
+      <c r="D427" s="7">
+        <v>336.65</v>
+      </c>
+      <c r="E427" t="s">
+        <v>173</v>
+      </c>
+      <c r="F427" s="9">
+        <v>46169</v>
+      </c>
     </row>
     <row r="428" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D428" s="7"/>
-      <c r="F428" s="9"/>
+      <c r="C428" t="s">
+        <v>773</v>
+      </c>
+      <c r="D428" s="7">
+        <v>376.2</v>
+      </c>
+      <c r="E428" t="s">
+        <v>173</v>
+      </c>
+      <c r="F428" s="9">
+        <v>46169</v>
+      </c>
     </row>
     <row r="429" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D429" s="7">
+      <c r="D429" s="7"/>
+      <c r="F429" s="9"/>
+    </row>
+    <row r="430" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D430" s="7"/>
+      <c r="F430" s="9"/>
+    </row>
+    <row r="431" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D431" s="7"/>
+      <c r="F431" s="9"/>
+    </row>
+    <row r="432" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D432" s="7"/>
+      <c r="F432" s="9"/>
+    </row>
+    <row r="433" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D433" s="7"/>
+      <c r="F433" s="9"/>
+    </row>
+    <row r="434" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D434" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>4256385.3600000013</v>
-      </c>
-      <c r="F429" s="9"/>
+        <v>4260775.3600000013</v>
+      </c>
+      <c r="F434" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1214" uniqueCount="774">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1237" uniqueCount="787">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3294,6 +3294,45 @@
   </si>
   <si>
     <t>канал круглый 0.5м 100мм 188,10х2</t>
+  </si>
+  <si>
+    <t>Герметик нейтральный силиконовый</t>
+  </si>
+  <si>
+    <t>вычистка для дымохода из нерж стали с заглушкой 0.6 D=80мм</t>
+  </si>
+  <si>
+    <t xml:space="preserve">труба для дымохода из нерж стали 0.6мм d=80 L=0.25m </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Винт-шуруп (шпилька сантехническая) TORX 20 M10х100мм 4 шт</t>
+  </si>
+  <si>
+    <t>Хомут с рез. упл. 100мм 4шт</t>
+  </si>
+  <si>
+    <t>Уголок монтажный 40х80х80x1,8мм</t>
+  </si>
+  <si>
+    <t>ИП Лукьянов Никита Антонович, ИНН 391201802940, 238563, Калининградская область, г.о. Светлогорский, г Светлогорск, ул Яблоневая, Дом 3, кв. 3</t>
+  </si>
+  <si>
+    <t>Счет на оплату № УТ-223 от 27 мая 2026 г. - металлочерепица и комплектующие Эбис</t>
+  </si>
+  <si>
+    <t>Счет на оплату № УТ-678 от 27 мая 2026 г. Эбис</t>
+  </si>
+  <si>
+    <t>Общество с ограниченной ответственностью "ЭБИС", ИНН 3905601123, КПП 390601001, 236010, Калининградская обл, Калининград г, Кутузова ул, дом 37, квартира 3, тел.: +7(4012) 99-40-4</t>
+  </si>
+  <si>
+    <t>Мурат строитель</t>
+  </si>
+  <si>
+    <t>Доставка манипулятором металочерепицы и комплектующие</t>
+  </si>
+  <si>
+    <t>Алексей грузоперевозки</t>
   </si>
 </sst>
 </file>
@@ -3596,7 +3635,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3698,6 +3737,7 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -4112,8 +4152,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F434" totalsRowCount="1">
-  <autoFilter ref="B5:F433"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F445" totalsRowCount="1">
+  <autoFilter ref="B5:F444"/>
   <tableColumns count="5">
     <tableColumn id="1" name="№ п/п"/>
     <tableColumn id="2" name="Наименование "/>
@@ -5684,12 +5724,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:I434"/>
+  <dimension ref="B3:I445"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="85.28515625" customWidth="1"/>
     <col min="4" max="4" width="22.5703125" customWidth="1"/>
-    <col min="5" max="5" width="80.85546875" customWidth="1"/>
+    <col min="5" max="5" width="90.85546875" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
     <col min="9" max="9" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
@@ -12253,31 +12293,199 @@
       </c>
     </row>
     <row r="429" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D429" s="7"/>
-      <c r="F429" s="9"/>
+      <c r="C429" t="s">
+        <v>774</v>
+      </c>
+      <c r="D429" s="7">
+        <v>399</v>
+      </c>
+      <c r="E429" t="s">
+        <v>211</v>
+      </c>
+      <c r="F429" s="9">
+        <v>46170</v>
+      </c>
     </row>
     <row r="430" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D430" s="7"/>
-      <c r="F430" s="9"/>
+      <c r="C430" t="s">
+        <v>775</v>
+      </c>
+      <c r="D430" s="7">
+        <v>1250</v>
+      </c>
+      <c r="E430" t="s">
+        <v>211</v>
+      </c>
+      <c r="F430" s="9">
+        <v>46170</v>
+      </c>
     </row>
     <row r="431" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D431" s="7"/>
-      <c r="F431" s="9"/>
+      <c r="C431" t="s">
+        <v>776</v>
+      </c>
+      <c r="D431" s="7">
+        <v>500</v>
+      </c>
+      <c r="E431" t="s">
+        <v>211</v>
+      </c>
+      <c r="F431" s="9">
+        <v>46170</v>
+      </c>
     </row>
     <row r="432" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D432" s="7"/>
-      <c r="F432" s="9"/>
-    </row>
-    <row r="433" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D433" s="7"/>
-      <c r="F433" s="9"/>
-    </row>
-    <row r="434" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="C432" t="s">
+        <v>743</v>
+      </c>
+      <c r="D432" s="7">
+        <f xml:space="preserve"> 290.4 * 4</f>
+        <v>1161.5999999999999</v>
+      </c>
+      <c r="E432" t="s">
+        <v>173</v>
+      </c>
+      <c r="F432" s="9">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="433" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C433" t="s">
+        <v>777</v>
+      </c>
+      <c r="D433" s="7">
+        <f>28.17*4</f>
+        <v>112.68</v>
+      </c>
+      <c r="E433" t="s">
+        <v>173</v>
+      </c>
+      <c r="F433" s="9">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="434" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C434" t="s">
+        <v>778</v>
+      </c>
       <c r="D434" s="7">
+        <f>105.87*4</f>
+        <v>423.48</v>
+      </c>
+      <c r="E434" t="s">
+        <v>173</v>
+      </c>
+      <c r="F434" s="9">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="435" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C435" s="18" t="s">
+        <v>443</v>
+      </c>
+      <c r="D435" s="7">
+        <v>290.39999999999998</v>
+      </c>
+      <c r="E435" t="s">
+        <v>173</v>
+      </c>
+      <c r="F435" s="9">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="436" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C436" s="18" t="s">
+        <v>779</v>
+      </c>
+      <c r="D436" s="7">
+        <f>(13+18)*34.96</f>
+        <v>1083.76</v>
+      </c>
+      <c r="E436" t="s">
+        <v>173</v>
+      </c>
+      <c r="F436" s="9">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="437" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C437" t="s">
+        <v>781</v>
+      </c>
+      <c r="D437" s="7">
+        <v>441993.2</v>
+      </c>
+      <c r="E437" t="s">
+        <v>780</v>
+      </c>
+      <c r="F437" s="9">
+        <v>46169</v>
+      </c>
+    </row>
+    <row r="438" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C438" t="s">
+        <v>782</v>
+      </c>
+      <c r="D438" s="7">
+        <v>47851.75</v>
+      </c>
+      <c r="E438" t="s">
+        <v>783</v>
+      </c>
+      <c r="F438" s="9">
+        <v>46169</v>
+      </c>
+    </row>
+    <row r="439" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C439" t="s">
+        <v>784</v>
+      </c>
+      <c r="D439" s="7">
+        <v>200000</v>
+      </c>
+      <c r="E439" s="55">
+        <v>0.5</v>
+      </c>
+      <c r="F439" s="9">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="440" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C440" t="s">
+        <v>785</v>
+      </c>
+      <c r="D440" s="7">
+        <v>6000</v>
+      </c>
+      <c r="E440" t="s">
+        <v>786</v>
+      </c>
+      <c r="F440" s="9">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="441" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D441" s="7"/>
+      <c r="F441" s="9"/>
+    </row>
+    <row r="442" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D442" s="7"/>
+      <c r="F442" s="9"/>
+    </row>
+    <row r="443" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D443" s="7"/>
+      <c r="F443" s="9"/>
+    </row>
+    <row r="444" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D444" s="7"/>
+      <c r="F444" s="9"/>
+    </row>
+    <row r="445" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D445" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>4260775.3600000013</v>
-      </c>
-      <c r="F434" s="9"/>
+        <v>4961841.2300000014</v>
+      </c>
+      <c r="F445" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1237" uniqueCount="787">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="791">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3333,6 +3333,18 @@
   </si>
   <si>
     <t>Алексей грузоперевозки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Перчатки полиэстер с полиуретановым обливом 10\xl черн. </t>
+  </si>
+  <si>
+    <t>клей для блока KLESTER zm22 25 кг - 2 мешка</t>
+  </si>
+  <si>
+    <t>соединитель круглых каналов D100vv 10СКП ERA 2 шт</t>
+  </si>
+  <si>
+    <t>канал круглый 100мм 1 метр, 2 шт</t>
   </si>
 </sst>
 </file>
@@ -4152,8 +4164,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F445" totalsRowCount="1">
-  <autoFilter ref="B5:F444"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F456" totalsRowCount="1">
+  <autoFilter ref="B5:F455"/>
   <tableColumns count="5">
     <tableColumn id="1" name="№ п/п"/>
     <tableColumn id="2" name="Наименование "/>
@@ -5724,7 +5736,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:I445"/>
+  <dimension ref="B3:I456"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="85.28515625" customWidth="1"/>
@@ -12465,27 +12477,122 @@
       </c>
     </row>
     <row r="441" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D441" s="7"/>
-      <c r="F441" s="9"/>
+      <c r="C441" t="s">
+        <v>787</v>
+      </c>
+      <c r="D441" s="7">
+        <v>88.82</v>
+      </c>
+      <c r="E441" t="s">
+        <v>173</v>
+      </c>
+      <c r="F441" s="9">
+        <v>46176</v>
+      </c>
     </row>
     <row r="442" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D442" s="7"/>
-      <c r="F442" s="9"/>
+      <c r="C442" t="s">
+        <v>788</v>
+      </c>
+      <c r="D442" s="7">
+        <f>357.97*2</f>
+        <v>715.94</v>
+      </c>
+      <c r="E442" t="s">
+        <v>173</v>
+      </c>
+      <c r="F442" s="9">
+        <v>46176</v>
+      </c>
     </row>
     <row r="443" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D443" s="7"/>
-      <c r="F443" s="9"/>
+      <c r="C443" t="s">
+        <v>437</v>
+      </c>
+      <c r="D443" s="7">
+        <v>268.25</v>
+      </c>
+      <c r="E443" t="s">
+        <v>173</v>
+      </c>
+      <c r="F443" s="9">
+        <v>46176</v>
+      </c>
     </row>
     <row r="444" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D444" s="7"/>
-      <c r="F444" s="9"/>
+      <c r="C444" t="s">
+        <v>789</v>
+      </c>
+      <c r="D444" s="7">
+        <v>191.02</v>
+      </c>
+      <c r="E444" t="s">
+        <v>173</v>
+      </c>
+      <c r="F444" s="9">
+        <v>46176</v>
+      </c>
     </row>
     <row r="445" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C445" t="s">
+        <v>790</v>
+      </c>
       <c r="D445" s="7">
+        <v>723.98</v>
+      </c>
+      <c r="E445" t="s">
+        <v>173</v>
+      </c>
+      <c r="F445" s="9">
+        <v>46176</v>
+      </c>
+    </row>
+    <row r="446" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D446" s="7"/>
+      <c r="F446" s="9"/>
+    </row>
+    <row r="447" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D447" s="7"/>
+      <c r="F447" s="9"/>
+    </row>
+    <row r="448" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D448" s="7"/>
+      <c r="F448" s="9"/>
+    </row>
+    <row r="449" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D449" s="7"/>
+      <c r="F449" s="9"/>
+    </row>
+    <row r="450" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D450" s="7"/>
+      <c r="F450" s="9"/>
+    </row>
+    <row r="451" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D451" s="7"/>
+      <c r="F451" s="9"/>
+    </row>
+    <row r="452" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D452" s="7"/>
+      <c r="F452" s="9"/>
+    </row>
+    <row r="453" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D453" s="7"/>
+      <c r="F453" s="9"/>
+    </row>
+    <row r="454" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D454" s="7"/>
+      <c r="F454" s="9"/>
+    </row>
+    <row r="455" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D455" s="7"/>
+      <c r="F455" s="9"/>
+    </row>
+    <row r="456" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D456" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>4961841.2300000014</v>
-      </c>
-      <c r="F445" s="9"/>
+        <v>4963829.2400000021</v>
+      </c>
+      <c r="F456" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="791">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="794">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3345,6 +3345,15 @@
   </si>
   <si>
     <t>канал круглый 100мм 1 метр, 2 шт</t>
+  </si>
+  <si>
+    <t>Гвозди ершёные оцинков. 4,2х40мм. 0,25кг</t>
+  </si>
+  <si>
+    <t>Саморез с п/шайбой по дереву 3,8х45мм 50шт. 4 упак</t>
+  </si>
+  <si>
+    <t>Замена коротких крюков на длинные (водосточная система)</t>
   </si>
 </sst>
 </file>
@@ -12548,15 +12557,45 @@
       </c>
     </row>
     <row r="446" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D446" s="7"/>
-      <c r="F446" s="9"/>
+      <c r="C446" t="s">
+        <v>791</v>
+      </c>
+      <c r="D446" s="7">
+        <f>7*91.47</f>
+        <v>640.29</v>
+      </c>
+      <c r="E446" t="s">
+        <v>173</v>
+      </c>
+      <c r="F446" s="9">
+        <v>46177</v>
+      </c>
     </row>
     <row r="447" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D447" s="7"/>
-      <c r="F447" s="9"/>
+      <c r="C447" s="18" t="s">
+        <v>792</v>
+      </c>
+      <c r="D447" s="7">
+        <f>4*174.18</f>
+        <v>696.72</v>
+      </c>
+      <c r="E447" t="s">
+        <v>173</v>
+      </c>
+      <c r="F447" s="9">
+        <v>46177</v>
+      </c>
     </row>
     <row r="448" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D448" s="7"/>
+      <c r="C448" t="s">
+        <v>793</v>
+      </c>
+      <c r="D448" s="7">
+        <v>6592.4</v>
+      </c>
+      <c r="E448" t="s">
+        <v>780</v>
+      </c>
       <c r="F448" s="9"/>
     </row>
     <row r="449" spans="4:6" x14ac:dyDescent="0.25">
@@ -12590,7 +12629,7 @@
     <row r="456" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D456" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>4963829.2400000021</v>
+        <v>4971758.6500000022</v>
       </c>
       <c r="F456" s="9"/>
     </row>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Building\my_home\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zip\develop\my_home\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -25,7 +25,7 @@
     <sheet name="котельная и вентиляция" sheetId="14" r:id="rId11"/>
     <sheet name="дерево заказ на 18 апр 2026" sheetId="15" r:id="rId12"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1255" uniqueCount="796">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3355,11 +3355,17 @@
   <si>
     <t>Замена коротких крюков на длинные (водосточная система)</t>
   </si>
+  <si>
+    <t>ООО "Мегаполис-Балтика"</t>
+  </si>
+  <si>
+    <t>труба для дымохода из нерж. Стали 0.6мм d80 L=0.25м</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
@@ -12598,38 +12604,48 @@
       </c>
       <c r="F448" s="9"/>
     </row>
-    <row r="449" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D449" s="7"/>
-      <c r="F449" s="9"/>
-    </row>
-    <row r="450" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="449" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C449" t="s">
+        <v>795</v>
+      </c>
+      <c r="D449" s="7">
+        <v>500</v>
+      </c>
+      <c r="E449" t="s">
+        <v>794</v>
+      </c>
+      <c r="F449" s="9">
+        <v>46178</v>
+      </c>
+    </row>
+    <row r="450" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D450" s="7"/>
       <c r="F450" s="9"/>
     </row>
-    <row r="451" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="451" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D451" s="7"/>
       <c r="F451" s="9"/>
     </row>
-    <row r="452" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="452" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D452" s="7"/>
       <c r="F452" s="9"/>
     </row>
-    <row r="453" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="453" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D453" s="7"/>
       <c r="F453" s="9"/>
     </row>
-    <row r="454" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="454" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D454" s="7"/>
       <c r="F454" s="9"/>
     </row>
-    <row r="455" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="455" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D455" s="7"/>
       <c r="F455" s="9"/>
     </row>
-    <row r="456" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="456" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D456" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>4971758.6500000022</v>
+        <v>4972258.6500000022</v>
       </c>
       <c r="F456" s="9"/>
     </row>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1255" uniqueCount="796">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1259" uniqueCount="798">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3360,6 +3360,12 @@
   </si>
   <si>
     <t>труба для дымохода из нерж. Стали 0.6мм d80 L=0.25м</t>
+  </si>
+  <si>
+    <t>вентиляционный выход ventos x metal f22 d=150mm</t>
+  </si>
+  <si>
+    <t>Эмаль-спрей акриловая color art 520ml ral7024</t>
   </si>
 </sst>
 </file>
@@ -12619,12 +12625,32 @@
       </c>
     </row>
     <row r="450" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D450" s="7"/>
-      <c r="F450" s="9"/>
+      <c r="C450" t="s">
+        <v>796</v>
+      </c>
+      <c r="D450" s="7">
+        <v>6630</v>
+      </c>
+      <c r="E450" t="s">
+        <v>783</v>
+      </c>
+      <c r="F450" s="9">
+        <v>46181</v>
+      </c>
     </row>
     <row r="451" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D451" s="7"/>
-      <c r="F451" s="9"/>
+      <c r="C451" t="s">
+        <v>797</v>
+      </c>
+      <c r="D451" s="7">
+        <v>279</v>
+      </c>
+      <c r="E451" t="s">
+        <v>173</v>
+      </c>
+      <c r="F451" s="9">
+        <v>46182</v>
+      </c>
     </row>
     <row r="452" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D452" s="7"/>
@@ -12645,7 +12671,7 @@
     <row r="456" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D456" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>4972258.6500000022</v>
+        <v>4979167.6500000022</v>
       </c>
       <c r="F456" s="9"/>
     </row>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25320" windowHeight="8145" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25320" windowHeight="8145" firstSheet="6" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Расчёт колличества бетона " sheetId="2" r:id="rId1"/>
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1259" uniqueCount="798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1259" uniqueCount="799">
   <si>
     <t>№ п/п</t>
   </si>
@@ -1781,9 +1781,6 @@
     <t>3 шт Бауцентр</t>
   </si>
   <si>
-    <t>100 мм</t>
-  </si>
-  <si>
     <t>50 мм</t>
   </si>
   <si>
@@ -1796,13 +1793,7 @@
     <t>Стена + мп1/мп2 (от плиты до мп1/мп2)</t>
   </si>
   <si>
-    <t>полная высота стены (газобетон)</t>
-  </si>
-  <si>
     <t>850+230=1080мм</t>
-  </si>
-  <si>
-    <t>100+50+15=165 (230-165 = 65мм разница между проектами)</t>
   </si>
   <si>
     <t>0 - отметка. Верхний уровень чистового пола</t>
@@ -3366,6 +3357,18 @@
   </si>
   <si>
     <t>Эмаль-спрей акриловая color art 520ml ral7024</t>
+  </si>
+  <si>
+    <t>100 мм (50 + 50 мм)</t>
+  </si>
+  <si>
+    <t>клей + плитка</t>
+  </si>
+  <si>
+    <t>нижний край проёма окна</t>
+  </si>
+  <si>
+    <t xml:space="preserve">скорее всего 3 фазная розетка, сечение провода - </t>
   </si>
 </sst>
 </file>
@@ -3778,12 +3781,6 @@
   </cellStyles>
   <dxfs count="35">
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -3832,6 +3829,12 @@
         <top/>
         <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
@@ -4190,9 +4193,9 @@
   <tableColumns count="5">
     <tableColumn id="1" name="№ п/п"/>
     <tableColumn id="2" name="Наименование "/>
-    <tableColumn id="3" name="Цена (руб)" totalsRowFunction="sum" dataDxfId="34" totalsRowDxfId="1"/>
+    <tableColumn id="3" name="Цена (руб)" totalsRowFunction="sum" dataDxfId="34" totalsRowDxfId="7"/>
     <tableColumn id="4" name="Примечание"/>
-    <tableColumn id="5" name="дата" dataDxfId="33" totalsRowDxfId="0"/>
+    <tableColumn id="5" name="дата" dataDxfId="33" totalsRowDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4326,15 +4329,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Таблица2" displayName="Таблица2" ref="A4:F28" totalsRowCount="1">
   <autoFilter ref="A4:F27"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="№ п/п" totalsRowLabel="Итого:" totalsRowDxfId="7"/>
-    <tableColumn id="2" name="Тип" totalsRowDxfId="6"/>
-    <tableColumn id="3" name="Количество (М3/шт)" totalsRowDxfId="5"/>
-    <tableColumn id="4" name="Цена  (м3 или штук)" dataDxfId="32" totalsRowDxfId="4"/>
-    <tableColumn id="5" name="Сумма" totalsRowFunction="custom" dataDxfId="31" totalsRowDxfId="3">
+    <tableColumn id="1" name="№ п/п" totalsRowLabel="Итого:" totalsRowDxfId="5"/>
+    <tableColumn id="2" name="Тип" totalsRowDxfId="4"/>
+    <tableColumn id="3" name="Количество (М3/шт)" totalsRowDxfId="3"/>
+    <tableColumn id="4" name="Цена  (м3 или штук)" dataDxfId="32" totalsRowDxfId="2"/>
+    <tableColumn id="5" name="Сумма" totalsRowFunction="custom" dataDxfId="31" totalsRowDxfId="1">
       <calculatedColumnFormula>Таблица2[[#This Row],[Цена  (м3 или штук)]]*Таблица2[[#This Row],[Количество (М3/шт)]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(E5:E27)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" name="Примечание" totalsRowDxfId="2"/>
+    <tableColumn id="6" name="Примечание" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4920,51 +4923,51 @@
         <v>173</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="11" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="C4" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="F4" t="s">
+        <v>602</v>
+      </c>
+      <c r="G4" t="s">
+        <v>603</v>
+      </c>
+      <c r="H4" t="s">
+        <v>604</v>
+      </c>
+      <c r="I4" t="s">
         <v>605</v>
       </c>
-      <c r="G4" t="s">
+      <c r="J4" t="s">
         <v>606</v>
       </c>
-      <c r="H4" t="s">
+      <c r="K4" t="s">
         <v>607</v>
       </c>
-      <c r="I4" t="s">
-        <v>608</v>
-      </c>
-      <c r="J4" t="s">
-        <v>609</v>
-      </c>
-      <c r="K4" t="s">
-        <v>610</v>
-      </c>
       <c r="L4" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="C5" s="7">
         <v>2790</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="F5" s="7">
         <v>2150</v>
@@ -4984,14 +4987,14 @@
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="C6" s="7">
         <v>2890</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="7">
@@ -5007,14 +5010,14 @@
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="C7" s="7">
         <v>1390</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="F7" s="7"/>
       <c r="G7" s="7">
@@ -5030,14 +5033,14 @@
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="C8" s="7">
         <v>339</v>
       </c>
       <c r="D8" s="7"/>
       <c r="E8" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
@@ -5049,14 +5052,14 @@
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="C9" s="7">
         <v>5190</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
@@ -5068,14 +5071,14 @@
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="C10" s="7">
         <v>329</v>
       </c>
       <c r="D10" s="7"/>
       <c r="E10" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="F10" s="7"/>
       <c r="G10" s="7">
@@ -5089,12 +5092,12 @@
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
       <c r="E11" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -5106,14 +5109,14 @@
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="C12" s="7">
         <v>125</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
@@ -5125,14 +5128,14 @@
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="C13" s="7">
         <v>299</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
@@ -5155,14 +5158,14 @@
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="C15" s="7">
         <v>3190</v>
       </c>
       <c r="D15" s="7"/>
       <c r="E15" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
@@ -5176,14 +5179,14 @@
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="C16" s="7">
         <v>1790</v>
       </c>
       <c r="D16" s="7"/>
       <c r="E16" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -5197,14 +5200,14 @@
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="C17" s="7">
         <v>109</v>
       </c>
       <c r="D17" s="7"/>
       <c r="E17" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
@@ -5219,40 +5222,40 @@
     <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B21" s="11"/>
       <c r="E21" s="11" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B22" s="11"/>
       <c r="E22" s="11" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="F22" t="s">
+        <v>602</v>
+      </c>
+      <c r="G22" t="s">
+        <v>603</v>
+      </c>
+      <c r="H22" t="s">
+        <v>604</v>
+      </c>
+      <c r="I22" t="s">
         <v>605</v>
       </c>
-      <c r="G22" t="s">
+      <c r="J22" t="s">
         <v>606</v>
       </c>
-      <c r="H22" t="s">
+      <c r="K22" t="s">
         <v>607</v>
       </c>
-      <c r="I22" t="s">
-        <v>608</v>
-      </c>
-      <c r="J22" t="s">
+      <c r="L22" t="s">
         <v>609</v>
-      </c>
-      <c r="K22" t="s">
-        <v>610</v>
-      </c>
-      <c r="L22" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C23" s="7"/>
       <c r="E23" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
@@ -5267,7 +5270,7 @@
     <row r="24" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C24" s="7"/>
       <c r="E24" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
@@ -5282,7 +5285,7 @@
     <row r="25" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C25" s="7"/>
       <c r="E25" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
@@ -5297,7 +5300,7 @@
     <row r="26" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C26" s="7"/>
       <c r="E26" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="F26" s="7"/>
       <c r="G26" s="7"/>
@@ -5310,7 +5313,7 @@
     <row r="27" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C27" s="7"/>
       <c r="E27" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
@@ -5325,7 +5328,7 @@
     <row r="28" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C28" s="7"/>
       <c r="E28" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="F28" s="7"/>
       <c r="G28" s="7"/>
@@ -5340,7 +5343,7 @@
     <row r="29" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C29" s="7"/>
       <c r="E29" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
@@ -5353,7 +5356,7 @@
     <row r="30" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C30" s="7"/>
       <c r="E30" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
@@ -5368,7 +5371,7 @@
     <row r="31" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C31" s="7"/>
       <c r="E31" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="F31" s="7"/>
       <c r="G31" s="7"/>
@@ -5393,7 +5396,7 @@
     <row r="33" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C33" s="7"/>
       <c r="E33" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="F33" s="7"/>
       <c r="G33" s="7"/>
@@ -5408,7 +5411,7 @@
     <row r="34" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C34" s="7"/>
       <c r="E34" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="F34" s="7"/>
       <c r="G34" s="7"/>
@@ -5421,7 +5424,7 @@
     <row r="35" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C35" s="7"/>
       <c r="E35" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="F35" s="7"/>
       <c r="G35" s="7"/>
@@ -5454,112 +5457,112 @@
   <sheetData>
     <row r="3" spans="2:6" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="43" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="F3" s="43" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="44"/>
       <c r="F4" s="49" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="129.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="43" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="F5" s="50" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B6" s="44"/>
       <c r="F6" s="46" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="45" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="F7" s="46" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="122.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="43" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="F8" s="46" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="44" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="F9" s="51" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="46" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="F10" s="43" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="46" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
     </row>
     <row r="12" spans="2:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B12" s="46" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="13" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B13" s="46" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="47" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="15" spans="2:6" ht="133.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="47" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B16" s="48" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
     </row>
     <row r="17" spans="2:2" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="45" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="18" spans="2:2" ht="161.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="46" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
     </row>
     <row r="19" spans="2:2" ht="105.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="46" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
     </row>
     <row r="20" spans="2:2" ht="144" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="46" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
   </sheetData>
@@ -5583,10 +5586,10 @@
   <sheetData>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="C3" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="D3" t="s">
         <v>1</v>
@@ -5594,79 +5597,79 @@
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="C4">
         <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="C5">
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="C6" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="D6" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="C7" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="D7" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
+        <v>695</v>
+      </c>
+      <c r="C8" t="s">
         <v>698</v>
       </c>
-      <c r="C8" t="s">
-        <v>701</v>
-      </c>
       <c r="D8" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
+        <v>703</v>
+      </c>
+      <c r="C14" t="s">
+        <v>704</v>
+      </c>
+      <c r="D14" t="s">
+        <v>705</v>
+      </c>
+      <c r="E14" t="s">
         <v>706</v>
       </c>
-      <c r="C14" t="s">
+      <c r="F14" t="s">
         <v>707</v>
-      </c>
-      <c r="D14" t="s">
-        <v>708</v>
-      </c>
-      <c r="E14" t="s">
-        <v>709</v>
-      </c>
-      <c r="F14" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="C15">
         <v>109</v>
@@ -5683,7 +5686,7 @@
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="C16">
         <v>25</v>
@@ -5700,7 +5703,7 @@
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="C17">
         <v>3</v>
@@ -5717,7 +5720,7 @@
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="C18">
         <v>104</v>
@@ -9295,7 +9298,7 @@
         <v>211</v>
       </c>
       <c r="C215" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="D215" s="7">
         <v>4551</v>
@@ -9312,7 +9315,7 @@
         <v>212</v>
       </c>
       <c r="C216" s="38" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D216" s="7">
         <v>49.77</v>
@@ -9329,7 +9332,7 @@
         <v>213</v>
       </c>
       <c r="C217" s="38" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="D217" s="7">
         <v>55.88</v>
@@ -9346,7 +9349,7 @@
         <v>214</v>
       </c>
       <c r="C218" s="38" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D218" s="7">
         <v>103.04</v>
@@ -9363,7 +9366,7 @@
         <v>215</v>
       </c>
       <c r="C219" s="38" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D219" s="7">
         <v>64.61</v>
@@ -9380,7 +9383,7 @@
         <v>216</v>
       </c>
       <c r="C220" s="38" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="D220" s="7">
         <v>132.72999999999999</v>
@@ -9414,7 +9417,7 @@
         <v>218</v>
       </c>
       <c r="C222" s="38" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="D222" s="7">
         <v>130.1</v>
@@ -9431,7 +9434,7 @@
         <v>219</v>
       </c>
       <c r="C223" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="D223" s="7">
         <v>15789</v>
@@ -9448,7 +9451,7 @@
         <v>220</v>
       </c>
       <c r="C224" s="18" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D224" s="39">
         <v>389</v>
@@ -9482,7 +9485,7 @@
         <v>222</v>
       </c>
       <c r="C226" s="18" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D226" s="7">
         <v>2590</v>
@@ -9499,7 +9502,7 @@
         <v>223</v>
       </c>
       <c r="C227" s="18" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="D227" s="7">
         <v>2590</v>
@@ -9516,7 +9519,7 @@
         <v>224</v>
       </c>
       <c r="C228" s="40" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="D228" s="41">
         <v>1490</v>
@@ -9533,7 +9536,7 @@
         <v>225</v>
       </c>
       <c r="C229" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="D229" s="7">
         <v>8000</v>
@@ -9550,7 +9553,7 @@
         <v>226</v>
       </c>
       <c r="C230" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="D230" s="7">
         <v>7000</v>
@@ -9567,13 +9570,13 @@
         <v>227</v>
       </c>
       <c r="C231" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="D231" s="7">
         <v>500</v>
       </c>
       <c r="E231" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="F231" s="9">
         <v>45844</v>
@@ -9584,13 +9587,13 @@
         <v>228</v>
       </c>
       <c r="C232" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="D232" s="7">
         <v>6675</v>
       </c>
       <c r="E232" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="F232" s="9"/>
     </row>
@@ -9599,7 +9602,7 @@
         <v>229</v>
       </c>
       <c r="C233" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D233" s="7">
         <v>605</v>
@@ -9611,7 +9614,7 @@
     </row>
     <row r="234" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C234" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="D234" s="7">
         <v>1148</v>
@@ -9623,7 +9626,7 @@
     </row>
     <row r="235" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C235" s="42" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D235" s="7">
         <v>153.61000000000001</v>
@@ -9635,7 +9638,7 @@
     </row>
     <row r="236" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C236" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="D236" s="7">
         <v>373.45</v>
@@ -9647,7 +9650,7 @@
     </row>
     <row r="237" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C237" s="42" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="D237" s="7">
         <v>1143</v>
@@ -9659,7 +9662,7 @@
     </row>
     <row r="238" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C238" s="42" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D238" s="7">
         <v>1843</v>
@@ -9671,7 +9674,7 @@
     </row>
     <row r="239" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C239" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="D239" s="7">
         <v>1140</v>
@@ -9683,7 +9686,7 @@
     </row>
     <row r="240" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C240" s="18" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D240" s="19">
         <v>2089.8000000000002</v>
@@ -9697,7 +9700,7 @@
     </row>
     <row r="241" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C241" s="18" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D241" s="7">
         <v>37.22</v>
@@ -9711,7 +9714,7 @@
     </row>
     <row r="242" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C242" s="18" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="D242" s="7">
         <v>208.98</v>
@@ -9725,7 +9728,7 @@
     </row>
     <row r="243" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C243" s="18" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="D243" s="7">
         <v>289</v>
@@ -9739,7 +9742,7 @@
     </row>
     <row r="244" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C244" s="18" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D244" s="7">
         <v>169</v>
@@ -9753,7 +9756,7 @@
     </row>
     <row r="245" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C245" s="18" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="D245" s="7">
         <v>849</v>
@@ -9767,7 +9770,7 @@
     </row>
     <row r="246" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C246" s="18" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D246" s="7">
         <v>339</v>
@@ -9781,13 +9784,13 @@
     </row>
     <row r="247" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C247" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D247" s="7">
         <v>881.91</v>
       </c>
       <c r="E247" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="F247" s="9">
         <v>45879</v>
@@ -9795,7 +9798,7 @@
     </row>
     <row r="248" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C248" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="D248" s="7">
         <v>1464.94</v>
@@ -9809,13 +9812,13 @@
     </row>
     <row r="249" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C249" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D249" s="7">
         <v>785.56</v>
       </c>
       <c r="E249" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="F249" s="9">
         <v>45879</v>
@@ -9823,13 +9826,13 @@
     </row>
     <row r="250" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C250" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D250" s="7">
         <v>1451.16</v>
       </c>
       <c r="E250" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="F250" s="9">
         <v>45879</v>
@@ -9837,13 +9840,13 @@
     </row>
     <row r="251" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C251" s="18" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D251" s="7">
         <v>515.94000000000005</v>
       </c>
       <c r="E251" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="F251" s="9">
         <v>45886</v>
@@ -9851,7 +9854,7 @@
     </row>
     <row r="252" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C252" s="18" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="D252" s="7">
         <v>197.58</v>
@@ -9865,7 +9868,7 @@
     </row>
     <row r="253" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C253" s="18" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="D253" s="7">
         <v>292.48</v>
@@ -9879,13 +9882,13 @@
     </row>
     <row r="254" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C254" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="D254" s="7">
         <v>58000</v>
       </c>
       <c r="E254" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="F254" s="9">
         <v>45913</v>
@@ -9893,13 +9896,13 @@
     </row>
     <row r="255" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C255" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D255" s="7">
         <v>194700</v>
       </c>
       <c r="E255" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F255" s="9">
         <v>45915</v>
@@ -9907,13 +9910,13 @@
     </row>
     <row r="256" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C256" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="D256" s="7">
         <v>7000</v>
       </c>
       <c r="E256" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F256" s="9">
         <v>45915</v>
@@ -9921,7 +9924,7 @@
     </row>
     <row r="257" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C257" s="18" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D257" s="7">
         <v>829</v>
@@ -9935,7 +9938,7 @@
     </row>
     <row r="258" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C258" s="18" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="D258" s="7">
         <v>117</v>
@@ -9949,7 +9952,7 @@
     </row>
     <row r="259" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C259" s="18" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D259" s="7">
         <v>179</v>
@@ -9963,7 +9966,7 @@
     </row>
     <row r="260" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C260" s="18" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D260" s="7">
         <v>169</v>
@@ -9977,7 +9980,7 @@
     </row>
     <row r="261" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C261" s="18" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="D261" s="7">
         <v>1269</v>
@@ -9991,13 +9994,13 @@
     </row>
     <row r="262" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C262" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D262" s="7">
         <v>4000</v>
       </c>
       <c r="E262" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="F262" s="9">
         <v>45916</v>
@@ -10005,7 +10008,7 @@
     </row>
     <row r="263" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C263" s="18" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="D263" s="7">
         <v>262.33999999999997</v>
@@ -10016,7 +10019,7 @@
     </row>
     <row r="264" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C264" s="18" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D264" s="7">
         <v>56.15</v>
@@ -10027,13 +10030,13 @@
     </row>
     <row r="265" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C265" s="18" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="D265" s="7">
         <v>697.5</v>
       </c>
       <c r="E265" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="F265" s="9">
         <v>45917</v>
@@ -10041,13 +10044,13 @@
     </row>
     <row r="266" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C266" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="D266" s="7">
         <v>13300</v>
       </c>
       <c r="E266" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="F266" s="9">
         <v>45917</v>
@@ -10055,7 +10058,7 @@
     </row>
     <row r="267" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C267" s="18" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="D267" s="7">
         <v>299</v>
@@ -10069,13 +10072,13 @@
     </row>
     <row r="268" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C268" s="18" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="D268" s="7">
         <v>124</v>
       </c>
       <c r="E268" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="F268" s="9">
         <v>45919</v>
@@ -10083,7 +10086,7 @@
     </row>
     <row r="269" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C269" s="18" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D269" s="7">
         <v>59</v>
@@ -10097,7 +10100,7 @@
     </row>
     <row r="270" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C270" s="18" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="D270" s="7">
         <v>32</v>
@@ -10111,7 +10114,7 @@
     </row>
     <row r="271" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C271" s="18" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="D271" s="7">
         <v>69</v>
@@ -10125,13 +10128,13 @@
     </row>
     <row r="272" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C272" s="18" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="D272" s="7">
         <v>195</v>
       </c>
       <c r="E272" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="F272" s="9">
         <v>45919</v>
@@ -10139,7 +10142,7 @@
     </row>
     <row r="273" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C273" s="18" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D273" s="7">
         <v>99.84</v>
@@ -10153,7 +10156,7 @@
     </row>
     <row r="274" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C274" s="18" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="D274" s="7">
         <v>585.32000000000005</v>
@@ -10167,7 +10170,7 @@
     </row>
     <row r="275" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C275" s="18" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="D275" s="7">
         <v>99.84</v>
@@ -10181,7 +10184,7 @@
     </row>
     <row r="276" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C276" s="18" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D276" s="7">
         <v>829</v>
@@ -10195,7 +10198,7 @@
     </row>
     <row r="277" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C277" s="18" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D277" s="7">
         <v>829</v>
@@ -10209,7 +10212,7 @@
     </row>
     <row r="278" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C278" s="18" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D278" s="7">
         <v>731</v>
@@ -10223,7 +10226,7 @@
     </row>
     <row r="279" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C279" s="18" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="D279" s="7">
         <v>1269</v>
@@ -10237,7 +10240,7 @@
     </row>
     <row r="280" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C280" s="18" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D280" s="7">
         <v>375</v>
@@ -10251,7 +10254,7 @@
     </row>
     <row r="281" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C281" s="18" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D281" s="7">
         <v>375</v>
@@ -10265,13 +10268,13 @@
     </row>
     <row r="282" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C282" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D282" s="7">
         <v>11300</v>
       </c>
       <c r="E282" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="F282" s="9">
         <v>45946</v>
@@ -10279,13 +10282,13 @@
     </row>
     <row r="283" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C283" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="D283" s="7">
         <v>7722</v>
       </c>
       <c r="E283" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="F283" s="9">
         <v>45947</v>
@@ -10293,13 +10296,13 @@
     </row>
     <row r="284" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C284" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="D284" s="7">
         <v>1764</v>
       </c>
       <c r="E284" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="F284" s="9">
         <v>45947</v>
@@ -10307,13 +10310,13 @@
     </row>
     <row r="285" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C285" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="D285" s="7">
         <v>136</v>
       </c>
       <c r="E285" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="F285" s="9">
         <v>45947</v>
@@ -10327,7 +10330,7 @@
         <v>717</v>
       </c>
       <c r="E286" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="F286" s="9">
         <v>45947</v>
@@ -10335,7 +10338,7 @@
     </row>
     <row r="287" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C287" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D287" s="7">
         <v>716</v>
@@ -10349,7 +10352,7 @@
     </row>
     <row r="288" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C288" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="D288" s="7">
         <v>604</v>
@@ -10363,7 +10366,7 @@
     </row>
     <row r="289" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C289" s="18" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D289" s="7">
         <v>139.35</v>
@@ -10377,7 +10380,7 @@
     </row>
     <row r="290" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C290" s="18" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="D290" s="7">
         <v>131.11000000000001</v>
@@ -10391,7 +10394,7 @@
     </row>
     <row r="291" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C291" s="18" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="D291" s="7">
         <v>246.54</v>
@@ -10405,13 +10408,13 @@
     </row>
     <row r="292" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C292" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D292" s="7">
         <v>44500</v>
       </c>
       <c r="E292" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="F292" s="9">
         <v>45953</v>
@@ -10419,13 +10422,13 @@
     </row>
     <row r="293" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C293" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="D293" s="7">
         <v>44050</v>
       </c>
       <c r="E293" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="F293" s="9">
         <v>45954</v>
@@ -10433,13 +10436,13 @@
     </row>
     <row r="294" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C294" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="D294" s="7">
         <v>500</v>
       </c>
       <c r="E294" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="F294" s="9">
         <v>45954</v>
@@ -10447,13 +10450,13 @@
     </row>
     <row r="295" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C295" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D295" s="7">
         <v>136080</v>
       </c>
       <c r="E295" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F295" s="9">
         <v>45968</v>
@@ -10461,13 +10464,13 @@
     </row>
     <row r="296" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C296" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="D296" s="7">
         <v>8500</v>
       </c>
       <c r="E296" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="F296" s="9">
         <v>45968</v>
@@ -10475,7 +10478,7 @@
     </row>
     <row r="297" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C297" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D297" s="7">
         <v>3290</v>
@@ -10489,7 +10492,7 @@
     </row>
     <row r="298" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C298" s="18" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D298" s="7">
         <v>2893</v>
@@ -10503,13 +10506,13 @@
     </row>
     <row r="299" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C299" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D299" s="7">
         <v>569.9</v>
       </c>
       <c r="E299" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="F299" s="9">
         <v>45974</v>
@@ -10517,7 +10520,7 @@
     </row>
     <row r="300" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C300" s="18" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D300" s="7">
         <v>265.61</v>
@@ -10531,7 +10534,7 @@
     </row>
     <row r="301" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C301" s="18" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="D301" s="7">
         <v>76.39</v>
@@ -10545,7 +10548,7 @@
     </row>
     <row r="302" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C302" s="18" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D302" s="7">
         <v>153</v>
@@ -10559,7 +10562,7 @@
     </row>
     <row r="303" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C303" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D303" s="7">
         <v>154.12</v>
@@ -10573,7 +10576,7 @@
     </row>
     <row r="304" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C304" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="D304" s="7">
         <v>154.12</v>
@@ -10587,7 +10590,7 @@
     </row>
     <row r="305" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C305" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="D305" s="7">
         <v>168.76</v>
@@ -10601,7 +10604,7 @@
     </row>
     <row r="306" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C306" s="18" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D306" s="7">
         <v>59</v>
@@ -10615,7 +10618,7 @@
     </row>
     <row r="307" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C307" s="18" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="D307" s="7">
         <v>209</v>
@@ -10629,7 +10632,7 @@
     </row>
     <row r="308" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C308" s="18" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D308" s="7">
         <v>989</v>
@@ -10643,7 +10646,7 @@
     </row>
     <row r="309" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C309" s="18" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="D309" s="7">
         <v>256</v>
@@ -10657,7 +10660,7 @@
     </row>
     <row r="310" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C310" s="18" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="D310" s="7">
         <v>50</v>
@@ -10671,7 +10674,7 @@
     </row>
     <row r="311" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C311" s="18" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="D311" s="7">
         <v>69</v>
@@ -10685,13 +10688,13 @@
     </row>
     <row r="312" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C312" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="D312" s="7">
         <v>2100</v>
       </c>
       <c r="E312" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="F312" s="20">
         <v>46001</v>
@@ -10699,13 +10702,13 @@
     </row>
     <row r="313" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C313" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="D313" s="7">
         <v>380</v>
       </c>
       <c r="E313" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="F313" s="20">
         <v>46001</v>
@@ -10713,13 +10716,13 @@
     </row>
     <row r="314" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C314" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="D314" s="7">
         <v>220</v>
       </c>
       <c r="E314" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="F314" s="20">
         <v>46001</v>
@@ -10727,7 +10730,7 @@
     </row>
     <row r="315" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C315" s="18" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="D315" s="7">
         <v>158.31</v>
@@ -10741,7 +10744,7 @@
     </row>
     <row r="316" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C316" s="18" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="D316" s="7">
         <v>367.2</v>
@@ -10755,7 +10758,7 @@
     </row>
     <row r="317" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C317" s="18" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="D317" s="7">
         <v>167.68</v>
@@ -10769,13 +10772,13 @@
     </row>
     <row r="318" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C318" s="18" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="D318" s="7">
         <v>550.80999999999995</v>
       </c>
       <c r="E318" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="F318" s="9">
         <v>46014</v>
@@ -10783,7 +10786,7 @@
     </row>
     <row r="319" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C319" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="D319" s="7">
         <v>125</v>
@@ -10797,7 +10800,7 @@
     </row>
     <row r="320" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C320" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="D320" s="7">
         <v>209</v>
@@ -10811,7 +10814,7 @@
     </row>
     <row r="321" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C321" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="D321" s="7">
         <v>138</v>
@@ -10825,7 +10828,7 @@
     </row>
     <row r="322" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C322" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="D322" s="7">
         <v>539</v>
@@ -10839,7 +10842,7 @@
     </row>
     <row r="323" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C323" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="D323" s="7">
         <v>479</v>
@@ -10853,7 +10856,7 @@
     </row>
     <row r="324" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C324" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="D324" s="7">
         <v>839</v>
@@ -10867,13 +10870,13 @@
     </row>
     <row r="325" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C325" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="D325" s="7">
         <v>2471</v>
       </c>
       <c r="E325" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="F325" s="9">
         <v>46071</v>
@@ -10881,13 +10884,13 @@
     </row>
     <row r="326" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C326" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="D326" s="7">
         <v>3700</v>
       </c>
       <c r="E326" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="F326" s="9">
         <v>46071</v>
@@ -10895,13 +10898,13 @@
     </row>
     <row r="327" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C327" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="D327" s="7">
         <v>473</v>
       </c>
       <c r="E327" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="F327" s="9">
         <v>46071</v>
@@ -10909,13 +10912,13 @@
     </row>
     <row r="328" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C328" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="D328" s="7">
         <v>2040</v>
       </c>
       <c r="E328" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="F328" s="9">
         <v>46070</v>
@@ -10923,16 +10926,16 @@
     </row>
     <row r="329" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B329" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="C329" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="D329" s="7">
         <v>348</v>
       </c>
       <c r="E329" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="F329" s="9">
         <v>46070</v>
@@ -10940,13 +10943,13 @@
     </row>
     <row r="330" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C330" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="D330" s="7">
         <v>988</v>
       </c>
       <c r="E330" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="F330" s="9">
         <v>46084</v>
@@ -10954,7 +10957,7 @@
     </row>
     <row r="331" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C331" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="D331" s="7">
         <v>8000</v>
@@ -10968,13 +10971,13 @@
     </row>
     <row r="332" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C332" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="D332" s="7">
         <v>1215</v>
       </c>
       <c r="E332" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="F332" s="9">
         <v>46085</v>
@@ -10982,13 +10985,13 @@
     </row>
     <row r="333" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C333" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="D333" s="7">
         <v>3275</v>
       </c>
       <c r="E333" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="F333" s="9">
         <v>46085</v>
@@ -10996,13 +10999,13 @@
     </row>
     <row r="334" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C334" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="D334" s="7">
         <v>677</v>
       </c>
       <c r="E334" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="F334" s="9">
         <v>46080</v>
@@ -11010,13 +11013,13 @@
     </row>
     <row r="335" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C335" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="D335" s="7">
         <v>1123</v>
       </c>
       <c r="E335" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="F335" s="9">
         <v>46079</v>
@@ -11024,7 +11027,7 @@
     </row>
     <row r="336" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C336" s="18" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="D336" s="7">
         <v>127.78</v>
@@ -11038,7 +11041,7 @@
     </row>
     <row r="337" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C337" s="18" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="D337" s="7">
         <v>450</v>
@@ -11052,7 +11055,7 @@
     </row>
     <row r="338" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C338" s="18" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="D338" s="7">
         <v>182</v>
@@ -11066,7 +11069,7 @@
     </row>
     <row r="339" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C339" s="18" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="D339" s="7">
         <v>228.89</v>
@@ -11080,7 +11083,7 @@
     </row>
     <row r="340" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C340" s="18" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="D340" s="7">
         <v>228.89</v>
@@ -11094,7 +11097,7 @@
     </row>
     <row r="341" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C341" s="18" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="D341" s="7">
         <v>102</v>
@@ -11108,7 +11111,7 @@
     </row>
     <row r="342" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C342" s="18" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="D342" s="7">
         <v>116.15</v>
@@ -11122,7 +11125,7 @@
     </row>
     <row r="343" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C343" s="18" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="D343" s="7">
         <v>224.2</v>
@@ -11136,13 +11139,13 @@
     </row>
     <row r="344" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C344" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="D344" s="7">
         <v>845</v>
       </c>
       <c r="E344" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="F344" s="9">
         <v>46105</v>
@@ -11150,7 +11153,7 @@
     </row>
     <row r="345" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C345" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="D345" s="7">
         <v>898</v>
@@ -11164,7 +11167,7 @@
     </row>
     <row r="346" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C346" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="D346" s="7">
         <v>444</v>
@@ -11178,7 +11181,7 @@
     </row>
     <row r="347" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C347" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="D347" s="7">
         <v>179</v>
@@ -11192,7 +11195,7 @@
     </row>
     <row r="348" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C348" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="D348" s="7">
         <v>98</v>
@@ -11206,7 +11209,7 @@
     </row>
     <row r="349" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C349" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="D349" s="7">
         <v>374</v>
@@ -11220,7 +11223,7 @@
     </row>
     <row r="350" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C350" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="D350" s="7">
         <v>271</v>
@@ -11234,7 +11237,7 @@
     </row>
     <row r="351" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C351" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="D351" s="7">
         <v>57</v>
@@ -11248,7 +11251,7 @@
     </row>
     <row r="352" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C352" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="D352" s="7">
         <v>1100</v>
@@ -11262,7 +11265,7 @@
     </row>
     <row r="353" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C353" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="D353" s="7">
         <v>756</v>
@@ -11276,7 +11279,7 @@
     </row>
     <row r="354" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C354" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="D354" s="7">
         <v>358</v>
@@ -11310,7 +11313,7 @@
         <v>4000</v>
       </c>
       <c r="E356" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="F356" s="9">
         <v>46113</v>
@@ -11318,13 +11321,13 @@
     </row>
     <row r="357" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C357" s="54" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="D357" s="7">
         <v>6138</v>
       </c>
       <c r="E357" s="52" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="F357" s="9">
         <v>46119</v>
@@ -11333,13 +11336,13 @@
     </row>
     <row r="358" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C358" s="54" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="D358" s="7">
         <v>8890</v>
       </c>
       <c r="E358" s="52" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="F358" s="9">
         <v>46119</v>
@@ -11347,13 +11350,13 @@
     </row>
     <row r="359" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C359" s="54" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D359" s="7">
         <v>17960</v>
       </c>
       <c r="E359" s="52" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="F359" s="9">
         <v>46119</v>
@@ -11361,13 +11364,13 @@
     </row>
     <row r="360" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C360" s="53" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="D360" s="7">
         <v>529</v>
       </c>
       <c r="E360" s="52" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="F360" s="9">
         <v>46119</v>
@@ -11375,13 +11378,13 @@
     </row>
     <row r="361" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C361" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="D361" s="7">
         <v>1092.22</v>
       </c>
       <c r="E361" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="F361" s="9">
         <v>46123</v>
@@ -11389,13 +11392,13 @@
     </row>
     <row r="362" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C362" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="D362" s="7">
         <v>16.489999999999998</v>
       </c>
       <c r="E362" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="F362" s="9">
         <v>46123</v>
@@ -11403,13 +11406,13 @@
     </row>
     <row r="363" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C363" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="D363" s="7">
         <v>183</v>
       </c>
       <c r="E363" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="F363" s="9">
         <v>46123</v>
@@ -11417,13 +11420,13 @@
     </row>
     <row r="364" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C364" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="D364" s="7">
         <v>792</v>
       </c>
       <c r="E364" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="F364" s="9">
         <v>46124</v>
@@ -11431,13 +11434,13 @@
     </row>
     <row r="365" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C365" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="D365" s="7">
         <v>136</v>
       </c>
       <c r="E365" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="F365" s="9">
         <v>46124</v>
@@ -11445,13 +11448,13 @@
     </row>
     <row r="366" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C366" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="D366" s="7">
         <v>101</v>
       </c>
       <c r="E366" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="F366" s="9">
         <v>46124</v>
@@ -11459,13 +11462,13 @@
     </row>
     <row r="367" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C367" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="D367" s="7">
         <v>72</v>
       </c>
       <c r="E367" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="F367" s="9">
         <v>46124</v>
@@ -11473,13 +11476,13 @@
     </row>
     <row r="368" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C368" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="D368" s="7">
         <v>164</v>
       </c>
       <c r="E368" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="F368" s="9">
         <v>46127</v>
@@ -11487,13 +11490,13 @@
     </row>
     <row r="369" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C369" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="D369" s="7">
         <v>162</v>
       </c>
       <c r="E369" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="F369" s="9">
         <v>46127</v>
@@ -11501,13 +11504,13 @@
     </row>
     <row r="370" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C370" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="D370" s="7">
         <v>42510</v>
       </c>
       <c r="E370" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F370" s="9">
         <v>46132</v>
@@ -11515,13 +11518,13 @@
     </row>
     <row r="371" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C371" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="D371" s="7">
         <v>39000</v>
       </c>
       <c r="E371" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F371" s="9">
         <v>46132</v>
@@ -11529,13 +11532,13 @@
     </row>
     <row r="372" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C372" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="D372" s="7">
         <v>3510</v>
       </c>
       <c r="E372" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F372" s="9">
         <v>46132</v>
@@ -11543,13 +11546,13 @@
     </row>
     <row r="373" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C373" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="D373" s="7">
         <v>20280</v>
       </c>
       <c r="E373" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F373" s="9">
         <v>46132</v>
@@ -11557,13 +11560,13 @@
     </row>
     <row r="374" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C374" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="D374" s="7">
         <v>6000</v>
       </c>
       <c r="E374" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="F374" s="9">
         <v>46132</v>
@@ -11571,7 +11574,7 @@
     </row>
     <row r="375" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C375" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="D375" s="7">
         <v>259.95999999999998</v>
@@ -11585,7 +11588,7 @@
     </row>
     <row r="376" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C376" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="D376" s="7">
         <v>183</v>
@@ -11599,7 +11602,7 @@
     </row>
     <row r="377" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C377" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="D377" s="7">
         <v>251.23</v>
@@ -11613,7 +11616,7 @@
     </row>
     <row r="378" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C378" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="D378" s="7">
         <v>1092.22</v>
@@ -11627,7 +11630,7 @@
     </row>
     <row r="379" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C379" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="D379" s="7">
         <v>182.22</v>
@@ -11641,7 +11644,7 @@
     </row>
     <row r="380" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C380" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="D380" s="7">
         <v>46.02</v>
@@ -11655,7 +11658,7 @@
     </row>
     <row r="381" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C381" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="D381" s="7">
         <v>108.6</v>
@@ -11669,7 +11672,7 @@
     </row>
     <row r="382" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C382" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="D382" s="7">
         <v>323.95999999999998</v>
@@ -11683,13 +11686,13 @@
     </row>
     <row r="383" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C383" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="D383" s="7">
         <v>175</v>
       </c>
       <c r="E383" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="F383" s="9">
         <v>46139</v>
@@ -11697,13 +11700,13 @@
     </row>
     <row r="384" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C384" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="D384" s="7">
         <v>109</v>
       </c>
       <c r="E384" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="F384" s="9">
         <v>46139</v>
@@ -11711,13 +11714,13 @@
     </row>
     <row r="385" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C385" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="D385" s="7">
         <v>171</v>
       </c>
       <c r="E385" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="F385" s="9">
         <v>46139</v>
@@ -11725,13 +11728,13 @@
     </row>
     <row r="386" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C386" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="D386" s="7">
         <v>196</v>
       </c>
       <c r="E386" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="F386" s="9">
         <v>46139</v>
@@ -11739,7 +11742,7 @@
     </row>
     <row r="387" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C387" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="D387" s="7">
         <v>480.8</v>
@@ -11753,7 +11756,7 @@
     </row>
     <row r="388" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C388" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="D388" s="7">
         <v>182.47</v>
@@ -11767,7 +11770,7 @@
     </row>
     <row r="389" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C389" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="D389" s="7">
         <v>547.41</v>
@@ -11781,13 +11784,13 @@
     </row>
     <row r="390" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C390" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="D390" s="7">
         <v>29640</v>
       </c>
       <c r="E390" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="F390" s="9">
         <v>46147</v>
@@ -11795,13 +11798,13 @@
     </row>
     <row r="391" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C391" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="D391" s="7">
         <v>1560</v>
       </c>
       <c r="E391" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="F391" s="9">
         <v>46147</v>
@@ -11809,7 +11812,7 @@
     </row>
     <row r="392" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C392" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="D392" s="7">
         <v>3000</v>
@@ -11823,7 +11826,7 @@
     </row>
     <row r="393" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C393" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="D393" s="7">
         <v>57.94</v>
@@ -11837,7 +11840,7 @@
     </row>
     <row r="394" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C394" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="D394" s="7">
         <v>98.67</v>
@@ -11851,7 +11854,7 @@
     </row>
     <row r="395" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C395" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="D395" s="7">
         <v>152.08000000000001</v>
@@ -11865,7 +11868,7 @@
     </row>
     <row r="396" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C396" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="D396" s="7">
         <v>207.31</v>
@@ -11879,7 +11882,7 @@
     </row>
     <row r="397" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C397" s="18" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="D397" s="7">
         <v>899</v>
@@ -11893,7 +11896,7 @@
     </row>
     <row r="398" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C398" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="D398" s="7">
         <v>1196</v>
@@ -11907,7 +11910,7 @@
     </row>
     <row r="399" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C399" s="18" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="D399" s="7">
         <v>238</v>
@@ -11921,7 +11924,7 @@
     </row>
     <row r="400" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C400" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="D400" s="7">
         <v>9164.33</v>
@@ -11935,7 +11938,7 @@
     </row>
     <row r="401" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C401" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="D401" s="7">
         <v>8507.39</v>
@@ -11949,7 +11952,7 @@
     </row>
     <row r="402" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C402" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="D402" s="7">
         <v>890.85</v>
@@ -11963,7 +11966,7 @@
     </row>
     <row r="403" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C403" s="18" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="D403" s="7">
         <v>1570.68</v>
@@ -11977,7 +11980,7 @@
     </row>
     <row r="404" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C404" s="18" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="D404" s="7">
         <v>2780.06</v>
@@ -11991,7 +11994,7 @@
     </row>
     <row r="405" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C405" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="D405" s="7">
         <v>1570.7</v>
@@ -12005,7 +12008,7 @@
     </row>
     <row r="406" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C406" s="18" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="D406" s="7">
         <v>2030</v>
@@ -12019,13 +12022,13 @@
     </row>
     <row r="407" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C407" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="D407" s="7">
         <v>1900</v>
       </c>
       <c r="E407" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="F407" s="9">
         <v>46164</v>
@@ -12033,7 +12036,7 @@
     </row>
     <row r="408" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C408" s="18" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="D408" s="7">
         <v>277.24</v>
@@ -12047,7 +12050,7 @@
     </row>
     <row r="409" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C409" s="18" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="D409" s="7">
         <v>110.62</v>
@@ -12061,13 +12064,13 @@
     </row>
     <row r="410" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C410" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="D410" s="7">
         <v>7414</v>
       </c>
       <c r="E410" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="F410" s="9">
         <v>46165</v>
@@ -12075,13 +12078,13 @@
     </row>
     <row r="411" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C411" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="D411" s="7">
         <v>81</v>
       </c>
       <c r="E411" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="F411" s="9">
         <v>46165</v>
@@ -12095,7 +12098,7 @@
         <v>670</v>
       </c>
       <c r="E412" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="F412" s="9">
         <v>46165</v>
@@ -12103,7 +12106,7 @@
     </row>
     <row r="413" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C413" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="D413" s="7">
         <v>548.04999999999995</v>
@@ -12117,7 +12120,7 @@
     </row>
     <row r="414" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C414" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="D414" s="7">
         <v>703.25</v>
@@ -12131,7 +12134,7 @@
     </row>
     <row r="415" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C415" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="D415" s="7">
         <v>960.3</v>
@@ -12145,7 +12148,7 @@
     </row>
     <row r="416" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C416" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="D416" s="7">
         <v>348.23</v>
@@ -12159,7 +12162,7 @@
     </row>
     <row r="417" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C417" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="D417" s="7">
         <v>3841.2</v>
@@ -12173,7 +12176,7 @@
     </row>
     <row r="418" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C418" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="D418" s="7">
         <v>192.06</v>
@@ -12187,7 +12190,7 @@
     </row>
     <row r="419" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C419" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="D419" s="7">
         <v>1203.43</v>
@@ -12201,7 +12204,7 @@
     </row>
     <row r="420" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C420" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="D420" s="7">
         <v>649.45000000000005</v>
@@ -12215,7 +12218,7 @@
     </row>
     <row r="421" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C421" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="D421" s="7">
         <v>246.12</v>
@@ -12229,7 +12232,7 @@
     </row>
     <row r="422" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C422" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="D422" s="7">
         <v>384.89</v>
@@ -12243,7 +12246,7 @@
     </row>
     <row r="423" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C423" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="D423" s="7">
         <v>257.56</v>
@@ -12257,7 +12260,7 @@
     </row>
     <row r="424" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C424" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="D424" s="7">
         <v>622.17999999999995</v>
@@ -12271,7 +12274,7 @@
     </row>
     <row r="425" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C425" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="D425" s="7">
         <v>120.58</v>
@@ -12285,7 +12288,7 @@
     </row>
     <row r="426" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C426" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="D426" s="7">
         <v>192.94</v>
@@ -12299,7 +12302,7 @@
     </row>
     <row r="427" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C427" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="D427" s="7">
         <v>336.65</v>
@@ -12313,7 +12316,7 @@
     </row>
     <row r="428" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C428" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="D428" s="7">
         <v>376.2</v>
@@ -12327,7 +12330,7 @@
     </row>
     <row r="429" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C429" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="D429" s="7">
         <v>399</v>
@@ -12341,7 +12344,7 @@
     </row>
     <row r="430" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C430" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="D430" s="7">
         <v>1250</v>
@@ -12355,7 +12358,7 @@
     </row>
     <row r="431" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C431" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="D431" s="7">
         <v>500</v>
@@ -12369,7 +12372,7 @@
     </row>
     <row r="432" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C432" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="D432" s="7">
         <f xml:space="preserve"> 290.4 * 4</f>
@@ -12384,7 +12387,7 @@
     </row>
     <row r="433" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C433" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="D433" s="7">
         <f>28.17*4</f>
@@ -12399,7 +12402,7 @@
     </row>
     <row r="434" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C434" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="D434" s="7">
         <f>105.87*4</f>
@@ -12414,7 +12417,7 @@
     </row>
     <row r="435" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C435" s="18" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D435" s="7">
         <v>290.39999999999998</v>
@@ -12428,7 +12431,7 @@
     </row>
     <row r="436" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C436" s="18" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="D436" s="7">
         <f>(13+18)*34.96</f>
@@ -12443,13 +12446,13 @@
     </row>
     <row r="437" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C437" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="D437" s="7">
         <v>441993.2</v>
       </c>
       <c r="E437" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="F437" s="9">
         <v>46169</v>
@@ -12457,13 +12460,13 @@
     </row>
     <row r="438" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C438" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="D438" s="7">
         <v>47851.75</v>
       </c>
       <c r="E438" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="F438" s="9">
         <v>46169</v>
@@ -12471,7 +12474,7 @@
     </row>
     <row r="439" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C439" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="D439" s="7">
         <v>200000</v>
@@ -12485,13 +12488,13 @@
     </row>
     <row r="440" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C440" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="D440" s="7">
         <v>6000</v>
       </c>
       <c r="E440" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="F440" s="9">
         <v>46174</v>
@@ -12499,7 +12502,7 @@
     </row>
     <row r="441" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C441" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="D441" s="7">
         <v>88.82</v>
@@ -12513,7 +12516,7 @@
     </row>
     <row r="442" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C442" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="D442" s="7">
         <f>357.97*2</f>
@@ -12528,7 +12531,7 @@
     </row>
     <row r="443" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C443" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D443" s="7">
         <v>268.25</v>
@@ -12542,7 +12545,7 @@
     </row>
     <row r="444" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C444" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="D444" s="7">
         <v>191.02</v>
@@ -12556,7 +12559,7 @@
     </row>
     <row r="445" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C445" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="D445" s="7">
         <v>723.98</v>
@@ -12570,7 +12573,7 @@
     </row>
     <row r="446" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C446" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="D446" s="7">
         <f>7*91.47</f>
@@ -12585,7 +12588,7 @@
     </row>
     <row r="447" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C447" s="18" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="D447" s="7">
         <f>4*174.18</f>
@@ -12600,25 +12603,25 @@
     </row>
     <row r="448" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C448" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="D448" s="7">
         <v>6592.4</v>
       </c>
       <c r="E448" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="F448" s="9"/>
     </row>
     <row r="449" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C449" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="D449" s="7">
         <v>500</v>
       </c>
       <c r="E449" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="F449" s="9">
         <v>46178</v>
@@ -12626,13 +12629,13 @@
     </row>
     <row r="450" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C450" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="D450" s="7">
         <v>6630</v>
       </c>
       <c r="E450" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="F450" s="9">
         <v>46181</v>
@@ -12640,7 +12643,7 @@
     </row>
     <row r="451" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C451" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="D451" s="7">
         <v>279</v>
@@ -12706,12 +12709,12 @@
         <v>343</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C4">
         <v>0.47</v>
@@ -12719,7 +12722,7 @@
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C5">
         <v>0.12</v>
@@ -12727,7 +12730,7 @@
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C6">
         <v>0.54</v>
@@ -12735,7 +12738,7 @@
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C7">
         <v>0.13</v>
@@ -12743,7 +12746,7 @@
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C8">
         <v>0.45</v>
@@ -12751,7 +12754,7 @@
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C9">
         <v>0.26</v>
@@ -12759,7 +12762,7 @@
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C10">
         <v>0.56999999999999995</v>
@@ -12767,7 +12770,7 @@
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C11">
         <v>0.45</v>
@@ -12775,7 +12778,7 @@
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C12">
         <v>0.3</v>
@@ -12783,7 +12786,7 @@
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C13">
         <v>7.0000000000000007E-2</v>
@@ -12791,7 +12794,7 @@
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C14">
         <v>0.27</v>
@@ -12799,7 +12802,7 @@
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C15">
         <v>0.51</v>
@@ -12814,7 +12817,7 @@
         <v>4.1399999999999997</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="18" spans="3:3" x14ac:dyDescent="0.25">
@@ -12840,13 +12843,13 @@
   <sheetData>
     <row r="3" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C3" s="11" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D3" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="E3" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="G3">
         <v>11</v>
@@ -12856,13 +12859,13 @@
         <v>120000000</v>
       </c>
       <c r="J3" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="K3">
         <v>0.12</v>
       </c>
       <c r="L3" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="4" spans="3:12" x14ac:dyDescent="0.25">
@@ -12897,7 +12900,7 @@
     </row>
     <row r="10" spans="3:12" x14ac:dyDescent="0.25">
       <c r="F10" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="G10">
         <f>SUM(G3:G9)</f>
@@ -12913,12 +12916,12 @@
         <v>6.6</v>
       </c>
       <c r="I14" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="15" spans="3:12" x14ac:dyDescent="0.25">
       <c r="G15" s="23" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -13874,7 +13877,7 @@
         <v>100</v>
       </c>
       <c r="D5" t="s">
-        <v>393</v>
+        <v>795</v>
       </c>
       <c r="G5" t="s">
         <v>346</v>
@@ -13888,10 +13891,10 @@
         <v>347</v>
       </c>
       <c r="C6" s="27">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G6" t="s">
         <v>347</v>
@@ -13905,10 +13908,10 @@
         <v>348</v>
       </c>
       <c r="C7" s="28">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>400</v>
+        <v>796</v>
       </c>
       <c r="G7" t="s">
         <v>348</v>
@@ -13917,48 +13920,46 @@
         <v>20</v>
       </c>
       <c r="I7" s="29" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>398</v>
+        <v>797</v>
       </c>
       <c r="C8" s="36">
-        <f>C9-250</f>
-        <v>2765</v>
+        <v>1015</v>
       </c>
       <c r="D8" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G8" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H8" s="23">
         <f>2550+H5+H6+H7</f>
         <v>2780</v>
       </c>
       <c r="I8" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C9" s="24">
-        <f>C5+C6+C7+850+1500+500</f>
-        <v>3015</v>
+        <v>3020</v>
       </c>
       <c r="G9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H9" s="24">
         <f>H8+250</f>
         <v>3030</v>
       </c>
       <c r="I9" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="K9" s="23"/>
     </row>
@@ -13976,18 +13977,18 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="F13" s="23"/>
       <c r="G13" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="H13" s="24">
         <f>850+H5+H6+H7</f>
         <v>1080</v>
       </c>
       <c r="I13" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="K13" s="23"/>
     </row>
@@ -14055,15 +14056,15 @@
   <sheetData>
     <row r="3" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B3" s="8" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="C4" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="D4" t="s">
         <v>1</v>
@@ -14071,18 +14072,18 @@
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="C5" s="23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>550</v>
+        <v>798</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="C6" s="23">
         <v>1</v>
@@ -14090,7 +14091,7 @@
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="C7" s="23">
         <v>1</v>
@@ -14098,7 +14099,7 @@
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="C8" s="23">
         <v>1</v>
@@ -14106,7 +14107,7 @@
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="C9" s="23">
         <v>2</v>
@@ -14114,15 +14115,15 @@
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="C10" s="23">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="C11" s="23">
         <v>1</v>
@@ -14130,7 +14131,7 @@
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="C12" s="23">
         <v>3</v>
@@ -14138,7 +14139,7 @@
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="C13" s="23">
         <v>1</v>
@@ -14146,7 +14147,7 @@
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="C14" s="23">
         <v>3</v>
@@ -14154,24 +14155,24 @@
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="C15" s="23">
         <f>SUM(C5:C14)</f>
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B18" s="8" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="C19" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="D19" t="s">
         <v>1</v>
@@ -14179,18 +14180,18 @@
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="C20" s="23">
         <v>4</v>
       </c>
       <c r="D20" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="C21" s="23">
         <v>3</v>
@@ -14198,7 +14199,7 @@
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="C22" s="23">
         <v>2</v>
@@ -14206,7 +14207,7 @@
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="C23" s="23">
         <f>SUM(C20:C22)</f>
@@ -14224,16 +14225,16 @@
     </row>
     <row r="27" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B27" s="8" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C27" s="23"/>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="C28" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="D28" t="s">
         <v>1</v>
@@ -14241,18 +14242,18 @@
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="C29" s="23">
         <v>4</v>
       </c>
       <c r="D29" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="C30" s="23">
         <v>3</v>
@@ -14260,7 +14261,7 @@
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="C31" s="23">
         <v>2</v>
@@ -14268,7 +14269,7 @@
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="C32" s="23">
         <f>SUM(C29:C31)</f>
@@ -14277,16 +14278,16 @@
     </row>
     <row r="35" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B35" s="8" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="C35" s="23"/>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="C36" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="D36" t="s">
         <v>1</v>
@@ -14294,18 +14295,18 @@
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="C37" s="23">
         <v>4</v>
       </c>
       <c r="D37" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="C38" s="23">
         <v>3</v>
@@ -14313,7 +14314,7 @@
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="C39" s="23">
         <v>2</v>
@@ -14321,7 +14322,7 @@
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="C40" s="23">
         <f>SUM(C37:C39)</f>
@@ -14330,16 +14331,16 @@
     </row>
     <row r="43" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B43" s="8" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C43" s="23"/>
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="C44" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="D44" t="s">
         <v>1</v>
@@ -14347,40 +14348,40 @@
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="C45" s="23">
         <v>2</v>
       </c>
       <c r="D45" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
     </row>
     <row r="46" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C46" s="23">
         <v>1</v>
       </c>
       <c r="D46" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="C47" s="23">
         <v>2</v>
       </c>
       <c r="D47" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="48" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="C48" s="23">
         <f>SUM(C45:C47)</f>
@@ -14389,16 +14390,16 @@
     </row>
     <row r="51" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B51" s="8" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="C51" s="23"/>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="C52" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="D52" t="s">
         <v>1</v>
@@ -14406,29 +14407,29 @@
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="C53" s="23">
         <v>1</v>
       </c>
       <c r="D53" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="C54" s="23">
         <v>1</v>
       </c>
       <c r="D54" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="C55" s="23">
         <f>SUM(C53:C54)</f>
@@ -14440,16 +14441,16 @@
     </row>
     <row r="58" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B58" s="8" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="C58" s="23"/>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="C59" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="D59" t="s">
         <v>1</v>
@@ -14457,18 +14458,18 @@
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="C60" s="23">
         <v>2</v>
       </c>
       <c r="D60" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="C61" s="23">
         <v>2</v>
@@ -14476,7 +14477,7 @@
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="C62" s="23">
         <v>1</v>
@@ -14484,39 +14485,39 @@
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="C63" s="23">
         <v>1</v>
       </c>
       <c r="D63" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="C64" s="23">
         <v>1</v>
       </c>
       <c r="D64" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="C65" s="23"/>
       <c r="D65" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C66" s="23"/>
       <c r="D66" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.25">
@@ -14524,16 +14525,16 @@
     </row>
     <row r="68" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B68" s="8" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="C68" s="23"/>
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="C69" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="D69" t="s">
         <v>1</v>
@@ -14541,18 +14542,18 @@
     </row>
     <row r="70" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="C70" s="23">
         <v>1</v>
       </c>
       <c r="D70" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
     </row>
     <row r="71" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="C71" s="23">
         <v>1</v>
@@ -14560,7 +14561,7 @@
     </row>
     <row r="72" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="C72" s="23">
         <f>SUM(C70:C71)</f>
@@ -14569,22 +14570,22 @@
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
     </row>
     <row r="76" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
     </row>
     <row r="78" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
     </row>
   </sheetData>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zip\develop\my_home\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Building\my_home\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25320" windowHeight="8145" firstSheet="6" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25320" windowHeight="8145" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Расчёт колличества бетона " sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <sheet name="котельная и вентиляция" sheetId="14" r:id="rId11"/>
     <sheet name="дерево заказ на 18 апр 2026" sheetId="15" r:id="rId12"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1259" uniqueCount="799">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1273" uniqueCount="803">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3370,11 +3370,23 @@
   <si>
     <t xml:space="preserve">скорее всего 3 фазная розетка, сечение провода - </t>
   </si>
+  <si>
+    <t>Рулетка 5м х 19мм, Бауцентр</t>
+  </si>
+  <si>
+    <t>Саморезы кровельные, графитово серые, RAL7024 4,8х35мм. 60шт.</t>
+  </si>
+  <si>
+    <t>Саморезы кровельные, графитово серые, RAL7024 4,8х19мм. 70шт.</t>
+  </si>
+  <si>
+    <t>планка снегозадержания 250 мм Satin matt grand line 7024 - 3 шт</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
@@ -3781,6 +3793,12 @@
   </cellStyles>
   <dxfs count="35">
     <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -3829,12 +3847,6 @@
         <top/>
         <bottom/>
       </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
@@ -4188,14 +4200,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F456" totalsRowCount="1">
-  <autoFilter ref="B5:F455"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F466" totalsRowCount="1">
+  <autoFilter ref="B5:F465"/>
   <tableColumns count="5">
     <tableColumn id="1" name="№ п/п"/>
     <tableColumn id="2" name="Наименование "/>
-    <tableColumn id="3" name="Цена (руб)" totalsRowFunction="sum" dataDxfId="34" totalsRowDxfId="7"/>
+    <tableColumn id="3" name="Цена (руб)" totalsRowFunction="sum" dataDxfId="34" totalsRowDxfId="1"/>
     <tableColumn id="4" name="Примечание"/>
-    <tableColumn id="5" name="дата" dataDxfId="33" totalsRowDxfId="6"/>
+    <tableColumn id="5" name="дата" dataDxfId="33" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4329,15 +4341,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Таблица2" displayName="Таблица2" ref="A4:F28" totalsRowCount="1">
   <autoFilter ref="A4:F27"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="№ п/п" totalsRowLabel="Итого:" totalsRowDxfId="5"/>
-    <tableColumn id="2" name="Тип" totalsRowDxfId="4"/>
-    <tableColumn id="3" name="Количество (М3/шт)" totalsRowDxfId="3"/>
-    <tableColumn id="4" name="Цена  (м3 или штук)" dataDxfId="32" totalsRowDxfId="2"/>
-    <tableColumn id="5" name="Сумма" totalsRowFunction="custom" dataDxfId="31" totalsRowDxfId="1">
+    <tableColumn id="1" name="№ п/п" totalsRowLabel="Итого:" totalsRowDxfId="7"/>
+    <tableColumn id="2" name="Тип" totalsRowDxfId="6"/>
+    <tableColumn id="3" name="Количество (М3/шт)" totalsRowDxfId="5"/>
+    <tableColumn id="4" name="Цена  (м3 или штук)" dataDxfId="32" totalsRowDxfId="4"/>
+    <tableColumn id="5" name="Сумма" totalsRowFunction="custom" dataDxfId="31" totalsRowDxfId="3">
       <calculatedColumnFormula>Таблица2[[#This Row],[Цена  (м3 или штук)]]*Таблица2[[#This Row],[Количество (М3/шт)]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(E5:E27)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" name="Примечание" totalsRowDxfId="0"/>
+    <tableColumn id="6" name="Примечание" totalsRowDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5760,7 +5772,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:I456"/>
+  <dimension ref="B3:I466"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="85.28515625" customWidth="1"/>
@@ -12656,27 +12668,137 @@
       </c>
     </row>
     <row r="452" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D452" s="7"/>
-      <c r="F452" s="9"/>
+      <c r="C452" s="18" t="s">
+        <v>799</v>
+      </c>
+      <c r="D452" s="7">
+        <v>179</v>
+      </c>
+      <c r="E452" t="s">
+        <v>173</v>
+      </c>
+      <c r="F452" s="9">
+        <v>46189</v>
+      </c>
     </row>
     <row r="453" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D453" s="7"/>
-      <c r="F453" s="9"/>
+      <c r="C453" t="s">
+        <v>800</v>
+      </c>
+      <c r="D453" s="7">
+        <v>199</v>
+      </c>
+      <c r="E453" t="s">
+        <v>173</v>
+      </c>
+      <c r="F453" s="9">
+        <v>46189</v>
+      </c>
     </row>
     <row r="454" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D454" s="7"/>
-      <c r="F454" s="9"/>
+      <c r="C454" t="s">
+        <v>801</v>
+      </c>
+      <c r="D454" s="7">
+        <v>199</v>
+      </c>
+      <c r="E454" t="s">
+        <v>173</v>
+      </c>
+      <c r="F454" s="9">
+        <v>46189</v>
+      </c>
     </row>
     <row r="455" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D455" s="7"/>
-      <c r="F455" s="9"/>
+      <c r="C455" t="s">
+        <v>428</v>
+      </c>
+      <c r="D455" s="7">
+        <v>39</v>
+      </c>
+      <c r="E455" t="s">
+        <v>173</v>
+      </c>
+      <c r="F455" s="9">
+        <v>46189</v>
+      </c>
     </row>
     <row r="456" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C456" t="s">
+        <v>429</v>
+      </c>
       <c r="D456" s="7">
+        <v>219</v>
+      </c>
+      <c r="E456" t="s">
+        <v>173</v>
+      </c>
+      <c r="F456" s="9">
+        <v>46189</v>
+      </c>
+    </row>
+    <row r="457" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C457" t="s">
+        <v>373</v>
+      </c>
+      <c r="D457" s="7">
+        <v>59</v>
+      </c>
+      <c r="E457" t="s">
+        <v>173</v>
+      </c>
+      <c r="F457" s="9">
+        <v>46189</v>
+      </c>
+    </row>
+    <row r="458" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C458" t="s">
+        <v>802</v>
+      </c>
+      <c r="D458" s="7">
+        <v>2511</v>
+      </c>
+      <c r="E458" t="s">
+        <v>777</v>
+      </c>
+      <c r="F458" s="9">
+        <v>46189</v>
+      </c>
+    </row>
+    <row r="459" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D459" s="7"/>
+      <c r="F459" s="9"/>
+    </row>
+    <row r="460" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D460" s="7"/>
+      <c r="F460" s="9"/>
+    </row>
+    <row r="461" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D461" s="7"/>
+      <c r="F461" s="9"/>
+    </row>
+    <row r="462" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D462" s="7"/>
+      <c r="F462" s="9"/>
+    </row>
+    <row r="463" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D463" s="7"/>
+      <c r="F463" s="9"/>
+    </row>
+    <row r="464" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D464" s="7"/>
+      <c r="F464" s="9"/>
+    </row>
+    <row r="465" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D465" s="7"/>
+      <c r="F465" s="9"/>
+    </row>
+    <row r="466" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D466" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>4979167.6500000022</v>
-      </c>
-      <c r="F456" s="9"/>
+        <v>4982572.6500000022</v>
+      </c>
+      <c r="F466" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1273" uniqueCount="803">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1279" uniqueCount="805">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3381,6 +3381,12 @@
   </si>
   <si>
     <t>планка снегозадержания 250 мм Satin matt grand line 7024 - 3 шт</t>
+  </si>
+  <si>
+    <t>Плита ОСП-3 Муром 12 мм 2500x1250 мм 3.125 м2 - 45 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Уголок металлический 50x50x5.0 мм 3м - 5шт</t>
   </si>
 </sst>
 </file>
@@ -12766,16 +12772,46 @@
       </c>
     </row>
     <row r="459" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D459" s="7"/>
-      <c r="F459" s="9"/>
+      <c r="C459" t="s">
+        <v>803</v>
+      </c>
+      <c r="D459" s="7">
+        <v>51210</v>
+      </c>
+      <c r="E459" t="s">
+        <v>754</v>
+      </c>
+      <c r="F459" s="9">
+        <v>46194</v>
+      </c>
     </row>
     <row r="460" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D460" s="7"/>
-      <c r="F460" s="9"/>
+      <c r="C460" t="s">
+        <v>804</v>
+      </c>
+      <c r="D460" s="7">
+        <v>5390</v>
+      </c>
+      <c r="E460" t="s">
+        <v>754</v>
+      </c>
+      <c r="F460" s="9">
+        <v>46194</v>
+      </c>
     </row>
     <row r="461" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D461" s="7"/>
-      <c r="F461" s="9"/>
+      <c r="C461" t="s">
+        <v>209</v>
+      </c>
+      <c r="D461" s="7">
+        <v>2030</v>
+      </c>
+      <c r="E461" t="s">
+        <v>754</v>
+      </c>
+      <c r="F461" s="9">
+        <v>46194</v>
+      </c>
     </row>
     <row r="462" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D462" s="7"/>
@@ -12796,7 +12832,7 @@
     <row r="466" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D466" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>4982572.6500000022</v>
+        <v>5041202.6500000022</v>
       </c>
       <c r="F466" s="9"/>
     </row>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Building\my_home\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zip\develop\my_home\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -25,7 +25,7 @@
     <sheet name="котельная и вентиляция" sheetId="14" r:id="rId11"/>
     <sheet name="дерево заказ на 18 апр 2026" sheetId="15" r:id="rId12"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1279" uniqueCount="805">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1287" uniqueCount="810">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3388,11 +3388,26 @@
   <si>
     <t xml:space="preserve"> Уголок металлический 50x50x5.0 мм 3м - 5шт</t>
   </si>
+  <si>
+    <t>Дюбель нейлоновый D12x100mm 2 шт</t>
+  </si>
+  <si>
+    <t>комплект дюбель d12x60mm шуруп с шестигр головкой d8x60mm 3 шт</t>
+  </si>
+  <si>
+    <t>гвозди для пневмостеплера 1.4x30 mm 1000 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Бауцентр </t>
+  </si>
+  <si>
+    <t>шурупы универсальные 4.5х35мм желт 200шт</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
@@ -4206,8 +4221,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F466" totalsRowCount="1">
-  <autoFilter ref="B5:F465"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F470" totalsRowCount="1">
+  <autoFilter ref="B5:F469"/>
   <tableColumns count="5">
     <tableColumn id="1" name="№ п/п"/>
     <tableColumn id="2" name="Наименование "/>
@@ -5778,7 +5793,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:I466"/>
+  <dimension ref="B3:I470"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="85.28515625" customWidth="1"/>
@@ -12814,27 +12829,83 @@
       </c>
     </row>
     <row r="462" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D462" s="7"/>
-      <c r="F462" s="9"/>
+      <c r="C462" t="s">
+        <v>805</v>
+      </c>
+      <c r="D462" s="7">
+        <v>43.65</v>
+      </c>
+      <c r="E462" t="s">
+        <v>808</v>
+      </c>
+      <c r="F462" s="9">
+        <v>46197</v>
+      </c>
     </row>
     <row r="463" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D463" s="7"/>
-      <c r="F463" s="9"/>
+      <c r="C463" t="s">
+        <v>806</v>
+      </c>
+      <c r="D463" s="7">
+        <v>65.92</v>
+      </c>
+      <c r="E463" t="s">
+        <v>808</v>
+      </c>
+      <c r="F463" s="9">
+        <v>46197</v>
+      </c>
     </row>
     <row r="464" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D464" s="7"/>
-      <c r="F464" s="9"/>
-    </row>
-    <row r="465" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D465" s="7"/>
-      <c r="F465" s="9"/>
-    </row>
-    <row r="466" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D466" s="7">
+      <c r="C464" t="s">
+        <v>807</v>
+      </c>
+      <c r="D464" s="7">
+        <v>257.43</v>
+      </c>
+      <c r="E464" t="s">
+        <v>808</v>
+      </c>
+      <c r="F464" s="9">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="465" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C465" t="s">
+        <v>809</v>
+      </c>
+      <c r="D465" s="7">
+        <v>174</v>
+      </c>
+      <c r="E465" t="s">
+        <v>808</v>
+      </c>
+      <c r="F465" s="9">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="466" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D466" s="7"/>
+      <c r="F466" s="9"/>
+    </row>
+    <row r="467" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D467" s="7"/>
+      <c r="F467" s="9"/>
+    </row>
+    <row r="468" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D468" s="7"/>
+      <c r="F468" s="9"/>
+    </row>
+    <row r="469" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D469" s="7"/>
+      <c r="F469" s="9"/>
+    </row>
+    <row r="470" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D470" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>5041202.6500000022</v>
-      </c>
-      <c r="F466" s="9"/>
+        <v>5041743.6500000022</v>
+      </c>
+      <c r="F470" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -3814,12 +3814,6 @@
   </cellStyles>
   <dxfs count="35">
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -3868,6 +3862,12 @@
         <top/>
         <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
@@ -4226,9 +4226,9 @@
   <tableColumns count="5">
     <tableColumn id="1" name="№ п/п"/>
     <tableColumn id="2" name="Наименование "/>
-    <tableColumn id="3" name="Цена (руб)" totalsRowFunction="sum" dataDxfId="34" totalsRowDxfId="1"/>
+    <tableColumn id="3" name="Цена (руб)" totalsRowFunction="sum" dataDxfId="34" totalsRowDxfId="7"/>
     <tableColumn id="4" name="Примечание"/>
-    <tableColumn id="5" name="дата" dataDxfId="33" totalsRowDxfId="0"/>
+    <tableColumn id="5" name="дата" dataDxfId="33" totalsRowDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4362,15 +4362,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Таблица2" displayName="Таблица2" ref="A4:F28" totalsRowCount="1">
   <autoFilter ref="A4:F27"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="№ п/п" totalsRowLabel="Итого:" totalsRowDxfId="7"/>
-    <tableColumn id="2" name="Тип" totalsRowDxfId="6"/>
-    <tableColumn id="3" name="Количество (М3/шт)" totalsRowDxfId="5"/>
-    <tableColumn id="4" name="Цена  (м3 или штук)" dataDxfId="32" totalsRowDxfId="4"/>
-    <tableColumn id="5" name="Сумма" totalsRowFunction="custom" dataDxfId="31" totalsRowDxfId="3">
+    <tableColumn id="1" name="№ п/п" totalsRowLabel="Итого:" totalsRowDxfId="5"/>
+    <tableColumn id="2" name="Тип" totalsRowDxfId="4"/>
+    <tableColumn id="3" name="Количество (М3/шт)" totalsRowDxfId="3"/>
+    <tableColumn id="4" name="Цена  (м3 или штук)" dataDxfId="32" totalsRowDxfId="2"/>
+    <tableColumn id="5" name="Сумма" totalsRowFunction="custom" dataDxfId="31" totalsRowDxfId="1">
       <calculatedColumnFormula>Таблица2[[#This Row],[Цена  (м3 или штук)]]*Таблица2[[#This Row],[Количество (М3/шт)]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(E5:E27)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" name="Примечание" totalsRowDxfId="2"/>
+    <tableColumn id="6" name="Примечание" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zip\develop\my_home\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Building\my_home\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -25,7 +25,7 @@
     <sheet name="котельная и вентиляция" sheetId="14" r:id="rId11"/>
     <sheet name="дерево заказ на 18 апр 2026" sheetId="15" r:id="rId12"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1287" uniqueCount="810">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1321" uniqueCount="826">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3403,11 +3403,59 @@
   <si>
     <t>шурупы универсальные 4.5х35мм желт 200шт</t>
   </si>
+  <si>
+    <t>трубка термоусаживаемая тут 6/3 набор (21шт 100 мм)</t>
+  </si>
+  <si>
+    <t>шурупы универсальные 4.5х30мм желт 260шт fixberg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">шурупы универсальные 4х35 мм желт 230 шт </t>
+  </si>
+  <si>
+    <t>Саморез по дереву 3,5х35 мм (200шт - упаковка)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">анкер втулочный с болтом d12x70mm fsl fischer 2 шт </t>
+  </si>
+  <si>
+    <t>Шурупы универс. 3,5х40мм желт. 250шт FIXBERG</t>
+  </si>
+  <si>
+    <t>Гвозди строительные 4,0x120мм 1кг</t>
+  </si>
+  <si>
+    <t>Саморез д/г/пл.по мет. 4,8х100мм 30шт FIXBERG</t>
+  </si>
+  <si>
+    <t>Пластина анкерная 140x55х2,5мм 2 шт</t>
+  </si>
+  <si>
+    <t>Круги шлифовальные с отверстиями Р40,125мм, 5шт/уп., DORN</t>
+  </si>
+  <si>
+    <t>Круг лепестковый торцевой 125 Х 22 мм цирконий Р 80 плоский Dorn PRO</t>
+  </si>
+  <si>
+    <t>Ручка-скоба РС-120мм цинк</t>
+  </si>
+  <si>
+    <t>Задвижка плоская ЗД 100мм цинк</t>
+  </si>
+  <si>
+    <t>Петля накладная ПН1-110мм цинк левая</t>
+  </si>
+  <si>
+    <t>Сверло по металлу 3,5мм HSS-Co 5% DORN PRO</t>
+  </si>
+  <si>
+    <t>Сверло по металлу 3,5мм HSS-TiN DORN</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
@@ -4221,8 +4269,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F470" totalsRowCount="1">
-  <autoFilter ref="B5:F469"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F485" totalsRowCount="1">
+  <autoFilter ref="B5:F484"/>
   <tableColumns count="5">
     <tableColumn id="1" name="№ п/п"/>
     <tableColumn id="2" name="Наименование "/>
@@ -5793,7 +5841,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:I470"/>
+  <dimension ref="B3:I485"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="85.28515625" customWidth="1"/>
@@ -12885,27 +12933,259 @@
       </c>
     </row>
     <row r="466" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D466" s="7"/>
-      <c r="F466" s="9"/>
+      <c r="C466" t="s">
+        <v>810</v>
+      </c>
+      <c r="D466" s="7">
+        <v>45</v>
+      </c>
+      <c r="E466" t="s">
+        <v>808</v>
+      </c>
+      <c r="F466" s="9">
+        <v>46208</v>
+      </c>
     </row>
     <row r="467" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D467" s="7"/>
-      <c r="F467" s="9"/>
+      <c r="C467" t="s">
+        <v>811</v>
+      </c>
+      <c r="D467" s="7">
+        <v>229</v>
+      </c>
+      <c r="E467" t="s">
+        <v>808</v>
+      </c>
+      <c r="F467" s="9">
+        <v>46208</v>
+      </c>
     </row>
     <row r="468" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D468" s="7"/>
-      <c r="F468" s="9"/>
+      <c r="C468" t="s">
+        <v>812</v>
+      </c>
+      <c r="D468" s="7">
+        <v>209</v>
+      </c>
+      <c r="E468" t="s">
+        <v>808</v>
+      </c>
+      <c r="F468" s="9">
+        <v>46208</v>
+      </c>
     </row>
     <row r="469" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D469" s="7"/>
-      <c r="F469" s="9"/>
+      <c r="C469" t="s">
+        <v>813</v>
+      </c>
+      <c r="D469" s="7">
+        <v>249</v>
+      </c>
+      <c r="E469" t="s">
+        <v>808</v>
+      </c>
+      <c r="F469" s="9">
+        <v>46208</v>
+      </c>
     </row>
     <row r="470" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C470" t="s">
+        <v>806</v>
+      </c>
       <c r="D470" s="7">
+        <v>74</v>
+      </c>
+      <c r="E470" t="s">
+        <v>808</v>
+      </c>
+      <c r="F470" s="9">
+        <v>46208</v>
+      </c>
+    </row>
+    <row r="471" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C471" t="s">
+        <v>814</v>
+      </c>
+      <c r="D471" s="7">
+        <v>180</v>
+      </c>
+      <c r="E471" t="s">
+        <v>808</v>
+      </c>
+      <c r="F471" s="9">
+        <v>46208</v>
+      </c>
+    </row>
+    <row r="472" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C472" s="18" t="s">
+        <v>815</v>
+      </c>
+      <c r="D472" s="7">
+        <v>218.52</v>
+      </c>
+      <c r="E472" t="s">
+        <v>808</v>
+      </c>
+      <c r="F472" s="9">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="473" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C473" t="s">
+        <v>816</v>
+      </c>
+      <c r="D473" s="7">
+        <v>174.62</v>
+      </c>
+      <c r="E473" t="s">
+        <v>808</v>
+      </c>
+      <c r="F473" s="9">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="474" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C474" t="s">
+        <v>817</v>
+      </c>
+      <c r="D474" s="7">
+        <v>125.85</v>
+      </c>
+      <c r="E474" t="s">
+        <v>808</v>
+      </c>
+      <c r="F474" s="9">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="475" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C475" t="s">
+        <v>818</v>
+      </c>
+      <c r="D475" s="7">
+        <f xml:space="preserve"> 42.93 + 42.92</f>
+        <v>85.85</v>
+      </c>
+      <c r="E475" t="s">
+        <v>808</v>
+      </c>
+      <c r="F475" s="9">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="476" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C476" t="s">
+        <v>819</v>
+      </c>
+      <c r="D476" s="7">
+        <v>106.33</v>
+      </c>
+      <c r="E476" t="s">
+        <v>808</v>
+      </c>
+      <c r="F476" s="9">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="477" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C477" t="s">
+        <v>820</v>
+      </c>
+      <c r="D477" s="7">
+        <v>174.62</v>
+      </c>
+      <c r="E477" t="s">
+        <v>808</v>
+      </c>
+      <c r="F477" s="9">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="478" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C478" t="s">
+        <v>821</v>
+      </c>
+      <c r="D478" s="7">
+        <v>77.069999999999993</v>
+      </c>
+      <c r="E478" t="s">
+        <v>808</v>
+      </c>
+      <c r="F478" s="9">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="479" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C479" t="s">
+        <v>822</v>
+      </c>
+      <c r="D479" s="7">
+        <v>291.69</v>
+      </c>
+      <c r="E479" t="s">
+        <v>808</v>
+      </c>
+      <c r="F479" s="9">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="480" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C480" t="s">
+        <v>823</v>
+      </c>
+      <c r="D480" s="7">
+        <f xml:space="preserve"> 125.85 *3</f>
+        <v>377.54999999999995</v>
+      </c>
+      <c r="E480" t="s">
+        <v>808</v>
+      </c>
+      <c r="F480" s="9">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="481" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C481" t="s">
+        <v>824</v>
+      </c>
+      <c r="D481" s="7">
+        <v>135.6</v>
+      </c>
+      <c r="E481" t="s">
+        <v>808</v>
+      </c>
+      <c r="F481" s="9">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="482" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C482" t="s">
+        <v>825</v>
+      </c>
+      <c r="D482" s="7">
+        <v>67.31</v>
+      </c>
+      <c r="E482" t="s">
+        <v>808</v>
+      </c>
+      <c r="F482" s="9">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="483" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D483" s="7"/>
+      <c r="F483" s="9"/>
+    </row>
+    <row r="484" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D484" s="7"/>
+      <c r="F484" s="9"/>
+    </row>
+    <row r="485" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D485" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>5041743.6500000022</v>
-      </c>
-      <c r="F470" s="9"/>
+        <v>5044564.6600000011</v>
+      </c>
+      <c r="F485" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1321" uniqueCount="826">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1353" uniqueCount="843">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3450,6 +3450,57 @@
   </si>
   <si>
     <t>Сверло по металлу 3,5мм HSS-TiN DORN</t>
+  </si>
+  <si>
+    <t>Индивидуальный предприниматель Плотников Игорь Владимирович Адрес: г. Калининград, Советскийпроспект, 286, с. 5.10 Телефон: 89937314527</t>
+  </si>
+  <si>
+    <t>Заказ №0050 от 23.06.2026 г. Окна в дом</t>
+  </si>
+  <si>
+    <t>Прожектор Диодный 70Вт 6000к онлайт</t>
+  </si>
+  <si>
+    <t>провод гибкий круглый пвс 3х1.5 10 м</t>
+  </si>
+  <si>
+    <t>Замок навесной чугунный вс14-060 extra 60х45мм алюр</t>
+  </si>
+  <si>
+    <t>ввилка с заземл угловая в16-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">клема 3х проводная wago 3шт </t>
+  </si>
+  <si>
+    <t>вилка с заземл белая иэк</t>
+  </si>
+  <si>
+    <t>термоусадочная трубка набор №5 rexant</t>
+  </si>
+  <si>
+    <t>трубка термоусаживаемая тут 4/2 набор (21шт 100 мм)</t>
+  </si>
+  <si>
+    <t>Пенополистирол экструдированный ТЕХНОПЛЕКС 1180х580х50 мм - 48 шт для цоколя</t>
+  </si>
+  <si>
+    <t>Клей для пенополистирола ZM 01 KLESTER (25кг) 5 мешков для цоколя</t>
+  </si>
+  <si>
+    <t>Клей для пенополистирола и сетки ZM 02 KLESTER (25кг) - 5 мешков для цоколя</t>
+  </si>
+  <si>
+    <t>Сетка фасадная Крепикс 1800 1х50м (160г/м2) BauTex для цоколя</t>
+  </si>
+  <si>
+    <t>Дюбель с термоголовкой д/пустотелых материалов D10x140мм 50 шт Koelner - 2 упак для цоколя</t>
+  </si>
+  <si>
+    <t>ООО "Региональная кадастровая компания"</t>
+  </si>
+  <si>
+    <t>кадастровые и геодезические работы - Регистрация дома</t>
   </si>
 </sst>
 </file>
@@ -3862,6 +3913,12 @@
   </cellStyles>
   <dxfs count="35">
     <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -3910,12 +3967,6 @@
         <top/>
         <bottom/>
       </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
@@ -4269,14 +4320,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F485" totalsRowCount="1">
-  <autoFilter ref="B5:F484"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F507" totalsRowCount="1">
+  <autoFilter ref="B5:F506"/>
   <tableColumns count="5">
     <tableColumn id="1" name="№ п/п"/>
     <tableColumn id="2" name="Наименование "/>
-    <tableColumn id="3" name="Цена (руб)" totalsRowFunction="sum" dataDxfId="34" totalsRowDxfId="7"/>
+    <tableColumn id="3" name="Цена (руб)" totalsRowFunction="sum" dataDxfId="34" totalsRowDxfId="1"/>
     <tableColumn id="4" name="Примечание"/>
-    <tableColumn id="5" name="дата" dataDxfId="33" totalsRowDxfId="6"/>
+    <tableColumn id="5" name="дата" dataDxfId="33" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4410,15 +4461,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Таблица2" displayName="Таблица2" ref="A4:F28" totalsRowCount="1">
   <autoFilter ref="A4:F27"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="№ п/п" totalsRowLabel="Итого:" totalsRowDxfId="5"/>
-    <tableColumn id="2" name="Тип" totalsRowDxfId="4"/>
-    <tableColumn id="3" name="Количество (М3/шт)" totalsRowDxfId="3"/>
-    <tableColumn id="4" name="Цена  (м3 или штук)" dataDxfId="32" totalsRowDxfId="2"/>
-    <tableColumn id="5" name="Сумма" totalsRowFunction="custom" dataDxfId="31" totalsRowDxfId="1">
+    <tableColumn id="1" name="№ п/п" totalsRowLabel="Итого:" totalsRowDxfId="7"/>
+    <tableColumn id="2" name="Тип" totalsRowDxfId="6"/>
+    <tableColumn id="3" name="Количество (М3/шт)" totalsRowDxfId="5"/>
+    <tableColumn id="4" name="Цена  (м3 или штук)" dataDxfId="32" totalsRowDxfId="4"/>
+    <tableColumn id="5" name="Сумма" totalsRowFunction="custom" dataDxfId="31" totalsRowDxfId="3">
       <calculatedColumnFormula>Таблица2[[#This Row],[Цена  (м3 или штук)]]*Таблица2[[#This Row],[Количество (М3/шт)]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(E5:E27)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" name="Примечание" totalsRowDxfId="0"/>
+    <tableColumn id="6" name="Примечание" totalsRowDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5841,7 +5892,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:I485"/>
+  <dimension ref="B3:I507"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="85.28515625" customWidth="1"/>
@@ -13173,19 +13224,265 @@
       </c>
     </row>
     <row r="483" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D483" s="7"/>
-      <c r="F483" s="9"/>
+      <c r="C483" t="s">
+        <v>827</v>
+      </c>
+      <c r="D483" s="7">
+        <v>319865.36</v>
+      </c>
+      <c r="E483" t="s">
+        <v>826</v>
+      </c>
+      <c r="F483" s="9">
+        <v>46196</v>
+      </c>
     </row>
     <row r="484" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D484" s="7"/>
-      <c r="F484" s="9"/>
+      <c r="C484" t="s">
+        <v>828</v>
+      </c>
+      <c r="D484" s="7">
+        <v>298.48</v>
+      </c>
+      <c r="E484" t="s">
+        <v>173</v>
+      </c>
+      <c r="F484" s="9">
+        <v>46214</v>
+      </c>
     </row>
     <row r="485" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C485" t="s">
+        <v>829</v>
+      </c>
       <c r="D485" s="7">
+        <v>791.13</v>
+      </c>
+      <c r="E485" t="s">
+        <v>173</v>
+      </c>
+      <c r="F485" s="9">
+        <v>46214</v>
+      </c>
+    </row>
+    <row r="486" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C486" t="s">
+        <v>830</v>
+      </c>
+      <c r="D486" s="7">
+        <v>462.7</v>
+      </c>
+      <c r="E486" t="s">
+        <v>173</v>
+      </c>
+      <c r="F486" s="9">
+        <v>46214</v>
+      </c>
+    </row>
+    <row r="487" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C487" t="s">
+        <v>831</v>
+      </c>
+      <c r="D487" s="7">
+        <v>76.31</v>
+      </c>
+      <c r="E487" t="s">
+        <v>173</v>
+      </c>
+      <c r="F487" s="9">
+        <v>46214</v>
+      </c>
+    </row>
+    <row r="488" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C488" t="s">
+        <v>832</v>
+      </c>
+      <c r="D488" s="7">
+        <v>211.55</v>
+      </c>
+      <c r="E488" t="s">
+        <v>173</v>
+      </c>
+      <c r="F488" s="9">
+        <v>46214</v>
+      </c>
+    </row>
+    <row r="489" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C489" t="s">
+        <v>833</v>
+      </c>
+      <c r="D489" s="7">
+        <v>91.77</v>
+      </c>
+      <c r="E489" t="s">
+        <v>173</v>
+      </c>
+      <c r="F489" s="9">
+        <v>46214</v>
+      </c>
+    </row>
+    <row r="490" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C490" t="s">
+        <v>834</v>
+      </c>
+      <c r="D490" s="7">
+        <v>100.46</v>
+      </c>
+      <c r="E490" t="s">
+        <v>173</v>
+      </c>
+      <c r="F490" s="9">
+        <v>46214</v>
+      </c>
+    </row>
+    <row r="491" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C491" t="s">
+        <v>835</v>
+      </c>
+      <c r="D491" s="7">
+        <v>39.6</v>
+      </c>
+      <c r="E491" t="s">
+        <v>173</v>
+      </c>
+      <c r="F491" s="9">
+        <v>46214</v>
+      </c>
+    </row>
+    <row r="492" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C492" t="s">
+        <v>836</v>
+      </c>
+      <c r="D492" s="7">
+        <v>16176</v>
+      </c>
+      <c r="E492" t="s">
+        <v>173</v>
+      </c>
+      <c r="F492" s="9">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="493" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C493" s="18" t="s">
+        <v>837</v>
+      </c>
+      <c r="D493" s="7">
+        <v>2200</v>
+      </c>
+      <c r="E493" t="s">
+        <v>173</v>
+      </c>
+      <c r="F493" s="9">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="494" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C494" t="s">
+        <v>838</v>
+      </c>
+      <c r="D494" s="7">
+        <v>3050</v>
+      </c>
+      <c r="E494" t="s">
+        <v>173</v>
+      </c>
+      <c r="F494" s="9">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="495" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C495" t="s">
+        <v>839</v>
+      </c>
+      <c r="D495" s="7">
+        <v>2990</v>
+      </c>
+      <c r="E495" t="s">
+        <v>173</v>
+      </c>
+      <c r="F495" s="9">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="496" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C496" t="s">
+        <v>840</v>
+      </c>
+      <c r="D496" s="7">
+        <v>1980</v>
+      </c>
+      <c r="E496" t="s">
+        <v>173</v>
+      </c>
+      <c r="F496" s="9">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="497" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C497" t="s">
+        <v>426</v>
+      </c>
+      <c r="D497" s="7">
+        <v>1100</v>
+      </c>
+      <c r="E497" t="s">
+        <v>173</v>
+      </c>
+      <c r="F497" s="9">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="498" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C498" t="s">
+        <v>842</v>
+      </c>
+      <c r="D498" s="7">
+        <v>17000</v>
+      </c>
+      <c r="E498" t="s">
+        <v>841</v>
+      </c>
+      <c r="F498" s="9"/>
+    </row>
+    <row r="499" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D499" s="7"/>
+      <c r="F499" s="9"/>
+    </row>
+    <row r="500" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D500" s="7"/>
+      <c r="F500" s="9"/>
+    </row>
+    <row r="501" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D501" s="7"/>
+      <c r="F501" s="9"/>
+    </row>
+    <row r="502" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D502" s="7"/>
+      <c r="F502" s="9"/>
+    </row>
+    <row r="503" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D503" s="7"/>
+      <c r="F503" s="9"/>
+    </row>
+    <row r="504" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D504" s="7"/>
+      <c r="F504" s="9"/>
+    </row>
+    <row r="505" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D505" s="7"/>
+      <c r="F505" s="9"/>
+    </row>
+    <row r="506" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D506" s="7"/>
+      <c r="F506" s="9"/>
+    </row>
+    <row r="507" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D507" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>5044564.6600000011</v>
-      </c>
-      <c r="F485" s="9"/>
+        <v>5410998.0200000005</v>
+      </c>
+      <c r="F507" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1353" uniqueCount="843">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1363" uniqueCount="849">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3501,6 +3501,24 @@
   </si>
   <si>
     <t>кадастровые и геодезические работы - Регистрация дома</t>
+  </si>
+  <si>
+    <t>утепление цоколя - работы</t>
+  </si>
+  <si>
+    <t>Зафарбек</t>
+  </si>
+  <si>
+    <t>Саморез д/г/пл.по дер.3,5х25мм 250шт FIXBERG</t>
+  </si>
+  <si>
+    <t>Воздуховод круглый пластиковый 125 мм х 0,5 м 12,5ВП ERA</t>
+  </si>
+  <si>
+    <t>Редуктор эксцентриковый D100/D150 мм 1015РЭП ERA</t>
+  </si>
+  <si>
+    <t>Пена для полистерола + эппс</t>
   </si>
 </sst>
 </file>
@@ -4320,8 +4338,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F507" totalsRowCount="1">
-  <autoFilter ref="B5:F506"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F520" totalsRowCount="1">
+  <autoFilter ref="B5:F519"/>
   <tableColumns count="5">
     <tableColumn id="1" name="№ п/п"/>
     <tableColumn id="2" name="Наименование "/>
@@ -5892,7 +5910,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:I507"/>
+  <dimension ref="B3:I520"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="85.28515625" customWidth="1"/>
@@ -13443,27 +13461,79 @@
       <c r="E498" t="s">
         <v>841</v>
       </c>
-      <c r="F498" s="9"/>
+      <c r="F498" s="9">
+        <v>46217</v>
+      </c>
     </row>
     <row r="499" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D499" s="7"/>
-      <c r="F499" s="9"/>
+      <c r="C499" t="s">
+        <v>843</v>
+      </c>
+      <c r="D499" s="7">
+        <v>25000</v>
+      </c>
+      <c r="E499" t="s">
+        <v>844</v>
+      </c>
+      <c r="F499" s="9">
+        <v>46220</v>
+      </c>
     </row>
     <row r="500" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D500" s="7"/>
-      <c r="F500" s="9"/>
+      <c r="C500" s="18" t="s">
+        <v>845</v>
+      </c>
+      <c r="D500" s="7">
+        <v>249</v>
+      </c>
+      <c r="E500" t="s">
+        <v>173</v>
+      </c>
+      <c r="F500" s="9">
+        <v>46221</v>
+      </c>
     </row>
     <row r="501" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D501" s="7"/>
-      <c r="F501" s="9"/>
+      <c r="C501" t="s">
+        <v>846</v>
+      </c>
+      <c r="D501" s="7">
+        <v>259</v>
+      </c>
+      <c r="E501" t="s">
+        <v>173</v>
+      </c>
+      <c r="F501" s="9">
+        <v>46221</v>
+      </c>
     </row>
     <row r="502" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D502" s="7"/>
-      <c r="F502" s="9"/>
+      <c r="C502" t="s">
+        <v>847</v>
+      </c>
+      <c r="D502" s="7">
+        <v>205</v>
+      </c>
+      <c r="E502" t="s">
+        <v>173</v>
+      </c>
+      <c r="F502" s="9">
+        <v>46221</v>
+      </c>
     </row>
     <row r="503" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D503" s="7"/>
-      <c r="F503" s="9"/>
+      <c r="C503" t="s">
+        <v>848</v>
+      </c>
+      <c r="D503" s="7">
+        <v>5000</v>
+      </c>
+      <c r="E503" t="s">
+        <v>844</v>
+      </c>
+      <c r="F503" s="9">
+        <v>46219</v>
+      </c>
     </row>
     <row r="504" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D504" s="7"/>
@@ -13478,11 +13548,63 @@
       <c r="F506" s="9"/>
     </row>
     <row r="507" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D507" s="7">
+      <c r="D507" s="7"/>
+      <c r="F507" s="9"/>
+    </row>
+    <row r="508" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D508" s="7"/>
+      <c r="F508" s="9"/>
+    </row>
+    <row r="509" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D509" s="7"/>
+      <c r="F509" s="9"/>
+    </row>
+    <row r="510" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D510" s="7"/>
+      <c r="F510" s="9"/>
+    </row>
+    <row r="511" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D511" s="7"/>
+      <c r="F511" s="9"/>
+    </row>
+    <row r="512" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D512" s="7"/>
+      <c r="F512" s="9"/>
+    </row>
+    <row r="513" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D513" s="7"/>
+      <c r="F513" s="9"/>
+    </row>
+    <row r="514" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D514" s="7"/>
+      <c r="F514" s="9"/>
+    </row>
+    <row r="515" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D515" s="7"/>
+      <c r="F515" s="9"/>
+    </row>
+    <row r="516" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D516" s="7"/>
+      <c r="F516" s="9"/>
+    </row>
+    <row r="517" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D517" s="7"/>
+      <c r="F517" s="9"/>
+    </row>
+    <row r="518" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D518" s="7"/>
+      <c r="F518" s="9"/>
+    </row>
+    <row r="519" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D519" s="7"/>
+      <c r="F519" s="9"/>
+    </row>
+    <row r="520" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D520" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>5410998.0200000005</v>
-      </c>
-      <c r="F507" s="9"/>
+        <v>5441711.0200000005</v>
+      </c>
+      <c r="F520" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1363" uniqueCount="849">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1373" uniqueCount="853">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3519,6 +3519,18 @@
   </si>
   <si>
     <t>Пена для полистерола + эппс</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Дюбель с пластиковым стержнем D10х140мм 50 шт Koelner x 2 </t>
+  </si>
+  <si>
+    <t>Ручка-скоба РС-100-3 цинк</t>
+  </si>
+  <si>
+    <t>Клей для пенополистирола и сетки ZM 02 KLESTER (25кг)</t>
+  </si>
+  <si>
+    <t>Сетка фасадная Крепикс 1500 1х10м (145г/м2) BauTex</t>
   </si>
 </sst>
 </file>
@@ -13536,24 +13548,75 @@
       </c>
     </row>
     <row r="504" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D504" s="7"/>
-      <c r="F504" s="9"/>
+      <c r="C504" t="s">
+        <v>849</v>
+      </c>
+      <c r="D504" s="7">
+        <f xml:space="preserve"> 224.43 * 2</f>
+        <v>448.86</v>
+      </c>
+      <c r="E504" t="s">
+        <v>173</v>
+      </c>
+      <c r="F504" s="9">
+        <v>46222</v>
+      </c>
     </row>
     <row r="505" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D505" s="7"/>
-      <c r="F505" s="9"/>
+      <c r="C505" s="11" t="s">
+        <v>850</v>
+      </c>
+      <c r="D505" s="7">
+        <v>48.33</v>
+      </c>
+      <c r="E505" t="s">
+        <v>173</v>
+      </c>
+      <c r="F505" s="9">
+        <v>46222</v>
+      </c>
     </row>
     <row r="506" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D506" s="7"/>
-      <c r="F506" s="9"/>
+      <c r="C506" t="s">
+        <v>851</v>
+      </c>
+      <c r="D506" s="7">
+        <v>427.22</v>
+      </c>
+      <c r="E506" t="s">
+        <v>173</v>
+      </c>
+      <c r="F506" s="9">
+        <v>46222</v>
+      </c>
     </row>
     <row r="507" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D507" s="7"/>
-      <c r="F507" s="9"/>
+      <c r="C507" t="s">
+        <v>852</v>
+      </c>
+      <c r="D507" s="7">
+        <v>573.6</v>
+      </c>
+      <c r="E507" t="s">
+        <v>173</v>
+      </c>
+      <c r="F507" s="9">
+        <v>46222</v>
+      </c>
     </row>
     <row r="508" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D508" s="7"/>
-      <c r="F508" s="9"/>
+      <c r="C508" t="s">
+        <v>843</v>
+      </c>
+      <c r="D508" s="7">
+        <v>26000</v>
+      </c>
+      <c r="E508" t="s">
+        <v>844</v>
+      </c>
+      <c r="F508" s="9">
+        <v>46222</v>
+      </c>
     </row>
     <row r="509" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D509" s="7"/>
@@ -13602,7 +13665,7 @@
     <row r="520" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D520" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>5441711.0200000005</v>
+        <v>5469209.0300000003</v>
       </c>
       <c r="F520" s="9"/>
     </row>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Building\my_home\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zip\develop\my_home\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -25,7 +25,7 @@
     <sheet name="котельная и вентиляция" sheetId="14" r:id="rId11"/>
     <sheet name="дерево заказ на 18 апр 2026" sheetId="15" r:id="rId12"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1373" uniqueCount="853">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1381" uniqueCount="859">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3532,16 +3532,34 @@
   <si>
     <t>Сетка фасадная Крепикс 1500 1х10м (145г/м2) BauTex</t>
   </si>
+  <si>
+    <t>строительный пылесос ПС-1400-15</t>
+  </si>
+  <si>
+    <t>гидравлический ручной пресс для обжима наконечников кабеля</t>
+  </si>
+  <si>
+    <t>комплект заземления grountok 3 метра</t>
+  </si>
+  <si>
+    <t>паста кварцевазелиновая пкв защитная 20 мл</t>
+  </si>
+  <si>
+    <t>Пароизоляционная пленка ТехноНИКОЛЬ МАСТЕР БАРЬЕР 4.0  = 2рулона</t>
+  </si>
+  <si>
+    <t>штыревые наконечники для СИП16 = 8 шт</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
   </numFmts>
-  <fonts count="32" x14ac:knownFonts="1">
+  <fonts count="33" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3790,6 +3808,14 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF666666"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -3833,7 +3859,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3936,6 +3962,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -13619,53 +13648,89 @@
       </c>
     </row>
     <row r="509" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D509" s="7"/>
+      <c r="C509" t="s">
+        <v>853</v>
+      </c>
+      <c r="D509" s="7">
+        <v>4833</v>
+      </c>
+      <c r="E509" t="s">
+        <v>622</v>
+      </c>
       <c r="F509" s="9"/>
     </row>
     <row r="510" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D510" s="7"/>
+      <c r="C510" t="s">
+        <v>854</v>
+      </c>
+      <c r="D510" s="7">
+        <v>1814</v>
+      </c>
+      <c r="E510" t="s">
+        <v>622</v>
+      </c>
       <c r="F510" s="9"/>
     </row>
     <row r="511" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D511" s="7"/>
+      <c r="C511" t="s">
+        <v>855</v>
+      </c>
+      <c r="D511" s="7">
+        <v>4055</v>
+      </c>
       <c r="F511" s="9"/>
     </row>
     <row r="512" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D512" s="7"/>
+      <c r="C512" t="s">
+        <v>856</v>
+      </c>
+      <c r="D512" s="7">
+        <v>216</v>
+      </c>
       <c r="F512" s="9"/>
     </row>
-    <row r="513" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D513" s="7"/>
+    <row r="513" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C513" s="56" t="s">
+        <v>857</v>
+      </c>
+      <c r="D513" s="7">
+        <v>16666</v>
+      </c>
       <c r="F513" s="9"/>
     </row>
-    <row r="514" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D514" s="7"/>
+    <row r="514" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C514" t="s">
+        <v>858</v>
+      </c>
+      <c r="D514" s="7">
+        <v>343</v>
+      </c>
       <c r="F514" s="9"/>
     </row>
-    <row r="515" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="515" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D515" s="7"/>
       <c r="F515" s="9"/>
     </row>
-    <row r="516" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="516" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D516" s="7"/>
       <c r="F516" s="9"/>
     </row>
-    <row r="517" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="517" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D517" s="7"/>
       <c r="F517" s="9"/>
     </row>
-    <row r="518" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="518" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D518" s="7"/>
       <c r="F518" s="9"/>
     </row>
-    <row r="519" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="519" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D519" s="7"/>
       <c r="F519" s="9"/>
     </row>
-    <row r="520" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="520" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D520" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>5469209.0300000003</v>
+        <v>5497136.0300000003</v>
       </c>
       <c r="F520" s="9"/>
     </row>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -9,21 +9,22 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25320" windowHeight="8145" firstSheet="1" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25320" windowHeight="8145" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Расчёт колличества бетона " sheetId="2" r:id="rId1"/>
     <sheet name="Покупки" sheetId="6" r:id="rId2"/>
-    <sheet name="расчёт объёма бетона для мп1" sheetId="10" r:id="rId3"/>
-    <sheet name="Расчёт балок перекрытия" sheetId="11" r:id="rId4"/>
-    <sheet name="Материалы" sheetId="3" r:id="rId5"/>
-    <sheet name="Расчёт арматуры" sheetId="9" r:id="rId6"/>
-    <sheet name="Оси" sheetId="8" r:id="rId7"/>
-    <sheet name="Высоты" sheetId="7" r:id="rId8"/>
-    <sheet name="Розетки и освещение" sheetId="12" r:id="rId9"/>
-    <sheet name="сравнение цен на 13_02_26" sheetId="13" r:id="rId10"/>
-    <sheet name="котельная и вентиляция" sheetId="14" r:id="rId11"/>
-    <sheet name="дерево заказ на 18 апр 2026" sheetId="15" r:id="rId12"/>
+    <sheet name="расчёт площади утепления дома" sheetId="16" r:id="rId3"/>
+    <sheet name="расчёт объёма бетона для мп1" sheetId="10" r:id="rId4"/>
+    <sheet name="Расчёт балок перекрытия" sheetId="11" r:id="rId5"/>
+    <sheet name="Материалы" sheetId="3" r:id="rId6"/>
+    <sheet name="Расчёт арматуры" sheetId="9" r:id="rId7"/>
+    <sheet name="Оси" sheetId="8" r:id="rId8"/>
+    <sheet name="Высоты" sheetId="7" r:id="rId9"/>
+    <sheet name="Розетки и освещение" sheetId="12" r:id="rId10"/>
+    <sheet name="сравнение цен на 13_02_26" sheetId="13" r:id="rId11"/>
+    <sheet name="котельная и вентиляция" sheetId="14" r:id="rId12"/>
+    <sheet name="дерево заказ на 18 апр 2026" sheetId="15" r:id="rId13"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
@@ -440,7 +441,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1381" uniqueCount="859">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1409" uniqueCount="878">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3549,6 +3550,63 @@
   </si>
   <si>
     <t>штыревые наконечники для СИП16 = 8 шт</t>
+  </si>
+  <si>
+    <t>сторона дома</t>
+  </si>
+  <si>
+    <t>восток</t>
+  </si>
+  <si>
+    <t>запад</t>
+  </si>
+  <si>
+    <t>север</t>
+  </si>
+  <si>
+    <t>юг</t>
+  </si>
+  <si>
+    <t>площадь (м2)</t>
+  </si>
+  <si>
+    <t>ширина (м)</t>
+  </si>
+  <si>
+    <t>высота (м)</t>
+  </si>
+  <si>
+    <t>площадь проёмов (м2)</t>
+  </si>
+  <si>
+    <t>высота окна (м)</t>
+  </si>
+  <si>
+    <t>ширина окна (м)</t>
+  </si>
+  <si>
+    <t>высота окна двери на терасу (м)</t>
+  </si>
+  <si>
+    <t>площадь утепления (м2)</t>
+  </si>
+  <si>
+    <t>из общей площади -  площадь проёмов = площадь утепления</t>
+  </si>
+  <si>
+    <t>высота малого окна (м)</t>
+  </si>
+  <si>
+    <t>высота двери входной (м)</t>
+  </si>
+  <si>
+    <t>проём один - окно из с\у</t>
+  </si>
+  <si>
+    <t>два проёма</t>
+  </si>
+  <si>
+    <t>общая площадь утепления (с запасом думаю = 160м2 пенопласта)</t>
   </si>
 </sst>
 </file>
@@ -3859,7 +3917,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3965,12 +4023,19 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="35">
+  <dxfs count="37">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
@@ -4384,29 +4449,65 @@
   <tableColumns count="5">
     <tableColumn id="1" name="№ п/п"/>
     <tableColumn id="2" name="Наименование "/>
-    <tableColumn id="3" name="Цена (руб)" totalsRowFunction="sum" dataDxfId="34" totalsRowDxfId="1"/>
+    <tableColumn id="3" name="Цена (руб)" totalsRowFunction="sum" dataDxfId="36" totalsRowDxfId="3"/>
     <tableColumn id="4" name="Примечание"/>
-    <tableColumn id="5" name="дата" dataDxfId="33" totalsRowDxfId="0"/>
+    <tableColumn id="5" name="дата" dataDxfId="35" totalsRowDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Таблица14910" displayName="Таблица14910" ref="B3:D9" totalsRowShown="0">
+  <autoFilter ref="B3:D9"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="Наименование"/>
+    <tableColumn id="2" name="высота (мм)"/>
+    <tableColumn id="3" name="примечание"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="Таблица13" displayName="Таблица13" ref="B4:D15" totalsRowShown="0">
   <autoFilter ref="B4:D15"/>
   <tableColumns count="3">
     <tableColumn id="1" name="назначение"/>
-    <tableColumn id="2" name="количество розеток (шт)" dataDxfId="30"/>
+    <tableColumn id="2" name="количество розеток (шт)" dataDxfId="32"/>
     <tableColumn id="3" name="примечание"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="Таблица1316" displayName="Таблица1316" ref="B19:D23" totalsRowShown="0">
   <autoFilter ref="B19:D23"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="назначение"/>
+    <tableColumn id="2" name="количество (шт)" dataDxfId="31"/>
+    <tableColumn id="3" name="примечание"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="Таблица131617" displayName="Таблица131617" ref="B28:D32" totalsRowShown="0">
+  <autoFilter ref="B28:D32"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="назначение"/>
+    <tableColumn id="2" name="количество (шт)" dataDxfId="30"/>
+    <tableColumn id="3" name="примечание"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="Таблица13161718" displayName="Таблица13161718" ref="B36:D40" totalsRowShown="0">
+  <autoFilter ref="B36:D40"/>
   <tableColumns count="3">
     <tableColumn id="1" name="назначение"/>
     <tableColumn id="2" name="количество (шт)" dataDxfId="29"/>
@@ -4416,9 +4517,9 @@
 </table>
 </file>
 
-<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="Таблица131617" displayName="Таблица131617" ref="B28:D32" totalsRowShown="0">
-  <autoFilter ref="B28:D32"/>
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="Таблица1316171819" displayName="Таблица1316171819" ref="B44:D48" totalsRowShown="0">
+  <autoFilter ref="B44:D48"/>
   <tableColumns count="3">
     <tableColumn id="1" name="назначение"/>
     <tableColumn id="2" name="количество (шт)" dataDxfId="28"/>
@@ -4428,9 +4529,9 @@
 </table>
 </file>
 
-<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="Таблица13161718" displayName="Таблица13161718" ref="B36:D40" totalsRowShown="0">
-  <autoFilter ref="B36:D40"/>
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="Таблица131617181920" displayName="Таблица131617181920" ref="B52:D55" totalsRowShown="0">
+  <autoFilter ref="B52:D55"/>
   <tableColumns count="3">
     <tableColumn id="1" name="назначение"/>
     <tableColumn id="2" name="количество (шт)" dataDxfId="27"/>
@@ -4440,9 +4541,9 @@
 </table>
 </file>
 
-<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="Таблица1316171819" displayName="Таблица1316171819" ref="B44:D48" totalsRowShown="0">
-  <autoFilter ref="B44:D48"/>
+<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="Таблица13161721" displayName="Таблица13161721" ref="B59:D68" totalsRowShown="0">
+  <autoFilter ref="B59:D68"/>
   <tableColumns count="3">
     <tableColumn id="1" name="назначение"/>
     <tableColumn id="2" name="количество (шт)" dataDxfId="26"/>
@@ -4452,9 +4553,9 @@
 </table>
 </file>
 
-<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="Таблица131617181920" displayName="Таблица131617181920" ref="B52:D55" totalsRowShown="0">
-  <autoFilter ref="B52:D55"/>
+<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="Таблица13161718192023" displayName="Таблица13161718192023" ref="B69:D72" totalsRowShown="0">
+  <autoFilter ref="B69:D72"/>
   <tableColumns count="3">
     <tableColumn id="1" name="назначение"/>
     <tableColumn id="2" name="количество (шт)" dataDxfId="25"/>
@@ -4464,94 +4565,71 @@
 </table>
 </file>
 
-<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="Таблица13161721" displayName="Таблица13161721" ref="B59:D68" totalsRowShown="0">
-  <autoFilter ref="B59:D68"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="назначение"/>
-    <tableColumn id="2" name="количество (шт)" dataDxfId="24"/>
-    <tableColumn id="3" name="примечание"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="Таблица13161718192023" displayName="Таблица13161718192023" ref="B69:D72" totalsRowShown="0">
-  <autoFilter ref="B69:D72"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="назначение"/>
-    <tableColumn id="2" name="количество (шт)" dataDxfId="23"/>
-    <tableColumn id="3" name="примечание"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Таблица8" displayName="Таблица8" ref="B4:C17" totalsRowShown="0">
   <autoFilter ref="B4:C17"/>
   <tableColumns count="2">
     <tableColumn id="1" name="Комплектующие\Магазины"/>
-    <tableColumn id="2" name=" Цена в Бауцентр (руб)" dataDxfId="22"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Таблица811" displayName="Таблица811" ref="E4:L17" totalsRowShown="0">
-  <autoFilter ref="E4:L17"/>
-  <tableColumns count="8">
-    <tableColumn id="1" name="Комплектующие\Магазины"/>
-    <tableColumn id="2" name=" Legrand" dataDxfId="21"/>
-    <tableColumn id="6" name="Dekraft" dataDxfId="20"/>
-    <tableColumn id="7" name="EKF" dataDxfId="19"/>
-    <tableColumn id="8" name="TDM electric" dataDxfId="18"/>
-    <tableColumn id="9" name="IEK" dataDxfId="17"/>
-    <tableColumn id="10" name="Спец 800вт" dataDxfId="16"/>
-    <tableColumn id="11" name="Столбец1" dataDxfId="15"/>
+    <tableColumn id="2" name=" Цена в Бауцентр (руб)" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Таблица2" displayName="Таблица2" ref="A4:F28" totalsRowCount="1">
-  <autoFilter ref="A4:F27"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="Таблица24" displayName="Таблица24" ref="B2:G7" totalsRowShown="0">
+  <autoFilter ref="B2:G7"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="№ п/п" totalsRowLabel="Итого:" totalsRowDxfId="7"/>
-    <tableColumn id="2" name="Тип" totalsRowDxfId="6"/>
-    <tableColumn id="3" name="Количество (М3/шт)" totalsRowDxfId="5"/>
-    <tableColumn id="4" name="Цена  (м3 или штук)" dataDxfId="32" totalsRowDxfId="4"/>
-    <tableColumn id="5" name="Сумма" totalsRowFunction="custom" dataDxfId="31" totalsRowDxfId="3">
-      <calculatedColumnFormula>Таблица2[[#This Row],[Цена  (м3 или штук)]]*Таблица2[[#This Row],[Количество (М3/шт)]]</calculatedColumnFormula>
-      <totalsRowFormula>SUM(E5:E27)</totalsRowFormula>
+    <tableColumn id="1" name="сторона дома"/>
+    <tableColumn id="2" name="ширина (м)"/>
+    <tableColumn id="3" name="высота (м)"/>
+    <tableColumn id="4" name="площадь проёмов (м2)" dataDxfId="1">
+      <calculatedColumnFormula>M3*2+M7</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" name="Примечание" totalsRowDxfId="2"/>
+    <tableColumn id="5" name="площадь утепления (м2)" dataDxfId="0">
+      <calculatedColumnFormula>Таблица24[[#This Row],[ширина (м)]]*Таблица24[[#This Row],[высота (м)]]-Таблица24[[#This Row],[площадь проёмов (м2)]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" name="примечание"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="Таблица81122" displayName="Таблица81122" ref="E22:L35" totalsRowShown="0">
-  <autoFilter ref="E22:L35"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Таблица811" displayName="Таблица811" ref="E4:L17" totalsRowShown="0">
+  <autoFilter ref="E4:L17"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Комплектующие\Магазины"/>
-    <tableColumn id="2" name=" Legrand" dataDxfId="14"/>
-    <tableColumn id="6" name="Dekraft" dataDxfId="13"/>
-    <tableColumn id="7" name="EKF" dataDxfId="12"/>
-    <tableColumn id="8" name="TDM electric" dataDxfId="11"/>
-    <tableColumn id="9" name="IEK" dataDxfId="10"/>
-    <tableColumn id="10" name="Спец 800вт" dataDxfId="9"/>
-    <tableColumn id="11" name="Etimat" dataDxfId="8"/>
+    <tableColumn id="2" name=" Legrand" dataDxfId="23"/>
+    <tableColumn id="6" name="Dekraft" dataDxfId="22"/>
+    <tableColumn id="7" name="EKF" dataDxfId="21"/>
+    <tableColumn id="8" name="TDM electric" dataDxfId="20"/>
+    <tableColumn id="9" name="IEK" dataDxfId="19"/>
+    <tableColumn id="10" name="Спец 800вт" dataDxfId="18"/>
+    <tableColumn id="11" name="Столбец1" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="Таблица81122" displayName="Таблица81122" ref="E22:L35" totalsRowShown="0">
+  <autoFilter ref="E22:L35"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="Комплектующие\Магазины"/>
+    <tableColumn id="2" name=" Legrand" dataDxfId="16"/>
+    <tableColumn id="6" name="Dekraft" dataDxfId="15"/>
+    <tableColumn id="7" name="EKF" dataDxfId="14"/>
+    <tableColumn id="8" name="TDM electric" dataDxfId="13"/>
+    <tableColumn id="9" name="IEK" dataDxfId="12"/>
+    <tableColumn id="10" name="Спец 800вт" dataDxfId="11"/>
+    <tableColumn id="11" name="Etimat" dataDxfId="10"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Таблица11" displayName="Таблица11" ref="B3:D8" totalsRowShown="0">
   <autoFilter ref="B3:D8"/>
   <tableColumns count="3">
@@ -4563,7 +4641,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Таблица12" displayName="Таблица12" ref="B14:F19" totalsRowShown="0">
   <autoFilter ref="B14:F19"/>
   <tableColumns count="5">
@@ -4578,6 +4656,24 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Таблица2" displayName="Таблица2" ref="A4:F28" totalsRowCount="1">
+  <autoFilter ref="A4:F27"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name="№ п/п" totalsRowLabel="Итого:" totalsRowDxfId="9"/>
+    <tableColumn id="2" name="Тип" totalsRowDxfId="8"/>
+    <tableColumn id="3" name="Количество (М3/шт)" totalsRowDxfId="7"/>
+    <tableColumn id="4" name="Цена  (м3 или штук)" dataDxfId="34" totalsRowDxfId="6"/>
+    <tableColumn id="5" name="Сумма" totalsRowFunction="custom" dataDxfId="33" totalsRowDxfId="5">
+      <calculatedColumnFormula>Таблица2[[#This Row],[Цена  (м3 или штук)]]*Таблица2[[#This Row],[Количество (М3/шт)]]</calculatedColumnFormula>
+      <totalsRowFormula>SUM(E5:E27)</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="6" name="Примечание" totalsRowDxfId="4"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Таблица1" displayName="Таблица1" ref="B2:D9" totalsRowShown="0">
   <autoFilter ref="B2:D9"/>
   <tableColumns count="3">
@@ -4589,7 +4685,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Таблица5" displayName="Таблица5" ref="A3:C10" totalsRowShown="0">
   <autoFilter ref="A3:C10"/>
   <tableColumns count="3">
@@ -4601,7 +4697,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Таблица54" displayName="Таблица54" ref="E3:G10" totalsRowShown="0">
   <autoFilter ref="E3:G10"/>
   <tableColumns count="3">
@@ -4613,7 +4709,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Таблица57" displayName="Таблица57" ref="A15:C22" totalsRowShown="0">
   <autoFilter ref="A15:C22"/>
   <tableColumns count="3">
@@ -4625,7 +4721,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Таблица548" displayName="Таблица548" ref="E15:G22" totalsRowShown="0">
   <autoFilter ref="E15:G22"/>
   <tableColumns count="3">
@@ -4637,21 +4733,9 @@
 </table>
 </file>
 
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="Таблица14" displayName="Таблица14" ref="G3:I9" totalsRowShown="0">
   <autoFilter ref="G3:I9"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="Наименование"/>
-    <tableColumn id="2" name="высота (мм)"/>
-    <tableColumn id="3" name="примечание"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Таблица14910" displayName="Таблица14910" ref="B3:D9" totalsRowShown="0">
-  <autoFilter ref="B3:D9"/>
   <tableColumns count="3">
     <tableColumn id="1" name="Наименование"/>
     <tableColumn id="2" name="высота (мм)"/>
@@ -5092,6 +5176,573 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B3:D78"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="68.7109375" customWidth="1"/>
+    <col min="3" max="3" width="26.28515625" customWidth="1"/>
+    <col min="4" max="4" width="112" customWidth="1"/>
+    <col min="5" max="5" width="23.7109375" customWidth="1"/>
+    <col min="6" max="6" width="24.28515625" customWidth="1"/>
+    <col min="7" max="7" width="28" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="22" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" customWidth="1"/>
+    <col min="11" max="11" width="13.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B3" s="8" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>538</v>
+      </c>
+      <c r="C4" t="s">
+        <v>573</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>539</v>
+      </c>
+      <c r="C5" s="23">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>541</v>
+      </c>
+      <c r="C6" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>540</v>
+      </c>
+      <c r="C7" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>542</v>
+      </c>
+      <c r="C8" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>545</v>
+      </c>
+      <c r="C9" s="23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>543</v>
+      </c>
+      <c r="C10" s="23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>544</v>
+      </c>
+      <c r="C11" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>551</v>
+      </c>
+      <c r="C12" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>546</v>
+      </c>
+      <c r="C13" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>549</v>
+      </c>
+      <c r="C14" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>550</v>
+      </c>
+      <c r="C15" s="23">
+        <f>SUM(C5:C14)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B18" s="8" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>538</v>
+      </c>
+      <c r="C19" t="s">
+        <v>548</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>553</v>
+      </c>
+      <c r="C20" s="23">
+        <v>4</v>
+      </c>
+      <c r="D20" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>551</v>
+      </c>
+      <c r="C21" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>552</v>
+      </c>
+      <c r="C22" s="23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>550</v>
+      </c>
+      <c r="C23" s="23">
+        <f>SUM(C20:C22)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C24" s="23"/>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C25" s="23"/>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C26" s="23"/>
+    </row>
+    <row r="27" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B27" s="8" t="s">
+        <v>576</v>
+      </c>
+      <c r="C27" s="23"/>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>538</v>
+      </c>
+      <c r="C28" t="s">
+        <v>548</v>
+      </c>
+      <c r="D28" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>553</v>
+      </c>
+      <c r="C29" s="23">
+        <v>4</v>
+      </c>
+      <c r="D29" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>551</v>
+      </c>
+      <c r="C30" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>552</v>
+      </c>
+      <c r="C31" s="23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>550</v>
+      </c>
+      <c r="C32" s="23">
+        <f>SUM(C29:C31)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B35" s="8" t="s">
+        <v>577</v>
+      </c>
+      <c r="C35" s="23"/>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>538</v>
+      </c>
+      <c r="C36" t="s">
+        <v>548</v>
+      </c>
+      <c r="D36" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>553</v>
+      </c>
+      <c r="C37" s="23">
+        <v>4</v>
+      </c>
+      <c r="D37" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>551</v>
+      </c>
+      <c r="C38" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>552</v>
+      </c>
+      <c r="C39" s="23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>550</v>
+      </c>
+      <c r="C40" s="23">
+        <f>SUM(C37:C39)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B43" s="8" t="s">
+        <v>578</v>
+      </c>
+      <c r="C43" s="23"/>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>538</v>
+      </c>
+      <c r="C44" t="s">
+        <v>548</v>
+      </c>
+      <c r="D44" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
+        <v>555</v>
+      </c>
+      <c r="C45" s="23">
+        <v>2</v>
+      </c>
+      <c r="D45" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
+        <v>554</v>
+      </c>
+      <c r="C46" s="23">
+        <v>1</v>
+      </c>
+      <c r="D46" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
+        <v>556</v>
+      </c>
+      <c r="C47" s="23">
+        <v>2</v>
+      </c>
+      <c r="D47" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
+        <v>550</v>
+      </c>
+      <c r="C48" s="23">
+        <f>SUM(C45:C47)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B51" s="8" t="s">
+        <v>579</v>
+      </c>
+      <c r="C51" s="23"/>
+    </row>
+    <row r="52" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
+        <v>538</v>
+      </c>
+      <c r="C52" t="s">
+        <v>548</v>
+      </c>
+      <c r="D52" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
+        <v>559</v>
+      </c>
+      <c r="C53" s="23">
+        <v>1</v>
+      </c>
+      <c r="D53" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>560</v>
+      </c>
+      <c r="C54" s="23">
+        <v>1</v>
+      </c>
+      <c r="D54" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
+        <v>550</v>
+      </c>
+      <c r="C55" s="23">
+        <f>SUM(C53:C54)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C56" s="23"/>
+    </row>
+    <row r="58" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B58" s="8" t="s">
+        <v>580</v>
+      </c>
+      <c r="C58" s="23"/>
+    </row>
+    <row r="59" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
+        <v>538</v>
+      </c>
+      <c r="C59" t="s">
+        <v>548</v>
+      </c>
+      <c r="D59" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
+        <v>561</v>
+      </c>
+      <c r="C60" s="23">
+        <v>2</v>
+      </c>
+      <c r="D60" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B61" t="s">
+        <v>562</v>
+      </c>
+      <c r="C61" s="23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B62" t="s">
+        <v>563</v>
+      </c>
+      <c r="C62" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B63" t="s">
+        <v>564</v>
+      </c>
+      <c r="C63" s="23">
+        <v>1</v>
+      </c>
+      <c r="D63" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B64" t="s">
+        <v>565</v>
+      </c>
+      <c r="C64" s="23">
+        <v>1</v>
+      </c>
+      <c r="D64" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B65" t="s">
+        <v>568</v>
+      </c>
+      <c r="C65" s="23"/>
+      <c r="D65" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C66" s="23"/>
+      <c r="D66" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C67" s="23"/>
+    </row>
+    <row r="68" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B68" s="8" t="s">
+        <v>581</v>
+      </c>
+      <c r="C68" s="23"/>
+    </row>
+    <row r="69" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B69" t="s">
+        <v>538</v>
+      </c>
+      <c r="C69" t="s">
+        <v>548</v>
+      </c>
+      <c r="D69" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B70" t="s">
+        <v>570</v>
+      </c>
+      <c r="C70" s="23">
+        <v>1</v>
+      </c>
+      <c r="D70" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B71" t="s">
+        <v>571</v>
+      </c>
+      <c r="C71" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B72" t="s">
+        <v>550</v>
+      </c>
+      <c r="C72" s="23">
+        <f>SUM(C70:C71)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B75" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="76" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B76" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="77" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B77" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="78" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B78" t="s">
+        <v>585</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="8">
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
+    <tablePart r:id="rId7"/>
+    <tablePart r:id="rId8"/>
+    <tablePart r:id="rId9"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:L35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5637,7 +6288,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:F20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5763,7 +6414,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:F19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13657,7 +14308,9 @@
       <c r="E509" t="s">
         <v>622</v>
       </c>
-      <c r="F509" s="9"/>
+      <c r="F509" s="9">
+        <v>46225</v>
+      </c>
     </row>
     <row r="510" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C510" t="s">
@@ -13705,7 +14358,12 @@
       <c r="D514" s="7">
         <v>343</v>
       </c>
-      <c r="F514" s="9"/>
+      <c r="E514" t="s">
+        <v>232</v>
+      </c>
+      <c r="F514" s="9">
+        <v>46225</v>
+      </c>
     </row>
     <row r="515" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D515" s="7"/>
@@ -13754,6 +14412,231 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:M13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="21.28515625" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" customWidth="1"/>
+    <col min="5" max="5" width="25.28515625" customWidth="1"/>
+    <col min="6" max="6" width="27" customWidth="1"/>
+    <col min="7" max="7" width="62.140625" customWidth="1"/>
+    <col min="11" max="11" width="31" customWidth="1"/>
+    <col min="12" max="12" width="18.7109375" customWidth="1"/>
+    <col min="13" max="13" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>859</v>
+      </c>
+      <c r="C2" t="s">
+        <v>865</v>
+      </c>
+      <c r="D2" t="s">
+        <v>866</v>
+      </c>
+      <c r="E2" t="s">
+        <v>867</v>
+      </c>
+      <c r="F2" t="s">
+        <v>871</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" t="s">
+        <v>868</v>
+      </c>
+      <c r="L2" t="s">
+        <v>869</v>
+      </c>
+      <c r="M2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>860</v>
+      </c>
+      <c r="C3">
+        <v>13</v>
+      </c>
+      <c r="D3">
+        <v>3.47</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E6" si="0">M3*2+M7</f>
+        <v>9.7199999999999989</v>
+      </c>
+      <c r="F3">
+        <f>Таблица24[[#This Row],[ширина (м)]]*Таблица24[[#This Row],[высота (м)]]-Таблица24[[#This Row],[площадь проёмов (м2)]]</f>
+        <v>35.39</v>
+      </c>
+      <c r="G3" t="s">
+        <v>872</v>
+      </c>
+      <c r="K3">
+        <v>1.51</v>
+      </c>
+      <c r="L3">
+        <v>1.8</v>
+      </c>
+      <c r="M3">
+        <f>K3*L3</f>
+        <v>2.718</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>861</v>
+      </c>
+      <c r="C4">
+        <v>13</v>
+      </c>
+      <c r="D4">
+        <v>3.47</v>
+      </c>
+      <c r="E4">
+        <f>M10+(M3*2)+M13</f>
+        <v>10.155000000000001</v>
+      </c>
+      <c r="F4">
+        <f>Таблица24[[#This Row],[ширина (м)]]*Таблица24[[#This Row],[высота (м)]]-Таблица24[[#This Row],[площадь проёмов (м2)]]</f>
+        <v>34.954999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>862</v>
+      </c>
+      <c r="C5">
+        <v>11.85</v>
+      </c>
+      <c r="D5">
+        <v>3.47</v>
+      </c>
+      <c r="E5">
+        <v>1.359</v>
+      </c>
+      <c r="F5">
+        <f>Таблица24[[#This Row],[ширина (м)]]*Таблица24[[#This Row],[высота (м)]]-Таблица24[[#This Row],[площадь проёмов (м2)]]</f>
+        <v>39.7605</v>
+      </c>
+      <c r="G5" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>863</v>
+      </c>
+      <c r="C6">
+        <v>11.85</v>
+      </c>
+      <c r="D6">
+        <v>3.47</v>
+      </c>
+      <c r="E6">
+        <f>M3*2</f>
+        <v>5.4359999999999999</v>
+      </c>
+      <c r="F6">
+        <f>Таблица24[[#This Row],[ширина (м)]]*Таблица24[[#This Row],[высота (м)]]-Таблица24[[#This Row],[площадь проёмов (м2)]]</f>
+        <v>35.683500000000002</v>
+      </c>
+      <c r="G6" t="s">
+        <v>876</v>
+      </c>
+      <c r="K6" t="s">
+        <v>870</v>
+      </c>
+      <c r="L6" t="s">
+        <v>865</v>
+      </c>
+      <c r="M6" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="57"/>
+      <c r="F7" s="57">
+        <f>SUM(F3:F6)</f>
+        <v>145.78900000000002</v>
+      </c>
+      <c r="G7" t="s">
+        <v>877</v>
+      </c>
+      <c r="K7">
+        <v>2.38</v>
+      </c>
+      <c r="L7">
+        <v>1.8</v>
+      </c>
+      <c r="M7">
+        <f>K7*L7</f>
+        <v>4.2839999999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K9" t="s">
+        <v>873</v>
+      </c>
+      <c r="L9" t="s">
+        <v>869</v>
+      </c>
+      <c r="M9" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K10">
+        <v>1.51</v>
+      </c>
+      <c r="L10">
+        <v>0.9</v>
+      </c>
+      <c r="M10">
+        <f>K10*L10</f>
+        <v>1.359</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K12" t="s">
+        <v>874</v>
+      </c>
+      <c r="L12" t="s">
+        <v>865</v>
+      </c>
+      <c r="M12" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K13">
+        <v>2.1</v>
+      </c>
+      <c r="L13">
+        <v>1.6</v>
+      </c>
+      <c r="M13">
+        <f>K13*L13</f>
+        <v>3.3600000000000003</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:D18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -13887,7 +14770,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="C3:L15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13986,7 +14869,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A3:F28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14391,7 +15274,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:D9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14505,7 +15388,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14852,7 +15735,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -15091,571 +15974,4 @@
     <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:D78"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="68.7109375" customWidth="1"/>
-    <col min="3" max="3" width="26.28515625" customWidth="1"/>
-    <col min="4" max="4" width="112" customWidth="1"/>
-    <col min="5" max="5" width="23.7109375" customWidth="1"/>
-    <col min="6" max="6" width="24.28515625" customWidth="1"/>
-    <col min="7" max="7" width="28" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="22" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" customWidth="1"/>
-    <col min="11" max="11" width="13.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B3" s="8" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>538</v>
-      </c>
-      <c r="C4" t="s">
-        <v>573</v>
-      </c>
-      <c r="D4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>539</v>
-      </c>
-      <c r="C5" s="23">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>541</v>
-      </c>
-      <c r="C6" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>540</v>
-      </c>
-      <c r="C7" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>542</v>
-      </c>
-      <c r="C8" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>545</v>
-      </c>
-      <c r="C9" s="23">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>543</v>
-      </c>
-      <c r="C10" s="23">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>544</v>
-      </c>
-      <c r="C11" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>551</v>
-      </c>
-      <c r="C12" s="23">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>546</v>
-      </c>
-      <c r="C13" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>549</v>
-      </c>
-      <c r="C14" s="23">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>550</v>
-      </c>
-      <c r="C15" s="23">
-        <f>SUM(C5:C14)</f>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B18" s="8" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>538</v>
-      </c>
-      <c r="C19" t="s">
-        <v>548</v>
-      </c>
-      <c r="D19" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
-        <v>553</v>
-      </c>
-      <c r="C20" s="23">
-        <v>4</v>
-      </c>
-      <c r="D20" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
-        <v>551</v>
-      </c>
-      <c r="C21" s="23">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>552</v>
-      </c>
-      <c r="C22" s="23">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
-        <v>550</v>
-      </c>
-      <c r="C23" s="23">
-        <f>SUM(C20:C22)</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C24" s="23"/>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C25" s="23"/>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C26" s="23"/>
-    </row>
-    <row r="27" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B27" s="8" t="s">
-        <v>576</v>
-      </c>
-      <c r="C27" s="23"/>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B28" t="s">
-        <v>538</v>
-      </c>
-      <c r="C28" t="s">
-        <v>548</v>
-      </c>
-      <c r="D28" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B29" t="s">
-        <v>553</v>
-      </c>
-      <c r="C29" s="23">
-        <v>4</v>
-      </c>
-      <c r="D29" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B30" t="s">
-        <v>551</v>
-      </c>
-      <c r="C30" s="23">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B31" t="s">
-        <v>552</v>
-      </c>
-      <c r="C31" s="23">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B32" t="s">
-        <v>550</v>
-      </c>
-      <c r="C32" s="23">
-        <f>SUM(C29:C31)</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B35" s="8" t="s">
-        <v>577</v>
-      </c>
-      <c r="C35" s="23"/>
-    </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B36" t="s">
-        <v>538</v>
-      </c>
-      <c r="C36" t="s">
-        <v>548</v>
-      </c>
-      <c r="D36" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B37" t="s">
-        <v>553</v>
-      </c>
-      <c r="C37" s="23">
-        <v>4</v>
-      </c>
-      <c r="D37" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B38" t="s">
-        <v>551</v>
-      </c>
-      <c r="C38" s="23">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B39" t="s">
-        <v>552</v>
-      </c>
-      <c r="C39" s="23">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B40" t="s">
-        <v>550</v>
-      </c>
-      <c r="C40" s="23">
-        <f>SUM(C37:C39)</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B43" s="8" t="s">
-        <v>578</v>
-      </c>
-      <c r="C43" s="23"/>
-    </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B44" t="s">
-        <v>538</v>
-      </c>
-      <c r="C44" t="s">
-        <v>548</v>
-      </c>
-      <c r="D44" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B45" t="s">
-        <v>555</v>
-      </c>
-      <c r="C45" s="23">
-        <v>2</v>
-      </c>
-      <c r="D45" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B46" t="s">
-        <v>554</v>
-      </c>
-      <c r="C46" s="23">
-        <v>1</v>
-      </c>
-      <c r="D46" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B47" t="s">
-        <v>556</v>
-      </c>
-      <c r="C47" s="23">
-        <v>2</v>
-      </c>
-      <c r="D47" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B48" t="s">
-        <v>550</v>
-      </c>
-      <c r="C48" s="23">
-        <f>SUM(C45:C47)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B51" s="8" t="s">
-        <v>579</v>
-      </c>
-      <c r="C51" s="23"/>
-    </row>
-    <row r="52" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B52" t="s">
-        <v>538</v>
-      </c>
-      <c r="C52" t="s">
-        <v>548</v>
-      </c>
-      <c r="D52" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B53" t="s">
-        <v>559</v>
-      </c>
-      <c r="C53" s="23">
-        <v>1</v>
-      </c>
-      <c r="D53" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="54" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B54" t="s">
-        <v>560</v>
-      </c>
-      <c r="C54" s="23">
-        <v>1</v>
-      </c>
-      <c r="D54" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="55" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B55" t="s">
-        <v>550</v>
-      </c>
-      <c r="C55" s="23">
-        <f>SUM(C53:C54)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="56" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C56" s="23"/>
-    </row>
-    <row r="58" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B58" s="8" t="s">
-        <v>580</v>
-      </c>
-      <c r="C58" s="23"/>
-    </row>
-    <row r="59" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B59" t="s">
-        <v>538</v>
-      </c>
-      <c r="C59" t="s">
-        <v>548</v>
-      </c>
-      <c r="D59" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B60" t="s">
-        <v>561</v>
-      </c>
-      <c r="C60" s="23">
-        <v>2</v>
-      </c>
-      <c r="D60" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="61" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B61" t="s">
-        <v>562</v>
-      </c>
-      <c r="C61" s="23">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="62" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B62" t="s">
-        <v>563</v>
-      </c>
-      <c r="C62" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B63" t="s">
-        <v>564</v>
-      </c>
-      <c r="C63" s="23">
-        <v>1</v>
-      </c>
-      <c r="D63" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="64" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B64" t="s">
-        <v>565</v>
-      </c>
-      <c r="C64" s="23">
-        <v>1</v>
-      </c>
-      <c r="D64" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="65" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B65" t="s">
-        <v>568</v>
-      </c>
-      <c r="C65" s="23"/>
-      <c r="D65" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="66" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C66" s="23"/>
-      <c r="D66" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="67" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C67" s="23"/>
-    </row>
-    <row r="68" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B68" s="8" t="s">
-        <v>581</v>
-      </c>
-      <c r="C68" s="23"/>
-    </row>
-    <row r="69" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B69" t="s">
-        <v>538</v>
-      </c>
-      <c r="C69" t="s">
-        <v>548</v>
-      </c>
-      <c r="D69" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B70" t="s">
-        <v>570</v>
-      </c>
-      <c r="C70" s="23">
-        <v>1</v>
-      </c>
-      <c r="D70" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="71" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B71" t="s">
-        <v>571</v>
-      </c>
-      <c r="C71" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B72" t="s">
-        <v>550</v>
-      </c>
-      <c r="C72" s="23">
-        <f>SUM(C70:C71)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="75" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B75" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="76" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B76" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="77" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B77" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="78" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B78" t="s">
-        <v>585</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <tableParts count="8">
-    <tablePart r:id="rId2"/>
-    <tablePart r:id="rId3"/>
-    <tablePart r:id="rId4"/>
-    <tablePart r:id="rId5"/>
-    <tablePart r:id="rId6"/>
-    <tablePart r:id="rId7"/>
-    <tablePart r:id="rId8"/>
-    <tablePart r:id="rId9"/>
-  </tableParts>
-</worksheet>
 </file>
--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zip\develop\my_home\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Building\my_home\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25320" windowHeight="8145" firstSheet="1" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25320" windowHeight="8145" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Расчёт колличества бетона " sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
     <sheet name="котельная и вентиляция" sheetId="14" r:id="rId12"/>
     <sheet name="дерево заказ на 18 апр 2026" sheetId="15" r:id="rId13"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -441,7 +441,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1409" uniqueCount="878">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1414" uniqueCount="879">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3608,11 +3608,14 @@
   <si>
     <t>общая площадь утепления (с запасом думаю = 160м2 пенопласта)</t>
   </si>
+  <si>
+    <t>Шина для PE, алмазный диск-коронка, ручка-скоба рс-100-3 цинк</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
@@ -4031,12 +4034,6 @@
   </cellStyles>
   <dxfs count="37">
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
@@ -4166,6 +4163,12 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
@@ -4449,9 +4452,9 @@
   <tableColumns count="5">
     <tableColumn id="1" name="№ п/п"/>
     <tableColumn id="2" name="Наименование "/>
-    <tableColumn id="3" name="Цена (руб)" totalsRowFunction="sum" dataDxfId="36" totalsRowDxfId="3"/>
+    <tableColumn id="3" name="Цена (руб)" totalsRowFunction="sum" dataDxfId="36" totalsRowDxfId="1"/>
     <tableColumn id="4" name="Примечание"/>
-    <tableColumn id="5" name="дата" dataDxfId="35" totalsRowDxfId="2"/>
+    <tableColumn id="5" name="дата" dataDxfId="35" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4474,7 +4477,7 @@
   <autoFilter ref="B4:D15"/>
   <tableColumns count="3">
     <tableColumn id="1" name="назначение"/>
-    <tableColumn id="2" name="количество розеток (шт)" dataDxfId="32"/>
+    <tableColumn id="2" name="количество розеток (шт)" dataDxfId="30"/>
     <tableColumn id="3" name="примечание"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4486,7 +4489,7 @@
   <autoFilter ref="B19:D23"/>
   <tableColumns count="3">
     <tableColumn id="1" name="назначение"/>
-    <tableColumn id="2" name="количество (шт)" dataDxfId="31"/>
+    <tableColumn id="2" name="количество (шт)" dataDxfId="29"/>
     <tableColumn id="3" name="примечание"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4498,7 +4501,7 @@
   <autoFilter ref="B28:D32"/>
   <tableColumns count="3">
     <tableColumn id="1" name="назначение"/>
-    <tableColumn id="2" name="количество (шт)" dataDxfId="30"/>
+    <tableColumn id="2" name="количество (шт)" dataDxfId="28"/>
     <tableColumn id="3" name="примечание"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4510,7 +4513,7 @@
   <autoFilter ref="B36:D40"/>
   <tableColumns count="3">
     <tableColumn id="1" name="назначение"/>
-    <tableColumn id="2" name="количество (шт)" dataDxfId="29"/>
+    <tableColumn id="2" name="количество (шт)" dataDxfId="27"/>
     <tableColumn id="3" name="примечание"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4522,7 +4525,7 @@
   <autoFilter ref="B44:D48"/>
   <tableColumns count="3">
     <tableColumn id="1" name="назначение"/>
-    <tableColumn id="2" name="количество (шт)" dataDxfId="28"/>
+    <tableColumn id="2" name="количество (шт)" dataDxfId="26"/>
     <tableColumn id="3" name="примечание"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4534,7 +4537,7 @@
   <autoFilter ref="B52:D55"/>
   <tableColumns count="3">
     <tableColumn id="1" name="назначение"/>
-    <tableColumn id="2" name="количество (шт)" dataDxfId="27"/>
+    <tableColumn id="2" name="количество (шт)" dataDxfId="25"/>
     <tableColumn id="3" name="примечание"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4546,7 +4549,7 @@
   <autoFilter ref="B59:D68"/>
   <tableColumns count="3">
     <tableColumn id="1" name="назначение"/>
-    <tableColumn id="2" name="количество (шт)" dataDxfId="26"/>
+    <tableColumn id="2" name="количество (шт)" dataDxfId="24"/>
     <tableColumn id="3" name="примечание"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4558,7 +4561,7 @@
   <autoFilter ref="B69:D72"/>
   <tableColumns count="3">
     <tableColumn id="1" name="назначение"/>
-    <tableColumn id="2" name="количество (шт)" dataDxfId="25"/>
+    <tableColumn id="2" name="количество (шт)" dataDxfId="23"/>
     <tableColumn id="3" name="примечание"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4570,7 +4573,7 @@
   <autoFilter ref="B4:C17"/>
   <tableColumns count="2">
     <tableColumn id="1" name="Комплектующие\Магазины"/>
-    <tableColumn id="2" name=" Цена в Бауцентр (руб)" dataDxfId="24"/>
+    <tableColumn id="2" name=" Цена в Бауцентр (руб)" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4583,10 +4586,10 @@
     <tableColumn id="1" name="сторона дома"/>
     <tableColumn id="2" name="ширина (м)"/>
     <tableColumn id="3" name="высота (м)"/>
-    <tableColumn id="4" name="площадь проёмов (м2)" dataDxfId="1">
+    <tableColumn id="4" name="площадь проёмов (м2)" dataDxfId="34">
       <calculatedColumnFormula>M3*2+M7</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" name="площадь утепления (м2)" dataDxfId="0">
+    <tableColumn id="5" name="площадь утепления (м2)" dataDxfId="33">
       <calculatedColumnFormula>Таблица24[[#This Row],[ширина (м)]]*Таблица24[[#This Row],[высота (м)]]-Таблица24[[#This Row],[площадь проёмов (м2)]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" name="примечание"/>
@@ -4600,13 +4603,13 @@
   <autoFilter ref="E4:L17"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Комплектующие\Магазины"/>
-    <tableColumn id="2" name=" Legrand" dataDxfId="23"/>
-    <tableColumn id="6" name="Dekraft" dataDxfId="22"/>
-    <tableColumn id="7" name="EKF" dataDxfId="21"/>
-    <tableColumn id="8" name="TDM electric" dataDxfId="20"/>
-    <tableColumn id="9" name="IEK" dataDxfId="19"/>
-    <tableColumn id="10" name="Спец 800вт" dataDxfId="18"/>
-    <tableColumn id="11" name="Столбец1" dataDxfId="17"/>
+    <tableColumn id="2" name=" Legrand" dataDxfId="21"/>
+    <tableColumn id="6" name="Dekraft" dataDxfId="20"/>
+    <tableColumn id="7" name="EKF" dataDxfId="19"/>
+    <tableColumn id="8" name="TDM electric" dataDxfId="18"/>
+    <tableColumn id="9" name="IEK" dataDxfId="17"/>
+    <tableColumn id="10" name="Спец 800вт" dataDxfId="16"/>
+    <tableColumn id="11" name="Столбец1" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4617,13 +4620,13 @@
   <autoFilter ref="E22:L35"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Комплектующие\Магазины"/>
-    <tableColumn id="2" name=" Legrand" dataDxfId="16"/>
-    <tableColumn id="6" name="Dekraft" dataDxfId="15"/>
-    <tableColumn id="7" name="EKF" dataDxfId="14"/>
-    <tableColumn id="8" name="TDM electric" dataDxfId="13"/>
-    <tableColumn id="9" name="IEK" dataDxfId="12"/>
-    <tableColumn id="10" name="Спец 800вт" dataDxfId="11"/>
-    <tableColumn id="11" name="Etimat" dataDxfId="10"/>
+    <tableColumn id="2" name=" Legrand" dataDxfId="14"/>
+    <tableColumn id="6" name="Dekraft" dataDxfId="13"/>
+    <tableColumn id="7" name="EKF" dataDxfId="12"/>
+    <tableColumn id="8" name="TDM electric" dataDxfId="11"/>
+    <tableColumn id="9" name="IEK" dataDxfId="10"/>
+    <tableColumn id="10" name="Спец 800вт" dataDxfId="9"/>
+    <tableColumn id="11" name="Etimat" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4659,15 +4662,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Таблица2" displayName="Таблица2" ref="A4:F28" totalsRowCount="1">
   <autoFilter ref="A4:F27"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="№ п/п" totalsRowLabel="Итого:" totalsRowDxfId="9"/>
-    <tableColumn id="2" name="Тип" totalsRowDxfId="8"/>
-    <tableColumn id="3" name="Количество (М3/шт)" totalsRowDxfId="7"/>
-    <tableColumn id="4" name="Цена  (м3 или штук)" dataDxfId="34" totalsRowDxfId="6"/>
-    <tableColumn id="5" name="Сумма" totalsRowFunction="custom" dataDxfId="33" totalsRowDxfId="5">
+    <tableColumn id="1" name="№ п/п" totalsRowLabel="Итого:" totalsRowDxfId="7"/>
+    <tableColumn id="2" name="Тип" totalsRowDxfId="6"/>
+    <tableColumn id="3" name="Количество (М3/шт)" totalsRowDxfId="5"/>
+    <tableColumn id="4" name="Цена  (м3 или штук)" dataDxfId="32" totalsRowDxfId="4"/>
+    <tableColumn id="5" name="Сумма" totalsRowFunction="custom" dataDxfId="31" totalsRowDxfId="3">
       <calculatedColumnFormula>Таблица2[[#This Row],[Цена  (м3 или штук)]]*Таблица2[[#This Row],[Количество (М3/шт)]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(E5:E27)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" name="Примечание" totalsRowDxfId="4"/>
+    <tableColumn id="6" name="Примечание" totalsRowDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14322,7 +14325,9 @@
       <c r="E510" t="s">
         <v>622</v>
       </c>
-      <c r="F510" s="9"/>
+      <c r="F510" s="9">
+        <v>46226</v>
+      </c>
     </row>
     <row r="511" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C511" t="s">
@@ -14331,7 +14336,12 @@
       <c r="D511" s="7">
         <v>4055</v>
       </c>
-      <c r="F511" s="9"/>
+      <c r="E511" t="s">
+        <v>622</v>
+      </c>
+      <c r="F511" s="9">
+        <v>46228</v>
+      </c>
     </row>
     <row r="512" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C512" t="s">
@@ -14340,7 +14350,12 @@
       <c r="D512" s="7">
         <v>216</v>
       </c>
-      <c r="F512" s="9"/>
+      <c r="E512" t="s">
+        <v>232</v>
+      </c>
+      <c r="F512" s="9">
+        <v>46228</v>
+      </c>
     </row>
     <row r="513" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C513" s="56" t="s">
@@ -14349,6 +14364,9 @@
       <c r="D513" s="7">
         <v>16666</v>
       </c>
+      <c r="E513" t="s">
+        <v>232</v>
+      </c>
       <c r="F513" s="9"/>
     </row>
     <row r="514" spans="3:6" x14ac:dyDescent="0.25">
@@ -14366,8 +14384,18 @@
       </c>
     </row>
     <row r="515" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D515" s="7"/>
-      <c r="F515" s="9"/>
+      <c r="C515" t="s">
+        <v>878</v>
+      </c>
+      <c r="D515" s="7">
+        <v>1367</v>
+      </c>
+      <c r="E515" t="s">
+        <v>173</v>
+      </c>
+      <c r="F515" s="9">
+        <v>46228</v>
+      </c>
     </row>
     <row r="516" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D516" s="7"/>
@@ -14388,7 +14416,7 @@
     <row r="520" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D520" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>5497136.0300000003</v>
+        <v>5498503.0300000003</v>
       </c>
       <c r="F520" s="9"/>
     </row>
@@ -14466,7 +14494,7 @@
         <v>3.47</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E6" si="0">M3*2+M7</f>
+        <f t="shared" ref="E3" si="0">M3*2+M7</f>
         <v>9.7199999999999989</v>
       </c>
       <c r="F3">

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Building\my_home\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zip\develop\my_home\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -26,7 +26,7 @@
     <sheet name="котельная и вентиляция" sheetId="14" r:id="rId12"/>
     <sheet name="дерево заказ на 18 апр 2026" sheetId="15" r:id="rId13"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -3615,7 +3615,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
@@ -4034,12 +4034,6 @@
   </cellStyles>
   <dxfs count="37">
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -4088,6 +4082,12 @@
         <top/>
         <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
@@ -4452,9 +4452,9 @@
   <tableColumns count="5">
     <tableColumn id="1" name="№ п/п"/>
     <tableColumn id="2" name="Наименование "/>
-    <tableColumn id="3" name="Цена (руб)" totalsRowFunction="sum" dataDxfId="36" totalsRowDxfId="1"/>
+    <tableColumn id="3" name="Цена (руб)" totalsRowFunction="sum" dataDxfId="36" totalsRowDxfId="7"/>
     <tableColumn id="4" name="Примечание"/>
-    <tableColumn id="5" name="дата" dataDxfId="35" totalsRowDxfId="0"/>
+    <tableColumn id="5" name="дата" dataDxfId="35" totalsRowDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4662,15 +4662,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Таблица2" displayName="Таблица2" ref="A4:F28" totalsRowCount="1">
   <autoFilter ref="A4:F27"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="№ п/п" totalsRowLabel="Итого:" totalsRowDxfId="7"/>
-    <tableColumn id="2" name="Тип" totalsRowDxfId="6"/>
-    <tableColumn id="3" name="Количество (М3/шт)" totalsRowDxfId="5"/>
-    <tableColumn id="4" name="Цена  (м3 или штук)" dataDxfId="32" totalsRowDxfId="4"/>
-    <tableColumn id="5" name="Сумма" totalsRowFunction="custom" dataDxfId="31" totalsRowDxfId="3">
+    <tableColumn id="1" name="№ п/п" totalsRowLabel="Итого:" totalsRowDxfId="5"/>
+    <tableColumn id="2" name="Тип" totalsRowDxfId="4"/>
+    <tableColumn id="3" name="Количество (М3/шт)" totalsRowDxfId="3"/>
+    <tableColumn id="4" name="Цена  (м3 или штук)" dataDxfId="32" totalsRowDxfId="2"/>
+    <tableColumn id="5" name="Сумма" totalsRowFunction="custom" dataDxfId="31" totalsRowDxfId="1">
       <calculatedColumnFormula>Таблица2[[#This Row],[Цена  (м3 или штук)]]*Таблица2[[#This Row],[Количество (М3/шт)]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(E5:E27)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" name="Примечание" totalsRowDxfId="2"/>
+    <tableColumn id="6" name="Примечание" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zip\develop\my_home\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Building\my_home\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -26,7 +26,7 @@
     <sheet name="котельная и вентиляция" sheetId="14" r:id="rId12"/>
     <sheet name="дерево заказ на 18 апр 2026" sheetId="15" r:id="rId13"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -441,7 +441,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1414" uniqueCount="879">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1426" uniqueCount="886">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3611,11 +3611,32 @@
   <si>
     <t>Шина для PE, алмазный диск-коронка, ручка-скоба рс-100-3 цинк</t>
   </si>
+  <si>
+    <t>Грунтовка для стен, наконечники НШАМ 16</t>
+  </si>
+  <si>
+    <t>провод пугв PE 1х10 -4 метра, провод ПУгВ черный 1х10 -5метров</t>
+  </si>
+  <si>
+    <t>Данил</t>
+  </si>
+  <si>
+    <t>Гурьевский пенополистерол</t>
+  </si>
+  <si>
+    <t>Плита пеноп.ППС-16Ф (100мм) - 16.2 м3</t>
+  </si>
+  <si>
+    <t>Плита пеноп.ППС-25 (50мм) - 14,7 м3</t>
+  </si>
+  <si>
+    <t>Транспортные услуги</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
@@ -4034,6 +4055,12 @@
   </cellStyles>
   <dxfs count="37">
     <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -4082,12 +4109,6 @@
         <top/>
         <bottom/>
       </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
@@ -4447,14 +4468,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F520" totalsRowCount="1">
-  <autoFilter ref="B5:F519"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F530" totalsRowCount="1">
+  <autoFilter ref="B5:F529"/>
   <tableColumns count="5">
     <tableColumn id="1" name="№ п/п"/>
     <tableColumn id="2" name="Наименование "/>
-    <tableColumn id="3" name="Цена (руб)" totalsRowFunction="sum" dataDxfId="36" totalsRowDxfId="7"/>
+    <tableColumn id="3" name="Цена (руб)" totalsRowFunction="sum" dataDxfId="36" totalsRowDxfId="1"/>
     <tableColumn id="4" name="Примечание"/>
-    <tableColumn id="5" name="дата" dataDxfId="35" totalsRowDxfId="6"/>
+    <tableColumn id="5" name="дата" dataDxfId="35" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4662,15 +4683,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Таблица2" displayName="Таблица2" ref="A4:F28" totalsRowCount="1">
   <autoFilter ref="A4:F27"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="№ п/п" totalsRowLabel="Итого:" totalsRowDxfId="5"/>
-    <tableColumn id="2" name="Тип" totalsRowDxfId="4"/>
-    <tableColumn id="3" name="Количество (М3/шт)" totalsRowDxfId="3"/>
-    <tableColumn id="4" name="Цена  (м3 или штук)" dataDxfId="32" totalsRowDxfId="2"/>
-    <tableColumn id="5" name="Сумма" totalsRowFunction="custom" dataDxfId="31" totalsRowDxfId="1">
+    <tableColumn id="1" name="№ п/п" totalsRowLabel="Итого:" totalsRowDxfId="7"/>
+    <tableColumn id="2" name="Тип" totalsRowDxfId="6"/>
+    <tableColumn id="3" name="Количество (М3/шт)" totalsRowDxfId="5"/>
+    <tableColumn id="4" name="Цена  (м3 или штук)" dataDxfId="32" totalsRowDxfId="4"/>
+    <tableColumn id="5" name="Сумма" totalsRowFunction="custom" dataDxfId="31" totalsRowDxfId="3">
       <calculatedColumnFormula>Таблица2[[#This Row],[Цена  (м3 или штук)]]*Таблица2[[#This Row],[Количество (М3/шт)]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(E5:E27)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" name="Примечание" totalsRowDxfId="0"/>
+    <tableColumn id="6" name="Примечание" totalsRowDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6605,7 +6626,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:I520"/>
+  <dimension ref="B3:I530"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="85.28515625" customWidth="1"/>
@@ -14398,27 +14419,128 @@
       </c>
     </row>
     <row r="516" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D516" s="7"/>
-      <c r="F516" s="9"/>
+      <c r="C516" t="s">
+        <v>879</v>
+      </c>
+      <c r="D516" s="7">
+        <v>608</v>
+      </c>
+      <c r="E516" t="s">
+        <v>173</v>
+      </c>
+      <c r="F516" s="9">
+        <v>46230</v>
+      </c>
     </row>
     <row r="517" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D517" s="7"/>
-      <c r="F517" s="9"/>
+      <c r="C517" t="s">
+        <v>880</v>
+      </c>
+      <c r="D517" s="7">
+        <v>1755</v>
+      </c>
+      <c r="E517" t="s">
+        <v>722</v>
+      </c>
+      <c r="F517" s="9">
+        <v>46230</v>
+      </c>
     </row>
     <row r="518" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D518" s="7"/>
-      <c r="F518" s="9"/>
+      <c r="C518" t="s">
+        <v>473</v>
+      </c>
+      <c r="D518" s="7">
+        <v>12000</v>
+      </c>
+      <c r="E518" t="s">
+        <v>881</v>
+      </c>
+      <c r="F518" s="9">
+        <v>46230</v>
+      </c>
     </row>
     <row r="519" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D519" s="7"/>
-      <c r="F519" s="9"/>
+      <c r="C519" t="s">
+        <v>883</v>
+      </c>
+      <c r="D519" s="7">
+        <v>74439</v>
+      </c>
+      <c r="E519" t="s">
+        <v>882</v>
+      </c>
+      <c r="F519" s="9">
+        <v>46230</v>
+      </c>
     </row>
     <row r="520" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C520" t="s">
+        <v>884</v>
+      </c>
       <c r="D520" s="7">
+        <v>117306</v>
+      </c>
+      <c r="E520" t="s">
+        <v>882</v>
+      </c>
+      <c r="F520" s="9">
+        <v>46230</v>
+      </c>
+    </row>
+    <row r="521" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C521" t="s">
+        <v>885</v>
+      </c>
+      <c r="D521" s="7">
+        <v>2700</v>
+      </c>
+      <c r="E521" t="s">
+        <v>882</v>
+      </c>
+      <c r="F521" s="9">
+        <v>46230</v>
+      </c>
+    </row>
+    <row r="522" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D522" s="7"/>
+      <c r="F522" s="9"/>
+    </row>
+    <row r="523" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D523" s="7"/>
+      <c r="F523" s="9"/>
+    </row>
+    <row r="524" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D524" s="7"/>
+      <c r="F524" s="9"/>
+    </row>
+    <row r="525" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D525" s="7"/>
+      <c r="F525" s="9"/>
+    </row>
+    <row r="526" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D526" s="7"/>
+      <c r="F526" s="9"/>
+    </row>
+    <row r="527" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D527" s="7"/>
+      <c r="F527" s="9"/>
+    </row>
+    <row r="528" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D528" s="7"/>
+      <c r="F528" s="9"/>
+    </row>
+    <row r="529" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D529" s="7"/>
+      <c r="E529" s="7"/>
+      <c r="F529" s="9"/>
+    </row>
+    <row r="530" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D530" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>5498503.0300000003</v>
-      </c>
-      <c r="F520" s="9"/>
+        <v>5707311.0300000003</v>
+      </c>
+      <c r="F530" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -441,7 +441,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1426" uniqueCount="886">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="894">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3631,6 +3631,30 @@
   </si>
   <si>
     <t>Транспортные услуги</t>
+  </si>
+  <si>
+    <t>ООО "БАУЦЕНТР РУС"</t>
+  </si>
+  <si>
+    <t>Клей для пенополистирола ZM 01 KLESTER (25кг) - 30 мешков</t>
+  </si>
+  <si>
+    <t>Клей для пенополистирола и сетки ZM 02 KLESTER (25кг) - 30 мешков</t>
+  </si>
+  <si>
+    <t>Дюбель с пластиковым стержнем D10х180мм 50 шт Koelner - 18</t>
+  </si>
+  <si>
+    <t>Дюбель с пластиковым стержнем D10х180мм 50 шт Koelner - 2</t>
+  </si>
+  <si>
+    <t>Сетка фасадная Крепикс 1800 1х50м (160г/м2) BauTex - 4 рулона</t>
+  </si>
+  <si>
+    <t>Уголок штукатурный ПВХ с пластиковой сеткой Крепикс 1300 100х150х2500 BauTex - 5 рулонов</t>
+  </si>
+  <si>
+    <t>Клей-пена монтажная профессиональная 500 Professional 1000мл Технониколь - 2</t>
   </si>
 </sst>
 </file>
@@ -4468,8 +4492,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F530" totalsRowCount="1">
-  <autoFilter ref="B5:F529"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F537" totalsRowCount="1">
+  <autoFilter ref="B5:F536"/>
   <tableColumns count="5">
     <tableColumn id="1" name="№ п/п"/>
     <tableColumn id="2" name="Наименование "/>
@@ -6626,7 +6650,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:I530"/>
+  <dimension ref="B3:I537"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="85.28515625" customWidth="1"/>
@@ -14503,44 +14527,156 @@
       </c>
     </row>
     <row r="522" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D522" s="7"/>
-      <c r="F522" s="9"/>
+      <c r="C522" t="s">
+        <v>887</v>
+      </c>
+      <c r="D522" s="7">
+        <f>8115.85+4698.76</f>
+        <v>12814.61</v>
+      </c>
+      <c r="E522" t="s">
+        <v>886</v>
+      </c>
+      <c r="F522" s="9">
+        <v>46234</v>
+      </c>
     </row>
     <row r="523" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D523" s="7"/>
-      <c r="F523" s="9"/>
+      <c r="C523" t="s">
+        <v>888</v>
+      </c>
+      <c r="D523" s="7">
+        <f>17173.51+592.2</f>
+        <v>17765.71</v>
+      </c>
+      <c r="E523" t="s">
+        <v>886</v>
+      </c>
+      <c r="F523" s="9">
+        <v>46234</v>
+      </c>
     </row>
     <row r="524" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D524" s="7"/>
-      <c r="F524" s="9"/>
+      <c r="C524" t="s">
+        <v>889</v>
+      </c>
+      <c r="D524" s="7">
+        <v>6972.3</v>
+      </c>
+      <c r="E524" t="s">
+        <v>886</v>
+      </c>
+      <c r="F524" s="9">
+        <v>46234</v>
+      </c>
     </row>
     <row r="525" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D525" s="7"/>
-      <c r="F525" s="9"/>
+      <c r="C525" t="s">
+        <v>890</v>
+      </c>
+      <c r="D525" s="7">
+        <v>774.72</v>
+      </c>
+      <c r="E525" t="s">
+        <v>886</v>
+      </c>
+      <c r="F525" s="9">
+        <v>46234</v>
+      </c>
     </row>
     <row r="526" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D526" s="7"/>
-      <c r="F526" s="9"/>
+      <c r="C526" t="s">
+        <v>891</v>
+      </c>
+      <c r="D526" s="7">
+        <f>8708.1+2902.71</f>
+        <v>11610.810000000001</v>
+      </c>
+      <c r="E526" t="s">
+        <v>886</v>
+      </c>
+      <c r="F526" s="9">
+        <v>46234</v>
+      </c>
     </row>
     <row r="527" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D527" s="7"/>
-      <c r="F527" s="9"/>
+      <c r="C527" t="s">
+        <v>892</v>
+      </c>
+      <c r="D527" s="7">
+        <f>5*90.28</f>
+        <v>451.4</v>
+      </c>
+      <c r="E527" t="s">
+        <v>886</v>
+      </c>
+      <c r="F527" s="9">
+        <v>46234</v>
+      </c>
     </row>
     <row r="528" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D528" s="7"/>
-      <c r="F528" s="9"/>
-    </row>
-    <row r="529" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D529" s="7"/>
-      <c r="E529" s="7"/>
-      <c r="F529" s="9"/>
-    </row>
-    <row r="530" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D530" s="7">
+      <c r="C528" t="s">
+        <v>893</v>
+      </c>
+      <c r="D528" s="7">
+        <f>824.22*2</f>
+        <v>1648.44</v>
+      </c>
+      <c r="E528" t="s">
+        <v>886</v>
+      </c>
+      <c r="F528" s="9">
+        <v>46234</v>
+      </c>
+    </row>
+    <row r="529" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C529" t="s">
+        <v>426</v>
+      </c>
+      <c r="D529" s="7">
+        <v>2510</v>
+      </c>
+      <c r="E529" t="s">
+        <v>886</v>
+      </c>
+      <c r="F529" s="9">
+        <v>46234</v>
+      </c>
+    </row>
+    <row r="530" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D530" s="7"/>
+      <c r="F530" s="9"/>
+    </row>
+    <row r="531" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D531" s="7"/>
+      <c r="F531" s="9"/>
+    </row>
+    <row r="532" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D532" s="7"/>
+      <c r="F532" s="9"/>
+    </row>
+    <row r="533" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D533" s="7"/>
+      <c r="F533" s="9"/>
+    </row>
+    <row r="534" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D534" s="7"/>
+      <c r="F534" s="9"/>
+    </row>
+    <row r="535" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D535" s="7"/>
+      <c r="F535" s="9"/>
+    </row>
+    <row r="536" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D536" s="7"/>
+      <c r="F536" s="9"/>
+    </row>
+    <row r="537" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D537" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>5707311.0300000003</v>
-      </c>
-      <c r="F530" s="9"/>
+        <v>5761859.0200000005</v>
+      </c>
+      <c r="F537" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -441,7 +441,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="894">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="897">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3655,6 +3655,15 @@
   </si>
   <si>
     <t>Клей-пена монтажная профессиональная 500 Professional 1000мл Технониколь - 2</t>
+  </si>
+  <si>
+    <t>плёнка защитная с лентой, для вн работ 1.1х33м x-glass - 2 рулона</t>
+  </si>
+  <si>
+    <t>лента малярная 48мм х 25м для наружных работ (синяя) Фрегат - 9шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">наконечник штыревой втулочный изолированный 10 50шт ekf </t>
   </si>
 </sst>
 </file>
@@ -14644,16 +14653,48 @@
       </c>
     </row>
     <row r="530" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D530" s="7"/>
-      <c r="F530" s="9"/>
+      <c r="C530" t="s">
+        <v>894</v>
+      </c>
+      <c r="D530" s="7">
+        <f>251.35*2</f>
+        <v>502.7</v>
+      </c>
+      <c r="E530" t="s">
+        <v>886</v>
+      </c>
+      <c r="F530" s="9">
+        <v>46237</v>
+      </c>
     </row>
     <row r="531" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D531" s="7"/>
-      <c r="F531" s="9"/>
+      <c r="C531" t="s">
+        <v>895</v>
+      </c>
+      <c r="D531" s="7">
+        <f>174.33*9</f>
+        <v>1568.97</v>
+      </c>
+      <c r="E531" t="s">
+        <v>886</v>
+      </c>
+      <c r="F531" s="9">
+        <v>46237</v>
+      </c>
     </row>
     <row r="532" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D532" s="7"/>
-      <c r="F532" s="9"/>
+      <c r="C532" t="s">
+        <v>896</v>
+      </c>
+      <c r="D532" s="7">
+        <v>118.32</v>
+      </c>
+      <c r="E532" t="s">
+        <v>886</v>
+      </c>
+      <c r="F532" s="9">
+        <v>46237</v>
+      </c>
     </row>
     <row r="533" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D533" s="7"/>
@@ -14674,7 +14715,7 @@
     <row r="537" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D537" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>5761859.0200000005</v>
+        <v>5764049.0100000007</v>
       </c>
       <c r="F537" s="9"/>
     </row>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -9,22 +9,24 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25320" windowHeight="8145" firstSheet="1" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25320" windowHeight="8145" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Расчёт колличества бетона " sheetId="2" r:id="rId1"/>
-    <sheet name="Покупки" sheetId="6" r:id="rId2"/>
-    <sheet name="расчёт площади утепления дома" sheetId="16" r:id="rId3"/>
-    <sheet name="расчёт объёма бетона для мп1" sheetId="10" r:id="rId4"/>
-    <sheet name="Расчёт балок перекрытия" sheetId="11" r:id="rId5"/>
-    <sheet name="Материалы" sheetId="3" r:id="rId6"/>
-    <sheet name="Расчёт арматуры" sheetId="9" r:id="rId7"/>
-    <sheet name="Оси" sheetId="8" r:id="rId8"/>
-    <sheet name="Высоты" sheetId="7" r:id="rId9"/>
-    <sheet name="Розетки и освещение" sheetId="12" r:id="rId10"/>
-    <sheet name="сравнение цен на 13_02_26" sheetId="13" r:id="rId11"/>
-    <sheet name="котельная и вентиляция" sheetId="14" r:id="rId12"/>
-    <sheet name="дерево заказ на 18 апр 2026" sheetId="15" r:id="rId13"/>
+    <sheet name="Покупки для дома" sheetId="6" r:id="rId2"/>
+    <sheet name="расчёт труб отопления" sheetId="18" r:id="rId3"/>
+    <sheet name="расчёт площади утепления дома" sheetId="16" r:id="rId4"/>
+    <sheet name="расчёт объёма бетона для мп1" sheetId="10" r:id="rId5"/>
+    <sheet name="Расчёт балок перекрытия" sheetId="11" r:id="rId6"/>
+    <sheet name="Материалы" sheetId="3" r:id="rId7"/>
+    <sheet name="Расчёт арматуры" sheetId="9" r:id="rId8"/>
+    <sheet name="Оси" sheetId="8" r:id="rId9"/>
+    <sheet name="Высоты" sheetId="7" r:id="rId10"/>
+    <sheet name="Розетки и освещение" sheetId="12" r:id="rId11"/>
+    <sheet name="сравнение цен на 13_02_26" sheetId="13" r:id="rId12"/>
+    <sheet name="котельная и вентиляция" sheetId="14" r:id="rId13"/>
+    <sheet name="дерево заказ на 18 апр 2026" sheetId="15" r:id="rId14"/>
+    <sheet name="расчёт кол-ва профилей оконных" sheetId="17" r:id="rId15"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
@@ -441,7 +443,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="897">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1498" uniqueCount="927">
   <si>
     <t>№ п/п</t>
   </si>
@@ -2464,9 +2466,6 @@
   </si>
   <si>
     <t>Розетка на din рейку iek 16A 250В</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>wildberries</t>
@@ -3665,6 +3664,99 @@
   <si>
     <t xml:space="preserve">наконечник штыревой втулочный изолированный 10 50шт ekf </t>
   </si>
+  <si>
+    <t>окно</t>
+  </si>
+  <si>
+    <t>окно малое</t>
+  </si>
+  <si>
+    <t>дверь-окно на террасу</t>
+  </si>
+  <si>
+    <t>длинна (см)</t>
+  </si>
+  <si>
+    <t>см</t>
+  </si>
+  <si>
+    <t>м</t>
+  </si>
+  <si>
+    <t>труба отоп_под_детская</t>
+  </si>
+  <si>
+    <t>длинна с обратным трубопроводом (см)</t>
+  </si>
+  <si>
+    <t>труба_отоп_под_бабуш</t>
+  </si>
+  <si>
+    <t>труба_отоп_под_родит</t>
+  </si>
+  <si>
+    <t>труба_отоп_под_сануз</t>
+  </si>
+  <si>
+    <t>труба_отоп_под_тех</t>
+  </si>
+  <si>
+    <t>труба_отоп_под_дверь_терр</t>
+  </si>
+  <si>
+    <t>труба_отоп_под_кух_зап</t>
+  </si>
+  <si>
+    <t>труба_отоп_под_кух_юг</t>
+  </si>
+  <si>
+    <t>труба_отоп_под_гост_юг</t>
+  </si>
+  <si>
+    <t>в метрах -&gt;</t>
+  </si>
+  <si>
+    <t>Труба гофрированная ПВХ "легкая" 16мм с/з 10м Эра</t>
+  </si>
+  <si>
+    <t>Клеммный зажим на DIN-рейку ЗНИ-10 синий - 4шт</t>
+  </si>
+  <si>
+    <t>Профиль примыкающий оконный ПВХ с сеткой 9мм 2,4 м БауТекс - 20 шт</t>
+  </si>
+  <si>
+    <t>Уголок штукатурный ПВХ с пластиковой сеткой Крепикс 1300 100х150х2500 BauTex - 24 шт</t>
+  </si>
+  <si>
+    <t>Клей-пена монтажная профессиональная 500 Professional 1000мл Технониколь - 2шт</t>
+  </si>
+  <si>
+    <t>ДОСТ-ИМ18 Услуга доставки товара из интернет магазина</t>
+  </si>
+  <si>
+    <t>Выключатель автоматический 2п 4,5кА 16А С EKF</t>
+  </si>
+  <si>
+    <t>Пенополистирол ППС 16Ф 1000x500x100мм - 8шт</t>
+  </si>
+  <si>
+    <t>Провод гибкий круглый ПВС 3х2,5 5м ГОСТ</t>
+  </si>
+  <si>
+    <t>сборка крыши - плёнка, обрешётка, контр обрешётка, металлочерепица, вентгрибок, ливнестоки</t>
+  </si>
+  <si>
+    <t>Щиток электрический встраиваемый ЩРВ-П-54 TEKFOR,54 модуля</t>
+  </si>
+  <si>
+    <t>aideLife насадка штроборез</t>
+  </si>
+  <si>
+    <t>соединительная одностороняя лента Технониколь альфабэнд 60 - 8шт</t>
+  </si>
+  <si>
+    <t>Колцо гидрозатвора на вентиляцию 4 шт</t>
+  </si>
 </sst>
 </file>
 
@@ -3674,7 +3766,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
   </numFmts>
-  <fonts count="33" x14ac:knownFonts="1">
+  <fonts count="34" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3931,6 +4023,14 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242429"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -4076,23 +4176,19 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="37">
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
-    </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
@@ -4142,6 +4238,12 @@
         <top/>
         <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
@@ -4501,14 +4603,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F537" totalsRowCount="1">
-  <autoFilter ref="B5:F536"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F553" totalsRowCount="1">
+  <autoFilter ref="B5:F552"/>
   <tableColumns count="5">
     <tableColumn id="1" name="№ п/п"/>
     <tableColumn id="2" name="Наименование "/>
-    <tableColumn id="3" name="Цена (руб)" totalsRowFunction="sum" dataDxfId="36" totalsRowDxfId="1"/>
+    <tableColumn id="3" name="Цена (руб)" totalsRowFunction="sum" dataDxfId="36" totalsRowDxfId="7"/>
     <tableColumn id="4" name="Примечание"/>
-    <tableColumn id="5" name="дата" dataDxfId="35" totalsRowDxfId="0"/>
+    <tableColumn id="5" name="дата" dataDxfId="35" totalsRowDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4716,15 +4818,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Таблица2" displayName="Таблица2" ref="A4:F28" totalsRowCount="1">
   <autoFilter ref="A4:F27"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="№ п/п" totalsRowLabel="Итого:" totalsRowDxfId="7"/>
-    <tableColumn id="2" name="Тип" totalsRowDxfId="6"/>
-    <tableColumn id="3" name="Количество (М3/шт)" totalsRowDxfId="5"/>
-    <tableColumn id="4" name="Цена  (м3 или штук)" dataDxfId="32" totalsRowDxfId="4"/>
-    <tableColumn id="5" name="Сумма" totalsRowFunction="custom" dataDxfId="31" totalsRowDxfId="3">
+    <tableColumn id="1" name="№ п/п" totalsRowLabel="Итого:" totalsRowDxfId="5"/>
+    <tableColumn id="2" name="Тип" totalsRowDxfId="4"/>
+    <tableColumn id="3" name="Количество (М3/шт)" totalsRowDxfId="3"/>
+    <tableColumn id="4" name="Цена  (м3 или штук)" dataDxfId="32" totalsRowDxfId="2"/>
+    <tableColumn id="5" name="Сумма" totalsRowFunction="custom" dataDxfId="31" totalsRowDxfId="1">
       <calculatedColumnFormula>Таблица2[[#This Row],[Цена  (м3 или штук)]]*Таблица2[[#This Row],[Количество (М3/шт)]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(E5:E27)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" name="Примечание" totalsRowDxfId="2"/>
+    <tableColumn id="6" name="Примечание" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5234,6 +5336,247 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.42578125" customWidth="1"/>
+    <col min="2" max="2" width="42.28515625" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" customWidth="1"/>
+    <col min="4" max="4" width="56" customWidth="1"/>
+    <col min="6" max="6" width="6.85546875" customWidth="1"/>
+    <col min="7" max="7" width="43" customWidth="1"/>
+    <col min="8" max="8" width="24.5703125" customWidth="1"/>
+    <col min="9" max="9" width="62.140625" customWidth="1"/>
+    <col min="10" max="10" width="58.140625" customWidth="1"/>
+    <col min="11" max="11" width="14.140625" customWidth="1"/>
+    <col min="12" max="12" width="47.85546875" customWidth="1"/>
+    <col min="13" max="13" width="11.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+      <c r="C1" s="32" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B2" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>343</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>344</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>343</v>
+      </c>
+      <c r="H3" s="23" t="s">
+        <v>344</v>
+      </c>
+      <c r="I3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="23"/>
+      <c r="B4" t="s">
+        <v>345</v>
+      </c>
+      <c r="C4" s="23">
+        <v>160</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>349</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>342</v>
+      </c>
+      <c r="G4" t="s">
+        <v>345</v>
+      </c>
+      <c r="H4" s="23">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>346</v>
+      </c>
+      <c r="C5" s="31">
+        <v>100</v>
+      </c>
+      <c r="D5" t="s">
+        <v>794</v>
+      </c>
+      <c r="G5" t="s">
+        <v>346</v>
+      </c>
+      <c r="H5" s="27">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>347</v>
+      </c>
+      <c r="C6" s="27">
+        <v>65</v>
+      </c>
+      <c r="D6" t="s">
+        <v>393</v>
+      </c>
+      <c r="G6" t="s">
+        <v>347</v>
+      </c>
+      <c r="H6" s="27">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>348</v>
+      </c>
+      <c r="C7" s="28">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
+        <v>795</v>
+      </c>
+      <c r="G7" t="s">
+        <v>348</v>
+      </c>
+      <c r="H7" s="28">
+        <v>20</v>
+      </c>
+      <c r="I7" s="29" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>796</v>
+      </c>
+      <c r="C8" s="36">
+        <v>1015</v>
+      </c>
+      <c r="D8" t="s">
+        <v>395</v>
+      </c>
+      <c r="G8" t="s">
+        <v>394</v>
+      </c>
+      <c r="H8" s="23">
+        <f>2550+H5+H6+H7</f>
+        <v>2780</v>
+      </c>
+      <c r="I8" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>396</v>
+      </c>
+      <c r="C9" s="24">
+        <v>3020</v>
+      </c>
+      <c r="G9" t="s">
+        <v>396</v>
+      </c>
+      <c r="H9" s="24">
+        <f>H8+250</f>
+        <v>3030</v>
+      </c>
+      <c r="I9" t="s">
+        <v>400</v>
+      </c>
+      <c r="K9" s="23"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H10" s="24"/>
+      <c r="K10" s="23"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F11" s="23"/>
+      <c r="K11" s="23"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F12" s="23"/>
+      <c r="K12" s="23"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D13" t="s">
+        <v>402</v>
+      </c>
+      <c r="F13" s="23"/>
+      <c r="G13" t="s">
+        <v>401</v>
+      </c>
+      <c r="H13" s="24">
+        <f>850+H5+H6+H7</f>
+        <v>1080</v>
+      </c>
+      <c r="I13" t="s">
+        <v>397</v>
+      </c>
+      <c r="K13" s="23"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F14" s="23"/>
+      <c r="K14" s="23"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F15" s="30"/>
+      <c r="K15" s="23"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F16" s="23"/>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="F17" s="23"/>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="F18" s="23"/>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="F19" s="23"/>
+      <c r="K19" s="33"/>
+      <c r="L19" s="34"/>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="F20" s="23"/>
+      <c r="K20" s="22"/>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="F21" s="23"/>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B22" s="21"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="F22" s="23"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="2">
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:D78"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5273,7 +5616,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.25">
@@ -5799,7 +6142,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:L35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6345,7 +6688,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:F20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6356,112 +6699,112 @@
   <sheetData>
     <row r="3" spans="2:6" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="43" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F3" s="43" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="44"/>
       <c r="F4" s="49" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="129.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="43" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F5" s="50" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B6" s="44"/>
       <c r="F6" s="46" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="45" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F7" s="46" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="122.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="43" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F8" s="46" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="44" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F9" s="51" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="46" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F10" s="43" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="46" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="12" spans="2:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B12" s="46" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="13" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B13" s="46" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="47" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="15" spans="2:6" ht="133.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="47" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B16" s="48" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="17" spans="2:2" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="45" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="18" spans="2:2" ht="161.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="46" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="19" spans="2:2" ht="105.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="46" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="20" spans="2:2" ht="144" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="46" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
   </sheetData>
@@ -6471,7 +6814,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:F19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6485,10 +6828,10 @@
   <sheetData>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C3" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D3" t="s">
         <v>1</v>
@@ -6496,79 +6839,79 @@
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C4">
         <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C5">
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
+        <v>692</v>
+      </c>
+      <c r="C6" t="s">
         <v>693</v>
       </c>
-      <c r="C6" t="s">
-        <v>694</v>
-      </c>
       <c r="D6" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
+        <v>694</v>
+      </c>
+      <c r="C7" t="s">
         <v>695</v>
       </c>
-      <c r="C7" t="s">
-        <v>696</v>
-      </c>
       <c r="D7" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C8" t="s">
+        <v>697</v>
+      </c>
+      <c r="D8" t="s">
         <v>698</v>
-      </c>
-      <c r="D8" t="s">
-        <v>699</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
+        <v>702</v>
+      </c>
+      <c r="C14" t="s">
         <v>703</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>704</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>705</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>706</v>
-      </c>
-      <c r="F14" t="s">
-        <v>707</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C15">
         <v>109</v>
@@ -6585,7 +6928,7 @@
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C16">
         <v>25</v>
@@ -6602,7 +6945,7 @@
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C17">
         <v>3</v>
@@ -6619,7 +6962,7 @@
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C18">
         <v>104</v>
@@ -6657,9 +7000,179 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="C2:R18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>896</v>
+      </c>
+      <c r="N2" t="s">
+        <v>900</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="3" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="F3" t="s">
+        <v>899</v>
+      </c>
+      <c r="G3" t="s">
+        <v>703</v>
+      </c>
+      <c r="H3" t="s">
+        <v>900</v>
+      </c>
+      <c r="N3">
+        <v>1185</v>
+      </c>
+      <c r="O3">
+        <v>20</v>
+      </c>
+      <c r="P3">
+        <f>SUM(N3:O3)</f>
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="4" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C4">
+        <v>150</v>
+      </c>
+      <c r="D4">
+        <v>150</v>
+      </c>
+      <c r="E4">
+        <v>180</v>
+      </c>
+      <c r="F4">
+        <f>SUM(C4:E4)</f>
+        <v>480</v>
+      </c>
+      <c r="G4">
+        <v>6</v>
+      </c>
+      <c r="H4">
+        <f>F4*G4</f>
+        <v>2880</v>
+      </c>
+      <c r="N4">
+        <v>1300</v>
+      </c>
+      <c r="O4">
+        <v>20</v>
+      </c>
+      <c r="P4">
+        <f>SUM(N4:O4)</f>
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="5" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="P5">
+        <f>P3+P4</f>
+        <v>2525</v>
+      </c>
+      <c r="Q5">
+        <f>P5/100</f>
+        <v>25.25</v>
+      </c>
+      <c r="R5">
+        <f>Q5/2.5</f>
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="7" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="8" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C8">
+        <v>150</v>
+      </c>
+      <c r="D8">
+        <v>150</v>
+      </c>
+      <c r="E8">
+        <v>90</v>
+      </c>
+      <c r="F8">
+        <f>SUM(C8:E8)</f>
+        <v>390</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+      <c r="H8">
+        <f>F8*G8</f>
+        <v>780</v>
+      </c>
+    </row>
+    <row r="10" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="11" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C11">
+        <v>235</v>
+      </c>
+      <c r="D11">
+        <v>235</v>
+      </c>
+      <c r="E11">
+        <v>180</v>
+      </c>
+      <c r="F11">
+        <f>SUM(C11:E11)</f>
+        <v>650</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <f>F11*G11</f>
+        <v>650</v>
+      </c>
+    </row>
+    <row r="12" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>550</v>
+      </c>
+      <c r="H12">
+        <f>SUM(H4:H11)</f>
+        <v>4310</v>
+      </c>
+      <c r="I12">
+        <f>H12/100</f>
+        <v>43.1</v>
+      </c>
+      <c r="J12">
+        <f>I12/2.4</f>
+        <v>17.958333333333336</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C18">
+        <f>210+50+50</f>
+        <v>310</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:I537"/>
+  <dimension ref="B3:I553"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="85.28515625" customWidth="1"/>
@@ -10512,6 +11025,9 @@
       <c r="F233" s="9"/>
     </row>
     <row r="234" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B234">
+        <v>230</v>
+      </c>
       <c r="C234" t="s">
         <v>421</v>
       </c>
@@ -10524,6 +11040,9 @@
       <c r="F234" s="9"/>
     </row>
     <row r="235" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B235">
+        <v>231</v>
+      </c>
       <c r="C235" s="42" t="s">
         <v>422</v>
       </c>
@@ -10536,6 +11055,9 @@
       <c r="F235" s="9"/>
     </row>
     <row r="236" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B236">
+        <v>232</v>
+      </c>
       <c r="C236" t="s">
         <v>423</v>
       </c>
@@ -10548,6 +11070,9 @@
       <c r="F236" s="9"/>
     </row>
     <row r="237" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B237">
+        <v>233</v>
+      </c>
       <c r="C237" s="42" t="s">
         <v>424</v>
       </c>
@@ -10560,6 +11085,9 @@
       <c r="F237" s="9"/>
     </row>
     <row r="238" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B238">
+        <v>234</v>
+      </c>
       <c r="C238" s="42" t="s">
         <v>425</v>
       </c>
@@ -10572,6 +11100,9 @@
       <c r="F238" s="9"/>
     </row>
     <row r="239" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B239">
+        <v>235</v>
+      </c>
       <c r="C239" t="s">
         <v>426</v>
       </c>
@@ -10584,6 +11115,9 @@
       <c r="F239" s="9"/>
     </row>
     <row r="240" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B240">
+        <v>236</v>
+      </c>
       <c r="C240" s="18" t="s">
         <v>427</v>
       </c>
@@ -10597,7 +11131,10 @@
         <v>45880</v>
       </c>
     </row>
-    <row r="241" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="241" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B241">
+        <v>237</v>
+      </c>
       <c r="C241" s="18" t="s">
         <v>428</v>
       </c>
@@ -10611,7 +11148,10 @@
         <v>45880</v>
       </c>
     </row>
-    <row r="242" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="242" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B242">
+        <v>238</v>
+      </c>
       <c r="C242" s="18" t="s">
         <v>429</v>
       </c>
@@ -10625,7 +11165,10 @@
         <v>45880</v>
       </c>
     </row>
-    <row r="243" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="243" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B243">
+        <v>239</v>
+      </c>
       <c r="C243" s="18" t="s">
         <v>430</v>
       </c>
@@ -10639,7 +11182,10 @@
         <v>45882</v>
       </c>
     </row>
-    <row r="244" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="244" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B244">
+        <v>240</v>
+      </c>
       <c r="C244" s="18" t="s">
         <v>431</v>
       </c>
@@ -10653,7 +11199,10 @@
         <v>45882</v>
       </c>
     </row>
-    <row r="245" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="245" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B245">
+        <v>241</v>
+      </c>
       <c r="C245" s="18" t="s">
         <v>432</v>
       </c>
@@ -10667,7 +11216,10 @@
         <v>45882</v>
       </c>
     </row>
-    <row r="246" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="246" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B246">
+        <v>242</v>
+      </c>
       <c r="C246" s="18" t="s">
         <v>433</v>
       </c>
@@ -10681,7 +11233,10 @@
         <v>45882</v>
       </c>
     </row>
-    <row r="247" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="247" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B247">
+        <v>243</v>
+      </c>
       <c r="C247" t="s">
         <v>434</v>
       </c>
@@ -10695,7 +11250,10 @@
         <v>45879</v>
       </c>
     </row>
-    <row r="248" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="248" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B248">
+        <v>244</v>
+      </c>
       <c r="C248" t="s">
         <v>436</v>
       </c>
@@ -10709,7 +11267,10 @@
         <v>45879</v>
       </c>
     </row>
-    <row r="249" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="249" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B249">
+        <v>245</v>
+      </c>
       <c r="C249" t="s">
         <v>437</v>
       </c>
@@ -10723,7 +11284,10 @@
         <v>45879</v>
       </c>
     </row>
-    <row r="250" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="250" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B250">
+        <v>246</v>
+      </c>
       <c r="C250" t="s">
         <v>438</v>
       </c>
@@ -10737,7 +11301,10 @@
         <v>45879</v>
       </c>
     </row>
-    <row r="251" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="251" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B251">
+        <v>247</v>
+      </c>
       <c r="C251" s="18" t="s">
         <v>440</v>
       </c>
@@ -10751,7 +11318,10 @@
         <v>45886</v>
       </c>
     </row>
-    <row r="252" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="252" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B252">
+        <v>248</v>
+      </c>
       <c r="C252" s="18" t="s">
         <v>441</v>
       </c>
@@ -10765,7 +11335,10 @@
         <v>45886</v>
       </c>
     </row>
-    <row r="253" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="253" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B253">
+        <v>249</v>
+      </c>
       <c r="C253" s="18" t="s">
         <v>442</v>
       </c>
@@ -10779,7 +11352,10 @@
         <v>45886</v>
       </c>
     </row>
-    <row r="254" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="254" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B254">
+        <v>250</v>
+      </c>
       <c r="C254" t="s">
         <v>465</v>
       </c>
@@ -10793,7 +11369,10 @@
         <v>45913</v>
       </c>
     </row>
-    <row r="255" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="255" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B255">
+        <v>251</v>
+      </c>
       <c r="C255" t="s">
         <v>466</v>
       </c>
@@ -10807,7 +11386,10 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="256" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="256" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B256">
+        <v>252</v>
+      </c>
       <c r="C256" t="s">
         <v>468</v>
       </c>
@@ -10821,7 +11403,10 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="257" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B257">
+        <v>253</v>
+      </c>
       <c r="C257" s="18" t="s">
         <v>469</v>
       </c>
@@ -10835,7 +11420,10 @@
         <v>45916</v>
       </c>
     </row>
-    <row r="258" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B258">
+        <v>254</v>
+      </c>
       <c r="C258" s="18" t="s">
         <v>470</v>
       </c>
@@ -10849,7 +11437,10 @@
         <v>45916</v>
       </c>
     </row>
-    <row r="259" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B259">
+        <v>255</v>
+      </c>
       <c r="C259" s="18" t="s">
         <v>471</v>
       </c>
@@ -10863,7 +11454,10 @@
         <v>45916</v>
       </c>
     </row>
-    <row r="260" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="260" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B260">
+        <v>256</v>
+      </c>
       <c r="C260" s="18" t="s">
         <v>431</v>
       </c>
@@ -10877,7 +11471,10 @@
         <v>45916</v>
       </c>
     </row>
-    <row r="261" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B261">
+        <v>257</v>
+      </c>
       <c r="C261" s="18" t="s">
         <v>472</v>
       </c>
@@ -10891,7 +11488,10 @@
         <v>45916</v>
       </c>
     </row>
-    <row r="262" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="262" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B262">
+        <v>258</v>
+      </c>
       <c r="C262" t="s">
         <v>473</v>
       </c>
@@ -10905,7 +11505,10 @@
         <v>45916</v>
       </c>
     </row>
-    <row r="263" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B263">
+        <v>259</v>
+      </c>
       <c r="C263" s="18" t="s">
         <v>475</v>
       </c>
@@ -10916,7 +11519,10 @@
         <v>45917</v>
       </c>
     </row>
-    <row r="264" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B264">
+        <v>260</v>
+      </c>
       <c r="C264" s="18" t="s">
         <v>476</v>
       </c>
@@ -10927,7 +11533,10 @@
         <v>45917</v>
       </c>
     </row>
-    <row r="265" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B265">
+        <v>261</v>
+      </c>
       <c r="C265" s="18" t="s">
         <v>477</v>
       </c>
@@ -10941,7 +11550,10 @@
         <v>45917</v>
       </c>
     </row>
-    <row r="266" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B266">
+        <v>262</v>
+      </c>
       <c r="C266" t="s">
         <v>479</v>
       </c>
@@ -10955,7 +11567,10 @@
         <v>45917</v>
       </c>
     </row>
-    <row r="267" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B267">
+        <v>263</v>
+      </c>
       <c r="C267" s="18" t="s">
         <v>475</v>
       </c>
@@ -10969,7 +11584,10 @@
         <v>45919</v>
       </c>
     </row>
-    <row r="268" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B268">
+        <v>264</v>
+      </c>
       <c r="C268" s="18" t="s">
         <v>481</v>
       </c>
@@ -10983,7 +11601,10 @@
         <v>45919</v>
       </c>
     </row>
-    <row r="269" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B269">
+        <v>265</v>
+      </c>
       <c r="C269" s="18" t="s">
         <v>482</v>
       </c>
@@ -10997,7 +11618,10 @@
         <v>45919</v>
       </c>
     </row>
-    <row r="270" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B270">
+        <v>266</v>
+      </c>
       <c r="C270" s="18" t="s">
         <v>483</v>
       </c>
@@ -11011,7 +11635,10 @@
         <v>45919</v>
       </c>
     </row>
-    <row r="271" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="271" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B271">
+        <v>267</v>
+      </c>
       <c r="C271" s="18" t="s">
         <v>484</v>
       </c>
@@ -11025,7 +11652,10 @@
         <v>45919</v>
       </c>
     </row>
-    <row r="272" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="272" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B272">
+        <v>268</v>
+      </c>
       <c r="C272" s="18" t="s">
         <v>485</v>
       </c>
@@ -11039,7 +11669,10 @@
         <v>45919</v>
       </c>
     </row>
-    <row r="273" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B273">
+        <v>269</v>
+      </c>
       <c r="C273" s="18" t="s">
         <v>488</v>
       </c>
@@ -11053,7 +11686,10 @@
         <v>45920</v>
       </c>
     </row>
-    <row r="274" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B274">
+        <v>270</v>
+      </c>
       <c r="C274" s="18" t="s">
         <v>489</v>
       </c>
@@ -11067,7 +11703,10 @@
         <v>45920</v>
       </c>
     </row>
-    <row r="275" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B275">
+        <v>271</v>
+      </c>
       <c r="C275" s="18" t="s">
         <v>490</v>
       </c>
@@ -11081,7 +11720,10 @@
         <v>45920</v>
       </c>
     </row>
-    <row r="276" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B276">
+        <v>272</v>
+      </c>
       <c r="C276" s="18" t="s">
         <v>469</v>
       </c>
@@ -11095,7 +11737,10 @@
         <v>45921</v>
       </c>
     </row>
-    <row r="277" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B277">
+        <v>273</v>
+      </c>
       <c r="C277" s="18" t="s">
         <v>469</v>
       </c>
@@ -11109,7 +11754,10 @@
         <v>45921</v>
       </c>
     </row>
-    <row r="278" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B278">
+        <v>274</v>
+      </c>
       <c r="C278" s="18" t="s">
         <v>469</v>
       </c>
@@ -11123,7 +11771,10 @@
         <v>45923</v>
       </c>
     </row>
-    <row r="279" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B279">
+        <v>275</v>
+      </c>
       <c r="C279" s="18" t="s">
         <v>491</v>
       </c>
@@ -11137,7 +11788,10 @@
         <v>45929</v>
       </c>
     </row>
-    <row r="280" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="280" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B280">
+        <v>276</v>
+      </c>
       <c r="C280" s="18" t="s">
         <v>425</v>
       </c>
@@ -11151,7 +11805,10 @@
         <v>45929</v>
       </c>
     </row>
-    <row r="281" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="281" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B281">
+        <v>277</v>
+      </c>
       <c r="C281" s="18" t="s">
         <v>425</v>
       </c>
@@ -11165,7 +11822,10 @@
         <v>45933</v>
       </c>
     </row>
-    <row r="282" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B282">
+        <v>278</v>
+      </c>
       <c r="C282" t="s">
         <v>493</v>
       </c>
@@ -11179,7 +11839,10 @@
         <v>45946</v>
       </c>
     </row>
-    <row r="283" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B283">
+        <v>279</v>
+      </c>
       <c r="C283" t="s">
         <v>494</v>
       </c>
@@ -11193,7 +11856,10 @@
         <v>45947</v>
       </c>
     </row>
-    <row r="284" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B284">
+        <v>280</v>
+      </c>
       <c r="C284" t="s">
         <v>495</v>
       </c>
@@ -11207,7 +11873,10 @@
         <v>45947</v>
       </c>
     </row>
-    <row r="285" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B285">
+        <v>281</v>
+      </c>
       <c r="C285" t="s">
         <v>496</v>
       </c>
@@ -11221,7 +11890,10 @@
         <v>45947</v>
       </c>
     </row>
-    <row r="286" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B286">
+        <v>282</v>
+      </c>
       <c r="C286" t="s">
         <v>381</v>
       </c>
@@ -11235,7 +11907,10 @@
         <v>45947</v>
       </c>
     </row>
-    <row r="287" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B287">
+        <v>283</v>
+      </c>
       <c r="C287" t="s">
         <v>498</v>
       </c>
@@ -11249,7 +11924,10 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="288" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="288" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B288">
+        <v>284</v>
+      </c>
       <c r="C288" t="s">
         <v>499</v>
       </c>
@@ -11263,7 +11941,10 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="289" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="289" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B289">
+        <v>285</v>
+      </c>
       <c r="C289" s="18" t="s">
         <v>431</v>
       </c>
@@ -11277,7 +11958,10 @@
         <v>45952</v>
       </c>
     </row>
-    <row r="290" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="290" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B290">
+        <v>286</v>
+      </c>
       <c r="C290" s="18" t="s">
         <v>500</v>
       </c>
@@ -11291,7 +11975,10 @@
         <v>45952</v>
       </c>
     </row>
-    <row r="291" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B291">
+        <v>287</v>
+      </c>
       <c r="C291" s="18" t="s">
         <v>501</v>
       </c>
@@ -11305,7 +11992,10 @@
         <v>45952</v>
       </c>
     </row>
-    <row r="292" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="292" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B292">
+        <v>288</v>
+      </c>
       <c r="C292" t="s">
         <v>502</v>
       </c>
@@ -11319,7 +12009,10 @@
         <v>45953</v>
       </c>
     </row>
-    <row r="293" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="293" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B293">
+        <v>289</v>
+      </c>
       <c r="C293" t="s">
         <v>504</v>
       </c>
@@ -11333,7 +12026,10 @@
         <v>45954</v>
       </c>
     </row>
-    <row r="294" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="294" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B294">
+        <v>290</v>
+      </c>
       <c r="C294" t="s">
         <v>506</v>
       </c>
@@ -11347,7 +12043,10 @@
         <v>45954</v>
       </c>
     </row>
-    <row r="295" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="295" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B295">
+        <v>291</v>
+      </c>
       <c r="C295" t="s">
         <v>510</v>
       </c>
@@ -11361,7 +12060,10 @@
         <v>45968</v>
       </c>
     </row>
-    <row r="296" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="296" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B296">
+        <v>292</v>
+      </c>
       <c r="C296" t="s">
         <v>508</v>
       </c>
@@ -11375,7 +12077,10 @@
         <v>45968</v>
       </c>
     </row>
-    <row r="297" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="297" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B297">
+        <v>293</v>
+      </c>
       <c r="C297" t="s">
         <v>511</v>
       </c>
@@ -11389,7 +12094,10 @@
         <v>45967</v>
       </c>
     </row>
-    <row r="298" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="298" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B298">
+        <v>294</v>
+      </c>
       <c r="C298" s="18" t="s">
         <v>512</v>
       </c>
@@ -11403,7 +12111,10 @@
         <v>45972</v>
       </c>
     </row>
-    <row r="299" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="299" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B299">
+        <v>295</v>
+      </c>
       <c r="C299" t="s">
         <v>513</v>
       </c>
@@ -11417,7 +12128,10 @@
         <v>45974</v>
       </c>
     </row>
-    <row r="300" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="300" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B300">
+        <v>296</v>
+      </c>
       <c r="C300" s="18" t="s">
         <v>515</v>
       </c>
@@ -11431,7 +12145,10 @@
         <v>45979</v>
       </c>
     </row>
-    <row r="301" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="301" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B301">
+        <v>297</v>
+      </c>
       <c r="C301" s="18" t="s">
         <v>516</v>
       </c>
@@ -11445,7 +12162,10 @@
         <v>45979</v>
       </c>
     </row>
-    <row r="302" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="302" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B302">
+        <v>298</v>
+      </c>
       <c r="C302" s="18" t="s">
         <v>517</v>
       </c>
@@ -11459,7 +12179,10 @@
         <v>45984</v>
       </c>
     </row>
-    <row r="303" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="303" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B303">
+        <v>299</v>
+      </c>
       <c r="C303" t="s">
         <v>518</v>
       </c>
@@ -11473,7 +12196,10 @@
         <v>45995</v>
       </c>
     </row>
-    <row r="304" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="304" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B304">
+        <v>300</v>
+      </c>
       <c r="C304" t="s">
         <v>519</v>
       </c>
@@ -11487,7 +12213,10 @@
         <v>45995</v>
       </c>
     </row>
-    <row r="305" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="305" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B305">
+        <v>301</v>
+      </c>
       <c r="C305" t="s">
         <v>520</v>
       </c>
@@ -11501,7 +12230,10 @@
         <v>45995</v>
       </c>
     </row>
-    <row r="306" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="306" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B306">
+        <v>302</v>
+      </c>
       <c r="C306" s="18" t="s">
         <v>521</v>
       </c>
@@ -11515,7 +12247,10 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="307" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="307" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B307">
+        <v>303</v>
+      </c>
       <c r="C307" s="18" t="s">
         <v>522</v>
       </c>
@@ -11529,7 +12264,10 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="308" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="308" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B308">
+        <v>304</v>
+      </c>
       <c r="C308" s="18" t="s">
         <v>523</v>
       </c>
@@ -11543,7 +12281,10 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="309" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="309" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B309">
+        <v>305</v>
+      </c>
       <c r="C309" s="18" t="s">
         <v>524</v>
       </c>
@@ -11557,7 +12298,10 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="310" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="310" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B310">
+        <v>306</v>
+      </c>
       <c r="C310" s="18" t="s">
         <v>525</v>
       </c>
@@ -11571,7 +12315,10 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="311" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="311" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B311">
+        <v>307</v>
+      </c>
       <c r="C311" s="18" t="s">
         <v>526</v>
       </c>
@@ -11585,7 +12332,10 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="312" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="312" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B312">
+        <v>308</v>
+      </c>
       <c r="C312" t="s">
         <v>527</v>
       </c>
@@ -11599,7 +12349,10 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="313" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="313" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B313">
+        <v>309</v>
+      </c>
       <c r="C313" t="s">
         <v>528</v>
       </c>
@@ -11613,7 +12366,10 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="314" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="314" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B314">
+        <v>310</v>
+      </c>
       <c r="C314" t="s">
         <v>529</v>
       </c>
@@ -11627,7 +12383,10 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="315" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="315" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B315">
+        <v>311</v>
+      </c>
       <c r="C315" s="18" t="s">
         <v>533</v>
       </c>
@@ -11641,7 +12400,10 @@
         <v>46014</v>
       </c>
     </row>
-    <row r="316" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="316" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B316">
+        <v>312</v>
+      </c>
       <c r="C316" s="18" t="s">
         <v>534</v>
       </c>
@@ -11655,7 +12417,10 @@
         <v>46014</v>
       </c>
     </row>
-    <row r="317" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="317" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B317">
+        <v>313</v>
+      </c>
       <c r="C317" s="18" t="s">
         <v>535</v>
       </c>
@@ -11669,7 +12434,10 @@
         <v>46014</v>
       </c>
     </row>
-    <row r="318" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="318" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B318">
+        <v>314</v>
+      </c>
       <c r="C318" s="18" t="s">
         <v>536</v>
       </c>
@@ -11683,7 +12451,10 @@
         <v>46014</v>
       </c>
     </row>
-    <row r="319" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="319" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B319">
+        <v>315</v>
+      </c>
       <c r="C319" t="s">
         <v>610</v>
       </c>
@@ -11697,7 +12468,10 @@
         <v>46073</v>
       </c>
     </row>
-    <row r="320" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="320" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B320">
+        <v>316</v>
+      </c>
       <c r="C320" t="s">
         <v>611</v>
       </c>
@@ -11712,6 +12486,9 @@
       </c>
     </row>
     <row r="321" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B321">
+        <v>317</v>
+      </c>
       <c r="C321" t="s">
         <v>612</v>
       </c>
@@ -11726,6 +12503,9 @@
       </c>
     </row>
     <row r="322" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B322">
+        <v>318</v>
+      </c>
       <c r="C322" t="s">
         <v>613</v>
       </c>
@@ -11740,6 +12520,9 @@
       </c>
     </row>
     <row r="323" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B323">
+        <v>319</v>
+      </c>
       <c r="C323" t="s">
         <v>614</v>
       </c>
@@ -11754,6 +12537,9 @@
       </c>
     </row>
     <row r="324" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B324">
+        <v>320</v>
+      </c>
       <c r="C324" t="s">
         <v>615</v>
       </c>
@@ -11768,6 +12554,9 @@
       </c>
     </row>
     <row r="325" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B325">
+        <v>321</v>
+      </c>
       <c r="C325" t="s">
         <v>616</v>
       </c>
@@ -11775,13 +12564,16 @@
         <v>2471</v>
       </c>
       <c r="E325" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="F325" s="9">
         <v>46071</v>
       </c>
     </row>
     <row r="326" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B326">
+        <v>322</v>
+      </c>
       <c r="C326" t="s">
         <v>617</v>
       </c>
@@ -11789,13 +12581,16 @@
         <v>3700</v>
       </c>
       <c r="E326" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="F326" s="9">
         <v>46071</v>
       </c>
     </row>
     <row r="327" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B327">
+        <v>323</v>
+      </c>
       <c r="C327" t="s">
         <v>618</v>
       </c>
@@ -11803,13 +12598,16 @@
         <v>473</v>
       </c>
       <c r="E327" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="F327" s="9">
         <v>46071</v>
       </c>
     </row>
     <row r="328" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B328">
+        <v>324</v>
+      </c>
       <c r="C328" t="s">
         <v>619</v>
       </c>
@@ -11817,15 +12615,15 @@
         <v>2040</v>
       </c>
       <c r="E328" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="F328" s="9">
         <v>46070</v>
       </c>
     </row>
     <row r="329" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B329" t="s">
-        <v>621</v>
+      <c r="B329">
+        <v>325</v>
       </c>
       <c r="C329" t="s">
         <v>620</v>
@@ -11834,29 +12632,35 @@
         <v>348</v>
       </c>
       <c r="E329" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="F329" s="9">
         <v>46070</v>
       </c>
     </row>
     <row r="330" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B330">
+        <v>326</v>
+      </c>
       <c r="C330" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D330" s="7">
         <v>988</v>
       </c>
       <c r="E330" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="F330" s="9">
         <v>46084</v>
       </c>
     </row>
     <row r="331" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B331">
+        <v>327</v>
+      </c>
       <c r="C331" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D331" s="7">
         <v>8000</v>
@@ -11869,64 +12673,79 @@
       </c>
     </row>
     <row r="332" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B332">
+        <v>328</v>
+      </c>
       <c r="C332" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D332" s="7">
         <v>1215</v>
       </c>
       <c r="E332" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="F332" s="9">
         <v>46085</v>
       </c>
     </row>
     <row r="333" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B333">
+        <v>329</v>
+      </c>
       <c r="C333" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D333" s="7">
         <v>3275</v>
       </c>
       <c r="E333" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="F333" s="9">
         <v>46085</v>
       </c>
     </row>
     <row r="334" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B334">
+        <v>330</v>
+      </c>
       <c r="C334" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D334" s="7">
         <v>677</v>
       </c>
       <c r="E334" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="F334" s="9">
         <v>46080</v>
       </c>
     </row>
     <row r="335" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B335">
+        <v>331</v>
+      </c>
       <c r="C335" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D335" s="7">
         <v>1123</v>
       </c>
       <c r="E335" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="F335" s="9">
         <v>46079</v>
       </c>
     </row>
     <row r="336" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B336">
+        <v>332</v>
+      </c>
       <c r="C336" s="18" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D336" s="7">
         <v>127.78</v>
@@ -11938,9 +12757,12 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="337" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="337" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B337">
+        <v>333</v>
+      </c>
       <c r="C337" s="18" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D337" s="7">
         <v>450</v>
@@ -11952,9 +12774,12 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="338" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B338">
+        <v>334</v>
+      </c>
       <c r="C338" s="18" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D338" s="7">
         <v>182</v>
@@ -11966,9 +12791,12 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="339" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="339" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B339">
+        <v>335</v>
+      </c>
       <c r="C339" s="18" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D339" s="7">
         <v>228.89</v>
@@ -11980,9 +12808,12 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="340" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="340" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B340">
+        <v>336</v>
+      </c>
       <c r="C340" s="18" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D340" s="7">
         <v>228.89</v>
@@ -11994,9 +12825,12 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="341" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="341" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B341">
+        <v>337</v>
+      </c>
       <c r="C341" s="18" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D341" s="7">
         <v>102</v>
@@ -12008,9 +12842,12 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="342" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="342" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B342">
+        <v>338</v>
+      </c>
       <c r="C342" s="18" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D342" s="7">
         <v>116.15</v>
@@ -12022,9 +12859,12 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="343" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="343" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B343">
+        <v>339</v>
+      </c>
       <c r="C343" s="18" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D343" s="7">
         <v>224.2</v>
@@ -12036,23 +12876,29 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="344" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="344" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B344">
+        <v>340</v>
+      </c>
       <c r="C344" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D344" s="7">
         <v>845</v>
       </c>
       <c r="E344" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="F344" s="9">
         <v>46105</v>
       </c>
     </row>
-    <row r="345" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="345" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B345">
+        <v>341</v>
+      </c>
       <c r="C345" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D345" s="7">
         <v>898</v>
@@ -12064,9 +12910,12 @@
         <v>46105</v>
       </c>
     </row>
-    <row r="346" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="346" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B346">
+        <v>342</v>
+      </c>
       <c r="C346" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D346" s="7">
         <v>444</v>
@@ -12078,9 +12927,12 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="347" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="347" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B347">
+        <v>343</v>
+      </c>
       <c r="C347" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D347" s="7">
         <v>179</v>
@@ -12092,9 +12944,12 @@
         <v>46107</v>
       </c>
     </row>
-    <row r="348" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="348" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B348">
+        <v>344</v>
+      </c>
       <c r="C348" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D348" s="7">
         <v>98</v>
@@ -12106,9 +12961,12 @@
         <v>46107</v>
       </c>
     </row>
-    <row r="349" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="349" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B349">
+        <v>345</v>
+      </c>
       <c r="C349" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D349" s="7">
         <v>374</v>
@@ -12120,9 +12978,12 @@
         <v>46107</v>
       </c>
     </row>
-    <row r="350" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="350" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B350">
+        <v>346</v>
+      </c>
       <c r="C350" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D350" s="7">
         <v>271</v>
@@ -12134,9 +12995,12 @@
         <v>46110</v>
       </c>
     </row>
-    <row r="351" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="351" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B351">
+        <v>347</v>
+      </c>
       <c r="C351" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D351" s="7">
         <v>57</v>
@@ -12148,9 +13012,12 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="352" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="352" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B352">
+        <v>348</v>
+      </c>
       <c r="C352" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D352" s="7">
         <v>1100</v>
@@ -12162,9 +13029,12 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="353" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="353" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B353">
+        <v>349</v>
+      </c>
       <c r="C353" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D353" s="7">
         <v>756</v>
@@ -12176,9 +13046,12 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="354" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B354">
+        <v>350</v>
+      </c>
       <c r="C354" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D354" s="7">
         <v>358</v>
@@ -12190,7 +13063,10 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="355" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="355" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B355">
+        <v>351</v>
+      </c>
       <c r="C355" t="s">
         <v>187</v>
       </c>
@@ -12204,7 +13080,10 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="356" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B356">
+        <v>352</v>
+      </c>
       <c r="C356" t="s">
         <v>44</v>
       </c>
@@ -12212,114 +13091,138 @@
         <v>4000</v>
       </c>
       <c r="E356" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="F356" s="9">
         <v>46113</v>
       </c>
     </row>
-    <row r="357" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="357" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B357">
+        <v>353</v>
+      </c>
       <c r="C357" s="54" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D357" s="7">
         <v>6138</v>
       </c>
       <c r="E357" s="52" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F357" s="9">
         <v>46119</v>
       </c>
       <c r="I357" s="7"/>
     </row>
-    <row r="358" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="358" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B358">
+        <v>354</v>
+      </c>
       <c r="C358" s="54" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D358" s="7">
         <v>8890</v>
       </c>
       <c r="E358" s="52" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F358" s="9">
         <v>46119</v>
       </c>
     </row>
-    <row r="359" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="359" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B359">
+        <v>355</v>
+      </c>
       <c r="C359" s="54" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D359" s="7">
         <v>17960</v>
       </c>
       <c r="E359" s="52" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F359" s="9">
         <v>46119</v>
       </c>
     </row>
-    <row r="360" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="360" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B360">
+        <v>356</v>
+      </c>
       <c r="C360" s="53" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D360" s="7">
         <v>529</v>
       </c>
       <c r="E360" s="52" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F360" s="9">
         <v>46119</v>
       </c>
     </row>
-    <row r="361" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="361" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B361">
+        <v>357</v>
+      </c>
       <c r="C361" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="D361" s="7">
         <v>1092.22</v>
       </c>
       <c r="E361" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F361" s="9">
         <v>46123</v>
       </c>
     </row>
-    <row r="362" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="362" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B362">
+        <v>358</v>
+      </c>
       <c r="C362" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D362" s="7">
         <v>16.489999999999998</v>
       </c>
       <c r="E362" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F362" s="9">
         <v>46123</v>
       </c>
     </row>
-    <row r="363" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="363" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B363">
+        <v>359</v>
+      </c>
       <c r="C363" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D363" s="7">
         <v>183</v>
       </c>
       <c r="E363" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F363" s="9">
         <v>46123</v>
       </c>
     </row>
-    <row r="364" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="364" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B364">
+        <v>360</v>
+      </c>
       <c r="C364" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D364" s="7">
         <v>792</v>
@@ -12331,9 +13234,12 @@
         <v>46124</v>
       </c>
     </row>
-    <row r="365" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="365" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B365">
+        <v>361</v>
+      </c>
       <c r="C365" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="D365" s="7">
         <v>136</v>
@@ -12345,9 +13251,12 @@
         <v>46124</v>
       </c>
     </row>
-    <row r="366" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="366" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B366">
+        <v>362</v>
+      </c>
       <c r="C366" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D366" s="7">
         <v>101</v>
@@ -12359,9 +13268,12 @@
         <v>46124</v>
       </c>
     </row>
-    <row r="367" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="367" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B367">
+        <v>363</v>
+      </c>
       <c r="C367" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="D367" s="7">
         <v>72</v>
@@ -12373,9 +13285,12 @@
         <v>46124</v>
       </c>
     </row>
-    <row r="368" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="368" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B368">
+        <v>364</v>
+      </c>
       <c r="C368" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="D368" s="7">
         <v>164</v>
@@ -12387,9 +13302,12 @@
         <v>46127</v>
       </c>
     </row>
-    <row r="369" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="369" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B369">
+        <v>365</v>
+      </c>
       <c r="C369" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D369" s="7">
         <v>162</v>
@@ -12401,9 +13319,12 @@
         <v>46127</v>
       </c>
     </row>
-    <row r="370" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="370" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B370">
+        <v>366</v>
+      </c>
       <c r="C370" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="D370" s="7">
         <v>42510</v>
@@ -12415,9 +13336,12 @@
         <v>46132</v>
       </c>
     </row>
-    <row r="371" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="371" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B371">
+        <v>367</v>
+      </c>
       <c r="C371" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D371" s="7">
         <v>39000</v>
@@ -12429,9 +13353,12 @@
         <v>46132</v>
       </c>
     </row>
-    <row r="372" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="372" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B372">
+        <v>368</v>
+      </c>
       <c r="C372" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D372" s="7">
         <v>3510</v>
@@ -12443,9 +13370,12 @@
         <v>46132</v>
       </c>
     </row>
-    <row r="373" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="373" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B373">
+        <v>369</v>
+      </c>
       <c r="C373" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="D373" s="7">
         <v>20280</v>
@@ -12457,23 +13387,29 @@
         <v>46132</v>
       </c>
     </row>
-    <row r="374" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="374" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B374">
+        <v>370</v>
+      </c>
       <c r="C374" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D374" s="7">
         <v>6000</v>
       </c>
       <c r="E374" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F374" s="9">
         <v>46132</v>
       </c>
     </row>
-    <row r="375" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="375" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B375">
+        <v>371</v>
+      </c>
       <c r="C375" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D375" s="7">
         <v>259.95999999999998</v>
@@ -12485,9 +13421,12 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="376" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="376" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B376">
+        <v>372</v>
+      </c>
       <c r="C376" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D376" s="7">
         <v>183</v>
@@ -12499,9 +13438,12 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="377" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="377" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B377">
+        <v>373</v>
+      </c>
       <c r="C377" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D377" s="7">
         <v>251.23</v>
@@ -12513,9 +13455,12 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="378" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="378" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B378">
+        <v>374</v>
+      </c>
       <c r="C378" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D378" s="7">
         <v>1092.22</v>
@@ -12527,9 +13472,12 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="379" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="379" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B379">
+        <v>375</v>
+      </c>
       <c r="C379" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D379" s="7">
         <v>182.22</v>
@@ -12541,7 +13489,10 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="380" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="380" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B380">
+        <v>376</v>
+      </c>
       <c r="C380" t="s">
         <v>525</v>
       </c>
@@ -12555,9 +13506,12 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="381" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="381" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B381">
+        <v>377</v>
+      </c>
       <c r="C381" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D381" s="7">
         <v>108.6</v>
@@ -12569,9 +13523,12 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="382" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="382" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B382">
+        <v>378</v>
+      </c>
       <c r="C382" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D382" s="7">
         <v>323.95999999999998</v>
@@ -12583,65 +13540,80 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="383" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="383" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B383">
+        <v>379</v>
+      </c>
       <c r="C383" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D383" s="7">
         <v>175</v>
       </c>
       <c r="E383" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="F383" s="9">
         <v>46139</v>
       </c>
     </row>
-    <row r="384" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="384" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B384">
+        <v>380</v>
+      </c>
       <c r="C384" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D384" s="7">
         <v>109</v>
       </c>
       <c r="E384" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="F384" s="9">
         <v>46139</v>
       </c>
     </row>
-    <row r="385" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="385" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B385">
+        <v>381</v>
+      </c>
       <c r="C385" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D385" s="7">
         <v>171</v>
       </c>
       <c r="E385" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="F385" s="9">
         <v>46139</v>
       </c>
     </row>
-    <row r="386" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="386" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B386">
+        <v>382</v>
+      </c>
       <c r="C386" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D386" s="7">
         <v>196</v>
       </c>
       <c r="E386" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="F386" s="9">
         <v>46139</v>
       </c>
     </row>
-    <row r="387" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="387" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B387">
+        <v>383</v>
+      </c>
       <c r="C387" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D387" s="7">
         <v>480.8</v>
@@ -12653,9 +13625,12 @@
         <v>46144</v>
       </c>
     </row>
-    <row r="388" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="388" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B388">
+        <v>384</v>
+      </c>
       <c r="C388" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="D388" s="7">
         <v>182.47</v>
@@ -12667,9 +13642,12 @@
         <v>46144</v>
       </c>
     </row>
-    <row r="389" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="389" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B389">
+        <v>385</v>
+      </c>
       <c r="C389" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D389" s="7">
         <v>547.41</v>
@@ -12681,37 +13659,46 @@
         <v>46144</v>
       </c>
     </row>
-    <row r="390" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="390" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B390">
+        <v>386</v>
+      </c>
       <c r="C390" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D390" s="7">
         <v>29640</v>
       </c>
       <c r="E390" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="F390" s="9">
         <v>46147</v>
       </c>
     </row>
-    <row r="391" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="391" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B391">
+        <v>387</v>
+      </c>
       <c r="C391" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D391" s="7">
         <v>1560</v>
       </c>
       <c r="E391" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="F391" s="9">
         <v>46147</v>
       </c>
     </row>
-    <row r="392" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="392" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B392">
+        <v>388</v>
+      </c>
       <c r="C392" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D392" s="7">
         <v>3000</v>
@@ -12723,9 +13710,12 @@
         <v>46147</v>
       </c>
     </row>
-    <row r="393" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="393" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B393">
+        <v>389</v>
+      </c>
       <c r="C393" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D393" s="7">
         <v>57.94</v>
@@ -12737,9 +13727,12 @@
         <v>46149</v>
       </c>
     </row>
-    <row r="394" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="394" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B394">
+        <v>390</v>
+      </c>
       <c r="C394" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D394" s="7">
         <v>98.67</v>
@@ -12751,9 +13744,12 @@
         <v>46149</v>
       </c>
     </row>
-    <row r="395" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="395" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B395">
+        <v>391</v>
+      </c>
       <c r="C395" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D395" s="7">
         <v>152.08000000000001</v>
@@ -12765,9 +13761,12 @@
         <v>46149</v>
       </c>
     </row>
-    <row r="396" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="396" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B396">
+        <v>392</v>
+      </c>
       <c r="C396" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D396" s="7">
         <v>207.31</v>
@@ -12779,9 +13778,12 @@
         <v>46149</v>
       </c>
     </row>
-    <row r="397" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="397" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B397">
+        <v>393</v>
+      </c>
       <c r="C397" s="18" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D397" s="7">
         <v>899</v>
@@ -12793,9 +13795,12 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="398" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="398" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B398">
+        <v>394</v>
+      </c>
       <c r="C398" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D398" s="7">
         <v>1196</v>
@@ -12807,9 +13812,12 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="399" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="399" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B399">
+        <v>395</v>
+      </c>
       <c r="C399" s="18" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D399" s="7">
         <v>238</v>
@@ -12821,9 +13829,12 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="400" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="400" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B400">
+        <v>396</v>
+      </c>
       <c r="C400" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D400" s="7">
         <v>9164.33</v>
@@ -12835,9 +13846,12 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="401" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="401" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B401">
+        <v>397</v>
+      </c>
       <c r="C401" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D401" s="7">
         <v>8507.39</v>
@@ -12849,9 +13863,12 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="402" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="402" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B402">
+        <v>398</v>
+      </c>
       <c r="C402" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="D402" s="7">
         <v>890.85</v>
@@ -12863,9 +13880,12 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="403" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="403" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B403">
+        <v>399</v>
+      </c>
       <c r="C403" s="18" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D403" s="7">
         <v>1570.68</v>
@@ -12877,9 +13897,12 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="404" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="404" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B404">
+        <v>400</v>
+      </c>
       <c r="C404" s="18" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D404" s="7">
         <v>2780.06</v>
@@ -12891,9 +13914,12 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="405" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="405" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B405">
+        <v>401</v>
+      </c>
       <c r="C405" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D405" s="7">
         <v>1570.7</v>
@@ -12905,7 +13931,10 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="406" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="406" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B406">
+        <v>402</v>
+      </c>
       <c r="C406" s="18" t="s">
         <v>426</v>
       </c>
@@ -12919,23 +13948,29 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="407" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="407" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B407">
+        <v>403</v>
+      </c>
       <c r="C407" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D407" s="7">
         <v>1900</v>
       </c>
       <c r="E407" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F407" s="9">
         <v>46164</v>
       </c>
     </row>
-    <row r="408" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="408" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B408">
+        <v>404</v>
+      </c>
       <c r="C408" s="18" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D408" s="7">
         <v>277.24</v>
@@ -12947,9 +13982,12 @@
         <v>46165</v>
       </c>
     </row>
-    <row r="409" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="409" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B409">
+        <v>405</v>
+      </c>
       <c r="C409" s="18" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D409" s="7">
         <v>110.62</v>
@@ -12961,35 +13999,44 @@
         <v>46165</v>
       </c>
     </row>
-    <row r="410" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="410" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B410">
+        <v>406</v>
+      </c>
       <c r="C410" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="D410" s="7">
         <v>7414</v>
       </c>
       <c r="E410" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="F410" s="9">
         <v>46165</v>
       </c>
     </row>
-    <row r="411" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="411" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B411">
+        <v>407</v>
+      </c>
       <c r="C411" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="D411" s="7">
         <v>81</v>
       </c>
       <c r="E411" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="F411" s="9">
         <v>46165</v>
       </c>
     </row>
-    <row r="412" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="412" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B412">
+        <v>408</v>
+      </c>
       <c r="C412" t="s">
         <v>209</v>
       </c>
@@ -12997,15 +14044,18 @@
         <v>670</v>
       </c>
       <c r="E412" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="F412" s="9">
         <v>46165</v>
       </c>
     </row>
-    <row r="413" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="413" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B413">
+        <v>409</v>
+      </c>
       <c r="C413" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="D413" s="7">
         <v>548.04999999999995</v>
@@ -13017,9 +14067,12 @@
         <v>46165</v>
       </c>
     </row>
-    <row r="414" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="414" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B414">
+        <v>410</v>
+      </c>
       <c r="C414" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="D414" s="7">
         <v>703.25</v>
@@ -13031,9 +14084,12 @@
         <v>46165</v>
       </c>
     </row>
-    <row r="415" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="415" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B415">
+        <v>411</v>
+      </c>
       <c r="C415" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D415" s="7">
         <v>960.3</v>
@@ -13045,9 +14101,12 @@
         <v>46165</v>
       </c>
     </row>
-    <row r="416" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="416" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B416">
+        <v>412</v>
+      </c>
       <c r="C416" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="D416" s="7">
         <v>348.23</v>
@@ -13059,9 +14118,12 @@
         <v>46165</v>
       </c>
     </row>
-    <row r="417" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="417" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B417">
+        <v>413</v>
+      </c>
       <c r="C417" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="D417" s="7">
         <v>3841.2</v>
@@ -13073,9 +14135,12 @@
         <v>46165</v>
       </c>
     </row>
-    <row r="418" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="418" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B418">
+        <v>414</v>
+      </c>
       <c r="C418" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="D418" s="7">
         <v>192.06</v>
@@ -13087,9 +14152,12 @@
         <v>46165</v>
       </c>
     </row>
-    <row r="419" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="419" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B419">
+        <v>415</v>
+      </c>
       <c r="C419" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D419" s="7">
         <v>1203.43</v>
@@ -13101,9 +14169,12 @@
         <v>46168</v>
       </c>
     </row>
-    <row r="420" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="420" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B420">
+        <v>416</v>
+      </c>
       <c r="C420" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D420" s="7">
         <v>649.45000000000005</v>
@@ -13115,9 +14186,12 @@
         <v>46168</v>
       </c>
     </row>
-    <row r="421" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="421" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B421">
+        <v>417</v>
+      </c>
       <c r="C421" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D421" s="7">
         <v>246.12</v>
@@ -13129,9 +14203,12 @@
         <v>46168</v>
       </c>
     </row>
-    <row r="422" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="422" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B422">
+        <v>418</v>
+      </c>
       <c r="C422" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D422" s="7">
         <v>384.89</v>
@@ -13143,9 +14220,12 @@
         <v>46169</v>
       </c>
     </row>
-    <row r="423" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="423" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B423">
+        <v>419</v>
+      </c>
       <c r="C423" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D423" s="7">
         <v>257.56</v>
@@ -13157,9 +14237,12 @@
         <v>46169</v>
       </c>
     </row>
-    <row r="424" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="424" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B424">
+        <v>420</v>
+      </c>
       <c r="C424" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D424" s="7">
         <v>622.17999999999995</v>
@@ -13171,9 +14254,12 @@
         <v>46169</v>
       </c>
     </row>
-    <row r="425" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="425" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B425">
+        <v>421</v>
+      </c>
       <c r="C425" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D425" s="7">
         <v>120.58</v>
@@ -13185,9 +14271,12 @@
         <v>46169</v>
       </c>
     </row>
-    <row r="426" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="426" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B426">
+        <v>422</v>
+      </c>
       <c r="C426" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="D426" s="7">
         <v>192.94</v>
@@ -13199,9 +14288,12 @@
         <v>46169</v>
       </c>
     </row>
-    <row r="427" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="427" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B427">
+        <v>423</v>
+      </c>
       <c r="C427" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="D427" s="7">
         <v>336.65</v>
@@ -13213,9 +14305,12 @@
         <v>46169</v>
       </c>
     </row>
-    <row r="428" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="428" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B428">
+        <v>424</v>
+      </c>
       <c r="C428" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D428" s="7">
         <v>376.2</v>
@@ -13227,9 +14322,12 @@
         <v>46169</v>
       </c>
     </row>
-    <row r="429" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="429" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B429">
+        <v>425</v>
+      </c>
       <c r="C429" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="D429" s="7">
         <v>399</v>
@@ -13241,9 +14339,12 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="430" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="430" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B430">
+        <v>426</v>
+      </c>
       <c r="C430" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="D430" s="7">
         <v>1250</v>
@@ -13255,9 +14356,12 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="431" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="431" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B431">
+        <v>427</v>
+      </c>
       <c r="C431" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="D431" s="7">
         <v>500</v>
@@ -13269,9 +14373,12 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="432" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="432" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B432">
+        <v>428</v>
+      </c>
       <c r="C432" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D432" s="7">
         <f xml:space="preserve"> 290.4 * 4</f>
@@ -13284,9 +14391,12 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="433" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="433" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B433">
+        <v>429</v>
+      </c>
       <c r="C433" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="D433" s="7">
         <f>28.17*4</f>
@@ -13299,9 +14409,12 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="434" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="434" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B434">
+        <v>430</v>
+      </c>
       <c r="C434" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="D434" s="7">
         <f>105.87*4</f>
@@ -13314,7 +14427,10 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="435" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="435" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B435">
+        <v>431</v>
+      </c>
       <c r="C435" s="18" t="s">
         <v>440</v>
       </c>
@@ -13328,9 +14444,12 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="436" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="436" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B436">
+        <v>432</v>
+      </c>
       <c r="C436" s="18" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="D436" s="7">
         <f>(13+18)*34.96</f>
@@ -13343,65 +14462,80 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="437" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="437" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B437">
+        <v>433</v>
+      </c>
       <c r="C437" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="D437" s="7">
         <v>441993.2</v>
       </c>
       <c r="E437" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="F437" s="9">
         <v>46169</v>
       </c>
     </row>
-    <row r="438" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="438" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B438">
+        <v>434</v>
+      </c>
       <c r="C438" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="D438" s="7">
         <v>47851.75</v>
       </c>
       <c r="E438" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="F438" s="9">
         <v>46169</v>
       </c>
     </row>
-    <row r="439" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="439" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B439">
+        <v>435</v>
+      </c>
       <c r="C439" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="D439" s="7">
-        <v>200000</v>
-      </c>
-      <c r="E439" s="55">
-        <v>0.5</v>
+        <v>400000</v>
+      </c>
+      <c r="E439" s="56" t="s">
+        <v>922</v>
       </c>
       <c r="F439" s="9">
         <v>46173</v>
       </c>
     </row>
-    <row r="440" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="440" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B440">
+        <v>436</v>
+      </c>
       <c r="C440" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="D440" s="7">
         <v>6000</v>
       </c>
       <c r="E440" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="F440" s="9">
         <v>46174</v>
       </c>
     </row>
-    <row r="441" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="441" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B441">
+        <v>437</v>
+      </c>
       <c r="C441" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="D441" s="7">
         <v>88.82</v>
@@ -13413,9 +14547,12 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="442" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="442" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B442">
+        <v>438</v>
+      </c>
       <c r="C442" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="D442" s="7">
         <f>357.97*2</f>
@@ -13428,7 +14565,10 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="443" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="443" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B443">
+        <v>439</v>
+      </c>
       <c r="C443" t="s">
         <v>434</v>
       </c>
@@ -13442,9 +14582,12 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="444" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="444" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B444">
+        <v>440</v>
+      </c>
       <c r="C444" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="D444" s="7">
         <v>191.02</v>
@@ -13456,9 +14599,12 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="445" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="445" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B445">
+        <v>441</v>
+      </c>
       <c r="C445" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="D445" s="7">
         <v>723.98</v>
@@ -13470,9 +14616,12 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="446" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="446" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B446">
+        <v>442</v>
+      </c>
       <c r="C446" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="D446" s="7">
         <f>7*91.47</f>
@@ -13485,9 +14634,12 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="447" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="447" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B447">
+        <v>443</v>
+      </c>
       <c r="C447" s="18" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D447" s="7">
         <f>4*174.18</f>
@@ -13500,49 +14652,61 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="448" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="448" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B448">
+        <v>444</v>
+      </c>
       <c r="C448" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D448" s="7">
         <v>6592.4</v>
       </c>
       <c r="E448" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="F448" s="9"/>
     </row>
-    <row r="449" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="449" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B449">
+        <v>445</v>
+      </c>
       <c r="C449" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D449" s="7">
         <v>500</v>
       </c>
       <c r="E449" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="F449" s="9">
         <v>46178</v>
       </c>
     </row>
-    <row r="450" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="450" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B450">
+        <v>446</v>
+      </c>
       <c r="C450" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D450" s="7">
         <v>6630</v>
       </c>
       <c r="E450" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="F450" s="9">
         <v>46181</v>
       </c>
     </row>
-    <row r="451" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="451" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B451">
+        <v>447</v>
+      </c>
       <c r="C451" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D451" s="7">
         <v>279</v>
@@ -13554,9 +14718,12 @@
         <v>46182</v>
       </c>
     </row>
-    <row r="452" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="452" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B452">
+        <v>448</v>
+      </c>
       <c r="C452" s="18" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="D452" s="7">
         <v>179</v>
@@ -13568,9 +14735,12 @@
         <v>46189</v>
       </c>
     </row>
-    <row r="453" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="453" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B453">
+        <v>449</v>
+      </c>
       <c r="C453" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="D453" s="7">
         <v>199</v>
@@ -13582,9 +14752,12 @@
         <v>46189</v>
       </c>
     </row>
-    <row r="454" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="454" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B454">
+        <v>450</v>
+      </c>
       <c r="C454" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D454" s="7">
         <v>199</v>
@@ -13596,7 +14769,10 @@
         <v>46189</v>
       </c>
     </row>
-    <row r="455" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="455" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B455">
+        <v>451</v>
+      </c>
       <c r="C455" t="s">
         <v>428</v>
       </c>
@@ -13610,7 +14786,10 @@
         <v>46189</v>
       </c>
     </row>
-    <row r="456" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="456" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B456">
+        <v>452</v>
+      </c>
       <c r="C456" t="s">
         <v>429</v>
       </c>
@@ -13624,7 +14803,10 @@
         <v>46189</v>
       </c>
     </row>
-    <row r="457" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="457" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B457">
+        <v>453</v>
+      </c>
       <c r="C457" t="s">
         <v>373</v>
       </c>
@@ -13638,49 +14820,61 @@
         <v>46189</v>
       </c>
     </row>
-    <row r="458" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="458" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B458">
+        <v>454</v>
+      </c>
       <c r="C458" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="D458" s="7">
         <v>2511</v>
       </c>
       <c r="E458" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="F458" s="9">
         <v>46189</v>
       </c>
     </row>
-    <row r="459" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="459" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B459">
+        <v>455</v>
+      </c>
       <c r="C459" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="D459" s="7">
         <v>51210</v>
       </c>
       <c r="E459" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="F459" s="9">
         <v>46194</v>
       </c>
     </row>
-    <row r="460" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="460" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B460">
+        <v>456</v>
+      </c>
       <c r="C460" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="D460" s="7">
         <v>5390</v>
       </c>
       <c r="E460" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="F460" s="9">
         <v>46194</v>
       </c>
     </row>
-    <row r="461" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="461" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B461">
+        <v>457</v>
+      </c>
       <c r="C461" t="s">
         <v>209</v>
       </c>
@@ -13688,325 +14882,394 @@
         <v>2030</v>
       </c>
       <c r="E461" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="F461" s="9">
         <v>46194</v>
       </c>
     </row>
-    <row r="462" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="462" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B462">
+        <v>458</v>
+      </c>
       <c r="C462" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="D462" s="7">
         <v>43.65</v>
       </c>
       <c r="E462" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="F462" s="9">
         <v>46197</v>
       </c>
     </row>
-    <row r="463" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="463" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B463">
+        <v>459</v>
+      </c>
       <c r="C463" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="D463" s="7">
         <v>65.92</v>
       </c>
       <c r="E463" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="F463" s="9">
         <v>46197</v>
       </c>
     </row>
-    <row r="464" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="464" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B464">
+        <v>460</v>
+      </c>
       <c r="C464" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="D464" s="7">
         <v>257.43</v>
       </c>
       <c r="E464" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="F464" s="9">
         <v>46197</v>
       </c>
     </row>
-    <row r="465" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="465" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B465">
+        <v>461</v>
+      </c>
       <c r="C465" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="D465" s="7">
         <v>174</v>
       </c>
       <c r="E465" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="F465" s="9">
         <v>46198</v>
       </c>
     </row>
-    <row r="466" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="466" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B466">
+        <v>462</v>
+      </c>
       <c r="C466" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="D466" s="7">
         <v>45</v>
       </c>
       <c r="E466" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="F466" s="9">
         <v>46208</v>
       </c>
     </row>
-    <row r="467" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="467" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B467">
+        <v>463</v>
+      </c>
       <c r="C467" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="D467" s="7">
         <v>229</v>
       </c>
       <c r="E467" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="F467" s="9">
         <v>46208</v>
       </c>
     </row>
-    <row r="468" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="468" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B468">
+        <v>464</v>
+      </c>
       <c r="C468" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D468" s="7">
         <v>209</v>
       </c>
       <c r="E468" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="F468" s="9">
         <v>46208</v>
       </c>
     </row>
-    <row r="469" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="469" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B469">
+        <v>465</v>
+      </c>
       <c r="C469" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="D469" s="7">
         <v>249</v>
       </c>
       <c r="E469" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="F469" s="9">
         <v>46208</v>
       </c>
     </row>
-    <row r="470" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="470" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B470">
+        <v>466</v>
+      </c>
       <c r="C470" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="D470" s="7">
         <v>74</v>
       </c>
       <c r="E470" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="F470" s="9">
         <v>46208</v>
       </c>
     </row>
-    <row r="471" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="471" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B471">
+        <v>467</v>
+      </c>
       <c r="C471" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="D471" s="7">
         <v>180</v>
       </c>
       <c r="E471" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="F471" s="9">
         <v>46208</v>
       </c>
     </row>
-    <row r="472" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="472" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B472">
+        <v>468</v>
+      </c>
       <c r="C472" s="18" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="D472" s="7">
         <v>218.52</v>
       </c>
       <c r="E472" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="F472" s="9">
         <v>46210</v>
       </c>
     </row>
-    <row r="473" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="473" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B473">
+        <v>469</v>
+      </c>
       <c r="C473" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="D473" s="7">
         <v>174.62</v>
       </c>
       <c r="E473" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="F473" s="9">
         <v>46210</v>
       </c>
     </row>
-    <row r="474" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="474" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B474">
+        <v>470</v>
+      </c>
       <c r="C474" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="D474" s="7">
         <v>125.85</v>
       </c>
       <c r="E474" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="F474" s="9">
         <v>46210</v>
       </c>
     </row>
-    <row r="475" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="475" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B475">
+        <v>471</v>
+      </c>
       <c r="C475" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="D475" s="7">
         <f xml:space="preserve"> 42.93 + 42.92</f>
         <v>85.85</v>
       </c>
       <c r="E475" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="F475" s="9">
         <v>46210</v>
       </c>
     </row>
-    <row r="476" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="476" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B476">
+        <v>472</v>
+      </c>
       <c r="C476" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="D476" s="7">
         <v>106.33</v>
       </c>
       <c r="E476" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="F476" s="9">
         <v>46210</v>
       </c>
     </row>
-    <row r="477" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="477" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B477">
+        <v>473</v>
+      </c>
       <c r="C477" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="D477" s="7">
         <v>174.62</v>
       </c>
       <c r="E477" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="F477" s="9">
         <v>46210</v>
       </c>
     </row>
-    <row r="478" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="478" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B478">
+        <v>474</v>
+      </c>
       <c r="C478" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="D478" s="7">
         <v>77.069999999999993</v>
       </c>
       <c r="E478" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="F478" s="9">
         <v>46210</v>
       </c>
     </row>
-    <row r="479" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="479" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B479">
+        <v>475</v>
+      </c>
       <c r="C479" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="D479" s="7">
         <v>291.69</v>
       </c>
       <c r="E479" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="F479" s="9">
         <v>46210</v>
       </c>
     </row>
-    <row r="480" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="480" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B480">
+        <v>476</v>
+      </c>
       <c r="C480" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="D480" s="7">
         <f xml:space="preserve"> 125.85 *3</f>
         <v>377.54999999999995</v>
       </c>
       <c r="E480" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="F480" s="9">
         <v>46210</v>
       </c>
     </row>
-    <row r="481" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="481" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B481">
+        <v>477</v>
+      </c>
       <c r="C481" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="D481" s="7">
         <v>135.6</v>
       </c>
       <c r="E481" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="F481" s="9">
         <v>46210</v>
       </c>
     </row>
-    <row r="482" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="482" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B482">
+        <v>478</v>
+      </c>
       <c r="C482" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D482" s="7">
         <v>67.31</v>
       </c>
       <c r="E482" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="F482" s="9">
         <v>46210</v>
       </c>
     </row>
-    <row r="483" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="483" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B483">
+        <v>479</v>
+      </c>
       <c r="C483" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="D483" s="7">
         <v>319865.36</v>
       </c>
       <c r="E483" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="F483" s="9">
         <v>46196</v>
       </c>
     </row>
-    <row r="484" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="484" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B484">
+        <v>480</v>
+      </c>
       <c r="C484" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="D484" s="7">
         <v>298.48</v>
@@ -14018,9 +15281,12 @@
         <v>46214</v>
       </c>
     </row>
-    <row r="485" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="485" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B485">
+        <v>481</v>
+      </c>
       <c r="C485" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="D485" s="7">
         <v>791.13</v>
@@ -14032,9 +15298,12 @@
         <v>46214</v>
       </c>
     </row>
-    <row r="486" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="486" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B486">
+        <v>482</v>
+      </c>
       <c r="C486" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="D486" s="7">
         <v>462.7</v>
@@ -14046,9 +15315,12 @@
         <v>46214</v>
       </c>
     </row>
-    <row r="487" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="487" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B487">
+        <v>483</v>
+      </c>
       <c r="C487" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="D487" s="7">
         <v>76.31</v>
@@ -14060,9 +15332,12 @@
         <v>46214</v>
       </c>
     </row>
-    <row r="488" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="488" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B488">
+        <v>484</v>
+      </c>
       <c r="C488" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="D488" s="7">
         <v>211.55</v>
@@ -14074,9 +15349,12 @@
         <v>46214</v>
       </c>
     </row>
-    <row r="489" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="489" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B489">
+        <v>485</v>
+      </c>
       <c r="C489" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="D489" s="7">
         <v>91.77</v>
@@ -14088,9 +15366,12 @@
         <v>46214</v>
       </c>
     </row>
-    <row r="490" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="490" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B490">
+        <v>486</v>
+      </c>
       <c r="C490" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="D490" s="7">
         <v>100.46</v>
@@ -14102,9 +15383,12 @@
         <v>46214</v>
       </c>
     </row>
-    <row r="491" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="491" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B491">
+        <v>487</v>
+      </c>
       <c r="C491" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="D491" s="7">
         <v>39.6</v>
@@ -14116,9 +15400,12 @@
         <v>46214</v>
       </c>
     </row>
-    <row r="492" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="492" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B492">
+        <v>488</v>
+      </c>
       <c r="C492" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="D492" s="7">
         <v>16176</v>
@@ -14130,9 +15417,12 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="493" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="493" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B493">
+        <v>489</v>
+      </c>
       <c r="C493" s="18" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="D493" s="7">
         <v>2200</v>
@@ -14144,9 +15434,12 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="494" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="494" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B494">
+        <v>490</v>
+      </c>
       <c r="C494" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="D494" s="7">
         <v>3050</v>
@@ -14158,9 +15451,12 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="495" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="495" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B495">
+        <v>491</v>
+      </c>
       <c r="C495" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="D495" s="7">
         <v>2990</v>
@@ -14172,9 +15468,12 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="496" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="496" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B496">
+        <v>492</v>
+      </c>
       <c r="C496" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="D496" s="7">
         <v>1980</v>
@@ -14186,7 +15485,10 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="497" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="497" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B497">
+        <v>493</v>
+      </c>
       <c r="C497" t="s">
         <v>426</v>
       </c>
@@ -14200,37 +15502,46 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="498" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="498" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B498">
+        <v>494</v>
+      </c>
       <c r="C498" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="D498" s="7">
         <v>17000</v>
       </c>
       <c r="E498" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="F498" s="9">
         <v>46217</v>
       </c>
     </row>
-    <row r="499" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="499" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B499">
+        <v>495</v>
+      </c>
       <c r="C499" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="D499" s="7">
         <v>25000</v>
       </c>
       <c r="E499" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="F499" s="9">
         <v>46220</v>
       </c>
     </row>
-    <row r="500" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="500" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B500">
+        <v>496</v>
+      </c>
       <c r="C500" s="18" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="D500" s="7">
         <v>249</v>
@@ -14242,9 +15553,12 @@
         <v>46221</v>
       </c>
     </row>
-    <row r="501" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="501" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B501">
+        <v>497</v>
+      </c>
       <c r="C501" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="D501" s="7">
         <v>259</v>
@@ -14256,9 +15570,12 @@
         <v>46221</v>
       </c>
     </row>
-    <row r="502" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="502" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B502">
+        <v>498</v>
+      </c>
       <c r="C502" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="D502" s="7">
         <v>205</v>
@@ -14270,23 +15587,29 @@
         <v>46221</v>
       </c>
     </row>
-    <row r="503" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="503" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B503">
+        <v>499</v>
+      </c>
       <c r="C503" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="D503" s="7">
         <v>5000</v>
       </c>
       <c r="E503" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="F503" s="9">
         <v>46219</v>
       </c>
     </row>
-    <row r="504" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="504" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B504">
+        <v>500</v>
+      </c>
       <c r="C504" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="D504" s="7">
         <f xml:space="preserve"> 224.43 * 2</f>
@@ -14299,9 +15622,12 @@
         <v>46222</v>
       </c>
     </row>
-    <row r="505" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="505" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B505">
+        <v>501</v>
+      </c>
       <c r="C505" s="11" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="D505" s="7">
         <v>48.33</v>
@@ -14313,9 +15639,12 @@
         <v>46222</v>
       </c>
     </row>
-    <row r="506" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="506" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B506">
+        <v>502</v>
+      </c>
       <c r="C506" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="D506" s="7">
         <v>427.22</v>
@@ -14327,9 +15656,12 @@
         <v>46222</v>
       </c>
     </row>
-    <row r="507" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="507" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B507">
+        <v>503</v>
+      </c>
       <c r="C507" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D507" s="7">
         <v>573.6</v>
@@ -14341,65 +15673,80 @@
         <v>46222</v>
       </c>
     </row>
-    <row r="508" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="508" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B508">
+        <v>504</v>
+      </c>
       <c r="C508" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="D508" s="7">
         <v>26000</v>
       </c>
       <c r="E508" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="F508" s="9">
         <v>46222</v>
       </c>
     </row>
-    <row r="509" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="509" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B509">
+        <v>505</v>
+      </c>
       <c r="C509" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="D509" s="7">
         <v>4833</v>
       </c>
       <c r="E509" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="F509" s="9">
         <v>46225</v>
       </c>
     </row>
-    <row r="510" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="510" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B510">
+        <v>506</v>
+      </c>
       <c r="C510" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D510" s="7">
         <v>1814</v>
       </c>
       <c r="E510" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="F510" s="9">
         <v>46226</v>
       </c>
     </row>
-    <row r="511" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="511" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B511">
+        <v>507</v>
+      </c>
       <c r="C511" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="D511" s="7">
-        <v>4055</v>
+        <v>3678</v>
       </c>
       <c r="E511" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="F511" s="9">
         <v>46228</v>
       </c>
     </row>
-    <row r="512" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="512" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B512">
+        <v>508</v>
+      </c>
       <c r="C512" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="D512" s="7">
         <v>216</v>
@@ -14411,9 +15758,12 @@
         <v>46228</v>
       </c>
     </row>
-    <row r="513" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C513" s="56" t="s">
-        <v>857</v>
+    <row r="513" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B513">
+        <v>509</v>
+      </c>
+      <c r="C513" s="55" t="s">
+        <v>856</v>
       </c>
       <c r="D513" s="7">
         <v>16666</v>
@@ -14421,11 +15771,16 @@
       <c r="E513" t="s">
         <v>232</v>
       </c>
-      <c r="F513" s="9"/>
-    </row>
-    <row r="514" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="F513" s="9">
+        <v>46243</v>
+      </c>
+    </row>
+    <row r="514" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B514">
+        <v>510</v>
+      </c>
       <c r="C514" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="D514" s="7">
         <v>343</v>
@@ -14437,9 +15792,12 @@
         <v>46225</v>
       </c>
     </row>
-    <row r="515" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="515" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B515">
+        <v>511</v>
+      </c>
       <c r="C515" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="D515" s="7">
         <v>1367</v>
@@ -14451,9 +15809,12 @@
         <v>46228</v>
       </c>
     </row>
-    <row r="516" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="516" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B516">
+        <v>512</v>
+      </c>
       <c r="C516" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="D516" s="7">
         <v>608</v>
@@ -14465,21 +15826,27 @@
         <v>46230</v>
       </c>
     </row>
-    <row r="517" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="517" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B517">
+        <v>513</v>
+      </c>
       <c r="C517" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="D517" s="7">
         <v>1755</v>
       </c>
       <c r="E517" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="F517" s="9">
         <v>46230</v>
       </c>
     </row>
-    <row r="518" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="518" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B518">
+        <v>514</v>
+      </c>
       <c r="C518" t="s">
         <v>473</v>
       </c>
@@ -14487,158 +15854,191 @@
         <v>12000</v>
       </c>
       <c r="E518" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="F518" s="9">
         <v>46230</v>
       </c>
     </row>
-    <row r="519" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="519" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B519">
+        <v>515</v>
+      </c>
       <c r="C519" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="D519" s="7">
         <v>74439</v>
       </c>
       <c r="E519" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="F519" s="9">
         <v>46230</v>
       </c>
     </row>
-    <row r="520" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="520" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B520">
+        <v>516</v>
+      </c>
       <c r="C520" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="D520" s="7">
         <v>117306</v>
       </c>
       <c r="E520" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="F520" s="9">
         <v>46230</v>
       </c>
     </row>
-    <row r="521" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="521" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B521">
+        <v>517</v>
+      </c>
       <c r="C521" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="D521" s="7">
         <v>2700</v>
       </c>
       <c r="E521" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="F521" s="9">
         <v>46230</v>
       </c>
     </row>
-    <row r="522" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="522" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B522">
+        <v>518</v>
+      </c>
       <c r="C522" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="D522" s="7">
         <f>8115.85+4698.76</f>
         <v>12814.61</v>
       </c>
       <c r="E522" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="F522" s="9">
         <v>46234</v>
       </c>
     </row>
-    <row r="523" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="523" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B523">
+        <v>519</v>
+      </c>
       <c r="C523" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="D523" s="7">
         <f>17173.51+592.2</f>
         <v>17765.71</v>
       </c>
       <c r="E523" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="F523" s="9">
         <v>46234</v>
       </c>
     </row>
-    <row r="524" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="524" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B524">
+        <v>520</v>
+      </c>
       <c r="C524" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="D524" s="7">
         <v>6972.3</v>
       </c>
       <c r="E524" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="F524" s="9">
         <v>46234</v>
       </c>
     </row>
-    <row r="525" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="525" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B525">
+        <v>521</v>
+      </c>
       <c r="C525" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="D525" s="7">
         <v>774.72</v>
       </c>
       <c r="E525" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="F525" s="9">
         <v>46234</v>
       </c>
     </row>
-    <row r="526" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="526" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B526">
+        <v>522</v>
+      </c>
       <c r="C526" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="D526" s="7">
         <f>8708.1+2902.71</f>
         <v>11610.810000000001</v>
       </c>
       <c r="E526" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="F526" s="9">
         <v>46234</v>
       </c>
     </row>
-    <row r="527" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="527" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B527">
+        <v>523</v>
+      </c>
       <c r="C527" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="D527" s="7">
         <f>5*90.28</f>
         <v>451.4</v>
       </c>
       <c r="E527" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="F527" s="9">
         <v>46234</v>
       </c>
     </row>
-    <row r="528" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="528" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B528">
+        <v>524</v>
+      </c>
       <c r="C528" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="D528" s="7">
         <f>824.22*2</f>
         <v>1648.44</v>
       </c>
       <c r="E528" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="F528" s="9">
         <v>46234</v>
       </c>
     </row>
-    <row r="529" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="529" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B529">
+        <v>525</v>
+      </c>
       <c r="C529" t="s">
         <v>426</v>
       </c>
@@ -14646,78 +16046,331 @@
         <v>2510</v>
       </c>
       <c r="E529" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="F529" s="9">
         <v>46234</v>
       </c>
     </row>
-    <row r="530" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="530" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B530">
+        <v>526</v>
+      </c>
       <c r="C530" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="D530" s="7">
         <f>251.35*2</f>
         <v>502.7</v>
       </c>
       <c r="E530" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="F530" s="9">
         <v>46237</v>
       </c>
     </row>
-    <row r="531" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="531" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B531">
+        <v>527</v>
+      </c>
       <c r="C531" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="D531" s="7">
         <f>174.33*9</f>
         <v>1568.97</v>
       </c>
       <c r="E531" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="F531" s="9">
         <v>46237</v>
       </c>
     </row>
-    <row r="532" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="532" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B532">
+        <v>528</v>
+      </c>
       <c r="C532" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="D532" s="7">
         <v>118.32</v>
       </c>
       <c r="E532" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="F532" s="9">
         <v>46237</v>
       </c>
     </row>
-    <row r="533" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D533" s="7"/>
-      <c r="F533" s="9"/>
-    </row>
-    <row r="534" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D534" s="7"/>
-      <c r="F534" s="9"/>
-    </row>
-    <row r="535" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D535" s="7"/>
-      <c r="F535" s="9"/>
-    </row>
-    <row r="536" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D536" s="7"/>
-      <c r="F536" s="9"/>
-    </row>
-    <row r="537" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="533" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B533">
+        <v>529</v>
+      </c>
+      <c r="C533" t="s">
+        <v>913</v>
+      </c>
+      <c r="D533" s="7">
+        <v>153.30000000000001</v>
+      </c>
+      <c r="E533" t="s">
+        <v>885</v>
+      </c>
+      <c r="F533" s="9">
+        <v>46239</v>
+      </c>
+    </row>
+    <row r="534" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B534">
+        <v>530</v>
+      </c>
+      <c r="C534" t="s">
+        <v>914</v>
+      </c>
+      <c r="D534" s="7">
+        <v>221.2</v>
+      </c>
+      <c r="E534" t="s">
+        <v>885</v>
+      </c>
+      <c r="F534" s="9">
+        <v>46239</v>
+      </c>
+    </row>
+    <row r="535" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B535">
+        <v>531</v>
+      </c>
+      <c r="C535" t="s">
+        <v>915</v>
+      </c>
+      <c r="D535" s="7">
+        <f>147.87*20</f>
+        <v>2957.4</v>
+      </c>
+      <c r="E535" t="s">
+        <v>885</v>
+      </c>
+      <c r="F535" s="9">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="536" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B536">
+        <v>532</v>
+      </c>
+      <c r="C536" t="s">
+        <v>916</v>
+      </c>
+      <c r="D536" s="7">
+        <f>24*72.76</f>
+        <v>1746.2400000000002</v>
+      </c>
+      <c r="E536" t="s">
+        <v>885</v>
+      </c>
+      <c r="F536" s="9">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="537" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B537">
+        <v>533</v>
+      </c>
+      <c r="C537" t="s">
+        <v>917</v>
+      </c>
       <c r="D537" s="7">
+        <f>664.23*2</f>
+        <v>1328.46</v>
+      </c>
+      <c r="E537" t="s">
+        <v>885</v>
+      </c>
+      <c r="F537" s="9">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="538" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B538">
+        <v>534</v>
+      </c>
+      <c r="C538" t="s">
+        <v>918</v>
+      </c>
+      <c r="D538" s="7">
+        <v>900</v>
+      </c>
+      <c r="E538" t="s">
+        <v>885</v>
+      </c>
+      <c r="F538" s="9">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="539" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B539">
+        <v>535</v>
+      </c>
+      <c r="C539" t="s">
+        <v>919</v>
+      </c>
+      <c r="D539" s="7">
+        <v>319</v>
+      </c>
+      <c r="E539" t="s">
+        <v>885</v>
+      </c>
+      <c r="F539" s="9">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="540" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B540">
+        <v>536</v>
+      </c>
+      <c r="C540" t="s">
+        <v>920</v>
+      </c>
+      <c r="D540" s="7">
+        <f>8*248</f>
+        <v>1984</v>
+      </c>
+      <c r="E540" t="s">
+        <v>885</v>
+      </c>
+      <c r="F540" s="9">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="541" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B541">
+        <v>537</v>
+      </c>
+      <c r="C541" t="s">
+        <v>921</v>
+      </c>
+      <c r="D541" s="7">
+        <v>809</v>
+      </c>
+      <c r="E541" t="s">
+        <v>885</v>
+      </c>
+      <c r="F541" s="9">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="542" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B542">
+        <v>538</v>
+      </c>
+      <c r="C542" s="57" t="s">
+        <v>923</v>
+      </c>
+      <c r="D542" s="7">
+        <v>5352</v>
+      </c>
+      <c r="E542" t="s">
+        <v>621</v>
+      </c>
+      <c r="F542" s="9">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="543" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B543">
+        <v>539</v>
+      </c>
+      <c r="C543" t="s">
+        <v>924</v>
+      </c>
+      <c r="D543" s="7">
+        <v>1704</v>
+      </c>
+      <c r="E543" t="s">
+        <v>621</v>
+      </c>
+      <c r="F543" s="9">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="544" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B544">
+        <v>540</v>
+      </c>
+      <c r="C544" t="s">
+        <v>925</v>
+      </c>
+      <c r="D544" s="7">
+        <v>10671</v>
+      </c>
+      <c r="E544" t="s">
+        <v>372</v>
+      </c>
+      <c r="F544" s="9">
+        <v>46228</v>
+      </c>
+    </row>
+    <row r="545" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B545">
+        <v>541</v>
+      </c>
+      <c r="C545" t="s">
+        <v>926</v>
+      </c>
+      <c r="D545" s="7">
+        <f>845*4</f>
+        <v>3380</v>
+      </c>
+      <c r="E545" t="s">
+        <v>372</v>
+      </c>
+      <c r="F545" s="9">
+        <v>46228</v>
+      </c>
+    </row>
+    <row r="546" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B546">
+        <v>542</v>
+      </c>
+      <c r="D546" s="7"/>
+      <c r="F546" s="9"/>
+    </row>
+    <row r="547" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B547">
+        <v>543</v>
+      </c>
+      <c r="D547" s="7"/>
+      <c r="F547" s="9"/>
+    </row>
+    <row r="548" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D548" s="7"/>
+      <c r="F548" s="9"/>
+    </row>
+    <row r="549" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D549" s="7"/>
+      <c r="F549" s="9"/>
+    </row>
+    <row r="550" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D550" s="7"/>
+      <c r="F550" s="9"/>
+    </row>
+    <row r="551" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D551" s="7"/>
+      <c r="F551" s="9"/>
+    </row>
+    <row r="552" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D552" s="7"/>
+      <c r="F552" s="9"/>
+    </row>
+    <row r="553" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D553" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>5764049.0100000007</v>
-      </c>
-      <c r="F537" s="9"/>
+        <v>5995197.6100000013</v>
+      </c>
+      <c r="F553" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -14739,6 +16392,161 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B3:F13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="40.140625" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" customWidth="1"/>
+    <col min="4" max="4" width="39.5703125" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>343</v>
+      </c>
+      <c r="C3" t="s">
+        <v>899</v>
+      </c>
+      <c r="D3" t="s">
+        <v>903</v>
+      </c>
+      <c r="E3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>902</v>
+      </c>
+      <c r="C4">
+        <v>1160.52</v>
+      </c>
+      <c r="D4">
+        <f t="shared" ref="D4:D12" si="0">C4*2</f>
+        <v>2321.04</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>904</v>
+      </c>
+      <c r="C5">
+        <v>680</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>905</v>
+      </c>
+      <c r="C6">
+        <v>1187.5</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>2375</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>906</v>
+      </c>
+      <c r="C7">
+        <v>721.65</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>1443.3</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>907</v>
+      </c>
+      <c r="C8">
+        <v>383.66</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>767.32</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>908</v>
+      </c>
+      <c r="C9">
+        <v>1368.97</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>2737.94</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>909</v>
+      </c>
+      <c r="C10">
+        <v>1311.86</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>2623.72</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>910</v>
+      </c>
+      <c r="C11">
+        <v>1116.8699999999999</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>2233.7399999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>911</v>
+      </c>
+      <c r="C12">
+        <v>1477.63</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="0"/>
+        <v>2955.26</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>550</v>
+      </c>
+      <c r="D13">
+        <f>SUM(D4:D12)</f>
+        <v>18817.32</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>912</v>
+      </c>
+      <c r="F13">
+        <f>D13/100</f>
+        <v>188.17320000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -14755,36 +16563,36 @@
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C2" t="s">
+        <v>864</v>
+      </c>
+      <c r="D2" t="s">
         <v>865</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>866</v>
       </c>
-      <c r="E2" t="s">
-        <v>867</v>
-      </c>
       <c r="F2" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="G2" t="s">
         <v>1</v>
       </c>
       <c r="K2" t="s">
+        <v>867</v>
+      </c>
+      <c r="L2" t="s">
         <v>868</v>
       </c>
-      <c r="L2" t="s">
-        <v>869</v>
-      </c>
       <c r="M2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C3">
         <v>13</v>
@@ -14801,7 +16609,7 @@
         <v>35.39</v>
       </c>
       <c r="G3" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="K3">
         <v>1.51</v>
@@ -14816,7 +16624,7 @@
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="C4">
         <v>13</v>
@@ -14835,7 +16643,7 @@
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="C5">
         <v>11.85</v>
@@ -14851,12 +16659,12 @@
         <v>39.7605</v>
       </c>
       <c r="G5" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="C6">
         <v>11.85</v>
@@ -14873,29 +16681,29 @@
         <v>35.683500000000002</v>
       </c>
       <c r="G6" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="K6" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="L6" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="M6" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="57"/>
-      <c r="F7" s="57">
+      <c r="E7" s="56"/>
+      <c r="F7" s="56">
         <f>SUM(F3:F6)</f>
         <v>145.78900000000002</v>
       </c>
       <c r="G7" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="K7">
         <v>2.38</v>
@@ -14910,13 +16718,13 @@
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.25">
       <c r="K9" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="L9" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="M9" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">
@@ -14933,13 +16741,13 @@
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="K12" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="L12" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="M12" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.25">
@@ -14962,7 +16770,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:D18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -15097,7 +16905,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="C3:L15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -15196,7 +17004,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A3:F28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -15601,7 +17409,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:D9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -15715,7 +17523,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -16060,245 +17868,4 @@
     <tablePart r:id="rId5"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="6.42578125" customWidth="1"/>
-    <col min="2" max="2" width="42.28515625" customWidth="1"/>
-    <col min="3" max="3" width="22.28515625" customWidth="1"/>
-    <col min="4" max="4" width="56" customWidth="1"/>
-    <col min="6" max="6" width="6.85546875" customWidth="1"/>
-    <col min="7" max="7" width="43" customWidth="1"/>
-    <col min="8" max="8" width="24.5703125" customWidth="1"/>
-    <col min="9" max="9" width="62.140625" customWidth="1"/>
-    <col min="10" max="10" width="58.140625" customWidth="1"/>
-    <col min="11" max="11" width="14.140625" customWidth="1"/>
-    <col min="12" max="12" width="47.85546875" customWidth="1"/>
-    <col min="13" max="13" width="11.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="21" x14ac:dyDescent="0.35">
-      <c r="C1" s="32" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B2" s="11" t="s">
-        <v>280</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>343</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>344</v>
-      </c>
-      <c r="D3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" t="s">
-        <v>343</v>
-      </c>
-      <c r="H3" s="23" t="s">
-        <v>344</v>
-      </c>
-      <c r="I3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="23"/>
-      <c r="B4" t="s">
-        <v>345</v>
-      </c>
-      <c r="C4" s="23">
-        <v>160</v>
-      </c>
-      <c r="D4" s="29" t="s">
-        <v>349</v>
-      </c>
-      <c r="F4" s="23" t="s">
-        <v>342</v>
-      </c>
-      <c r="G4" t="s">
-        <v>345</v>
-      </c>
-      <c r="H4" s="23">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>346</v>
-      </c>
-      <c r="C5" s="31">
-        <v>100</v>
-      </c>
-      <c r="D5" t="s">
-        <v>795</v>
-      </c>
-      <c r="G5" t="s">
-        <v>346</v>
-      </c>
-      <c r="H5" s="27">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>347</v>
-      </c>
-      <c r="C6" s="27">
-        <v>65</v>
-      </c>
-      <c r="D6" t="s">
-        <v>393</v>
-      </c>
-      <c r="G6" t="s">
-        <v>347</v>
-      </c>
-      <c r="H6" s="27">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>348</v>
-      </c>
-      <c r="C7" s="28">
-        <v>20</v>
-      </c>
-      <c r="D7" t="s">
-        <v>796</v>
-      </c>
-      <c r="G7" t="s">
-        <v>348</v>
-      </c>
-      <c r="H7" s="28">
-        <v>20</v>
-      </c>
-      <c r="I7" s="29" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>797</v>
-      </c>
-      <c r="C8" s="36">
-        <v>1015</v>
-      </c>
-      <c r="D8" t="s">
-        <v>395</v>
-      </c>
-      <c r="G8" t="s">
-        <v>394</v>
-      </c>
-      <c r="H8" s="23">
-        <f>2550+H5+H6+H7</f>
-        <v>2780</v>
-      </c>
-      <c r="I8" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>396</v>
-      </c>
-      <c r="C9" s="24">
-        <v>3020</v>
-      </c>
-      <c r="G9" t="s">
-        <v>396</v>
-      </c>
-      <c r="H9" s="24">
-        <f>H8+250</f>
-        <v>3030</v>
-      </c>
-      <c r="I9" t="s">
-        <v>400</v>
-      </c>
-      <c r="K9" s="23"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H10" s="24"/>
-      <c r="K10" s="23"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F11" s="23"/>
-      <c r="K11" s="23"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F12" s="23"/>
-      <c r="K12" s="23"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D13" t="s">
-        <v>402</v>
-      </c>
-      <c r="F13" s="23"/>
-      <c r="G13" t="s">
-        <v>401</v>
-      </c>
-      <c r="H13" s="24">
-        <f>850+H5+H6+H7</f>
-        <v>1080</v>
-      </c>
-      <c r="I13" t="s">
-        <v>397</v>
-      </c>
-      <c r="K13" s="23"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F14" s="23"/>
-      <c r="K14" s="23"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F15" s="30"/>
-      <c r="K15" s="23"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F16" s="23"/>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="F17" s="23"/>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="F18" s="23"/>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="F19" s="23"/>
-      <c r="K19" s="33"/>
-      <c r="L19" s="34"/>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="F20" s="23"/>
-      <c r="K20" s="22"/>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="F21" s="23"/>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B22" s="21"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="F22" s="23"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <tableParts count="2">
-    <tablePart r:id="rId2"/>
-    <tablePart r:id="rId3"/>
-  </tableParts>
-</worksheet>
 </file>
--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -443,7 +443,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1498" uniqueCount="927">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="933">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3756,6 +3756,24 @@
   </si>
   <si>
     <t>Колцо гидрозатвора на вентиляцию 4 шт</t>
+  </si>
+  <si>
+    <t>Бутил-каучуковая лента двухстороняя - 10 рулонов</t>
+  </si>
+  <si>
+    <t>Заглушка из пенополистирола для фасадных дюбелей (упак. 500 шт.) - 2 упак</t>
+  </si>
+  <si>
+    <t>Уголок штукатурный ПВХ с пластиковой сеткой Крепикс 1300 100х150х2500 - 37 штук</t>
+  </si>
+  <si>
+    <t>Тепло Авангард +7905 246 7672. +7962 253 26 41 Игорь Сергеевич П - Сбер</t>
+  </si>
+  <si>
+    <t>17 ведёр силиконовой фасадной штукатурки (барашек) 1.5 мм фракция. 2 ведра грунта. Доставка 4000р</t>
+  </si>
+  <si>
+    <t>утепление фасада</t>
   </si>
 </sst>
 </file>
@@ -4190,6 +4208,12 @@
   </cellStyles>
   <dxfs count="37">
     <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -4238,12 +4262,6 @@
         <top/>
         <bottom/>
       </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
@@ -4603,14 +4621,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F553" totalsRowCount="1">
-  <autoFilter ref="B5:F552"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F558" totalsRowCount="1">
+  <autoFilter ref="B5:F557"/>
   <tableColumns count="5">
     <tableColumn id="1" name="№ п/п"/>
     <tableColumn id="2" name="Наименование "/>
-    <tableColumn id="3" name="Цена (руб)" totalsRowFunction="sum" dataDxfId="36" totalsRowDxfId="7"/>
+    <tableColumn id="3" name="Цена (руб)" totalsRowFunction="sum" dataDxfId="36" totalsRowDxfId="1"/>
     <tableColumn id="4" name="Примечание"/>
-    <tableColumn id="5" name="дата" dataDxfId="35" totalsRowDxfId="6"/>
+    <tableColumn id="5" name="дата" dataDxfId="35" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4818,15 +4836,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Таблица2" displayName="Таблица2" ref="A4:F28" totalsRowCount="1">
   <autoFilter ref="A4:F27"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="№ п/п" totalsRowLabel="Итого:" totalsRowDxfId="5"/>
-    <tableColumn id="2" name="Тип" totalsRowDxfId="4"/>
-    <tableColumn id="3" name="Количество (М3/шт)" totalsRowDxfId="3"/>
-    <tableColumn id="4" name="Цена  (м3 или штук)" dataDxfId="32" totalsRowDxfId="2"/>
-    <tableColumn id="5" name="Сумма" totalsRowFunction="custom" dataDxfId="31" totalsRowDxfId="1">
+    <tableColumn id="1" name="№ п/п" totalsRowLabel="Итого:" totalsRowDxfId="7"/>
+    <tableColumn id="2" name="Тип" totalsRowDxfId="6"/>
+    <tableColumn id="3" name="Количество (М3/шт)" totalsRowDxfId="5"/>
+    <tableColumn id="4" name="Цена  (м3 или штук)" dataDxfId="32" totalsRowDxfId="4"/>
+    <tableColumn id="5" name="Сумма" totalsRowFunction="custom" dataDxfId="31" totalsRowDxfId="3">
       <calculatedColumnFormula>Таблица2[[#This Row],[Цена  (м3 или штук)]]*Таблица2[[#This Row],[Количество (М3/шт)]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(E5:E27)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" name="Примечание" totalsRowDxfId="0"/>
+    <tableColumn id="6" name="Примечание" totalsRowDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7172,10 +7190,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:I553"/>
+  <dimension ref="B3:I558"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="85.28515625" customWidth="1"/>
+    <col min="3" max="3" width="94.7109375" customWidth="1"/>
     <col min="4" max="4" width="22.5703125" customWidth="1"/>
     <col min="5" max="5" width="90.85546875" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
@@ -16335,42 +16353,144 @@
       <c r="B546">
         <v>542</v>
       </c>
-      <c r="D546" s="7"/>
-      <c r="F546" s="9"/>
+      <c r="C546" t="s">
+        <v>927</v>
+      </c>
+      <c r="D546" s="7">
+        <v>6080</v>
+      </c>
+      <c r="E546" t="s">
+        <v>621</v>
+      </c>
+      <c r="F546" s="9">
+        <v>46243</v>
+      </c>
     </row>
     <row r="547" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B547">
         <v>543</v>
       </c>
-      <c r="D547" s="7"/>
-      <c r="F547" s="9"/>
+      <c r="C547" t="s">
+        <v>928</v>
+      </c>
+      <c r="D547" s="7">
+        <f>1579.75*2</f>
+        <v>3159.5</v>
+      </c>
+      <c r="E547" t="s">
+        <v>885</v>
+      </c>
+      <c r="F547" s="9">
+        <v>46243</v>
+      </c>
     </row>
     <row r="548" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D548" s="7"/>
-      <c r="F548" s="9"/>
+      <c r="B548">
+        <v>544</v>
+      </c>
+      <c r="C548" t="s">
+        <v>929</v>
+      </c>
+      <c r="D548" s="7">
+        <f>86.93*37</f>
+        <v>3216.4100000000003</v>
+      </c>
+      <c r="E548" t="s">
+        <v>885</v>
+      </c>
+      <c r="F548" s="9">
+        <v>46243</v>
+      </c>
     </row>
     <row r="549" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D549" s="7"/>
-      <c r="F549" s="9"/>
+      <c r="B549">
+        <v>545</v>
+      </c>
+      <c r="C549" t="s">
+        <v>931</v>
+      </c>
+      <c r="D549" s="7">
+        <v>80160</v>
+      </c>
+      <c r="E549" t="s">
+        <v>930</v>
+      </c>
+      <c r="F549" s="9">
+        <v>46244</v>
+      </c>
     </row>
     <row r="550" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D550" s="7"/>
-      <c r="F550" s="9"/>
+      <c r="B550">
+        <v>546</v>
+      </c>
+      <c r="C550" t="s">
+        <v>932</v>
+      </c>
+      <c r="D550" s="7">
+        <v>120000</v>
+      </c>
+      <c r="E550" t="s">
+        <v>843</v>
+      </c>
+      <c r="F550" s="9">
+        <v>46244</v>
+      </c>
     </row>
     <row r="551" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B551">
+        <v>547</v>
+      </c>
       <c r="D551" s="7"/>
       <c r="F551" s="9"/>
     </row>
     <row r="552" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B552">
+        <v>548</v>
+      </c>
       <c r="D552" s="7"/>
       <c r="F552" s="9"/>
     </row>
     <row r="553" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D553" s="7">
+      <c r="B553">
+        <v>549</v>
+      </c>
+      <c r="D553" s="7"/>
+      <c r="F553" s="9"/>
+    </row>
+    <row r="554" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B554">
+        <v>550</v>
+      </c>
+      <c r="D554" s="7"/>
+      <c r="F554" s="9"/>
+    </row>
+    <row r="555" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B555">
+        <v>551</v>
+      </c>
+      <c r="D555" s="7"/>
+      <c r="F555" s="9"/>
+    </row>
+    <row r="556" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B556">
+        <v>552</v>
+      </c>
+      <c r="D556" s="7"/>
+      <c r="F556" s="9"/>
+    </row>
+    <row r="557" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B557">
+        <v>553</v>
+      </c>
+      <c r="D557" s="7"/>
+      <c r="F557" s="9"/>
+    </row>
+    <row r="558" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D558" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>5995197.6100000013</v>
-      </c>
-      <c r="F553" s="9"/>
+        <v>6207813.5200000014</v>
+      </c>
+      <c r="F558" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -443,7 +443,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="933">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="937">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3774,6 +3774,18 @@
   </si>
   <si>
     <t>утепление фасада</t>
+  </si>
+  <si>
+    <t>саморез по дер 3,5х25мм 500 шт</t>
+  </si>
+  <si>
+    <t>Клей-пена DONEWELL Мощная хватка</t>
+  </si>
+  <si>
+    <t>ВИПЛАСТ Московский проспект 184</t>
+  </si>
+  <si>
+    <t>Водоотлив антрацит (0.5) 6 шт 181 см х 17,5 см, 91 см х 17,5 см -2 шт</t>
   </si>
 </sst>
 </file>
@@ -16440,22 +16452,52 @@
       <c r="B551">
         <v>547</v>
       </c>
-      <c r="D551" s="7"/>
-      <c r="F551" s="9"/>
+      <c r="C551" t="s">
+        <v>933</v>
+      </c>
+      <c r="D551" s="7">
+        <v>498</v>
+      </c>
+      <c r="E551" t="s">
+        <v>885</v>
+      </c>
+      <c r="F551" s="9">
+        <v>46246</v>
+      </c>
     </row>
     <row r="552" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B552">
         <v>548</v>
       </c>
-      <c r="D552" s="7"/>
-      <c r="F552" s="9"/>
+      <c r="C552" t="s">
+        <v>934</v>
+      </c>
+      <c r="D552" s="7">
+        <v>425</v>
+      </c>
+      <c r="E552" t="s">
+        <v>935</v>
+      </c>
+      <c r="F552" s="9">
+        <v>46246</v>
+      </c>
     </row>
     <row r="553" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B553">
         <v>549</v>
       </c>
-      <c r="D553" s="7"/>
-      <c r="F553" s="9"/>
+      <c r="C553" t="s">
+        <v>936</v>
+      </c>
+      <c r="D553" s="7">
+        <v>4678.92</v>
+      </c>
+      <c r="E553" t="s">
+        <v>935</v>
+      </c>
+      <c r="F553" s="9">
+        <v>46246</v>
+      </c>
     </row>
     <row r="554" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B554">
@@ -16488,7 +16530,7 @@
     <row r="558" spans="2:6" x14ac:dyDescent="0.25">
       <c r="D558" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>6207813.5200000014</v>
+        <v>6213415.4400000013</v>
       </c>
       <c r="F558" s="9"/>
     </row>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Building\my_home\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zip\develop\my_home\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -28,7 +28,7 @@
     <sheet name="дерево заказ на 18 апр 2026" sheetId="15" r:id="rId14"/>
     <sheet name="расчёт кол-ва профилей оконных" sheetId="17" r:id="rId15"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -443,7 +443,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="937">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1518" uniqueCount="939">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3787,11 +3787,17 @@
   <si>
     <t>Водоотлив антрацит (0.5) 6 шт 181 см х 17,5 см, 91 см х 17,5 см -2 шт</t>
   </si>
+  <si>
+    <t xml:space="preserve"> Кисть для красок 50мм, Акор - 2 шт</t>
+  </si>
+  <si>
+    <t>Перчатки полиэстер с полиуретановым обливом, чер, 9/L, DORN - 5 пар</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
@@ -4633,8 +4639,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F558" totalsRowCount="1">
-  <autoFilter ref="B5:F557"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F570" totalsRowCount="1">
+  <autoFilter ref="B5:F569"/>
   <tableColumns count="5">
     <tableColumn id="1" name="№ п/п"/>
     <tableColumn id="2" name="Наименование "/>
@@ -7202,7 +7208,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:I558"/>
+  <dimension ref="B3:I570"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="94.7109375" customWidth="1"/>
@@ -16503,15 +16509,36 @@
       <c r="B554">
         <v>550</v>
       </c>
-      <c r="D554" s="7"/>
-      <c r="F554" s="9"/>
+      <c r="C554" t="s">
+        <v>937</v>
+      </c>
+      <c r="D554" s="7">
+        <v>158</v>
+      </c>
+      <c r="E554" t="s">
+        <v>885</v>
+      </c>
+      <c r="F554" s="9">
+        <v>46247</v>
+      </c>
     </row>
     <row r="555" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B555">
         <v>551</v>
       </c>
-      <c r="D555" s="7"/>
-      <c r="F555" s="9"/>
+      <c r="C555" t="s">
+        <v>938</v>
+      </c>
+      <c r="D555" s="7">
+        <f>5*79</f>
+        <v>395</v>
+      </c>
+      <c r="E555" t="s">
+        <v>885</v>
+      </c>
+      <c r="F555" s="9">
+        <v>46247</v>
+      </c>
     </row>
     <row r="556" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B556">
@@ -16528,11 +16555,59 @@
       <c r="F557" s="9"/>
     </row>
     <row r="558" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D558" s="7">
+      <c r="D558" s="7"/>
+      <c r="F558" s="9"/>
+    </row>
+    <row r="559" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D559" s="7"/>
+      <c r="F559" s="9"/>
+    </row>
+    <row r="560" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D560" s="7"/>
+      <c r="F560" s="9"/>
+    </row>
+    <row r="561" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D561" s="7"/>
+      <c r="F561" s="9"/>
+    </row>
+    <row r="562" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D562" s="7"/>
+      <c r="F562" s="9"/>
+    </row>
+    <row r="563" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D563" s="7"/>
+      <c r="F563" s="9"/>
+    </row>
+    <row r="564" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D564" s="7"/>
+      <c r="F564" s="9"/>
+    </row>
+    <row r="565" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D565" s="7"/>
+      <c r="F565" s="9"/>
+    </row>
+    <row r="566" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D566" s="7"/>
+      <c r="F566" s="9"/>
+    </row>
+    <row r="567" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D567" s="7"/>
+      <c r="F567" s="9"/>
+    </row>
+    <row r="568" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D568" s="7"/>
+      <c r="F568" s="9"/>
+    </row>
+    <row r="569" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D569" s="7"/>
+      <c r="F569" s="9"/>
+    </row>
+    <row r="570" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D570" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>6213415.4400000013</v>
-      </c>
-      <c r="F558" s="9"/>
+        <v>6213968.4400000013</v>
+      </c>
+      <c r="F570" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zip\develop\my_home\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Building\my_home\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -28,7 +28,7 @@
     <sheet name="дерево заказ на 18 апр 2026" sheetId="15" r:id="rId14"/>
     <sheet name="расчёт кол-ва профилей оконных" sheetId="17" r:id="rId15"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -443,7 +443,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1518" uniqueCount="939">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1524" uniqueCount="943">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3793,16 +3793,28 @@
   <si>
     <t>Перчатки полиэстер с полиуретановым обливом, чер, 9/L, DORN - 5 пар</t>
   </si>
+  <si>
+    <t>ВНЕШНЕЕ УТЕПЛЕНИЕ ДОМА</t>
+  </si>
+  <si>
+    <t>СТОИМОСТЬ РАБОТ</t>
+  </si>
+  <si>
+    <t>РАБОТЫ ОТ ВСЕЙ СТОИМОСТИ</t>
+  </si>
+  <si>
+    <t>СТОИМОСТЬ МАТЕРИАЛА</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
   </numFmts>
-  <fonts count="34" x14ac:knownFonts="1">
+  <fonts count="35" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4067,6 +4079,14 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -4094,7 +4114,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -4102,15 +4122,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="9" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4219,10 +4249,14 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Процентный" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="37">
     <dxf>
@@ -7215,7 +7249,8 @@
     <col min="4" max="4" width="22.5703125" customWidth="1"/>
     <col min="5" max="5" width="90.85546875" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="9" max="9" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="31.140625" customWidth="1"/>
+    <col min="9" max="9" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
@@ -15249,7 +15284,7 @@
         <v>46210</v>
       </c>
     </row>
-    <row r="481" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="481" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B481">
         <v>477</v>
       </c>
@@ -15266,7 +15301,7 @@
         <v>46210</v>
       </c>
     </row>
-    <row r="482" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="482" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B482">
         <v>478</v>
       </c>
@@ -15283,7 +15318,7 @@
         <v>46210</v>
       </c>
     </row>
-    <row r="483" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="483" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B483">
         <v>479</v>
       </c>
@@ -15300,7 +15335,7 @@
         <v>46196</v>
       </c>
     </row>
-    <row r="484" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="484" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B484">
         <v>480</v>
       </c>
@@ -15317,7 +15352,7 @@
         <v>46214</v>
       </c>
     </row>
-    <row r="485" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="485" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B485">
         <v>481</v>
       </c>
@@ -15334,7 +15369,7 @@
         <v>46214</v>
       </c>
     </row>
-    <row r="486" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="486" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B486">
         <v>482</v>
       </c>
@@ -15351,7 +15386,7 @@
         <v>46214</v>
       </c>
     </row>
-    <row r="487" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="487" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B487">
         <v>483</v>
       </c>
@@ -15368,7 +15403,7 @@
         <v>46214</v>
       </c>
     </row>
-    <row r="488" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="488" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B488">
         <v>484</v>
       </c>
@@ -15385,7 +15420,7 @@
         <v>46214</v>
       </c>
     </row>
-    <row r="489" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="489" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B489">
         <v>485</v>
       </c>
@@ -15402,7 +15437,7 @@
         <v>46214</v>
       </c>
     </row>
-    <row r="490" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="490" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B490">
         <v>486</v>
       </c>
@@ -15419,7 +15454,7 @@
         <v>46214</v>
       </c>
     </row>
-    <row r="491" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="491" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B491">
         <v>487</v>
       </c>
@@ -15435,8 +15470,15 @@
       <c r="F491" s="9">
         <v>46214</v>
       </c>
-    </row>
-    <row r="492" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="H491" s="59" t="s">
+        <v>939</v>
+      </c>
+      <c r="I491" s="60">
+        <f>SUM(D492:D497,D499,D503,D504,D506:D508,D521:D531,D536:D538,D540,D547:D550,D552:D553,D519)+90000</f>
+        <v>526302.87</v>
+      </c>
+    </row>
+    <row r="492" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B492">
         <v>488</v>
       </c>
@@ -15452,8 +15494,15 @@
       <c r="F492" s="9">
         <v>46217</v>
       </c>
-    </row>
-    <row r="493" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="H492" t="s">
+        <v>940</v>
+      </c>
+      <c r="I492" s="7">
+        <f>90000+120000</f>
+        <v>210000</v>
+      </c>
+    </row>
+    <row r="493" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B493">
         <v>489</v>
       </c>
@@ -15469,8 +15518,15 @@
       <c r="F493" s="9">
         <v>46217</v>
       </c>
-    </row>
-    <row r="494" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="H493" t="s">
+        <v>942</v>
+      </c>
+      <c r="I493" s="7">
+        <f>I491-I492</f>
+        <v>316302.87</v>
+      </c>
+    </row>
+    <row r="494" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B494">
         <v>490</v>
       </c>
@@ -15486,8 +15542,15 @@
       <c r="F494" s="9">
         <v>46217</v>
       </c>
-    </row>
-    <row r="495" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="H494" t="s">
+        <v>941</v>
+      </c>
+      <c r="I494" s="58">
+        <f>I492/I491</f>
+        <v>0.39900979449342544</v>
+      </c>
+    </row>
+    <row r="495" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B495">
         <v>491</v>
       </c>
@@ -15504,7 +15567,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="496" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="496" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B496">
         <v>492</v>
       </c>
@@ -16544,8 +16607,18 @@
       <c r="B556">
         <v>552</v>
       </c>
-      <c r="D556" s="7"/>
-      <c r="F556" s="9"/>
+      <c r="C556" t="s">
+        <v>932</v>
+      </c>
+      <c r="D556" s="7">
+        <v>90000</v>
+      </c>
+      <c r="E556" t="s">
+        <v>843</v>
+      </c>
+      <c r="F556" s="9">
+        <v>46255</v>
+      </c>
     </row>
     <row r="557" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B557">
@@ -16605,7 +16678,7 @@
     <row r="570" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D570" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>6213968.4400000013</v>
+        <v>6303968.4400000013</v>
       </c>
       <c r="F570" s="9"/>
     </row>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -443,7 +443,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1524" uniqueCount="943">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1534" uniqueCount="949">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3804,6 +3804,24 @@
   </si>
   <si>
     <t>СТОИМОСТЬ МАТЕРИАЛА</t>
+  </si>
+  <si>
+    <t>АО "Газпром Газораспределение"</t>
+  </si>
+  <si>
+    <t>оплата по договору ТП-КЛГ-389.26-ДГ</t>
+  </si>
+  <si>
+    <t>клей-пена монтажная профессиональная 500 1000 мл Технониколь</t>
+  </si>
+  <si>
+    <t>паста герметизирующая технониколь альфа пэйст 1,34 кг</t>
+  </si>
+  <si>
+    <t>степлер тип 140 скобы 6-14мм miles</t>
+  </si>
+  <si>
+    <t>лента одностороняя ondutiss fix tape 50 мм 50 м</t>
   </si>
 </sst>
 </file>
@@ -16624,61 +16642,114 @@
       <c r="B557">
         <v>553</v>
       </c>
-      <c r="D557" s="7"/>
-      <c r="F557" s="9"/>
+      <c r="C557" t="s">
+        <v>944</v>
+      </c>
+      <c r="D557" s="7">
+        <v>54019.55</v>
+      </c>
+      <c r="E557" t="s">
+        <v>943</v>
+      </c>
+      <c r="F557" s="9">
+        <v>46267</v>
+      </c>
     </row>
     <row r="558" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D558" s="7"/>
-      <c r="F558" s="9"/>
+      <c r="B558">
+        <v>554</v>
+      </c>
+      <c r="C558" t="s">
+        <v>945</v>
+      </c>
+      <c r="D558" s="7">
+        <v>796.68</v>
+      </c>
+      <c r="E558" t="s">
+        <v>885</v>
+      </c>
+      <c r="F558" s="9">
+        <v>46267</v>
+      </c>
     </row>
     <row r="559" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D559" s="7"/>
-      <c r="F559" s="9"/>
+      <c r="C559" t="s">
+        <v>946</v>
+      </c>
+      <c r="D559" s="7">
+        <v>1304.33</v>
+      </c>
+      <c r="E559" t="s">
+        <v>885</v>
+      </c>
+      <c r="F559" s="9">
+        <v>46267</v>
+      </c>
     </row>
     <row r="560" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D560" s="7"/>
-      <c r="F560" s="9"/>
-    </row>
-    <row r="561" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D561" s="7"/>
-      <c r="F561" s="9"/>
-    </row>
-    <row r="562" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="C560" t="s">
+        <v>947</v>
+      </c>
+      <c r="D560" s="7">
+        <v>1304.33</v>
+      </c>
+      <c r="E560" t="s">
+        <v>885</v>
+      </c>
+      <c r="F560" s="9">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="561" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C561" t="s">
+        <v>948</v>
+      </c>
+      <c r="D561" s="7">
+        <v>1116.6600000000001</v>
+      </c>
+      <c r="E561" t="s">
+        <v>885</v>
+      </c>
+      <c r="F561" s="9">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="562" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D562" s="7"/>
       <c r="F562" s="9"/>
     </row>
-    <row r="563" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="563" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D563" s="7"/>
       <c r="F563" s="9"/>
     </row>
-    <row r="564" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="564" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D564" s="7"/>
       <c r="F564" s="9"/>
     </row>
-    <row r="565" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="565" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D565" s="7"/>
       <c r="F565" s="9"/>
     </row>
-    <row r="566" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="566" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D566" s="7"/>
       <c r="F566" s="9"/>
     </row>
-    <row r="567" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="567" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D567" s="7"/>
       <c r="F567" s="9"/>
     </row>
-    <row r="568" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="568" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D568" s="7"/>
       <c r="F568" s="9"/>
     </row>
-    <row r="569" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="569" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D569" s="7"/>
       <c r="F569" s="9"/>
     </row>
-    <row r="570" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="570" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D570" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>6303968.4400000013</v>
+        <v>6362509.9900000012</v>
       </c>
       <c r="F570" s="9"/>
     </row>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -5,30 +5,31 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Building\my_home\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zip\develop\my_home\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25320" windowHeight="8145" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25320" windowHeight="8145" firstSheet="2" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Расчёт колличества бетона " sheetId="2" r:id="rId1"/>
     <sheet name="Покупки для дома" sheetId="6" r:id="rId2"/>
     <sheet name="расчёт труб отопления" sheetId="18" r:id="rId3"/>
-    <sheet name="расчёт площади утепления дома" sheetId="16" r:id="rId4"/>
-    <sheet name="расчёт объёма бетона для мп1" sheetId="10" r:id="rId5"/>
-    <sheet name="Расчёт балок перекрытия" sheetId="11" r:id="rId6"/>
-    <sheet name="Материалы" sheetId="3" r:id="rId7"/>
-    <sheet name="Расчёт арматуры" sheetId="9" r:id="rId8"/>
-    <sheet name="Оси" sheetId="8" r:id="rId9"/>
-    <sheet name="Высоты" sheetId="7" r:id="rId10"/>
-    <sheet name="Розетки и освещение" sheetId="12" r:id="rId11"/>
-    <sheet name="сравнение цен на 13_02_26" sheetId="13" r:id="rId12"/>
-    <sheet name="котельная и вентиляция" sheetId="14" r:id="rId13"/>
-    <sheet name="дерево заказ на 18 апр 2026" sheetId="15" r:id="rId14"/>
-    <sheet name="расчёт кол-ва профилей оконных" sheetId="17" r:id="rId15"/>
+    <sheet name="Лист1" sheetId="19" r:id="rId4"/>
+    <sheet name="расчёт площади утепления дома" sheetId="16" r:id="rId5"/>
+    <sheet name="расчёт объёма бетона для мп1" sheetId="10" r:id="rId6"/>
+    <sheet name="Расчёт балок перекрытия" sheetId="11" r:id="rId7"/>
+    <sheet name="Материалы" sheetId="3" r:id="rId8"/>
+    <sheet name="Расчёт арматуры" sheetId="9" r:id="rId9"/>
+    <sheet name="Оси" sheetId="8" r:id="rId10"/>
+    <sheet name="Высоты" sheetId="7" r:id="rId11"/>
+    <sheet name="Розетки и освещение" sheetId="12" r:id="rId12"/>
+    <sheet name="сравнение цен на 13_02_26" sheetId="13" r:id="rId13"/>
+    <sheet name="котельная и вентиляция" sheetId="14" r:id="rId14"/>
+    <sheet name="дерево заказ на 18 апр 2026" sheetId="15" r:id="rId15"/>
+    <sheet name="расчёт кол-ва профилей оконных" sheetId="17" r:id="rId16"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -443,7 +444,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1534" uniqueCount="949">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="964">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3823,16 +3824,62 @@
   <si>
     <t>лента одностороняя ondutiss fix tape 50 мм 50 м</t>
   </si>
+  <si>
+    <t>№</t>
+  </si>
+  <si>
+    <t>цена</t>
+  </si>
+  <si>
+    <t>наименование</t>
+  </si>
+  <si>
+    <t>Труба металлопластиковая VALTEC PEX-AL-PEX 16х2,0 мм</t>
+  </si>
+  <si>
+    <t>200 м</t>
+  </si>
+  <si>
+    <t>Кабель ВВГп-нг(A)-LS 3х1,5 мм2 100 м твердый плоский Конкорд</t>
+  </si>
+  <si>
+    <t>100 м</t>
+  </si>
+  <si>
+    <t>Кабель ВВГп-нг(A)-LS 3х2,5 мм2 100 м твердый плоский Конкорд</t>
+  </si>
+  <si>
+    <t>итого:</t>
+  </si>
+  <si>
+    <t>Кабель ВВГ-пнг(A)-LS 3* 1,5 (ГОСТ) (плоский)</t>
+  </si>
+  <si>
+    <t>Кабель ВВГ-пнг(A)-LS 3* 1,5 (ГОСТ) (плоский) ноунейм</t>
+  </si>
+  <si>
+    <t>Кабель ВВГ-пнг(A)-LS 3*2,5 (ГОСТ) (плоский)</t>
+  </si>
+  <si>
+    <t>Кабель ВВГ-пнг(A)-LS 3*2,5 (ГОСТ) (плоский) (бухтами по 100м) -0,66 зелёный</t>
+  </si>
+  <si>
+    <t>Кабель Партнер-Электро ВВГпнг(A)-LS 3x2.5 100 м ГОСТ цвет черный</t>
+  </si>
+  <si>
+    <t>Кабель Партнер-Электро ВВГпнг(A)-LS 3x1.5 100 м ГОСТ цвет черный</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="3">
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
   </numFmts>
-  <fonts count="35" x14ac:knownFonts="1">
+  <fonts count="38">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4105,6 +4152,27 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF061D37"/>
+      <name val="Formular Regular"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF21282B"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -4150,15 +4218,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="9" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4270,18 +4339,88 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
+    <cellStyle name="Денежный" xfId="3" builtinId="4"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Процентный" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="37">
+  <dxfs count="41">
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF061D37"/>
+        <name val="Formular Regular"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -4332,6 +4471,12 @@
         <top/>
         <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
@@ -4696,15 +4841,39 @@
   <tableColumns count="5">
     <tableColumn id="1" name="№ п/п"/>
     <tableColumn id="2" name="Наименование "/>
-    <tableColumn id="3" name="Цена (руб)" totalsRowFunction="sum" dataDxfId="36" totalsRowDxfId="1"/>
+    <tableColumn id="3" name="Цена (руб)" totalsRowFunction="sum" dataDxfId="40" totalsRowDxfId="11"/>
     <tableColumn id="4" name="Примечание"/>
-    <tableColumn id="5" name="дата" dataDxfId="35" totalsRowDxfId="0"/>
+    <tableColumn id="5" name="дата" dataDxfId="39" totalsRowDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Таблица548" displayName="Таблица548" ref="E15:G22" totalsRowShown="0">
+  <autoFilter ref="E15:G22"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="Название оси"/>
+    <tableColumn id="2" name="Расстояние (мм)"/>
+    <tableColumn id="3" name="комментарии"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="Таблица14" displayName="Таблица14" ref="G3:I9" totalsRowShown="0">
+  <autoFilter ref="G3:I9"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="Наименование"/>
+    <tableColumn id="2" name="высота (мм)"/>
+    <tableColumn id="3" name="примечание"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Таблица14910" displayName="Таблица14910" ref="B3:D9" totalsRowShown="0">
   <autoFilter ref="B3:D9"/>
   <tableColumns count="3">
@@ -4716,21 +4885,69 @@
 </table>
 </file>
 
-<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="Таблица13" displayName="Таблица13" ref="B4:D15" totalsRowShown="0">
   <autoFilter ref="B4:D15"/>
   <tableColumns count="3">
     <tableColumn id="1" name="назначение"/>
-    <tableColumn id="2" name="количество розеток (шт)" dataDxfId="30"/>
+    <tableColumn id="2" name="количество розеток (шт)" dataDxfId="34"/>
     <tableColumn id="3" name="примечание"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="Таблица1316" displayName="Таблица1316" ref="B19:D23" totalsRowShown="0">
   <autoFilter ref="B19:D23"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="назначение"/>
+    <tableColumn id="2" name="количество (шт)" dataDxfId="33"/>
+    <tableColumn id="3" name="примечание"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="Таблица131617" displayName="Таблица131617" ref="B28:D32" totalsRowShown="0">
+  <autoFilter ref="B28:D32"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="назначение"/>
+    <tableColumn id="2" name="количество (шт)" dataDxfId="32"/>
+    <tableColumn id="3" name="примечание"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="Таблица13161718" displayName="Таблица13161718" ref="B36:D40" totalsRowShown="0">
+  <autoFilter ref="B36:D40"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="назначение"/>
+    <tableColumn id="2" name="количество (шт)" dataDxfId="31"/>
+    <tableColumn id="3" name="примечание"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="Таблица1316171819" displayName="Таблица1316171819" ref="B44:D48" totalsRowShown="0">
+  <autoFilter ref="B44:D48"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="назначение"/>
+    <tableColumn id="2" name="количество (шт)" dataDxfId="30"/>
+    <tableColumn id="3" name="примечание"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="Таблица131617181920" displayName="Таблица131617181920" ref="B52:D55" totalsRowShown="0">
+  <autoFilter ref="B52:D55"/>
   <tableColumns count="3">
     <tableColumn id="1" name="назначение"/>
     <tableColumn id="2" name="количество (шт)" dataDxfId="29"/>
@@ -4740,9 +4957,9 @@
 </table>
 </file>
 
-<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="Таблица131617" displayName="Таблица131617" ref="B28:D32" totalsRowShown="0">
-  <autoFilter ref="B28:D32"/>
+<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="Таблица13161721" displayName="Таблица13161721" ref="B59:D68" totalsRowShown="0">
+  <autoFilter ref="B59:D68"/>
   <tableColumns count="3">
     <tableColumn id="1" name="назначение"/>
     <tableColumn id="2" name="количество (шт)" dataDxfId="28"/>
@@ -4752,9 +4969,22 @@
 </table>
 </file>
 
-<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="Таблица13161718" displayName="Таблица13161718" ref="B36:D40" totalsRowShown="0">
-  <autoFilter ref="B36:D40"/>
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="Таблица23" displayName="Таблица23" ref="I3:L7" totalsRowShown="0">
+  <autoFilter ref="I3:L7"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="№"/>
+    <tableColumn id="2" name="наименование" dataDxfId="3"/>
+    <tableColumn id="3" name="количество"/>
+    <tableColumn id="4" name="цена" dataDxfId="2" dataCellStyle="Денежный"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="Таблица13161718192023" displayName="Таблица13161718192023" ref="B69:D72" totalsRowShown="0">
+  <autoFilter ref="B69:D72"/>
   <tableColumns count="3">
     <tableColumn id="1" name="назначение"/>
     <tableColumn id="2" name="количество (шт)" dataDxfId="27"/>
@@ -4764,119 +4994,52 @@
 </table>
 </file>
 
-<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="Таблица1316171819" displayName="Таблица1316171819" ref="B44:D48" totalsRowShown="0">
-  <autoFilter ref="B44:D48"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="назначение"/>
-    <tableColumn id="2" name="количество (шт)" dataDxfId="26"/>
-    <tableColumn id="3" name="примечание"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="Таблица131617181920" displayName="Таблица131617181920" ref="B52:D55" totalsRowShown="0">
-  <autoFilter ref="B52:D55"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="назначение"/>
-    <tableColumn id="2" name="количество (шт)" dataDxfId="25"/>
-    <tableColumn id="3" name="примечание"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="Таблица13161721" displayName="Таблица13161721" ref="B59:D68" totalsRowShown="0">
-  <autoFilter ref="B59:D68"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="назначение"/>
-    <tableColumn id="2" name="количество (шт)" dataDxfId="24"/>
-    <tableColumn id="3" name="примечание"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="Таблица13161718192023" displayName="Таблица13161718192023" ref="B69:D72" totalsRowShown="0">
-  <autoFilter ref="B69:D72"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="назначение"/>
-    <tableColumn id="2" name="количество (шт)" dataDxfId="23"/>
-    <tableColumn id="3" name="примечание"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Таблица8" displayName="Таблица8" ref="B4:C17" totalsRowShown="0">
   <autoFilter ref="B4:C17"/>
   <tableColumns count="2">
     <tableColumn id="1" name="Комплектующие\Магазины"/>
-    <tableColumn id="2" name=" Цена в Бауцентр (руб)" dataDxfId="22"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="Таблица24" displayName="Таблица24" ref="B2:G7" totalsRowShown="0">
-  <autoFilter ref="B2:G7"/>
-  <tableColumns count="6">
-    <tableColumn id="1" name="сторона дома"/>
-    <tableColumn id="2" name="ширина (м)"/>
-    <tableColumn id="3" name="высота (м)"/>
-    <tableColumn id="4" name="площадь проёмов (м2)" dataDxfId="34">
-      <calculatedColumnFormula>M3*2+M7</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="5" name="площадь утепления (м2)" dataDxfId="33">
-      <calculatedColumnFormula>Таблица24[[#This Row],[ширина (м)]]*Таблица24[[#This Row],[высота (м)]]-Таблица24[[#This Row],[площадь проёмов (м2)]]</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="6" name="примечание"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Таблица811" displayName="Таблица811" ref="E4:L17" totalsRowShown="0">
-  <autoFilter ref="E4:L17"/>
-  <tableColumns count="8">
-    <tableColumn id="1" name="Комплектующие\Магазины"/>
-    <tableColumn id="2" name=" Legrand" dataDxfId="21"/>
-    <tableColumn id="6" name="Dekraft" dataDxfId="20"/>
-    <tableColumn id="7" name="EKF" dataDxfId="19"/>
-    <tableColumn id="8" name="TDM electric" dataDxfId="18"/>
-    <tableColumn id="9" name="IEK" dataDxfId="17"/>
-    <tableColumn id="10" name="Спец 800вт" dataDxfId="16"/>
-    <tableColumn id="11" name="Столбец1" dataDxfId="15"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="Таблица81122" displayName="Таблица81122" ref="E22:L35" totalsRowShown="0">
-  <autoFilter ref="E22:L35"/>
-  <tableColumns count="8">
-    <tableColumn id="1" name="Комплектующие\Магазины"/>
-    <tableColumn id="2" name=" Legrand" dataDxfId="14"/>
-    <tableColumn id="6" name="Dekraft" dataDxfId="13"/>
-    <tableColumn id="7" name="EKF" dataDxfId="12"/>
-    <tableColumn id="8" name="TDM electric" dataDxfId="11"/>
-    <tableColumn id="9" name="IEK" dataDxfId="10"/>
-    <tableColumn id="10" name="Спец 800вт" dataDxfId="9"/>
-    <tableColumn id="11" name="Etimat" dataDxfId="8"/>
+    <tableColumn id="2" name=" Цена в Бауцентр (руб)" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Таблица811" displayName="Таблица811" ref="E4:L17" totalsRowShown="0">
+  <autoFilter ref="E4:L17"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="Комплектующие\Магазины"/>
+    <tableColumn id="2" name=" Legrand" dataDxfId="25"/>
+    <tableColumn id="6" name="Dekraft" dataDxfId="24"/>
+    <tableColumn id="7" name="EKF" dataDxfId="23"/>
+    <tableColumn id="8" name="TDM electric" dataDxfId="22"/>
+    <tableColumn id="9" name="IEK" dataDxfId="21"/>
+    <tableColumn id="10" name="Спец 800вт" dataDxfId="20"/>
+    <tableColumn id="11" name="Столбец1" dataDxfId="19"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="Таблица81122" displayName="Таблица81122" ref="E22:L35" totalsRowShown="0">
+  <autoFilter ref="E22:L35"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="Комплектующие\Магазины"/>
+    <tableColumn id="2" name=" Legrand" dataDxfId="18"/>
+    <tableColumn id="6" name="Dekraft" dataDxfId="17"/>
+    <tableColumn id="7" name="EKF" dataDxfId="16"/>
+    <tableColumn id="8" name="TDM electric" dataDxfId="15"/>
+    <tableColumn id="9" name="IEK" dataDxfId="14"/>
+    <tableColumn id="10" name="Спец 800вт" dataDxfId="13"/>
+    <tableColumn id="11" name="Etimat" dataDxfId="12"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Таблица11" displayName="Таблица11" ref="B3:D8" totalsRowShown="0">
   <autoFilter ref="B3:D8"/>
   <tableColumns count="3">
@@ -4888,7 +5051,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Таблица12" displayName="Таблица12" ref="B14:F19" totalsRowShown="0">
   <autoFilter ref="B14:F19"/>
   <tableColumns count="5">
@@ -4903,24 +5066,56 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="Таблица26" displayName="Таблица26" ref="I10:L14" totalsRowShown="0">
+  <autoFilter ref="I10:L14"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="№"/>
+    <tableColumn id="2" name="наименование" dataDxfId="1"/>
+    <tableColumn id="3" name="количество"/>
+    <tableColumn id="4" name="цена" dataDxfId="0" dataCellStyle="Денежный"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="Таблица24" displayName="Таблица24" ref="B2:G7" totalsRowShown="0">
+  <autoFilter ref="B2:G7"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name="сторона дома"/>
+    <tableColumn id="2" name="ширина (м)"/>
+    <tableColumn id="3" name="высота (м)"/>
+    <tableColumn id="4" name="площадь проёмов (м2)" dataDxfId="38">
+      <calculatedColumnFormula>M3*2+M7</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" name="площадь утепления (м2)" dataDxfId="37">
+      <calculatedColumnFormula>Таблица24[[#This Row],[ширина (м)]]*Таблица24[[#This Row],[высота (м)]]-Таблица24[[#This Row],[площадь проёмов (м2)]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" name="примечание"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Таблица2" displayName="Таблица2" ref="A4:F28" totalsRowCount="1">
   <autoFilter ref="A4:F27"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="№ п/п" totalsRowLabel="Итого:" totalsRowDxfId="7"/>
-    <tableColumn id="2" name="Тип" totalsRowDxfId="6"/>
-    <tableColumn id="3" name="Количество (М3/шт)" totalsRowDxfId="5"/>
-    <tableColumn id="4" name="Цена  (м3 или штук)" dataDxfId="32" totalsRowDxfId="4"/>
-    <tableColumn id="5" name="Сумма" totalsRowFunction="custom" dataDxfId="31" totalsRowDxfId="3">
+    <tableColumn id="1" name="№ п/п" totalsRowLabel="Итого:" totalsRowDxfId="9"/>
+    <tableColumn id="2" name="Тип" totalsRowDxfId="8"/>
+    <tableColumn id="3" name="Количество (М3/шт)" totalsRowDxfId="7"/>
+    <tableColumn id="4" name="Цена  (м3 или штук)" dataDxfId="36" totalsRowDxfId="6"/>
+    <tableColumn id="5" name="Сумма" totalsRowFunction="custom" dataDxfId="35" totalsRowDxfId="5">
       <calculatedColumnFormula>Таблица2[[#This Row],[Цена  (м3 или штук)]]*Таблица2[[#This Row],[Количество (М3/шт)]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(E5:E27)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" name="Примечание" totalsRowDxfId="2"/>
+    <tableColumn id="6" name="Примечание" totalsRowDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Таблица1" displayName="Таблица1" ref="B2:D9" totalsRowShown="0">
   <autoFilter ref="B2:D9"/>
   <tableColumns count="3">
@@ -4932,7 +5127,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Таблица5" displayName="Таблица5" ref="A3:C10" totalsRowShown="0">
   <autoFilter ref="A3:C10"/>
   <tableColumns count="3">
@@ -4944,7 +5139,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Таблица54" displayName="Таблица54" ref="E3:G10" totalsRowShown="0">
   <autoFilter ref="E3:G10"/>
   <tableColumns count="3">
@@ -4956,37 +5151,13 @@
 </table>
 </file>
 
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Таблица57" displayName="Таблица57" ref="A15:C22" totalsRowShown="0">
   <autoFilter ref="A15:C22"/>
   <tableColumns count="3">
     <tableColumn id="1" name="Название оси"/>
     <tableColumn id="2" name="Расстояние (мм)"/>
     <tableColumn id="3" name="комментарии"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Таблица548" displayName="Таблица548" ref="E15:G22" totalsRowShown="0">
-  <autoFilter ref="E15:G22"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="Название оси"/>
-    <tableColumn id="2" name="Расстояние (мм)"/>
-    <tableColumn id="3" name="комментарии"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="Таблица14" displayName="Таблица14" ref="G3:I9" totalsRowShown="0">
-  <autoFilter ref="G3:I9"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="Наименование"/>
-    <tableColumn id="2" name="высота (мм)"/>
-    <tableColumn id="3" name="примечание"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5280,7 +5451,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B5:I9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="30.7109375" customWidth="1"/>
     <col min="3" max="3" width="19.42578125" customWidth="1"/>
@@ -5291,7 +5462,7 @@
     <col min="9" max="9" width="11.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:9">
       <c r="C5" t="s">
         <v>143</v>
       </c>
@@ -5314,7 +5485,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9">
       <c r="B6" t="s">
         <v>139</v>
       </c>
@@ -5337,7 +5508,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9">
       <c r="B7" t="s">
         <v>140</v>
       </c>
@@ -5360,7 +5531,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:9">
       <c r="B8" t="s">
         <v>141</v>
       </c>
@@ -5383,7 +5554,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9">
       <c r="B9" s="6" t="s">
         <v>142</v>
       </c>
@@ -5424,8 +5595,355 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.42578125" customWidth="1"/>
+    <col min="2" max="2" width="20.140625" customWidth="1"/>
+    <col min="3" max="3" width="75" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" customWidth="1"/>
+    <col min="7" max="7" width="59.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="11" t="s">
+        <v>309</v>
+      </c>
+      <c r="C1" s="11"/>
+      <c r="E1" s="11" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="B2" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C3" t="s">
+        <v>269</v>
+      </c>
+      <c r="E3" t="s">
+        <v>267</v>
+      </c>
+      <c r="F3" t="s">
+        <v>268</v>
+      </c>
+      <c r="G3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>308</v>
+      </c>
+      <c r="B4" s="23">
+        <v>300</v>
+      </c>
+      <c r="C4" t="s">
+        <v>270</v>
+      </c>
+      <c r="E4" t="s">
+        <v>308</v>
+      </c>
+      <c r="F4" s="23">
+        <v>375</v>
+      </c>
+      <c r="G4" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>318</v>
+      </c>
+      <c r="B5" s="23">
+        <v>1500</v>
+      </c>
+      <c r="C5" t="s">
+        <v>322</v>
+      </c>
+      <c r="E5" t="s">
+        <v>312</v>
+      </c>
+      <c r="F5" s="23">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>319</v>
+      </c>
+      <c r="B6" s="23">
+        <v>2125</v>
+      </c>
+      <c r="C6" t="s">
+        <v>324</v>
+      </c>
+      <c r="E6" t="s">
+        <v>313</v>
+      </c>
+      <c r="F6" s="23">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>320</v>
+      </c>
+      <c r="B7" s="23">
+        <v>3100</v>
+      </c>
+      <c r="C7" t="s">
+        <v>323</v>
+      </c>
+      <c r="E7" t="s">
+        <v>314</v>
+      </c>
+      <c r="F7" s="23">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>321</v>
+      </c>
+      <c r="B8" s="23">
+        <v>4525</v>
+      </c>
+      <c r="C8" t="s">
+        <v>325</v>
+      </c>
+      <c r="E8" t="s">
+        <v>315</v>
+      </c>
+      <c r="F8" s="23">
+        <v>4450</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>308</v>
+      </c>
+      <c r="B9" s="23">
+        <v>300</v>
+      </c>
+      <c r="E9" t="s">
+        <v>316</v>
+      </c>
+      <c r="F9" s="23">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="B10" s="24">
+        <f>SUM(B4:B9)</f>
+        <v>11850</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="F10" s="24">
+        <f>SUM(F4:F9)</f>
+        <v>11850</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="F11" s="23"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="C12" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="F12" s="23"/>
+      <c r="G12" s="11" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="F13" s="23"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="B14" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>267</v>
+      </c>
+      <c r="B15" t="s">
+        <v>268</v>
+      </c>
+      <c r="C15" t="s">
+        <v>269</v>
+      </c>
+      <c r="E15" t="s">
+        <v>267</v>
+      </c>
+      <c r="F15" t="s">
+        <v>268</v>
+      </c>
+      <c r="G15" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>308</v>
+      </c>
+      <c r="B16" s="23">
+        <v>300</v>
+      </c>
+      <c r="C16" t="s">
+        <v>270</v>
+      </c>
+      <c r="E16" t="s">
+        <v>308</v>
+      </c>
+      <c r="F16" s="23">
+        <v>375</v>
+      </c>
+      <c r="G16" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="25" t="s">
+        <v>328</v>
+      </c>
+      <c r="B17" s="23">
+        <v>3175</v>
+      </c>
+      <c r="C17" t="s">
+        <v>337</v>
+      </c>
+      <c r="E17" s="25" t="s">
+        <v>332</v>
+      </c>
+      <c r="F17" s="23">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="25" t="s">
+        <v>329</v>
+      </c>
+      <c r="B18" s="23">
+        <v>1700</v>
+      </c>
+      <c r="E18" s="25" t="s">
+        <v>333</v>
+      </c>
+      <c r="F18" s="23">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="25" t="s">
+        <v>330</v>
+      </c>
+      <c r="B19" s="23">
+        <v>1625</v>
+      </c>
+      <c r="C19" t="s">
+        <v>338</v>
+      </c>
+      <c r="E19" s="25" t="s">
+        <v>334</v>
+      </c>
+      <c r="F19" s="23">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="25" t="s">
+        <v>331</v>
+      </c>
+      <c r="B20" s="23">
+        <v>5900</v>
+      </c>
+      <c r="C20" t="s">
+        <v>339</v>
+      </c>
+      <c r="E20" s="25" t="s">
+        <v>335</v>
+      </c>
+      <c r="F20" s="23">
+        <v>5750</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" t="s">
+        <v>308</v>
+      </c>
+      <c r="B21" s="23">
+        <v>300</v>
+      </c>
+      <c r="C21" t="s">
+        <v>270</v>
+      </c>
+      <c r="E21" t="s">
+        <v>316</v>
+      </c>
+      <c r="F21" s="23">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="B22" s="24">
+        <f>SUM(B16:B21)</f>
+        <v>13000</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="F22" s="24">
+        <f>SUM(F16:F21)</f>
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="C25" s="26" t="s">
+        <v>341</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="4">
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.42578125" customWidth="1"/>
     <col min="2" max="2" width="42.28515625" customWidth="1"/>
@@ -5441,12 +5959,12 @@
     <col min="13" max="13" width="11.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="21">
       <c r="C1" s="32" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11">
       <c r="B2" s="11" t="s">
         <v>280</v>
       </c>
@@ -5454,7 +5972,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11">
       <c r="B3" t="s">
         <v>343</v>
       </c>
@@ -5474,7 +5992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11">
       <c r="A4" s="23"/>
       <c r="B4" t="s">
         <v>345</v>
@@ -5495,7 +6013,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11">
       <c r="B5" t="s">
         <v>346</v>
       </c>
@@ -5512,7 +6030,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11">
       <c r="B6" t="s">
         <v>347</v>
       </c>
@@ -5529,7 +6047,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11">
       <c r="B7" t="s">
         <v>348</v>
       </c>
@@ -5549,7 +6067,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11">
       <c r="B8" t="s">
         <v>796</v>
       </c>
@@ -5570,7 +6088,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11">
       <c r="B9" t="s">
         <v>396</v>
       </c>
@@ -5589,19 +6107,19 @@
       </c>
       <c r="K9" s="23"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11">
       <c r="H10" s="24"/>
       <c r="K10" s="23"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11">
       <c r="F11" s="23"/>
       <c r="K11" s="23"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11">
       <c r="F12" s="23"/>
       <c r="K12" s="23"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11">
       <c r="D13" t="s">
         <v>402</v>
       </c>
@@ -5618,36 +6136,36 @@
       </c>
       <c r="K13" s="23"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11">
       <c r="F14" s="23"/>
       <c r="K14" s="23"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11">
       <c r="F15" s="30"/>
       <c r="K15" s="23"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11">
       <c r="F16" s="23"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12">
       <c r="F17" s="23"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12">
       <c r="F18" s="23"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12">
       <c r="F19" s="23"/>
       <c r="K19" s="33"/>
       <c r="L19" s="34"/>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12">
       <c r="F20" s="23"/>
       <c r="K20" s="22"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12">
       <c r="F21" s="23"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12">
       <c r="B22" s="21"/>
       <c r="C22" s="23"/>
       <c r="D22" s="23"/>
@@ -5663,10 +6181,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:D78"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="68.7109375" customWidth="1"/>
     <col min="3" max="3" width="26.28515625" customWidth="1"/>
@@ -5680,12 +6198,12 @@
     <col min="11" max="11" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:4" ht="18.75">
       <c r="B3" s="8" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:4">
       <c r="B4" t="s">
         <v>538</v>
       </c>
@@ -5696,7 +6214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:4">
       <c r="B5" t="s">
         <v>539</v>
       </c>
@@ -5707,7 +6225,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4">
       <c r="B6" t="s">
         <v>541</v>
       </c>
@@ -5715,7 +6233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:4">
       <c r="B7" t="s">
         <v>540</v>
       </c>
@@ -5723,7 +6241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:4">
       <c r="B8" t="s">
         <v>542</v>
       </c>
@@ -5731,7 +6249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4">
       <c r="B9" t="s">
         <v>545</v>
       </c>
@@ -5739,7 +6257,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:4">
       <c r="B10" t="s">
         <v>543</v>
       </c>
@@ -5747,7 +6265,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:4">
       <c r="B11" t="s">
         <v>544</v>
       </c>
@@ -5755,7 +6273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:4">
       <c r="B12" t="s">
         <v>551</v>
       </c>
@@ -5763,7 +6281,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:4">
       <c r="B13" t="s">
         <v>546</v>
       </c>
@@ -5771,7 +6289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:4">
       <c r="B14" t="s">
         <v>549</v>
       </c>
@@ -5779,7 +6297,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:4">
       <c r="B15" t="s">
         <v>550</v>
       </c>
@@ -5788,12 +6306,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:4" ht="18.75">
       <c r="B18" s="8" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:4">
       <c r="B19" t="s">
         <v>538</v>
       </c>
@@ -5804,7 +6322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:4">
       <c r="B20" t="s">
         <v>553</v>
       </c>
@@ -5815,7 +6333,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:4">
       <c r="B21" t="s">
         <v>551</v>
       </c>
@@ -5823,7 +6341,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:4">
       <c r="B22" t="s">
         <v>552</v>
       </c>
@@ -5831,7 +6349,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:4">
       <c r="B23" t="s">
         <v>550</v>
       </c>
@@ -5840,22 +6358,22 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:4">
       <c r="C24" s="23"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:4">
       <c r="C25" s="23"/>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:4">
       <c r="C26" s="23"/>
     </row>
-    <row r="27" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:4" ht="18.75">
       <c r="B27" s="8" t="s">
         <v>576</v>
       </c>
       <c r="C27" s="23"/>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:4">
       <c r="B28" t="s">
         <v>538</v>
       </c>
@@ -5866,7 +6384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:4">
       <c r="B29" t="s">
         <v>553</v>
       </c>
@@ -5877,7 +6395,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:4">
       <c r="B30" t="s">
         <v>551</v>
       </c>
@@ -5885,7 +6403,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:4">
       <c r="B31" t="s">
         <v>552</v>
       </c>
@@ -5893,7 +6411,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:4">
       <c r="B32" t="s">
         <v>550</v>
       </c>
@@ -5902,13 +6420,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:4" ht="18.75">
       <c r="B35" s="8" t="s">
         <v>577</v>
       </c>
       <c r="C35" s="23"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:4">
       <c r="B36" t="s">
         <v>538</v>
       </c>
@@ -5919,7 +6437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:4">
       <c r="B37" t="s">
         <v>553</v>
       </c>
@@ -5930,7 +6448,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:4">
       <c r="B38" t="s">
         <v>551</v>
       </c>
@@ -5938,7 +6456,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:4">
       <c r="B39" t="s">
         <v>552</v>
       </c>
@@ -5946,7 +6464,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:4">
       <c r="B40" t="s">
         <v>550</v>
       </c>
@@ -5955,13 +6473,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:4" ht="18.75">
       <c r="B43" s="8" t="s">
         <v>578</v>
       </c>
       <c r="C43" s="23"/>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:4">
       <c r="B44" t="s">
         <v>538</v>
       </c>
@@ -5972,7 +6490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:4">
       <c r="B45" t="s">
         <v>555</v>
       </c>
@@ -5983,7 +6501,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:4">
       <c r="B46" t="s">
         <v>554</v>
       </c>
@@ -5994,7 +6512,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:4">
       <c r="B47" t="s">
         <v>556</v>
       </c>
@@ -6005,7 +6523,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:4">
       <c r="B48" t="s">
         <v>550</v>
       </c>
@@ -6014,13 +6532,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:4" ht="18.75">
       <c r="B51" s="8" t="s">
         <v>579</v>
       </c>
       <c r="C51" s="23"/>
     </row>
-    <row r="52" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:4">
       <c r="B52" t="s">
         <v>538</v>
       </c>
@@ -6031,7 +6549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:4">
       <c r="B53" t="s">
         <v>559</v>
       </c>
@@ -6042,7 +6560,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="54" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:4">
       <c r="B54" t="s">
         <v>560</v>
       </c>
@@ -6053,7 +6571,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="55" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:4">
       <c r="B55" t="s">
         <v>550</v>
       </c>
@@ -6062,16 +6580,16 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:4">
       <c r="C56" s="23"/>
     </row>
-    <row r="58" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:4" ht="18.75">
       <c r="B58" s="8" t="s">
         <v>580</v>
       </c>
       <c r="C58" s="23"/>
     </row>
-    <row r="59" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:4">
       <c r="B59" t="s">
         <v>538</v>
       </c>
@@ -6082,7 +6600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:4">
       <c r="B60" t="s">
         <v>561</v>
       </c>
@@ -6093,7 +6611,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="61" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:4">
       <c r="B61" t="s">
         <v>562</v>
       </c>
@@ -6101,7 +6619,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:4">
       <c r="B62" t="s">
         <v>563</v>
       </c>
@@ -6109,7 +6627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:4">
       <c r="B63" t="s">
         <v>564</v>
       </c>
@@ -6120,7 +6638,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="64" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:4">
       <c r="B64" t="s">
         <v>565</v>
       </c>
@@ -6131,7 +6649,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="65" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:4">
       <c r="B65" t="s">
         <v>568</v>
       </c>
@@ -6140,22 +6658,22 @@
         <v>569</v>
       </c>
     </row>
-    <row r="66" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:4">
       <c r="C66" s="23"/>
       <c r="D66" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="67" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:4">
       <c r="C67" s="23"/>
     </row>
-    <row r="68" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:4" ht="18.75">
       <c r="B68" s="8" t="s">
         <v>581</v>
       </c>
       <c r="C68" s="23"/>
     </row>
-    <row r="69" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:4">
       <c r="B69" t="s">
         <v>538</v>
       </c>
@@ -6166,7 +6684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:4">
       <c r="B70" t="s">
         <v>570</v>
       </c>
@@ -6177,7 +6695,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="71" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:4">
       <c r="B71" t="s">
         <v>571</v>
       </c>
@@ -6185,7 +6703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:4">
       <c r="B72" t="s">
         <v>550</v>
       </c>
@@ -6194,22 +6712,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:4">
       <c r="B75" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="76" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:4">
       <c r="B76" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="77" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:4">
       <c r="B77" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="78" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:4">
       <c r="B78" t="s">
         <v>585</v>
       </c>
@@ -6230,10 +6748,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:L35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="46.5703125" customWidth="1"/>
     <col min="3" max="3" width="25.7109375" customWidth="1"/>
@@ -6248,7 +6766,7 @@
     <col min="12" max="12" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12">
       <c r="B3" s="11" t="s">
         <v>173</v>
       </c>
@@ -6256,7 +6774,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12">
       <c r="B4" s="11" t="s">
         <v>587</v>
       </c>
@@ -6288,7 +6806,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12">
       <c r="B5" t="s">
         <v>588</v>
       </c>
@@ -6315,7 +6833,7 @@
       <c r="K5" s="7"/>
       <c r="L5" s="7"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12">
       <c r="B6" t="s">
         <v>589</v>
       </c>
@@ -6338,7 +6856,7 @@
       <c r="K6" s="7"/>
       <c r="L6" s="7"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12">
       <c r="B7" t="s">
         <v>590</v>
       </c>
@@ -6361,7 +6879,7 @@
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12">
       <c r="B8" t="s">
         <v>591</v>
       </c>
@@ -6380,7 +6898,7 @@
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12">
       <c r="B9" t="s">
         <v>592</v>
       </c>
@@ -6399,7 +6917,7 @@
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12">
       <c r="B10" t="s">
         <v>593</v>
       </c>
@@ -6420,7 +6938,7 @@
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12">
       <c r="B11" t="s">
         <v>595</v>
       </c>
@@ -6437,7 +6955,7 @@
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12">
       <c r="B12" t="s">
         <v>596</v>
       </c>
@@ -6456,7 +6974,7 @@
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12">
       <c r="B13" t="s">
         <v>597</v>
       </c>
@@ -6475,7 +6993,7 @@
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12">
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
       <c r="F14" s="7"/>
@@ -6486,7 +7004,7 @@
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12">
       <c r="B15" t="s">
         <v>598</v>
       </c>
@@ -6507,7 +7025,7 @@
       </c>
       <c r="L15" s="7"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12">
       <c r="B16" t="s">
         <v>599</v>
       </c>
@@ -6528,7 +7046,7 @@
       </c>
       <c r="L16" s="7"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12">
       <c r="B17" t="s">
         <v>600</v>
       </c>
@@ -6549,13 +7067,13 @@
         <v>181</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12">
       <c r="B21" s="11"/>
       <c r="E21" s="11" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12">
       <c r="B22" s="11"/>
       <c r="E22" s="11" t="s">
         <v>587</v>
@@ -6582,7 +7100,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12">
       <c r="C23" s="7"/>
       <c r="E23" t="s">
         <v>588</v>
@@ -6597,7 +7115,7 @@
         <v>2524</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12">
       <c r="C24" s="7"/>
       <c r="E24" t="s">
         <v>589</v>
@@ -6612,7 +7130,7 @@
         <v>2524</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12">
       <c r="C25" s="7"/>
       <c r="E25" t="s">
         <v>590</v>
@@ -6627,7 +7145,7 @@
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12">
       <c r="C26" s="7"/>
       <c r="E26" t="s">
         <v>591</v>
@@ -6640,7 +7158,7 @@
       <c r="K26" s="7"/>
       <c r="L26" s="7"/>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12">
       <c r="C27" s="7"/>
       <c r="E27" t="s">
         <v>592</v>
@@ -6655,7 +7173,7 @@
       <c r="K27" s="7"/>
       <c r="L27" s="7"/>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12">
       <c r="C28" s="7"/>
       <c r="E28" t="s">
         <v>593</v>
@@ -6670,7 +7188,7 @@
       <c r="K28" s="7"/>
       <c r="L28" s="7"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12">
       <c r="C29" s="7"/>
       <c r="E29" t="s">
         <v>595</v>
@@ -6683,7 +7201,7 @@
       <c r="K29" s="7"/>
       <c r="L29" s="7"/>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12">
       <c r="C30" s="7"/>
       <c r="E30" t="s">
         <v>596</v>
@@ -6698,7 +7216,7 @@
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12">
       <c r="C31" s="7"/>
       <c r="E31" t="s">
         <v>597</v>
@@ -6713,7 +7231,7 @@
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12">
       <c r="C32" s="7"/>
       <c r="F32" s="7"/>
       <c r="G32" s="7"/>
@@ -6723,7 +7241,7 @@
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
     </row>
-    <row r="33" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:12">
       <c r="C33" s="7"/>
       <c r="E33" t="s">
         <v>598</v>
@@ -6738,7 +7256,7 @@
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
     </row>
-    <row r="34" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:12">
       <c r="C34" s="7"/>
       <c r="E34" t="s">
         <v>599</v>
@@ -6751,7 +7269,7 @@
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
     </row>
-    <row r="35" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:12">
       <c r="C35" s="7"/>
       <c r="E35" t="s">
         <v>600</v>
@@ -6776,16 +7294,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:F20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="69.140625" customWidth="1"/>
     <col min="6" max="6" width="72.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:6" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:6" ht="98.25" customHeight="1">
       <c r="B3" s="43" t="s">
         <v>623</v>
       </c>
@@ -6793,13 +7311,13 @@
         <v>639</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:6">
       <c r="B4" s="44"/>
       <c r="F4" s="49" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="129.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:6" ht="129.75" customHeight="1">
       <c r="B5" s="43" t="s">
         <v>624</v>
       </c>
@@ -6807,13 +7325,13 @@
         <v>641</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:6" ht="15.75">
       <c r="B6" s="44"/>
       <c r="F6" s="46" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:6" ht="44.25" customHeight="1">
       <c r="B7" s="45" t="s">
         <v>625</v>
       </c>
@@ -6821,7 +7339,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="8" spans="2:6" ht="122.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:6" ht="122.25" customHeight="1">
       <c r="B8" s="43" t="s">
         <v>626</v>
       </c>
@@ -6829,7 +7347,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:6">
       <c r="B9" s="44" t="s">
         <v>627</v>
       </c>
@@ -6837,7 +7355,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:6" ht="41.25" customHeight="1">
       <c r="B10" s="46" t="s">
         <v>628</v>
       </c>
@@ -6845,52 +7363,52 @@
         <v>646</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:6" ht="50.25" customHeight="1">
       <c r="B11" s="46" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:6" ht="31.5">
       <c r="B12" s="46" t="s">
         <v>630</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:6" ht="15.75">
       <c r="B13" s="46" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:6" ht="72" customHeight="1">
       <c r="B14" s="47" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="133.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:6" ht="133.5" customHeight="1">
       <c r="B15" s="47" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:6">
       <c r="B16" s="48" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="17" spans="2:2" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:2" ht="44.25" customHeight="1">
       <c r="B17" s="45" t="s">
         <v>635</v>
       </c>
     </row>
-    <row r="18" spans="2:2" ht="161.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:2" ht="161.25" customHeight="1">
       <c r="B18" s="46" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="19" spans="2:2" ht="105.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:2" ht="105.75" customHeight="1">
       <c r="B19" s="46" t="s">
         <v>637</v>
       </c>
     </row>
-    <row r="20" spans="2:2" ht="144" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:2" ht="144" customHeight="1">
       <c r="B20" s="46" t="s">
         <v>638</v>
       </c>
@@ -6902,10 +7420,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:F19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="22.28515625" customWidth="1"/>
     <col min="3" max="3" width="22.5703125" customWidth="1"/>
@@ -6914,7 +7432,7 @@
     <col min="6" max="6" width="21.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:6">
       <c r="B3" t="s">
         <v>688</v>
       </c>
@@ -6925,7 +7443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:6">
       <c r="B4" t="s">
         <v>689</v>
       </c>
@@ -6936,7 +7454,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:6">
       <c r="B5" t="s">
         <v>690</v>
       </c>
@@ -6947,7 +7465,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:6">
       <c r="B6" t="s">
         <v>692</v>
       </c>
@@ -6958,7 +7476,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:6">
       <c r="B7" t="s">
         <v>694</v>
       </c>
@@ -6969,7 +7487,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:6">
       <c r="B8" t="s">
         <v>694</v>
       </c>
@@ -6980,7 +7498,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:6">
       <c r="B14" t="s">
         <v>702</v>
       </c>
@@ -6997,7 +7515,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:6">
       <c r="B15" t="s">
         <v>701</v>
       </c>
@@ -7014,7 +7532,7 @@
         <v>42510</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:6">
       <c r="B16" t="s">
         <v>689</v>
       </c>
@@ -7031,7 +7549,7 @@
         <v>39000</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:6">
       <c r="B17" t="s">
         <v>690</v>
       </c>
@@ -7048,7 +7566,7 @@
         <v>3510</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:6">
       <c r="B18" t="s">
         <v>707</v>
       </c>
@@ -7065,7 +7583,7 @@
         <v>20280</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6">
       <c r="B19" s="11" t="s">
         <v>18</v>
       </c>
@@ -7088,17 +7606,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="C2:R18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="13.7109375" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:18">
       <c r="D2" t="s">
         <v>896</v>
       </c>
@@ -7109,7 +7627,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="3" spans="3:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:18">
       <c r="F3" t="s">
         <v>899</v>
       </c>
@@ -7130,7 +7648,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="4" spans="3:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:18">
       <c r="C4">
         <v>150</v>
       </c>
@@ -7162,7 +7680,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="5" spans="3:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:18">
       <c r="P5">
         <f>P3+P4</f>
         <v>2525</v>
@@ -7176,12 +7694,12 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="7" spans="3:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:18">
       <c r="D7" t="s">
         <v>897</v>
       </c>
     </row>
-    <row r="8" spans="3:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:18">
       <c r="C8">
         <v>150</v>
       </c>
@@ -7203,12 +7721,12 @@
         <v>780</v>
       </c>
     </row>
-    <row r="10" spans="3:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:18">
       <c r="D10" t="s">
         <v>898</v>
       </c>
     </row>
-    <row r="11" spans="3:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:18">
       <c r="C11">
         <v>235</v>
       </c>
@@ -7230,7 +7748,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="12" spans="3:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:18">
       <c r="G12" t="s">
         <v>550</v>
       </c>
@@ -7247,7 +7765,7 @@
         <v>17.958333333333336</v>
       </c>
     </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:3">
       <c r="C18">
         <f>210+50+50</f>
         <v>310</v>
@@ -7261,7 +7779,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:I570"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="94.7109375" customWidth="1"/>
     <col min="4" max="4" width="22.5703125" customWidth="1"/>
@@ -7271,12 +7789,12 @@
     <col min="9" max="9" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:6" ht="18.75">
       <c r="C3" s="8" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:6">
       <c r="B5" t="s">
         <v>0</v>
       </c>
@@ -7293,7 +7811,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:6">
       <c r="B6">
         <v>1</v>
       </c>
@@ -7310,7 +7828,7 @@
         <v>45287</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:6">
       <c r="B7">
         <v>2</v>
       </c>
@@ -7325,7 +7843,7 @@
       </c>
       <c r="F7" s="9"/>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:6">
       <c r="B8">
         <v>3</v>
       </c>
@@ -7340,7 +7858,7 @@
       </c>
       <c r="F8" s="9"/>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:6">
       <c r="B9">
         <v>4</v>
       </c>
@@ -7355,7 +7873,7 @@
       </c>
       <c r="F9" s="9"/>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:6">
       <c r="B10">
         <v>5</v>
       </c>
@@ -7370,7 +7888,7 @@
       </c>
       <c r="F10" s="9"/>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:6">
       <c r="B11">
         <v>6</v>
       </c>
@@ -7382,7 +7900,7 @@
       </c>
       <c r="F11" s="9"/>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:6">
       <c r="B12">
         <v>7</v>
       </c>
@@ -7397,7 +7915,7 @@
       </c>
       <c r="F12" s="9"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:6">
       <c r="B13">
         <v>8</v>
       </c>
@@ -7412,7 +7930,7 @@
       </c>
       <c r="F13" s="9"/>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:6">
       <c r="B14">
         <v>9</v>
       </c>
@@ -7427,7 +7945,7 @@
       </c>
       <c r="F14" s="9"/>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:6">
       <c r="B15">
         <v>10</v>
       </c>
@@ -7442,7 +7960,7 @@
       </c>
       <c r="F15" s="9"/>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:6">
       <c r="B16">
         <v>11</v>
       </c>
@@ -7459,7 +7977,7 @@
         <v>45361</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:6">
       <c r="B17">
         <v>12</v>
       </c>
@@ -7476,7 +7994,7 @@
         <v>45361</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:6">
       <c r="B18">
         <v>13</v>
       </c>
@@ -7493,7 +8011,7 @@
         <v>45361</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6">
       <c r="B19">
         <v>14</v>
       </c>
@@ -7510,7 +8028,7 @@
         <v>45361</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:6">
       <c r="B20">
         <v>15</v>
       </c>
@@ -7527,7 +8045,7 @@
         <v>45366</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:6">
       <c r="B21">
         <v>16</v>
       </c>
@@ -7544,7 +8062,7 @@
         <v>45366</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:6">
       <c r="B22">
         <v>17</v>
       </c>
@@ -7561,7 +8079,7 @@
         <v>45374</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:6">
       <c r="B23">
         <v>18</v>
       </c>
@@ -7578,7 +8096,7 @@
         <v>45388</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:6">
       <c r="B24">
         <v>19</v>
       </c>
@@ -7595,7 +8113,7 @@
         <v>45388</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:6">
       <c r="B25">
         <v>20</v>
       </c>
@@ -7612,7 +8130,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:6">
       <c r="B26">
         <v>21</v>
       </c>
@@ -7629,7 +8147,7 @@
         <v>45384</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:6">
       <c r="B27">
         <v>22</v>
       </c>
@@ -7646,7 +8164,7 @@
         <v>45389</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:6">
       <c r="B28">
         <v>23</v>
       </c>
@@ -7663,7 +8181,7 @@
         <v>45389</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:6">
       <c r="B29">
         <v>24</v>
       </c>
@@ -7677,7 +8195,7 @@
         <v>45395</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:6">
       <c r="B30">
         <v>25</v>
       </c>
@@ -7694,7 +8212,7 @@
         <v>45394</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:6">
       <c r="B31">
         <v>26</v>
       </c>
@@ -7711,7 +8229,7 @@
         <v>45394</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:6">
       <c r="B32">
         <v>27</v>
       </c>
@@ -7725,7 +8243,7 @@
         <v>45394</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:6">
       <c r="B33">
         <v>28</v>
       </c>
@@ -7739,7 +8257,7 @@
         <v>45394</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:6">
       <c r="B34">
         <v>29</v>
       </c>
@@ -7756,7 +8274,7 @@
         <v>45394</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:6">
       <c r="B35">
         <v>30</v>
       </c>
@@ -7773,7 +8291,7 @@
         <v>45394</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:6">
       <c r="B36">
         <v>31</v>
       </c>
@@ -7790,7 +8308,7 @@
         <v>45395</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:6">
       <c r="B37">
         <v>32</v>
       </c>
@@ -7807,7 +8325,7 @@
         <v>45397</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:6">
       <c r="B38">
         <v>33</v>
       </c>
@@ -7824,7 +8342,7 @@
         <v>45400</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:6">
       <c r="B39">
         <v>34</v>
       </c>
@@ -7838,7 +8356,7 @@
         <v>45401</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:6">
       <c r="B40">
         <v>35</v>
       </c>
@@ -7852,7 +8370,7 @@
         <v>45402</v>
       </c>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:6">
       <c r="B41">
         <v>36</v>
       </c>
@@ -7869,7 +8387,7 @@
         <v>45405</v>
       </c>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:6">
       <c r="B42">
         <v>37</v>
       </c>
@@ -7886,7 +8404,7 @@
         <v>45405</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:6">
       <c r="B43">
         <v>38</v>
       </c>
@@ -7903,7 +8421,7 @@
         <v>45405</v>
       </c>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:6">
       <c r="B44">
         <v>39</v>
       </c>
@@ -7920,7 +8438,7 @@
         <v>45406</v>
       </c>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:6">
       <c r="B45">
         <v>40</v>
       </c>
@@ -7937,7 +8455,7 @@
         <v>45412</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:6">
       <c r="B46">
         <v>41</v>
       </c>
@@ -7954,7 +8472,7 @@
         <v>45412</v>
       </c>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:6">
       <c r="B47">
         <v>42</v>
       </c>
@@ -7971,7 +8489,7 @@
         <v>45412</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:6">
       <c r="B48">
         <v>43</v>
       </c>
@@ -7988,7 +8506,7 @@
         <v>45412</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:6">
       <c r="B49">
         <v>44</v>
       </c>
@@ -8005,7 +8523,7 @@
         <v>45412</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:6">
       <c r="B50">
         <v>45</v>
       </c>
@@ -8022,7 +8540,7 @@
         <v>45414</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:6">
       <c r="B51">
         <v>47</v>
       </c>
@@ -8039,7 +8557,7 @@
         <v>45414</v>
       </c>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:6">
       <c r="B52">
         <v>48</v>
       </c>
@@ -8056,7 +8574,7 @@
         <v>45414</v>
       </c>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:6">
       <c r="B53">
         <v>49</v>
       </c>
@@ -8073,7 +8591,7 @@
         <v>45418</v>
       </c>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:6">
       <c r="B54">
         <v>50</v>
       </c>
@@ -8090,7 +8608,7 @@
         <v>45418</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:6">
       <c r="B55">
         <v>51</v>
       </c>
@@ -8107,7 +8625,7 @@
         <v>45418</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:6">
       <c r="B56">
         <v>52</v>
       </c>
@@ -8124,7 +8642,7 @@
         <v>45418</v>
       </c>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:6">
       <c r="B57">
         <v>53</v>
       </c>
@@ -8141,7 +8659,7 @@
         <v>45420</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:6">
       <c r="B58">
         <v>54</v>
       </c>
@@ -8158,7 +8676,7 @@
         <v>45420</v>
       </c>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:6">
       <c r="B59">
         <v>55</v>
       </c>
@@ -8175,7 +8693,7 @@
         <v>45420</v>
       </c>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:6">
       <c r="B60">
         <v>56</v>
       </c>
@@ -8192,7 +8710,7 @@
         <v>45423</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:6">
       <c r="B61">
         <v>57</v>
       </c>
@@ -8209,7 +8727,7 @@
         <v>45423</v>
       </c>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:6">
       <c r="B62">
         <v>58</v>
       </c>
@@ -8226,7 +8744,7 @@
         <v>45423</v>
       </c>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:6">
       <c r="B63">
         <v>59</v>
       </c>
@@ -8243,7 +8761,7 @@
         <v>45423</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:6">
       <c r="B64">
         <v>60</v>
       </c>
@@ -8260,7 +8778,7 @@
         <v>45428</v>
       </c>
     </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:6">
       <c r="B65">
         <v>61</v>
       </c>
@@ -8277,7 +8795,7 @@
         <v>45435</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:6">
       <c r="B66">
         <v>62</v>
       </c>
@@ -8294,7 +8812,7 @@
         <v>45435</v>
       </c>
     </row>
-    <row r="67" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:6">
       <c r="B67">
         <v>63</v>
       </c>
@@ -8311,7 +8829,7 @@
         <v>45435</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:6">
       <c r="B68">
         <v>64</v>
       </c>
@@ -8328,7 +8846,7 @@
         <v>45435</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:6">
       <c r="B69">
         <v>65</v>
       </c>
@@ -8345,7 +8863,7 @@
         <v>45435</v>
       </c>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:6">
       <c r="B70">
         <v>66</v>
       </c>
@@ -8358,7 +8876,7 @@
       </c>
       <c r="F70" s="9"/>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:6">
       <c r="B71">
         <v>67</v>
       </c>
@@ -8375,7 +8893,7 @@
         <v>45439</v>
       </c>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:6">
       <c r="B72">
         <v>68</v>
       </c>
@@ -8392,7 +8910,7 @@
         <v>45438</v>
       </c>
     </row>
-    <row r="73" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:6">
       <c r="B73">
         <v>69</v>
       </c>
@@ -8409,7 +8927,7 @@
         <v>45444</v>
       </c>
     </row>
-    <row r="74" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:6">
       <c r="B74">
         <v>70</v>
       </c>
@@ -8426,7 +8944,7 @@
         <v>45444</v>
       </c>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:6">
       <c r="B75">
         <v>71</v>
       </c>
@@ -8443,7 +8961,7 @@
         <v>45444</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:6">
       <c r="B76">
         <v>72</v>
       </c>
@@ -8460,7 +8978,7 @@
         <v>45444</v>
       </c>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:6">
       <c r="B77">
         <v>73</v>
       </c>
@@ -8477,7 +8995,7 @@
         <v>45445</v>
       </c>
     </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:6">
       <c r="B78">
         <v>74</v>
       </c>
@@ -8494,7 +9012,7 @@
         <v>45451</v>
       </c>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:6">
       <c r="B79">
         <v>75</v>
       </c>
@@ -8511,7 +9029,7 @@
         <v>45451</v>
       </c>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:6">
       <c r="B80">
         <v>76</v>
       </c>
@@ -8528,7 +9046,7 @@
         <v>45451</v>
       </c>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:6">
       <c r="B81">
         <v>77</v>
       </c>
@@ -8545,7 +9063,7 @@
         <v>45452</v>
       </c>
     </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:6">
       <c r="B82">
         <v>78</v>
       </c>
@@ -8562,7 +9080,7 @@
         <v>45459</v>
       </c>
     </row>
-    <row r="83" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:6">
       <c r="B83">
         <v>79</v>
       </c>
@@ -8579,7 +9097,7 @@
         <v>45459</v>
       </c>
     </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:6">
       <c r="B84">
         <v>80</v>
       </c>
@@ -8596,7 +9114,7 @@
         <v>45459</v>
       </c>
     </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:6">
       <c r="B85">
         <v>81</v>
       </c>
@@ -8613,7 +9131,7 @@
         <v>45459</v>
       </c>
     </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:6">
       <c r="B86">
         <v>82</v>
       </c>
@@ -8630,7 +9148,7 @@
         <v>45459</v>
       </c>
     </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:6">
       <c r="B87">
         <v>83</v>
       </c>
@@ -8647,7 +9165,7 @@
         <v>45459</v>
       </c>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:6">
       <c r="B88">
         <v>84</v>
       </c>
@@ -8664,7 +9182,7 @@
         <v>45464</v>
       </c>
     </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:6">
       <c r="B89">
         <v>85</v>
       </c>
@@ -8681,7 +9199,7 @@
         <v>45464</v>
       </c>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:6">
       <c r="B90">
         <v>86</v>
       </c>
@@ -8698,7 +9216,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:6">
       <c r="B91">
         <v>87</v>
       </c>
@@ -8715,7 +9233,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:6">
       <c r="B92">
         <v>88</v>
       </c>
@@ -8732,7 +9250,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:6">
       <c r="B93">
         <v>89</v>
       </c>
@@ -8749,7 +9267,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:6">
       <c r="B94">
         <v>90</v>
       </c>
@@ -8766,7 +9284,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:6">
       <c r="B95">
         <v>91</v>
       </c>
@@ -8783,7 +9301,7 @@
         <v>45467</v>
       </c>
     </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:6">
       <c r="B96">
         <v>92</v>
       </c>
@@ -8800,7 +9318,7 @@
         <v>45467</v>
       </c>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:6">
       <c r="B97">
         <v>93</v>
       </c>
@@ -8817,7 +9335,7 @@
         <v>45467</v>
       </c>
     </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:6">
       <c r="B98">
         <v>94</v>
       </c>
@@ -8834,7 +9352,7 @@
         <v>45469</v>
       </c>
     </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:6">
       <c r="B99">
         <v>95</v>
       </c>
@@ -8851,7 +9369,7 @@
         <v>45464</v>
       </c>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:6">
       <c r="B100">
         <v>96</v>
       </c>
@@ -8868,7 +9386,7 @@
         <v>45469</v>
       </c>
     </row>
-    <row r="101" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:6">
       <c r="B101">
         <v>97</v>
       </c>
@@ -8885,7 +9403,7 @@
         <v>45469</v>
       </c>
     </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:6">
       <c r="B102">
         <v>98</v>
       </c>
@@ -8902,7 +9420,7 @@
         <v>45476</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:6">
       <c r="B103">
         <v>99</v>
       </c>
@@ -8919,7 +9437,7 @@
         <v>45476</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:6">
       <c r="B104">
         <v>100</v>
       </c>
@@ -8936,7 +9454,7 @@
         <v>45476</v>
       </c>
     </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:6">
       <c r="B105">
         <v>101</v>
       </c>
@@ -8953,7 +9471,7 @@
         <v>45476</v>
       </c>
     </row>
-    <row r="106" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:6">
       <c r="B106">
         <v>102</v>
       </c>
@@ -8970,7 +9488,7 @@
         <v>45476</v>
       </c>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:6">
       <c r="B107">
         <v>103</v>
       </c>
@@ -8987,7 +9505,7 @@
         <v>45476</v>
       </c>
     </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:6">
       <c r="B108">
         <v>104</v>
       </c>
@@ -9004,7 +9522,7 @@
         <v>45476</v>
       </c>
     </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:6">
       <c r="B109">
         <v>105</v>
       </c>
@@ -9021,7 +9539,7 @@
         <v>45476</v>
       </c>
     </row>
-    <row r="110" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:6">
       <c r="B110">
         <v>106</v>
       </c>
@@ -9038,7 +9556,7 @@
         <v>45476</v>
       </c>
     </row>
-    <row r="111" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:6">
       <c r="B111">
         <v>107</v>
       </c>
@@ -9055,7 +9573,7 @@
         <v>45476</v>
       </c>
     </row>
-    <row r="112" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:6">
       <c r="B112">
         <v>108</v>
       </c>
@@ -9072,7 +9590,7 @@
         <v>45476</v>
       </c>
     </row>
-    <row r="113" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:6">
       <c r="B113">
         <v>109</v>
       </c>
@@ -9089,7 +9607,7 @@
         <v>45477</v>
       </c>
     </row>
-    <row r="114" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:6">
       <c r="B114">
         <v>110</v>
       </c>
@@ -9106,7 +9624,7 @@
         <v>45477</v>
       </c>
     </row>
-    <row r="115" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:6">
       <c r="B115">
         <v>111</v>
       </c>
@@ -9123,7 +9641,7 @@
         <v>45480</v>
       </c>
     </row>
-    <row r="116" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:6">
       <c r="B116">
         <v>112</v>
       </c>
@@ -9140,7 +9658,7 @@
         <v>45480</v>
       </c>
     </row>
-    <row r="117" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:6">
       <c r="B117">
         <v>113</v>
       </c>
@@ -9157,7 +9675,7 @@
         <v>45480</v>
       </c>
     </row>
-    <row r="118" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:6">
       <c r="B118">
         <v>114</v>
       </c>
@@ -9174,7 +9692,7 @@
         <v>45480</v>
       </c>
     </row>
-    <row r="119" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:6">
       <c r="B119">
         <v>115</v>
       </c>
@@ -9191,7 +9709,7 @@
         <v>45480</v>
       </c>
     </row>
-    <row r="120" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:6">
       <c r="B120">
         <v>116</v>
       </c>
@@ -9208,7 +9726,7 @@
         <v>45499</v>
       </c>
     </row>
-    <row r="121" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:6">
       <c r="B121">
         <v>117</v>
       </c>
@@ -9225,7 +9743,7 @@
         <v>45496</v>
       </c>
     </row>
-    <row r="122" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:6">
       <c r="B122">
         <v>118</v>
       </c>
@@ -9242,7 +9760,7 @@
         <v>45496</v>
       </c>
     </row>
-    <row r="123" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:6">
       <c r="B123">
         <v>119</v>
       </c>
@@ -9259,7 +9777,7 @@
         <v>45496</v>
       </c>
     </row>
-    <row r="124" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:6">
       <c r="B124">
         <v>120</v>
       </c>
@@ -9276,7 +9794,7 @@
         <v>45496</v>
       </c>
     </row>
-    <row r="125" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:6">
       <c r="B125">
         <v>121</v>
       </c>
@@ -9293,7 +9811,7 @@
         <v>45496</v>
       </c>
     </row>
-    <row r="126" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:6">
       <c r="B126">
         <v>122</v>
       </c>
@@ -9310,7 +9828,7 @@
         <v>45506</v>
       </c>
     </row>
-    <row r="127" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:6">
       <c r="B127">
         <v>123</v>
       </c>
@@ -9327,7 +9845,7 @@
         <v>45506</v>
       </c>
     </row>
-    <row r="128" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:6">
       <c r="B128">
         <v>124</v>
       </c>
@@ -9344,7 +9862,7 @@
         <v>45506</v>
       </c>
     </row>
-    <row r="129" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:6">
       <c r="B129">
         <v>125</v>
       </c>
@@ -9361,7 +9879,7 @@
         <v>45506</v>
       </c>
     </row>
-    <row r="130" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:6">
       <c r="B130">
         <v>126</v>
       </c>
@@ -9378,7 +9896,7 @@
         <v>45509</v>
       </c>
     </row>
-    <row r="131" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:6">
       <c r="B131">
         <v>127</v>
       </c>
@@ -9395,7 +9913,7 @@
         <v>45518</v>
       </c>
     </row>
-    <row r="132" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:6">
       <c r="B132">
         <v>128</v>
       </c>
@@ -9412,7 +9930,7 @@
         <v>45524</v>
       </c>
     </row>
-    <row r="133" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:6">
       <c r="B133">
         <v>129</v>
       </c>
@@ -9429,7 +9947,7 @@
         <v>45524</v>
       </c>
     </row>
-    <row r="134" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:6">
       <c r="B134">
         <v>130</v>
       </c>
@@ -9446,7 +9964,7 @@
         <v>45524</v>
       </c>
     </row>
-    <row r="135" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:6">
       <c r="B135">
         <v>131</v>
       </c>
@@ -9463,7 +9981,7 @@
         <v>45524</v>
       </c>
     </row>
-    <row r="136" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:6">
       <c r="B136">
         <v>132</v>
       </c>
@@ -9480,7 +9998,7 @@
         <v>45524</v>
       </c>
     </row>
-    <row r="137" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:6">
       <c r="B137">
         <v>133</v>
       </c>
@@ -9497,7 +10015,7 @@
         <v>45529</v>
       </c>
     </row>
-    <row r="138" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:6">
       <c r="B138">
         <v>134</v>
       </c>
@@ -9514,7 +10032,7 @@
         <v>45529</v>
       </c>
     </row>
-    <row r="139" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:6">
       <c r="B139">
         <v>135</v>
       </c>
@@ -9531,7 +10049,7 @@
         <v>45529</v>
       </c>
     </row>
-    <row r="140" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:6">
       <c r="B140">
         <v>136</v>
       </c>
@@ -9548,7 +10066,7 @@
         <v>45529</v>
       </c>
     </row>
-    <row r="141" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:6">
       <c r="B141">
         <v>137</v>
       </c>
@@ -9565,7 +10083,7 @@
         <v>45546</v>
       </c>
     </row>
-    <row r="142" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:6">
       <c r="B142">
         <v>138</v>
       </c>
@@ -9582,7 +10100,7 @@
         <v>45556</v>
       </c>
     </row>
-    <row r="143" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:6">
       <c r="B143">
         <v>139</v>
       </c>
@@ -9599,7 +10117,7 @@
         <v>45556</v>
       </c>
     </row>
-    <row r="144" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:6">
       <c r="B144">
         <v>140</v>
       </c>
@@ -9616,7 +10134,7 @@
         <v>45563</v>
       </c>
     </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:6">
       <c r="B145">
         <v>141</v>
       </c>
@@ -9633,7 +10151,7 @@
         <v>45563</v>
       </c>
     </row>
-    <row r="146" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:6">
       <c r="B146">
         <v>142</v>
       </c>
@@ -9650,7 +10168,7 @@
         <v>45566</v>
       </c>
     </row>
-    <row r="147" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:6">
       <c r="B147">
         <v>143</v>
       </c>
@@ -9667,7 +10185,7 @@
         <v>45570</v>
       </c>
     </row>
-    <row r="148" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:6">
       <c r="B148">
         <v>144</v>
       </c>
@@ -9684,7 +10202,7 @@
         <v>45571</v>
       </c>
     </row>
-    <row r="149" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:6">
       <c r="B149">
         <v>145</v>
       </c>
@@ -9701,7 +10219,7 @@
         <v>45573</v>
       </c>
     </row>
-    <row r="150" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:6">
       <c r="B150">
         <v>146</v>
       </c>
@@ -9715,7 +10233,7 @@
         <v>45573</v>
       </c>
     </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:6">
       <c r="B151">
         <v>147</v>
       </c>
@@ -9729,7 +10247,7 @@
         <v>45573</v>
       </c>
     </row>
-    <row r="152" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:6">
       <c r="B152">
         <v>148</v>
       </c>
@@ -9746,7 +10264,7 @@
         <v>45582</v>
       </c>
     </row>
-    <row r="153" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:6">
       <c r="B153">
         <v>149</v>
       </c>
@@ -9763,7 +10281,7 @@
         <v>45582</v>
       </c>
     </row>
-    <row r="154" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:6">
       <c r="B154">
         <v>150</v>
       </c>
@@ -9780,7 +10298,7 @@
         <v>45582</v>
       </c>
     </row>
-    <row r="155" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:6">
       <c r="B155">
         <v>151</v>
       </c>
@@ -9797,7 +10315,7 @@
         <v>45584</v>
       </c>
     </row>
-    <row r="156" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:6">
       <c r="B156">
         <v>152</v>
       </c>
@@ -9814,7 +10332,7 @@
         <v>45584</v>
       </c>
     </row>
-    <row r="157" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:6">
       <c r="B157">
         <v>153</v>
       </c>
@@ -9831,7 +10349,7 @@
         <v>45599</v>
       </c>
     </row>
-    <row r="158" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:6">
       <c r="B158">
         <v>154</v>
       </c>
@@ -9848,7 +10366,7 @@
         <v>45652</v>
       </c>
     </row>
-    <row r="159" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:6">
       <c r="B159">
         <v>155</v>
       </c>
@@ -9865,7 +10383,7 @@
         <v>45675</v>
       </c>
     </row>
-    <row r="160" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:6">
       <c r="B160">
         <v>156</v>
       </c>
@@ -9882,7 +10400,7 @@
         <v>45675</v>
       </c>
     </row>
-    <row r="161" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:6">
       <c r="B161">
         <v>157</v>
       </c>
@@ -9899,7 +10417,7 @@
         <v>45662</v>
       </c>
     </row>
-    <row r="162" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:6">
       <c r="B162">
         <v>158</v>
       </c>
@@ -9913,7 +10431,7 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="163" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:6">
       <c r="B163">
         <v>159</v>
       </c>
@@ -9927,7 +10445,7 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="164" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:6">
       <c r="B164">
         <v>160</v>
       </c>
@@ -9944,7 +10462,7 @@
         <v>45696</v>
       </c>
     </row>
-    <row r="165" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:6">
       <c r="B165">
         <v>161</v>
       </c>
@@ -9961,7 +10479,7 @@
         <v>45724</v>
       </c>
     </row>
-    <row r="166" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:6">
       <c r="B166">
         <v>162</v>
       </c>
@@ -9978,7 +10496,7 @@
         <v>45725</v>
       </c>
     </row>
-    <row r="167" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:6">
       <c r="B167">
         <v>163</v>
       </c>
@@ -9995,7 +10513,7 @@
         <v>45725</v>
       </c>
     </row>
-    <row r="168" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:6">
       <c r="B168">
         <v>164</v>
       </c>
@@ -10012,7 +10530,7 @@
         <v>45725</v>
       </c>
     </row>
-    <row r="169" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:6">
       <c r="B169">
         <v>165</v>
       </c>
@@ -10029,7 +10547,7 @@
         <v>45725</v>
       </c>
     </row>
-    <row r="170" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:6">
       <c r="B170">
         <v>166</v>
       </c>
@@ -10046,7 +10564,7 @@
         <v>45731</v>
       </c>
     </row>
-    <row r="171" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:6">
       <c r="B171">
         <v>167</v>
       </c>
@@ -10063,7 +10581,7 @@
         <v>45731</v>
       </c>
     </row>
-    <row r="172" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:6">
       <c r="B172">
         <v>168</v>
       </c>
@@ -10080,7 +10598,7 @@
         <v>45731</v>
       </c>
     </row>
-    <row r="173" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:6">
       <c r="B173">
         <v>169</v>
       </c>
@@ -10097,7 +10615,7 @@
         <v>45732</v>
       </c>
     </row>
-    <row r="174" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:6">
       <c r="B174">
         <v>170</v>
       </c>
@@ -10114,7 +10632,7 @@
         <v>45732</v>
       </c>
     </row>
-    <row r="175" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:6">
       <c r="B175">
         <v>171</v>
       </c>
@@ -10131,7 +10649,7 @@
         <v>45732</v>
       </c>
     </row>
-    <row r="176" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:6">
       <c r="B176">
         <v>172</v>
       </c>
@@ -10148,7 +10666,7 @@
         <v>45732</v>
       </c>
     </row>
-    <row r="177" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:6">
       <c r="B177">
         <v>173</v>
       </c>
@@ -10165,7 +10683,7 @@
         <v>45732</v>
       </c>
     </row>
-    <row r="178" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:6">
       <c r="B178">
         <v>174</v>
       </c>
@@ -10182,7 +10700,7 @@
         <v>45732</v>
       </c>
     </row>
-    <row r="179" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:6">
       <c r="B179">
         <v>175</v>
       </c>
@@ -10199,7 +10717,7 @@
         <v>45732</v>
       </c>
     </row>
-    <row r="180" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:6">
       <c r="B180">
         <v>176</v>
       </c>
@@ -10216,7 +10734,7 @@
         <v>45738</v>
       </c>
     </row>
-    <row r="181" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:6">
       <c r="B181">
         <v>177</v>
       </c>
@@ -10233,7 +10751,7 @@
         <v>45738</v>
       </c>
     </row>
-    <row r="182" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:6">
       <c r="B182">
         <v>178</v>
       </c>
@@ -10250,7 +10768,7 @@
         <v>45738</v>
       </c>
     </row>
-    <row r="183" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:6">
       <c r="B183">
         <v>179</v>
       </c>
@@ -10267,7 +10785,7 @@
         <v>45738</v>
       </c>
     </row>
-    <row r="184" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:6">
       <c r="B184">
         <v>180</v>
       </c>
@@ -10284,7 +10802,7 @@
         <v>45738</v>
       </c>
     </row>
-    <row r="185" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:6">
       <c r="B185">
         <v>181</v>
       </c>
@@ -10301,7 +10819,7 @@
         <v>45739</v>
       </c>
     </row>
-    <row r="186" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:6">
       <c r="B186">
         <v>182</v>
       </c>
@@ -10318,7 +10836,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="187" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:6">
       <c r="B187">
         <v>183</v>
       </c>
@@ -10335,7 +10853,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="188" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:6">
       <c r="B188">
         <v>184</v>
       </c>
@@ -10352,7 +10870,7 @@
         <v>45745</v>
       </c>
     </row>
-    <row r="189" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:6">
       <c r="B189">
         <v>185</v>
       </c>
@@ -10369,7 +10887,7 @@
         <v>45746</v>
       </c>
     </row>
-    <row r="190" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:6">
       <c r="B190">
         <v>186</v>
       </c>
@@ -10386,7 +10904,7 @@
         <v>45746</v>
       </c>
     </row>
-    <row r="191" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:6">
       <c r="B191">
         <v>187</v>
       </c>
@@ -10403,7 +10921,7 @@
         <v>45751</v>
       </c>
     </row>
-    <row r="192" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:6">
       <c r="B192">
         <v>188</v>
       </c>
@@ -10420,7 +10938,7 @@
         <v>45752</v>
       </c>
     </row>
-    <row r="193" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:6">
       <c r="B193">
         <v>189</v>
       </c>
@@ -10437,7 +10955,7 @@
         <v>45752</v>
       </c>
     </row>
-    <row r="194" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:6">
       <c r="B194">
         <v>190</v>
       </c>
@@ -10454,7 +10972,7 @@
         <v>45752</v>
       </c>
     </row>
-    <row r="195" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:6">
       <c r="B195">
         <v>191</v>
       </c>
@@ -10471,7 +10989,7 @@
         <v>45746</v>
       </c>
     </row>
-    <row r="196" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:6">
       <c r="B196">
         <v>192</v>
       </c>
@@ -10488,7 +11006,7 @@
         <v>45769</v>
       </c>
     </row>
-    <row r="197" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:6">
       <c r="B197">
         <v>193</v>
       </c>
@@ -10505,7 +11023,7 @@
         <v>45769</v>
       </c>
     </row>
-    <row r="198" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:6">
       <c r="B198">
         <v>194</v>
       </c>
@@ -10522,7 +11040,7 @@
         <v>45769</v>
       </c>
     </row>
-    <row r="199" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:6">
       <c r="B199">
         <v>195</v>
       </c>
@@ -10539,7 +11057,7 @@
         <v>45769</v>
       </c>
     </row>
-    <row r="200" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:6">
       <c r="B200">
         <v>196</v>
       </c>
@@ -10556,7 +11074,7 @@
         <v>45769</v>
       </c>
     </row>
-    <row r="201" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:6">
       <c r="B201">
         <v>197</v>
       </c>
@@ -10573,7 +11091,7 @@
         <v>45773</v>
       </c>
     </row>
-    <row r="202" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:6">
       <c r="B202">
         <v>198</v>
       </c>
@@ -10590,7 +11108,7 @@
         <v>45779</v>
       </c>
     </row>
-    <row r="203" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:6">
       <c r="B203">
         <v>199</v>
       </c>
@@ -10607,7 +11125,7 @@
         <v>45779</v>
       </c>
     </row>
-    <row r="204" spans="2:6" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:6" ht="17.25">
       <c r="B204">
         <v>200</v>
       </c>
@@ -10624,7 +11142,7 @@
         <v>45782</v>
       </c>
     </row>
-    <row r="205" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:6">
       <c r="B205">
         <v>201</v>
       </c>
@@ -10641,7 +11159,7 @@
         <v>45782</v>
       </c>
     </row>
-    <row r="206" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:6">
       <c r="B206">
         <v>202</v>
       </c>
@@ -10658,7 +11176,7 @@
         <v>45788</v>
       </c>
     </row>
-    <row r="207" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:6">
       <c r="B207">
         <v>203</v>
       </c>
@@ -10675,7 +11193,7 @@
         <v>45791</v>
       </c>
     </row>
-    <row r="208" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="208" spans="2:6">
       <c r="B208">
         <v>204</v>
       </c>
@@ -10692,7 +11210,7 @@
         <v>45796</v>
       </c>
     </row>
-    <row r="209" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:6">
       <c r="B209">
         <v>205</v>
       </c>
@@ -10709,7 +11227,7 @@
         <v>45808</v>
       </c>
     </row>
-    <row r="210" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:6">
       <c r="B210">
         <v>206</v>
       </c>
@@ -10726,7 +11244,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="211" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:6">
       <c r="B211">
         <v>207</v>
       </c>
@@ -10743,7 +11261,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="212" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:6">
       <c r="B212">
         <v>208</v>
       </c>
@@ -10760,7 +11278,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="213" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="213" spans="2:6">
       <c r="B213">
         <v>209</v>
       </c>
@@ -10777,7 +11295,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="214" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="214" spans="2:6">
       <c r="B214">
         <v>210</v>
       </c>
@@ -10794,7 +11312,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="215" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="215" spans="2:6">
       <c r="B215">
         <v>211</v>
       </c>
@@ -10811,7 +11329,7 @@
         <v>45829</v>
       </c>
     </row>
-    <row r="216" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="216" spans="2:6">
       <c r="B216">
         <v>212</v>
       </c>
@@ -10828,7 +11346,7 @@
         <v>45836</v>
       </c>
     </row>
-    <row r="217" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="217" spans="2:6">
       <c r="B217">
         <v>213</v>
       </c>
@@ -10845,7 +11363,7 @@
         <v>45836</v>
       </c>
     </row>
-    <row r="218" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="218" spans="2:6">
       <c r="B218">
         <v>214</v>
       </c>
@@ -10862,7 +11380,7 @@
         <v>45836</v>
       </c>
     </row>
-    <row r="219" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="219" spans="2:6">
       <c r="B219">
         <v>215</v>
       </c>
@@ -10879,7 +11397,7 @@
         <v>45836</v>
       </c>
     </row>
-    <row r="220" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="220" spans="2:6">
       <c r="B220">
         <v>216</v>
       </c>
@@ -10896,7 +11414,7 @@
         <v>45836</v>
       </c>
     </row>
-    <row r="221" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="221" spans="2:6">
       <c r="B221">
         <v>217</v>
       </c>
@@ -10913,7 +11431,7 @@
         <v>45836</v>
       </c>
     </row>
-    <row r="222" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="222" spans="2:6">
       <c r="B222">
         <v>218</v>
       </c>
@@ -10930,7 +11448,7 @@
         <v>45836</v>
       </c>
     </row>
-    <row r="223" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="223" spans="2:6">
       <c r="B223">
         <v>219</v>
       </c>
@@ -10947,7 +11465,7 @@
         <v>45837</v>
       </c>
     </row>
-    <row r="224" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="224" spans="2:6">
       <c r="B224">
         <v>220</v>
       </c>
@@ -10964,7 +11482,7 @@
         <v>45848</v>
       </c>
     </row>
-    <row r="225" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="225" spans="2:6">
       <c r="B225">
         <v>221</v>
       </c>
@@ -10981,7 +11499,7 @@
         <v>45848</v>
       </c>
     </row>
-    <row r="226" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="226" spans="2:6">
       <c r="B226">
         <v>222</v>
       </c>
@@ -10998,7 +11516,7 @@
         <v>45848</v>
       </c>
     </row>
-    <row r="227" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="227" spans="2:6">
       <c r="B227">
         <v>223</v>
       </c>
@@ -11015,7 +11533,7 @@
         <v>45848</v>
       </c>
     </row>
-    <row r="228" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="228" spans="2:6">
       <c r="B228">
         <v>224</v>
       </c>
@@ -11032,7 +11550,7 @@
         <v>45848</v>
       </c>
     </row>
-    <row r="229" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="229" spans="2:6">
       <c r="B229">
         <v>225</v>
       </c>
@@ -11049,7 +11567,7 @@
         <v>45849</v>
       </c>
     </row>
-    <row r="230" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="230" spans="2:6">
       <c r="B230">
         <v>226</v>
       </c>
@@ -11066,7 +11584,7 @@
         <v>45852</v>
       </c>
     </row>
-    <row r="231" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="231" spans="2:6">
       <c r="B231">
         <v>227</v>
       </c>
@@ -11083,7 +11601,7 @@
         <v>45844</v>
       </c>
     </row>
-    <row r="232" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="232" spans="2:6">
       <c r="B232">
         <v>228</v>
       </c>
@@ -11098,7 +11616,7 @@
       </c>
       <c r="F232" s="9"/>
     </row>
-    <row r="233" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="233" spans="2:6">
       <c r="B233">
         <v>229</v>
       </c>
@@ -11113,7 +11631,7 @@
       </c>
       <c r="F233" s="9"/>
     </row>
-    <row r="234" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="234" spans="2:6">
       <c r="B234">
         <v>230</v>
       </c>
@@ -11128,7 +11646,7 @@
       </c>
       <c r="F234" s="9"/>
     </row>
-    <row r="235" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="235" spans="2:6">
       <c r="B235">
         <v>231</v>
       </c>
@@ -11143,7 +11661,7 @@
       </c>
       <c r="F235" s="9"/>
     </row>
-    <row r="236" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="236" spans="2:6">
       <c r="B236">
         <v>232</v>
       </c>
@@ -11158,7 +11676,7 @@
       </c>
       <c r="F236" s="9"/>
     </row>
-    <row r="237" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="237" spans="2:6">
       <c r="B237">
         <v>233</v>
       </c>
@@ -11173,7 +11691,7 @@
       </c>
       <c r="F237" s="9"/>
     </row>
-    <row r="238" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="238" spans="2:6">
       <c r="B238">
         <v>234</v>
       </c>
@@ -11188,7 +11706,7 @@
       </c>
       <c r="F238" s="9"/>
     </row>
-    <row r="239" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:6">
       <c r="B239">
         <v>235</v>
       </c>
@@ -11203,7 +11721,7 @@
       </c>
       <c r="F239" s="9"/>
     </row>
-    <row r="240" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="240" spans="2:6">
       <c r="B240">
         <v>236</v>
       </c>
@@ -11220,7 +11738,7 @@
         <v>45880</v>
       </c>
     </row>
-    <row r="241" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="241" spans="2:6">
       <c r="B241">
         <v>237</v>
       </c>
@@ -11237,7 +11755,7 @@
         <v>45880</v>
       </c>
     </row>
-    <row r="242" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="242" spans="2:6">
       <c r="B242">
         <v>238</v>
       </c>
@@ -11254,7 +11772,7 @@
         <v>45880</v>
       </c>
     </row>
-    <row r="243" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="243" spans="2:6">
       <c r="B243">
         <v>239</v>
       </c>
@@ -11271,7 +11789,7 @@
         <v>45882</v>
       </c>
     </row>
-    <row r="244" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="244" spans="2:6">
       <c r="B244">
         <v>240</v>
       </c>
@@ -11288,7 +11806,7 @@
         <v>45882</v>
       </c>
     </row>
-    <row r="245" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="245" spans="2:6">
       <c r="B245">
         <v>241</v>
       </c>
@@ -11305,7 +11823,7 @@
         <v>45882</v>
       </c>
     </row>
-    <row r="246" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="246" spans="2:6">
       <c r="B246">
         <v>242</v>
       </c>
@@ -11322,7 +11840,7 @@
         <v>45882</v>
       </c>
     </row>
-    <row r="247" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="247" spans="2:6">
       <c r="B247">
         <v>243</v>
       </c>
@@ -11339,7 +11857,7 @@
         <v>45879</v>
       </c>
     </row>
-    <row r="248" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="248" spans="2:6">
       <c r="B248">
         <v>244</v>
       </c>
@@ -11356,7 +11874,7 @@
         <v>45879</v>
       </c>
     </row>
-    <row r="249" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="249" spans="2:6">
       <c r="B249">
         <v>245</v>
       </c>
@@ -11373,7 +11891,7 @@
         <v>45879</v>
       </c>
     </row>
-    <row r="250" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="250" spans="2:6">
       <c r="B250">
         <v>246</v>
       </c>
@@ -11390,7 +11908,7 @@
         <v>45879</v>
       </c>
     </row>
-    <row r="251" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="251" spans="2:6">
       <c r="B251">
         <v>247</v>
       </c>
@@ -11407,7 +11925,7 @@
         <v>45886</v>
       </c>
     </row>
-    <row r="252" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="252" spans="2:6">
       <c r="B252">
         <v>248</v>
       </c>
@@ -11424,7 +11942,7 @@
         <v>45886</v>
       </c>
     </row>
-    <row r="253" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="253" spans="2:6">
       <c r="B253">
         <v>249</v>
       </c>
@@ -11441,7 +11959,7 @@
         <v>45886</v>
       </c>
     </row>
-    <row r="254" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="254" spans="2:6">
       <c r="B254">
         <v>250</v>
       </c>
@@ -11458,7 +11976,7 @@
         <v>45913</v>
       </c>
     </row>
-    <row r="255" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="255" spans="2:6">
       <c r="B255">
         <v>251</v>
       </c>
@@ -11475,7 +11993,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="256" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="256" spans="2:6">
       <c r="B256">
         <v>252</v>
       </c>
@@ -11492,7 +12010,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="257" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="2:6">
       <c r="B257">
         <v>253</v>
       </c>
@@ -11509,7 +12027,7 @@
         <v>45916</v>
       </c>
     </row>
-    <row r="258" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="2:6">
       <c r="B258">
         <v>254</v>
       </c>
@@ -11526,7 +12044,7 @@
         <v>45916</v>
       </c>
     </row>
-    <row r="259" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="2:6">
       <c r="B259">
         <v>255</v>
       </c>
@@ -11543,7 +12061,7 @@
         <v>45916</v>
       </c>
     </row>
-    <row r="260" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="260" spans="2:6">
       <c r="B260">
         <v>256</v>
       </c>
@@ -11560,7 +12078,7 @@
         <v>45916</v>
       </c>
     </row>
-    <row r="261" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="2:6">
       <c r="B261">
         <v>257</v>
       </c>
@@ -11577,7 +12095,7 @@
         <v>45916</v>
       </c>
     </row>
-    <row r="262" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="262" spans="2:6">
       <c r="B262">
         <v>258</v>
       </c>
@@ -11594,7 +12112,7 @@
         <v>45916</v>
       </c>
     </row>
-    <row r="263" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="2:6">
       <c r="B263">
         <v>259</v>
       </c>
@@ -11608,7 +12126,7 @@
         <v>45917</v>
       </c>
     </row>
-    <row r="264" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="2:6">
       <c r="B264">
         <v>260</v>
       </c>
@@ -11622,7 +12140,7 @@
         <v>45917</v>
       </c>
     </row>
-    <row r="265" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="2:6">
       <c r="B265">
         <v>261</v>
       </c>
@@ -11639,7 +12157,7 @@
         <v>45917</v>
       </c>
     </row>
-    <row r="266" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="2:6">
       <c r="B266">
         <v>262</v>
       </c>
@@ -11656,7 +12174,7 @@
         <v>45917</v>
       </c>
     </row>
-    <row r="267" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="2:6">
       <c r="B267">
         <v>263</v>
       </c>
@@ -11673,7 +12191,7 @@
         <v>45919</v>
       </c>
     </row>
-    <row r="268" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="2:6">
       <c r="B268">
         <v>264</v>
       </c>
@@ -11690,7 +12208,7 @@
         <v>45919</v>
       </c>
     </row>
-    <row r="269" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="2:6">
       <c r="B269">
         <v>265</v>
       </c>
@@ -11707,7 +12225,7 @@
         <v>45919</v>
       </c>
     </row>
-    <row r="270" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="2:6">
       <c r="B270">
         <v>266</v>
       </c>
@@ -11724,7 +12242,7 @@
         <v>45919</v>
       </c>
     </row>
-    <row r="271" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="271" spans="2:6">
       <c r="B271">
         <v>267</v>
       </c>
@@ -11741,7 +12259,7 @@
         <v>45919</v>
       </c>
     </row>
-    <row r="272" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="272" spans="2:6">
       <c r="B272">
         <v>268</v>
       </c>
@@ -11758,7 +12276,7 @@
         <v>45919</v>
       </c>
     </row>
-    <row r="273" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="2:6">
       <c r="B273">
         <v>269</v>
       </c>
@@ -11775,7 +12293,7 @@
         <v>45920</v>
       </c>
     </row>
-    <row r="274" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="2:6">
       <c r="B274">
         <v>270</v>
       </c>
@@ -11792,7 +12310,7 @@
         <v>45920</v>
       </c>
     </row>
-    <row r="275" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="2:6">
       <c r="B275">
         <v>271</v>
       </c>
@@ -11809,7 +12327,7 @@
         <v>45920</v>
       </c>
     </row>
-    <row r="276" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="2:6">
       <c r="B276">
         <v>272</v>
       </c>
@@ -11826,7 +12344,7 @@
         <v>45921</v>
       </c>
     </row>
-    <row r="277" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="2:6">
       <c r="B277">
         <v>273</v>
       </c>
@@ -11843,7 +12361,7 @@
         <v>45921</v>
       </c>
     </row>
-    <row r="278" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="2:6">
       <c r="B278">
         <v>274</v>
       </c>
@@ -11860,7 +12378,7 @@
         <v>45923</v>
       </c>
     </row>
-    <row r="279" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="2:6">
       <c r="B279">
         <v>275</v>
       </c>
@@ -11877,7 +12395,7 @@
         <v>45929</v>
       </c>
     </row>
-    <row r="280" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="280" spans="2:6">
       <c r="B280">
         <v>276</v>
       </c>
@@ -11894,7 +12412,7 @@
         <v>45929</v>
       </c>
     </row>
-    <row r="281" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="281" spans="2:6">
       <c r="B281">
         <v>277</v>
       </c>
@@ -11911,7 +12429,7 @@
         <v>45933</v>
       </c>
     </row>
-    <row r="282" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="2:6">
       <c r="B282">
         <v>278</v>
       </c>
@@ -11928,7 +12446,7 @@
         <v>45946</v>
       </c>
     </row>
-    <row r="283" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="2:6">
       <c r="B283">
         <v>279</v>
       </c>
@@ -11945,7 +12463,7 @@
         <v>45947</v>
       </c>
     </row>
-    <row r="284" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="2:6">
       <c r="B284">
         <v>280</v>
       </c>
@@ -11962,7 +12480,7 @@
         <v>45947</v>
       </c>
     </row>
-    <row r="285" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="2:6">
       <c r="B285">
         <v>281</v>
       </c>
@@ -11979,7 +12497,7 @@
         <v>45947</v>
       </c>
     </row>
-    <row r="286" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="2:6">
       <c r="B286">
         <v>282</v>
       </c>
@@ -11996,7 +12514,7 @@
         <v>45947</v>
       </c>
     </row>
-    <row r="287" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="2:6">
       <c r="B287">
         <v>283</v>
       </c>
@@ -12013,7 +12531,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="288" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="288" spans="2:6">
       <c r="B288">
         <v>284</v>
       </c>
@@ -12030,7 +12548,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="289" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="289" spans="2:6">
       <c r="B289">
         <v>285</v>
       </c>
@@ -12047,7 +12565,7 @@
         <v>45952</v>
       </c>
     </row>
-    <row r="290" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="290" spans="2:6">
       <c r="B290">
         <v>286</v>
       </c>
@@ -12064,7 +12582,7 @@
         <v>45952</v>
       </c>
     </row>
-    <row r="291" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="2:6">
       <c r="B291">
         <v>287</v>
       </c>
@@ -12081,7 +12599,7 @@
         <v>45952</v>
       </c>
     </row>
-    <row r="292" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="292" spans="2:6">
       <c r="B292">
         <v>288</v>
       </c>
@@ -12098,7 +12616,7 @@
         <v>45953</v>
       </c>
     </row>
-    <row r="293" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="293" spans="2:6">
       <c r="B293">
         <v>289</v>
       </c>
@@ -12115,7 +12633,7 @@
         <v>45954</v>
       </c>
     </row>
-    <row r="294" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="294" spans="2:6">
       <c r="B294">
         <v>290</v>
       </c>
@@ -12132,7 +12650,7 @@
         <v>45954</v>
       </c>
     </row>
-    <row r="295" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="295" spans="2:6">
       <c r="B295">
         <v>291</v>
       </c>
@@ -12149,7 +12667,7 @@
         <v>45968</v>
       </c>
     </row>
-    <row r="296" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="296" spans="2:6">
       <c r="B296">
         <v>292</v>
       </c>
@@ -12166,7 +12684,7 @@
         <v>45968</v>
       </c>
     </row>
-    <row r="297" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="297" spans="2:6">
       <c r="B297">
         <v>293</v>
       </c>
@@ -12183,7 +12701,7 @@
         <v>45967</v>
       </c>
     </row>
-    <row r="298" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="298" spans="2:6">
       <c r="B298">
         <v>294</v>
       </c>
@@ -12200,7 +12718,7 @@
         <v>45972</v>
       </c>
     </row>
-    <row r="299" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="299" spans="2:6">
       <c r="B299">
         <v>295</v>
       </c>
@@ -12217,7 +12735,7 @@
         <v>45974</v>
       </c>
     </row>
-    <row r="300" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="300" spans="2:6">
       <c r="B300">
         <v>296</v>
       </c>
@@ -12234,7 +12752,7 @@
         <v>45979</v>
       </c>
     </row>
-    <row r="301" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="301" spans="2:6">
       <c r="B301">
         <v>297</v>
       </c>
@@ -12251,7 +12769,7 @@
         <v>45979</v>
       </c>
     </row>
-    <row r="302" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="302" spans="2:6">
       <c r="B302">
         <v>298</v>
       </c>
@@ -12268,7 +12786,7 @@
         <v>45984</v>
       </c>
     </row>
-    <row r="303" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="303" spans="2:6">
       <c r="B303">
         <v>299</v>
       </c>
@@ -12285,7 +12803,7 @@
         <v>45995</v>
       </c>
     </row>
-    <row r="304" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="304" spans="2:6">
       <c r="B304">
         <v>300</v>
       </c>
@@ -12302,7 +12820,7 @@
         <v>45995</v>
       </c>
     </row>
-    <row r="305" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="305" spans="2:6">
       <c r="B305">
         <v>301</v>
       </c>
@@ -12319,7 +12837,7 @@
         <v>45995</v>
       </c>
     </row>
-    <row r="306" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="306" spans="2:6">
       <c r="B306">
         <v>302</v>
       </c>
@@ -12336,7 +12854,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="307" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="307" spans="2:6">
       <c r="B307">
         <v>303</v>
       </c>
@@ -12353,7 +12871,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="308" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="308" spans="2:6">
       <c r="B308">
         <v>304</v>
       </c>
@@ -12370,7 +12888,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="309" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="309" spans="2:6">
       <c r="B309">
         <v>305</v>
       </c>
@@ -12387,7 +12905,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="310" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="310" spans="2:6">
       <c r="B310">
         <v>306</v>
       </c>
@@ -12404,7 +12922,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="311" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="311" spans="2:6">
       <c r="B311">
         <v>307</v>
       </c>
@@ -12421,7 +12939,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="312" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="312" spans="2:6">
       <c r="B312">
         <v>308</v>
       </c>
@@ -12438,7 +12956,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="313" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="313" spans="2:6">
       <c r="B313">
         <v>309</v>
       </c>
@@ -12455,7 +12973,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="314" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="314" spans="2:6">
       <c r="B314">
         <v>310</v>
       </c>
@@ -12472,7 +12990,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="315" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="315" spans="2:6">
       <c r="B315">
         <v>311</v>
       </c>
@@ -12489,7 +13007,7 @@
         <v>46014</v>
       </c>
     </row>
-    <row r="316" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="316" spans="2:6">
       <c r="B316">
         <v>312</v>
       </c>
@@ -12506,7 +13024,7 @@
         <v>46014</v>
       </c>
     </row>
-    <row r="317" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="317" spans="2:6">
       <c r="B317">
         <v>313</v>
       </c>
@@ -12523,7 +13041,7 @@
         <v>46014</v>
       </c>
     </row>
-    <row r="318" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="318" spans="2:6">
       <c r="B318">
         <v>314</v>
       </c>
@@ -12540,7 +13058,7 @@
         <v>46014</v>
       </c>
     </row>
-    <row r="319" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="319" spans="2:6">
       <c r="B319">
         <v>315</v>
       </c>
@@ -12557,7 +13075,7 @@
         <v>46073</v>
       </c>
     </row>
-    <row r="320" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="320" spans="2:6">
       <c r="B320">
         <v>316</v>
       </c>
@@ -12574,7 +13092,7 @@
         <v>46073</v>
       </c>
     </row>
-    <row r="321" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="321" spans="2:6">
       <c r="B321">
         <v>317</v>
       </c>
@@ -12591,7 +13109,7 @@
         <v>46073</v>
       </c>
     </row>
-    <row r="322" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="322" spans="2:6">
       <c r="B322">
         <v>318</v>
       </c>
@@ -12608,7 +13126,7 @@
         <v>46073</v>
       </c>
     </row>
-    <row r="323" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="323" spans="2:6">
       <c r="B323">
         <v>319</v>
       </c>
@@ -12625,7 +13143,7 @@
         <v>46075</v>
       </c>
     </row>
-    <row r="324" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="324" spans="2:6">
       <c r="B324">
         <v>320</v>
       </c>
@@ -12642,7 +13160,7 @@
         <v>46075</v>
       </c>
     </row>
-    <row r="325" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:6">
       <c r="B325">
         <v>321</v>
       </c>
@@ -12659,7 +13177,7 @@
         <v>46071</v>
       </c>
     </row>
-    <row r="326" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="326" spans="2:6">
       <c r="B326">
         <v>322</v>
       </c>
@@ -12676,7 +13194,7 @@
         <v>46071</v>
       </c>
     </row>
-    <row r="327" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="327" spans="2:6">
       <c r="B327">
         <v>323</v>
       </c>
@@ -12693,7 +13211,7 @@
         <v>46071</v>
       </c>
     </row>
-    <row r="328" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="328" spans="2:6">
       <c r="B328">
         <v>324</v>
       </c>
@@ -12710,7 +13228,7 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="329" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="329" spans="2:6">
       <c r="B329">
         <v>325</v>
       </c>
@@ -12727,7 +13245,7 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="330" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="330" spans="2:6">
       <c r="B330">
         <v>326</v>
       </c>
@@ -12744,7 +13262,7 @@
         <v>46084</v>
       </c>
     </row>
-    <row r="331" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="331" spans="2:6">
       <c r="B331">
         <v>327</v>
       </c>
@@ -12761,7 +13279,7 @@
         <v>46098</v>
       </c>
     </row>
-    <row r="332" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="332" spans="2:6">
       <c r="B332">
         <v>328</v>
       </c>
@@ -12778,7 +13296,7 @@
         <v>46085</v>
       </c>
     </row>
-    <row r="333" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="333" spans="2:6">
       <c r="B333">
         <v>329</v>
       </c>
@@ -12795,7 +13313,7 @@
         <v>46085</v>
       </c>
     </row>
-    <row r="334" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="334" spans="2:6">
       <c r="B334">
         <v>330</v>
       </c>
@@ -12812,7 +13330,7 @@
         <v>46080</v>
       </c>
     </row>
-    <row r="335" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="335" spans="2:6">
       <c r="B335">
         <v>331</v>
       </c>
@@ -12829,7 +13347,7 @@
         <v>46079</v>
       </c>
     </row>
-    <row r="336" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:6">
       <c r="B336">
         <v>332</v>
       </c>
@@ -12846,7 +13364,7 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="337" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="337" spans="2:6">
       <c r="B337">
         <v>333</v>
       </c>
@@ -12863,7 +13381,7 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="338" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:6">
       <c r="B338">
         <v>334</v>
       </c>
@@ -12880,7 +13398,7 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="339" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="339" spans="2:6">
       <c r="B339">
         <v>335</v>
       </c>
@@ -12897,7 +13415,7 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="340" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="340" spans="2:6">
       <c r="B340">
         <v>336</v>
       </c>
@@ -12914,7 +13432,7 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="341" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="341" spans="2:6">
       <c r="B341">
         <v>337</v>
       </c>
@@ -12931,7 +13449,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="342" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="342" spans="2:6">
       <c r="B342">
         <v>338</v>
       </c>
@@ -12948,7 +13466,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="343" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="343" spans="2:6">
       <c r="B343">
         <v>339</v>
       </c>
@@ -12965,7 +13483,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="344" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="344" spans="2:6">
       <c r="B344">
         <v>340</v>
       </c>
@@ -12982,7 +13500,7 @@
         <v>46105</v>
       </c>
     </row>
-    <row r="345" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="345" spans="2:6">
       <c r="B345">
         <v>341</v>
       </c>
@@ -12999,7 +13517,7 @@
         <v>46105</v>
       </c>
     </row>
-    <row r="346" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="346" spans="2:6">
       <c r="B346">
         <v>342</v>
       </c>
@@ -13016,7 +13534,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="347" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="347" spans="2:6">
       <c r="B347">
         <v>343</v>
       </c>
@@ -13033,7 +13551,7 @@
         <v>46107</v>
       </c>
     </row>
-    <row r="348" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="348" spans="2:6">
       <c r="B348">
         <v>344</v>
       </c>
@@ -13050,7 +13568,7 @@
         <v>46107</v>
       </c>
     </row>
-    <row r="349" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="349" spans="2:6">
       <c r="B349">
         <v>345</v>
       </c>
@@ -13067,7 +13585,7 @@
         <v>46107</v>
       </c>
     </row>
-    <row r="350" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="350" spans="2:6">
       <c r="B350">
         <v>346</v>
       </c>
@@ -13084,7 +13602,7 @@
         <v>46110</v>
       </c>
     </row>
-    <row r="351" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="351" spans="2:6">
       <c r="B351">
         <v>347</v>
       </c>
@@ -13101,7 +13619,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="352" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="352" spans="2:6">
       <c r="B352">
         <v>348</v>
       </c>
@@ -13118,7 +13636,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="353" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="353" spans="2:9">
       <c r="B353">
         <v>349</v>
       </c>
@@ -13135,7 +13653,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="354" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:9">
       <c r="B354">
         <v>350</v>
       </c>
@@ -13152,7 +13670,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="355" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="355" spans="2:9">
       <c r="B355">
         <v>351</v>
       </c>
@@ -13169,7 +13687,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="356" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:9">
       <c r="B356">
         <v>352</v>
       </c>
@@ -13186,7 +13704,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="357" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="357" spans="2:9">
       <c r="B357">
         <v>353</v>
       </c>
@@ -13204,7 +13722,7 @@
       </c>
       <c r="I357" s="7"/>
     </row>
-    <row r="358" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="358" spans="2:9">
       <c r="B358">
         <v>354</v>
       </c>
@@ -13221,7 +13739,7 @@
         <v>46119</v>
       </c>
     </row>
-    <row r="359" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="359" spans="2:9">
       <c r="B359">
         <v>355</v>
       </c>
@@ -13238,7 +13756,7 @@
         <v>46119</v>
       </c>
     </row>
-    <row r="360" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="360" spans="2:9">
       <c r="B360">
         <v>356</v>
       </c>
@@ -13255,7 +13773,7 @@
         <v>46119</v>
       </c>
     </row>
-    <row r="361" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="361" spans="2:9">
       <c r="B361">
         <v>357</v>
       </c>
@@ -13272,7 +13790,7 @@
         <v>46123</v>
       </c>
     </row>
-    <row r="362" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="362" spans="2:9">
       <c r="B362">
         <v>358</v>
       </c>
@@ -13289,7 +13807,7 @@
         <v>46123</v>
       </c>
     </row>
-    <row r="363" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="363" spans="2:9">
       <c r="B363">
         <v>359</v>
       </c>
@@ -13306,7 +13824,7 @@
         <v>46123</v>
       </c>
     </row>
-    <row r="364" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="364" spans="2:9">
       <c r="B364">
         <v>360</v>
       </c>
@@ -13323,7 +13841,7 @@
         <v>46124</v>
       </c>
     </row>
-    <row r="365" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="365" spans="2:9">
       <c r="B365">
         <v>361</v>
       </c>
@@ -13340,7 +13858,7 @@
         <v>46124</v>
       </c>
     </row>
-    <row r="366" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="366" spans="2:9">
       <c r="B366">
         <v>362</v>
       </c>
@@ -13357,7 +13875,7 @@
         <v>46124</v>
       </c>
     </row>
-    <row r="367" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="367" spans="2:9">
       <c r="B367">
         <v>363</v>
       </c>
@@ -13374,7 +13892,7 @@
         <v>46124</v>
       </c>
     </row>
-    <row r="368" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="368" spans="2:9">
       <c r="B368">
         <v>364</v>
       </c>
@@ -13391,7 +13909,7 @@
         <v>46127</v>
       </c>
     </row>
-    <row r="369" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="369" spans="2:6">
       <c r="B369">
         <v>365</v>
       </c>
@@ -13408,7 +13926,7 @@
         <v>46127</v>
       </c>
     </row>
-    <row r="370" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="370" spans="2:6">
       <c r="B370">
         <v>366</v>
       </c>
@@ -13425,7 +13943,7 @@
         <v>46132</v>
       </c>
     </row>
-    <row r="371" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="371" spans="2:6">
       <c r="B371">
         <v>367</v>
       </c>
@@ -13442,7 +13960,7 @@
         <v>46132</v>
       </c>
     </row>
-    <row r="372" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="372" spans="2:6">
       <c r="B372">
         <v>368</v>
       </c>
@@ -13459,7 +13977,7 @@
         <v>46132</v>
       </c>
     </row>
-    <row r="373" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="373" spans="2:6">
       <c r="B373">
         <v>369</v>
       </c>
@@ -13476,7 +13994,7 @@
         <v>46132</v>
       </c>
     </row>
-    <row r="374" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="374" spans="2:6">
       <c r="B374">
         <v>370</v>
       </c>
@@ -13493,7 +14011,7 @@
         <v>46132</v>
       </c>
     </row>
-    <row r="375" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="375" spans="2:6">
       <c r="B375">
         <v>371</v>
       </c>
@@ -13510,7 +14028,7 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="376" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="376" spans="2:6">
       <c r="B376">
         <v>372</v>
       </c>
@@ -13527,7 +14045,7 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="377" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="377" spans="2:6">
       <c r="B377">
         <v>373</v>
       </c>
@@ -13544,7 +14062,7 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="378" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="378" spans="2:6">
       <c r="B378">
         <v>374</v>
       </c>
@@ -13561,7 +14079,7 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="379" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="379" spans="2:6">
       <c r="B379">
         <v>375</v>
       </c>
@@ -13578,7 +14096,7 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="380" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="380" spans="2:6">
       <c r="B380">
         <v>376</v>
       </c>
@@ -13595,7 +14113,7 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="381" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="381" spans="2:6">
       <c r="B381">
         <v>377</v>
       </c>
@@ -13612,7 +14130,7 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="382" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="382" spans="2:6">
       <c r="B382">
         <v>378</v>
       </c>
@@ -13629,7 +14147,7 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="383" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="383" spans="2:6">
       <c r="B383">
         <v>379</v>
       </c>
@@ -13646,7 +14164,7 @@
         <v>46139</v>
       </c>
     </row>
-    <row r="384" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="384" spans="2:6">
       <c r="B384">
         <v>380</v>
       </c>
@@ -13663,7 +14181,7 @@
         <v>46139</v>
       </c>
     </row>
-    <row r="385" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="385" spans="2:6">
       <c r="B385">
         <v>381</v>
       </c>
@@ -13680,7 +14198,7 @@
         <v>46139</v>
       </c>
     </row>
-    <row r="386" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="386" spans="2:6">
       <c r="B386">
         <v>382</v>
       </c>
@@ -13697,7 +14215,7 @@
         <v>46139</v>
       </c>
     </row>
-    <row r="387" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="387" spans="2:6">
       <c r="B387">
         <v>383</v>
       </c>
@@ -13714,7 +14232,7 @@
         <v>46144</v>
       </c>
     </row>
-    <row r="388" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="388" spans="2:6">
       <c r="B388">
         <v>384</v>
       </c>
@@ -13731,7 +14249,7 @@
         <v>46144</v>
       </c>
     </row>
-    <row r="389" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="389" spans="2:6">
       <c r="B389">
         <v>385</v>
       </c>
@@ -13748,7 +14266,7 @@
         <v>46144</v>
       </c>
     </row>
-    <row r="390" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="390" spans="2:6">
       <c r="B390">
         <v>386</v>
       </c>
@@ -13765,7 +14283,7 @@
         <v>46147</v>
       </c>
     </row>
-    <row r="391" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="391" spans="2:6">
       <c r="B391">
         <v>387</v>
       </c>
@@ -13782,7 +14300,7 @@
         <v>46147</v>
       </c>
     </row>
-    <row r="392" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="392" spans="2:6">
       <c r="B392">
         <v>388</v>
       </c>
@@ -13799,7 +14317,7 @@
         <v>46147</v>
       </c>
     </row>
-    <row r="393" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="393" spans="2:6">
       <c r="B393">
         <v>389</v>
       </c>
@@ -13816,7 +14334,7 @@
         <v>46149</v>
       </c>
     </row>
-    <row r="394" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="394" spans="2:6">
       <c r="B394">
         <v>390</v>
       </c>
@@ -13833,7 +14351,7 @@
         <v>46149</v>
       </c>
     </row>
-    <row r="395" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="395" spans="2:6">
       <c r="B395">
         <v>391</v>
       </c>
@@ -13850,7 +14368,7 @@
         <v>46149</v>
       </c>
     </row>
-    <row r="396" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="396" spans="2:6">
       <c r="B396">
         <v>392</v>
       </c>
@@ -13867,7 +14385,7 @@
         <v>46149</v>
       </c>
     </row>
-    <row r="397" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="397" spans="2:6">
       <c r="B397">
         <v>393</v>
       </c>
@@ -13884,7 +14402,7 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="398" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="398" spans="2:6">
       <c r="B398">
         <v>394</v>
       </c>
@@ -13901,7 +14419,7 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="399" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="399" spans="2:6">
       <c r="B399">
         <v>395</v>
       </c>
@@ -13918,7 +14436,7 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="400" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="400" spans="2:6">
       <c r="B400">
         <v>396</v>
       </c>
@@ -13935,7 +14453,7 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="401" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="401" spans="2:6">
       <c r="B401">
         <v>397</v>
       </c>
@@ -13952,7 +14470,7 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="402" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="402" spans="2:6">
       <c r="B402">
         <v>398</v>
       </c>
@@ -13969,7 +14487,7 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="403" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="403" spans="2:6">
       <c r="B403">
         <v>399</v>
       </c>
@@ -13986,7 +14504,7 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="404" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="404" spans="2:6">
       <c r="B404">
         <v>400</v>
       </c>
@@ -14003,7 +14521,7 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="405" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="405" spans="2:6">
       <c r="B405">
         <v>401</v>
       </c>
@@ -14020,7 +14538,7 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="406" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="406" spans="2:6">
       <c r="B406">
         <v>402</v>
       </c>
@@ -14037,7 +14555,7 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="407" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="407" spans="2:6">
       <c r="B407">
         <v>403</v>
       </c>
@@ -14054,7 +14572,7 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="408" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="408" spans="2:6">
       <c r="B408">
         <v>404</v>
       </c>
@@ -14071,7 +14589,7 @@
         <v>46165</v>
       </c>
     </row>
-    <row r="409" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="409" spans="2:6">
       <c r="B409">
         <v>405</v>
       </c>
@@ -14088,7 +14606,7 @@
         <v>46165</v>
       </c>
     </row>
-    <row r="410" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="410" spans="2:6">
       <c r="B410">
         <v>406</v>
       </c>
@@ -14105,7 +14623,7 @@
         <v>46165</v>
       </c>
     </row>
-    <row r="411" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="411" spans="2:6">
       <c r="B411">
         <v>407</v>
       </c>
@@ -14122,7 +14640,7 @@
         <v>46165</v>
       </c>
     </row>
-    <row r="412" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="412" spans="2:6">
       <c r="B412">
         <v>408</v>
       </c>
@@ -14139,7 +14657,7 @@
         <v>46165</v>
       </c>
     </row>
-    <row r="413" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="413" spans="2:6">
       <c r="B413">
         <v>409</v>
       </c>
@@ -14156,7 +14674,7 @@
         <v>46165</v>
       </c>
     </row>
-    <row r="414" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="414" spans="2:6">
       <c r="B414">
         <v>410</v>
       </c>
@@ -14173,7 +14691,7 @@
         <v>46165</v>
       </c>
     </row>
-    <row r="415" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="415" spans="2:6">
       <c r="B415">
         <v>411</v>
       </c>
@@ -14190,7 +14708,7 @@
         <v>46165</v>
       </c>
     </row>
-    <row r="416" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="416" spans="2:6">
       <c r="B416">
         <v>412</v>
       </c>
@@ -14207,7 +14725,7 @@
         <v>46165</v>
       </c>
     </row>
-    <row r="417" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="417" spans="2:6">
       <c r="B417">
         <v>413</v>
       </c>
@@ -14224,7 +14742,7 @@
         <v>46165</v>
       </c>
     </row>
-    <row r="418" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="418" spans="2:6">
       <c r="B418">
         <v>414</v>
       </c>
@@ -14241,7 +14759,7 @@
         <v>46165</v>
       </c>
     </row>
-    <row r="419" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="419" spans="2:6">
       <c r="B419">
         <v>415</v>
       </c>
@@ -14258,7 +14776,7 @@
         <v>46168</v>
       </c>
     </row>
-    <row r="420" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="420" spans="2:6">
       <c r="B420">
         <v>416</v>
       </c>
@@ -14275,7 +14793,7 @@
         <v>46168</v>
       </c>
     </row>
-    <row r="421" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="421" spans="2:6">
       <c r="B421">
         <v>417</v>
       </c>
@@ -14292,7 +14810,7 @@
         <v>46168</v>
       </c>
     </row>
-    <row r="422" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="422" spans="2:6">
       <c r="B422">
         <v>418</v>
       </c>
@@ -14309,7 +14827,7 @@
         <v>46169</v>
       </c>
     </row>
-    <row r="423" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="423" spans="2:6">
       <c r="B423">
         <v>419</v>
       </c>
@@ -14326,7 +14844,7 @@
         <v>46169</v>
       </c>
     </row>
-    <row r="424" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="424" spans="2:6">
       <c r="B424">
         <v>420</v>
       </c>
@@ -14343,7 +14861,7 @@
         <v>46169</v>
       </c>
     </row>
-    <row r="425" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="425" spans="2:6">
       <c r="B425">
         <v>421</v>
       </c>
@@ -14360,7 +14878,7 @@
         <v>46169</v>
       </c>
     </row>
-    <row r="426" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="426" spans="2:6">
       <c r="B426">
         <v>422</v>
       </c>
@@ -14377,7 +14895,7 @@
         <v>46169</v>
       </c>
     </row>
-    <row r="427" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="427" spans="2:6">
       <c r="B427">
         <v>423</v>
       </c>
@@ -14394,7 +14912,7 @@
         <v>46169</v>
       </c>
     </row>
-    <row r="428" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="428" spans="2:6">
       <c r="B428">
         <v>424</v>
       </c>
@@ -14411,7 +14929,7 @@
         <v>46169</v>
       </c>
     </row>
-    <row r="429" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="429" spans="2:6">
       <c r="B429">
         <v>425</v>
       </c>
@@ -14428,7 +14946,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="430" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="430" spans="2:6">
       <c r="B430">
         <v>426</v>
       </c>
@@ -14445,7 +14963,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="431" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="431" spans="2:6">
       <c r="B431">
         <v>427</v>
       </c>
@@ -14462,7 +14980,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="432" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="432" spans="2:6">
       <c r="B432">
         <v>428</v>
       </c>
@@ -14480,7 +14998,7 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="433" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="433" spans="2:6">
       <c r="B433">
         <v>429</v>
       </c>
@@ -14498,7 +15016,7 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="434" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="434" spans="2:6">
       <c r="B434">
         <v>430</v>
       </c>
@@ -14516,7 +15034,7 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="435" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="435" spans="2:6">
       <c r="B435">
         <v>431</v>
       </c>
@@ -14533,7 +15051,7 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="436" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="436" spans="2:6">
       <c r="B436">
         <v>432</v>
       </c>
@@ -14551,7 +15069,7 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="437" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="437" spans="2:6">
       <c r="B437">
         <v>433</v>
       </c>
@@ -14568,7 +15086,7 @@
         <v>46169</v>
       </c>
     </row>
-    <row r="438" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="438" spans="2:6">
       <c r="B438">
         <v>434</v>
       </c>
@@ -14585,7 +15103,7 @@
         <v>46169</v>
       </c>
     </row>
-    <row r="439" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="439" spans="2:6">
       <c r="B439">
         <v>435</v>
       </c>
@@ -14602,7 +15120,7 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="440" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="440" spans="2:6">
       <c r="B440">
         <v>436</v>
       </c>
@@ -14619,7 +15137,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="441" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="441" spans="2:6">
       <c r="B441">
         <v>437</v>
       </c>
@@ -14636,7 +15154,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="442" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="442" spans="2:6">
       <c r="B442">
         <v>438</v>
       </c>
@@ -14654,7 +15172,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="443" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="443" spans="2:6">
       <c r="B443">
         <v>439</v>
       </c>
@@ -14671,7 +15189,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="444" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="444" spans="2:6">
       <c r="B444">
         <v>440</v>
       </c>
@@ -14688,7 +15206,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="445" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="445" spans="2:6">
       <c r="B445">
         <v>441</v>
       </c>
@@ -14705,7 +15223,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="446" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="446" spans="2:6">
       <c r="B446">
         <v>442</v>
       </c>
@@ -14723,7 +15241,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="447" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="447" spans="2:6">
       <c r="B447">
         <v>443</v>
       </c>
@@ -14741,7 +15259,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="448" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="448" spans="2:6">
       <c r="B448">
         <v>444</v>
       </c>
@@ -14756,7 +15274,7 @@
       </c>
       <c r="F448" s="9"/>
     </row>
-    <row r="449" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="449" spans="2:6">
       <c r="B449">
         <v>445</v>
       </c>
@@ -14773,7 +15291,7 @@
         <v>46178</v>
       </c>
     </row>
-    <row r="450" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="450" spans="2:6">
       <c r="B450">
         <v>446</v>
       </c>
@@ -14790,7 +15308,7 @@
         <v>46181</v>
       </c>
     </row>
-    <row r="451" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="451" spans="2:6">
       <c r="B451">
         <v>447</v>
       </c>
@@ -14807,7 +15325,7 @@
         <v>46182</v>
       </c>
     </row>
-    <row r="452" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="452" spans="2:6">
       <c r="B452">
         <v>448</v>
       </c>
@@ -14824,7 +15342,7 @@
         <v>46189</v>
       </c>
     </row>
-    <row r="453" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="453" spans="2:6">
       <c r="B453">
         <v>449</v>
       </c>
@@ -14841,7 +15359,7 @@
         <v>46189</v>
       </c>
     </row>
-    <row r="454" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="454" spans="2:6">
       <c r="B454">
         <v>450</v>
       </c>
@@ -14858,7 +15376,7 @@
         <v>46189</v>
       </c>
     </row>
-    <row r="455" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="455" spans="2:6">
       <c r="B455">
         <v>451</v>
       </c>
@@ -14875,7 +15393,7 @@
         <v>46189</v>
       </c>
     </row>
-    <row r="456" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="456" spans="2:6">
       <c r="B456">
         <v>452</v>
       </c>
@@ -14892,7 +15410,7 @@
         <v>46189</v>
       </c>
     </row>
-    <row r="457" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="457" spans="2:6">
       <c r="B457">
         <v>453</v>
       </c>
@@ -14909,7 +15427,7 @@
         <v>46189</v>
       </c>
     </row>
-    <row r="458" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="458" spans="2:6">
       <c r="B458">
         <v>454</v>
       </c>
@@ -14926,7 +15444,7 @@
         <v>46189</v>
       </c>
     </row>
-    <row r="459" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="459" spans="2:6">
       <c r="B459">
         <v>455</v>
       </c>
@@ -14943,7 +15461,7 @@
         <v>46194</v>
       </c>
     </row>
-    <row r="460" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="460" spans="2:6">
       <c r="B460">
         <v>456</v>
       </c>
@@ -14960,7 +15478,7 @@
         <v>46194</v>
       </c>
     </row>
-    <row r="461" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="461" spans="2:6">
       <c r="B461">
         <v>457</v>
       </c>
@@ -14977,7 +15495,7 @@
         <v>46194</v>
       </c>
     </row>
-    <row r="462" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="462" spans="2:6">
       <c r="B462">
         <v>458</v>
       </c>
@@ -14994,7 +15512,7 @@
         <v>46197</v>
       </c>
     </row>
-    <row r="463" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="463" spans="2:6">
       <c r="B463">
         <v>459</v>
       </c>
@@ -15011,7 +15529,7 @@
         <v>46197</v>
       </c>
     </row>
-    <row r="464" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="464" spans="2:6">
       <c r="B464">
         <v>460</v>
       </c>
@@ -15028,7 +15546,7 @@
         <v>46197</v>
       </c>
     </row>
-    <row r="465" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="465" spans="2:6">
       <c r="B465">
         <v>461</v>
       </c>
@@ -15045,7 +15563,7 @@
         <v>46198</v>
       </c>
     </row>
-    <row r="466" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="466" spans="2:6">
       <c r="B466">
         <v>462</v>
       </c>
@@ -15062,7 +15580,7 @@
         <v>46208</v>
       </c>
     </row>
-    <row r="467" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="467" spans="2:6">
       <c r="B467">
         <v>463</v>
       </c>
@@ -15079,7 +15597,7 @@
         <v>46208</v>
       </c>
     </row>
-    <row r="468" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="468" spans="2:6">
       <c r="B468">
         <v>464</v>
       </c>
@@ -15096,7 +15614,7 @@
         <v>46208</v>
       </c>
     </row>
-    <row r="469" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="469" spans="2:6">
       <c r="B469">
         <v>465</v>
       </c>
@@ -15113,7 +15631,7 @@
         <v>46208</v>
       </c>
     </row>
-    <row r="470" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="470" spans="2:6">
       <c r="B470">
         <v>466</v>
       </c>
@@ -15130,7 +15648,7 @@
         <v>46208</v>
       </c>
     </row>
-    <row r="471" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="471" spans="2:6">
       <c r="B471">
         <v>467</v>
       </c>
@@ -15147,7 +15665,7 @@
         <v>46208</v>
       </c>
     </row>
-    <row r="472" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="472" spans="2:6">
       <c r="B472">
         <v>468</v>
       </c>
@@ -15164,7 +15682,7 @@
         <v>46210</v>
       </c>
     </row>
-    <row r="473" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="473" spans="2:6">
       <c r="B473">
         <v>469</v>
       </c>
@@ -15181,7 +15699,7 @@
         <v>46210</v>
       </c>
     </row>
-    <row r="474" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="474" spans="2:6">
       <c r="B474">
         <v>470</v>
       </c>
@@ -15198,7 +15716,7 @@
         <v>46210</v>
       </c>
     </row>
-    <row r="475" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="475" spans="2:6">
       <c r="B475">
         <v>471</v>
       </c>
@@ -15216,7 +15734,7 @@
         <v>46210</v>
       </c>
     </row>
-    <row r="476" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="476" spans="2:6">
       <c r="B476">
         <v>472</v>
       </c>
@@ -15233,7 +15751,7 @@
         <v>46210</v>
       </c>
     </row>
-    <row r="477" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="477" spans="2:6">
       <c r="B477">
         <v>473</v>
       </c>
@@ -15250,7 +15768,7 @@
         <v>46210</v>
       </c>
     </row>
-    <row r="478" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="478" spans="2:6">
       <c r="B478">
         <v>474</v>
       </c>
@@ -15267,7 +15785,7 @@
         <v>46210</v>
       </c>
     </row>
-    <row r="479" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="479" spans="2:6">
       <c r="B479">
         <v>475</v>
       </c>
@@ -15284,7 +15802,7 @@
         <v>46210</v>
       </c>
     </row>
-    <row r="480" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="480" spans="2:6">
       <c r="B480">
         <v>476</v>
       </c>
@@ -15302,7 +15820,7 @@
         <v>46210</v>
       </c>
     </row>
-    <row r="481" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="481" spans="2:9">
       <c r="B481">
         <v>477</v>
       </c>
@@ -15319,7 +15837,7 @@
         <v>46210</v>
       </c>
     </row>
-    <row r="482" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="482" spans="2:9">
       <c r="B482">
         <v>478</v>
       </c>
@@ -15336,7 +15854,7 @@
         <v>46210</v>
       </c>
     </row>
-    <row r="483" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="483" spans="2:9">
       <c r="B483">
         <v>479</v>
       </c>
@@ -15353,7 +15871,7 @@
         <v>46196</v>
       </c>
     </row>
-    <row r="484" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="484" spans="2:9">
       <c r="B484">
         <v>480</v>
       </c>
@@ -15370,7 +15888,7 @@
         <v>46214</v>
       </c>
     </row>
-    <row r="485" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="485" spans="2:9">
       <c r="B485">
         <v>481</v>
       </c>
@@ -15387,7 +15905,7 @@
         <v>46214</v>
       </c>
     </row>
-    <row r="486" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="486" spans="2:9">
       <c r="B486">
         <v>482</v>
       </c>
@@ -15404,7 +15922,7 @@
         <v>46214</v>
       </c>
     </row>
-    <row r="487" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="487" spans="2:9">
       <c r="B487">
         <v>483</v>
       </c>
@@ -15421,7 +15939,7 @@
         <v>46214</v>
       </c>
     </row>
-    <row r="488" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="488" spans="2:9">
       <c r="B488">
         <v>484</v>
       </c>
@@ -15438,7 +15956,7 @@
         <v>46214</v>
       </c>
     </row>
-    <row r="489" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="489" spans="2:9">
       <c r="B489">
         <v>485</v>
       </c>
@@ -15455,7 +15973,7 @@
         <v>46214</v>
       </c>
     </row>
-    <row r="490" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="490" spans="2:9">
       <c r="B490">
         <v>486</v>
       </c>
@@ -15472,7 +15990,7 @@
         <v>46214</v>
       </c>
     </row>
-    <row r="491" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="491" spans="2:9">
       <c r="B491">
         <v>487</v>
       </c>
@@ -15496,7 +16014,7 @@
         <v>526302.87</v>
       </c>
     </row>
-    <row r="492" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="492" spans="2:9">
       <c r="B492">
         <v>488</v>
       </c>
@@ -15520,7 +16038,7 @@
         <v>210000</v>
       </c>
     </row>
-    <row r="493" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="493" spans="2:9">
       <c r="B493">
         <v>489</v>
       </c>
@@ -15544,7 +16062,7 @@
         <v>316302.87</v>
       </c>
     </row>
-    <row r="494" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="494" spans="2:9">
       <c r="B494">
         <v>490</v>
       </c>
@@ -15568,7 +16086,7 @@
         <v>0.39900979449342544</v>
       </c>
     </row>
-    <row r="495" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="495" spans="2:9">
       <c r="B495">
         <v>491</v>
       </c>
@@ -15585,7 +16103,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="496" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="496" spans="2:9">
       <c r="B496">
         <v>492</v>
       </c>
@@ -15602,7 +16120,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="497" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="497" spans="2:6">
       <c r="B497">
         <v>493</v>
       </c>
@@ -15619,7 +16137,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="498" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="498" spans="2:6">
       <c r="B498">
         <v>494</v>
       </c>
@@ -15636,7 +16154,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="499" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="499" spans="2:6">
       <c r="B499">
         <v>495</v>
       </c>
@@ -15653,7 +16171,7 @@
         <v>46220</v>
       </c>
     </row>
-    <row r="500" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="500" spans="2:6">
       <c r="B500">
         <v>496</v>
       </c>
@@ -15670,7 +16188,7 @@
         <v>46221</v>
       </c>
     </row>
-    <row r="501" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="501" spans="2:6">
       <c r="B501">
         <v>497</v>
       </c>
@@ -15687,7 +16205,7 @@
         <v>46221</v>
       </c>
     </row>
-    <row r="502" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="502" spans="2:6">
       <c r="B502">
         <v>498</v>
       </c>
@@ -15704,7 +16222,7 @@
         <v>46221</v>
       </c>
     </row>
-    <row r="503" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="503" spans="2:6">
       <c r="B503">
         <v>499</v>
       </c>
@@ -15721,7 +16239,7 @@
         <v>46219</v>
       </c>
     </row>
-    <row r="504" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="504" spans="2:6">
       <c r="B504">
         <v>500</v>
       </c>
@@ -15739,7 +16257,7 @@
         <v>46222</v>
       </c>
     </row>
-    <row r="505" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="505" spans="2:6">
       <c r="B505">
         <v>501</v>
       </c>
@@ -15756,7 +16274,7 @@
         <v>46222</v>
       </c>
     </row>
-    <row r="506" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="506" spans="2:6">
       <c r="B506">
         <v>502</v>
       </c>
@@ -15773,7 +16291,7 @@
         <v>46222</v>
       </c>
     </row>
-    <row r="507" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="507" spans="2:6">
       <c r="B507">
         <v>503</v>
       </c>
@@ -15790,7 +16308,7 @@
         <v>46222</v>
       </c>
     </row>
-    <row r="508" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="508" spans="2:6">
       <c r="B508">
         <v>504</v>
       </c>
@@ -15807,7 +16325,7 @@
         <v>46222</v>
       </c>
     </row>
-    <row r="509" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="509" spans="2:6">
       <c r="B509">
         <v>505</v>
       </c>
@@ -15824,7 +16342,7 @@
         <v>46225</v>
       </c>
     </row>
-    <row r="510" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="510" spans="2:6">
       <c r="B510">
         <v>506</v>
       </c>
@@ -15841,7 +16359,7 @@
         <v>46226</v>
       </c>
     </row>
-    <row r="511" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="511" spans="2:6">
       <c r="B511">
         <v>507</v>
       </c>
@@ -15858,7 +16376,7 @@
         <v>46228</v>
       </c>
     </row>
-    <row r="512" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="512" spans="2:6">
       <c r="B512">
         <v>508</v>
       </c>
@@ -15875,7 +16393,7 @@
         <v>46228</v>
       </c>
     </row>
-    <row r="513" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="513" spans="2:6">
       <c r="B513">
         <v>509</v>
       </c>
@@ -15892,7 +16410,7 @@
         <v>46243</v>
       </c>
     </row>
-    <row r="514" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="514" spans="2:6">
       <c r="B514">
         <v>510</v>
       </c>
@@ -15909,7 +16427,7 @@
         <v>46225</v>
       </c>
     </row>
-    <row r="515" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="515" spans="2:6">
       <c r="B515">
         <v>511</v>
       </c>
@@ -15926,7 +16444,7 @@
         <v>46228</v>
       </c>
     </row>
-    <row r="516" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="516" spans="2:6">
       <c r="B516">
         <v>512</v>
       </c>
@@ -15943,7 +16461,7 @@
         <v>46230</v>
       </c>
     </row>
-    <row r="517" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="517" spans="2:6">
       <c r="B517">
         <v>513</v>
       </c>
@@ -15960,7 +16478,7 @@
         <v>46230</v>
       </c>
     </row>
-    <row r="518" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="518" spans="2:6">
       <c r="B518">
         <v>514</v>
       </c>
@@ -15977,7 +16495,7 @@
         <v>46230</v>
       </c>
     </row>
-    <row r="519" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="519" spans="2:6">
       <c r="B519">
         <v>515</v>
       </c>
@@ -15994,7 +16512,7 @@
         <v>46230</v>
       </c>
     </row>
-    <row r="520" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="520" spans="2:6">
       <c r="B520">
         <v>516</v>
       </c>
@@ -16011,7 +16529,7 @@
         <v>46230</v>
       </c>
     </row>
-    <row r="521" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="521" spans="2:6">
       <c r="B521">
         <v>517</v>
       </c>
@@ -16028,7 +16546,7 @@
         <v>46230</v>
       </c>
     </row>
-    <row r="522" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="522" spans="2:6">
       <c r="B522">
         <v>518</v>
       </c>
@@ -16046,7 +16564,7 @@
         <v>46234</v>
       </c>
     </row>
-    <row r="523" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="523" spans="2:6">
       <c r="B523">
         <v>519</v>
       </c>
@@ -16064,7 +16582,7 @@
         <v>46234</v>
       </c>
     </row>
-    <row r="524" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="524" spans="2:6">
       <c r="B524">
         <v>520</v>
       </c>
@@ -16081,7 +16599,7 @@
         <v>46234</v>
       </c>
     </row>
-    <row r="525" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="525" spans="2:6">
       <c r="B525">
         <v>521</v>
       </c>
@@ -16098,7 +16616,7 @@
         <v>46234</v>
       </c>
     </row>
-    <row r="526" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="526" spans="2:6">
       <c r="B526">
         <v>522</v>
       </c>
@@ -16116,7 +16634,7 @@
         <v>46234</v>
       </c>
     </row>
-    <row r="527" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="527" spans="2:6">
       <c r="B527">
         <v>523</v>
       </c>
@@ -16134,7 +16652,7 @@
         <v>46234</v>
       </c>
     </row>
-    <row r="528" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="528" spans="2:6">
       <c r="B528">
         <v>524</v>
       </c>
@@ -16152,7 +16670,7 @@
         <v>46234</v>
       </c>
     </row>
-    <row r="529" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="529" spans="2:6">
       <c r="B529">
         <v>525</v>
       </c>
@@ -16169,7 +16687,7 @@
         <v>46234</v>
       </c>
     </row>
-    <row r="530" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="530" spans="2:6">
       <c r="B530">
         <v>526</v>
       </c>
@@ -16187,7 +16705,7 @@
         <v>46237</v>
       </c>
     </row>
-    <row r="531" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="531" spans="2:6">
       <c r="B531">
         <v>527</v>
       </c>
@@ -16205,7 +16723,7 @@
         <v>46237</v>
       </c>
     </row>
-    <row r="532" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="532" spans="2:6">
       <c r="B532">
         <v>528</v>
       </c>
@@ -16222,7 +16740,7 @@
         <v>46237</v>
       </c>
     </row>
-    <row r="533" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="533" spans="2:6">
       <c r="B533">
         <v>529</v>
       </c>
@@ -16239,7 +16757,7 @@
         <v>46239</v>
       </c>
     </row>
-    <row r="534" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="534" spans="2:6">
       <c r="B534">
         <v>530</v>
       </c>
@@ -16256,7 +16774,7 @@
         <v>46239</v>
       </c>
     </row>
-    <row r="535" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="535" spans="2:6">
       <c r="B535">
         <v>531</v>
       </c>
@@ -16274,7 +16792,7 @@
         <v>46240</v>
       </c>
     </row>
-    <row r="536" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="536" spans="2:6">
       <c r="B536">
         <v>532</v>
       </c>
@@ -16292,7 +16810,7 @@
         <v>46240</v>
       </c>
     </row>
-    <row r="537" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="537" spans="2:6">
       <c r="B537">
         <v>533</v>
       </c>
@@ -16310,7 +16828,7 @@
         <v>46240</v>
       </c>
     </row>
-    <row r="538" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="538" spans="2:6">
       <c r="B538">
         <v>534</v>
       </c>
@@ -16327,7 +16845,7 @@
         <v>46240</v>
       </c>
     </row>
-    <row r="539" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="539" spans="2:6">
       <c r="B539">
         <v>535</v>
       </c>
@@ -16344,7 +16862,7 @@
         <v>46242</v>
       </c>
     </row>
-    <row r="540" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="540" spans="2:6">
       <c r="B540">
         <v>536</v>
       </c>
@@ -16362,7 +16880,7 @@
         <v>46242</v>
       </c>
     </row>
-    <row r="541" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="541" spans="2:6">
       <c r="B541">
         <v>537</v>
       </c>
@@ -16379,7 +16897,7 @@
         <v>46242</v>
       </c>
     </row>
-    <row r="542" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="542" spans="2:6">
       <c r="B542">
         <v>538</v>
       </c>
@@ -16396,7 +16914,7 @@
         <v>46235</v>
       </c>
     </row>
-    <row r="543" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="543" spans="2:6">
       <c r="B543">
         <v>539</v>
       </c>
@@ -16413,7 +16931,7 @@
         <v>46235</v>
       </c>
     </row>
-    <row r="544" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="544" spans="2:6">
       <c r="B544">
         <v>540</v>
       </c>
@@ -16430,7 +16948,7 @@
         <v>46228</v>
       </c>
     </row>
-    <row r="545" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="545" spans="2:6">
       <c r="B545">
         <v>541</v>
       </c>
@@ -16448,7 +16966,7 @@
         <v>46228</v>
       </c>
     </row>
-    <row r="546" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="546" spans="2:6">
       <c r="B546">
         <v>542</v>
       </c>
@@ -16465,7 +16983,7 @@
         <v>46243</v>
       </c>
     </row>
-    <row r="547" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="547" spans="2:6">
       <c r="B547">
         <v>543</v>
       </c>
@@ -16483,7 +17001,7 @@
         <v>46243</v>
       </c>
     </row>
-    <row r="548" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="548" spans="2:6">
       <c r="B548">
         <v>544</v>
       </c>
@@ -16501,7 +17019,7 @@
         <v>46243</v>
       </c>
     </row>
-    <row r="549" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="549" spans="2:6">
       <c r="B549">
         <v>545</v>
       </c>
@@ -16518,7 +17036,7 @@
         <v>46244</v>
       </c>
     </row>
-    <row r="550" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="550" spans="2:6">
       <c r="B550">
         <v>546</v>
       </c>
@@ -16535,7 +17053,7 @@
         <v>46244</v>
       </c>
     </row>
-    <row r="551" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="551" spans="2:6">
       <c r="B551">
         <v>547</v>
       </c>
@@ -16552,7 +17070,7 @@
         <v>46246</v>
       </c>
     </row>
-    <row r="552" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="552" spans="2:6">
       <c r="B552">
         <v>548</v>
       </c>
@@ -16569,7 +17087,7 @@
         <v>46246</v>
       </c>
     </row>
-    <row r="553" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="553" spans="2:6">
       <c r="B553">
         <v>549</v>
       </c>
@@ -16586,7 +17104,7 @@
         <v>46246</v>
       </c>
     </row>
-    <row r="554" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="554" spans="2:6">
       <c r="B554">
         <v>550</v>
       </c>
@@ -16603,7 +17121,7 @@
         <v>46247</v>
       </c>
     </row>
-    <row r="555" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="555" spans="2:6">
       <c r="B555">
         <v>551</v>
       </c>
@@ -16621,7 +17139,7 @@
         <v>46247</v>
       </c>
     </row>
-    <row r="556" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="556" spans="2:6">
       <c r="B556">
         <v>552</v>
       </c>
@@ -16638,7 +17156,7 @@
         <v>46255</v>
       </c>
     </row>
-    <row r="557" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="557" spans="2:6">
       <c r="B557">
         <v>553</v>
       </c>
@@ -16655,7 +17173,7 @@
         <v>46267</v>
       </c>
     </row>
-    <row r="558" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="558" spans="2:6">
       <c r="B558">
         <v>554</v>
       </c>
@@ -16672,7 +17190,7 @@
         <v>46267</v>
       </c>
     </row>
-    <row r="559" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="559" spans="2:6">
       <c r="C559" t="s">
         <v>946</v>
       </c>
@@ -16686,7 +17204,7 @@
         <v>46267</v>
       </c>
     </row>
-    <row r="560" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="560" spans="2:6">
       <c r="C560" t="s">
         <v>947</v>
       </c>
@@ -16700,7 +17218,7 @@
         <v>46267</v>
       </c>
     </row>
-    <row r="561" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="561" spans="3:6">
       <c r="C561" t="s">
         <v>948</v>
       </c>
@@ -16714,39 +17232,39 @@
         <v>46267</v>
       </c>
     </row>
-    <row r="562" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="562" spans="3:6">
       <c r="D562" s="7"/>
       <c r="F562" s="9"/>
     </row>
-    <row r="563" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="563" spans="3:6">
       <c r="D563" s="7"/>
       <c r="F563" s="9"/>
     </row>
-    <row r="564" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="564" spans="3:6">
       <c r="D564" s="7"/>
       <c r="F564" s="9"/>
     </row>
-    <row r="565" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="565" spans="3:6">
       <c r="D565" s="7"/>
       <c r="F565" s="9"/>
     </row>
-    <row r="566" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="566" spans="3:6">
       <c r="D566" s="7"/>
       <c r="F566" s="9"/>
     </row>
-    <row r="567" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="567" spans="3:6">
       <c r="D567" s="7"/>
       <c r="F567" s="9"/>
     </row>
-    <row r="568" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="568" spans="3:6">
       <c r="D568" s="7"/>
       <c r="F568" s="9"/>
     </row>
-    <row r="569" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="569" spans="3:6">
       <c r="D569" s="7"/>
       <c r="F569" s="9"/>
     </row>
-    <row r="570" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="570" spans="3:6">
       <c r="D570" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
         <v>6362509.9900000012</v>
@@ -16773,17 +17291,25 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:F13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:L21"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="40.140625" customWidth="1"/>
     <col min="3" max="3" width="13.85546875" customWidth="1"/>
     <col min="4" max="4" width="39.5703125" customWidth="1"/>
     <col min="5" max="5" width="13.42578125" customWidth="1"/>
     <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="10" max="10" width="64.5703125" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" customWidth="1"/>
+    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:12">
+      <c r="J2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12">
       <c r="B3" t="s">
         <v>343</v>
       </c>
@@ -16796,8 +17322,20 @@
       <c r="E3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="I3" t="s">
+        <v>949</v>
+      </c>
+      <c r="J3" t="s">
+        <v>951</v>
+      </c>
+      <c r="K3" t="s">
+        <v>703</v>
+      </c>
+      <c r="L3" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12">
       <c r="B4" t="s">
         <v>902</v>
       </c>
@@ -16808,8 +17346,20 @@
         <f t="shared" ref="D4:D12" si="0">C4*2</f>
         <v>2321.04</v>
       </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4" s="61" t="s">
+        <v>952</v>
+      </c>
+      <c r="K4" t="s">
+        <v>953</v>
+      </c>
+      <c r="L4" s="62">
+        <v>25800</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12">
       <c r="B5" t="s">
         <v>904</v>
       </c>
@@ -16820,8 +17370,20 @@
         <f t="shared" si="0"/>
         <v>1360</v>
       </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5" s="61" t="s">
+        <v>954</v>
+      </c>
+      <c r="K5" t="s">
+        <v>955</v>
+      </c>
+      <c r="L5" s="62">
+        <v>9490</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12">
       <c r="B6" t="s">
         <v>905</v>
       </c>
@@ -16832,8 +17394,20 @@
         <f t="shared" si="0"/>
         <v>2375</v>
       </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6" s="61" t="s">
+        <v>956</v>
+      </c>
+      <c r="K6" t="s">
+        <v>955</v>
+      </c>
+      <c r="L6" s="62">
+        <v>13990</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12">
       <c r="B7" t="s">
         <v>906</v>
       </c>
@@ -16844,8 +17418,15 @@
         <f t="shared" si="0"/>
         <v>1443.3</v>
       </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="I7" t="s">
+        <v>957</v>
+      </c>
+      <c r="L7" s="62">
+        <f>SUM(L4:L6)</f>
+        <v>49280</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12">
       <c r="B8" t="s">
         <v>907</v>
       </c>
@@ -16856,8 +17437,9 @@
         <f t="shared" si="0"/>
         <v>767.32</v>
       </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="L8" s="62"/>
+    </row>
+    <row r="9" spans="2:12">
       <c r="B9" t="s">
         <v>908</v>
       </c>
@@ -16868,8 +17450,11 @@
         <f t="shared" si="0"/>
         <v>2737.94</v>
       </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="J9" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12">
       <c r="B10" t="s">
         <v>909</v>
       </c>
@@ -16880,8 +17465,20 @@
         <f t="shared" si="0"/>
         <v>2623.72</v>
       </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="I10" t="s">
+        <v>949</v>
+      </c>
+      <c r="J10" t="s">
+        <v>951</v>
+      </c>
+      <c r="K10" t="s">
+        <v>703</v>
+      </c>
+      <c r="L10" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12">
       <c r="B11" t="s">
         <v>910</v>
       </c>
@@ -16892,8 +17489,20 @@
         <f t="shared" si="0"/>
         <v>2233.7399999999998</v>
       </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11" s="63" t="s">
+        <v>959</v>
+      </c>
+      <c r="K11" t="s">
+        <v>955</v>
+      </c>
+      <c r="L11" s="62">
+        <v>7290</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12">
       <c r="B12" t="s">
         <v>911</v>
       </c>
@@ -16904,8 +17513,17 @@
         <f t="shared" si="0"/>
         <v>2955.26</v>
       </c>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="J12" s="63" t="s">
+        <v>958</v>
+      </c>
+      <c r="K12" t="s">
+        <v>955</v>
+      </c>
+      <c r="L12" s="62">
+        <v>7590</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12">
       <c r="B13" t="s">
         <v>550</v>
       </c>
@@ -16920,16 +17538,101 @@
         <f>D13/100</f>
         <v>188.17320000000001</v>
       </c>
+      <c r="J13" s="63" t="s">
+        <v>960</v>
+      </c>
+      <c r="K13" t="s">
+        <v>955</v>
+      </c>
+      <c r="L13" s="62">
+        <v>11190</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="25.5">
+      <c r="J14" s="63" t="s">
+        <v>961</v>
+      </c>
+      <c r="K14" t="s">
+        <v>955</v>
+      </c>
+      <c r="L14" s="62">
+        <v>11590</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12">
+      <c r="L15" s="62"/>
+    </row>
+    <row r="16" spans="2:12">
+      <c r="J16" t="s">
+        <v>497</v>
+      </c>
+      <c r="L16" s="62"/>
+    </row>
+    <row r="17" spans="9:12">
+      <c r="I17" t="s">
+        <v>949</v>
+      </c>
+      <c r="J17" t="s">
+        <v>951</v>
+      </c>
+      <c r="K17" t="s">
+        <v>703</v>
+      </c>
+      <c r="L17" s="62" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="18" spans="9:12">
+      <c r="J18" s="64" t="s">
+        <v>962</v>
+      </c>
+      <c r="K18" t="s">
+        <v>955</v>
+      </c>
+      <c r="L18" s="62">
+        <v>11248</v>
+      </c>
+    </row>
+    <row r="19" spans="9:12">
+      <c r="J19" s="64" t="s">
+        <v>963</v>
+      </c>
+      <c r="K19" t="s">
+        <v>955</v>
+      </c>
+      <c r="L19" s="62">
+        <v>7626</v>
+      </c>
+    </row>
+    <row r="20" spans="9:12">
+      <c r="L20" s="62"/>
+    </row>
+    <row r="21" spans="9:12">
+      <c r="L21" s="62"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="2">
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:M13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="21.28515625" customWidth="1"/>
     <col min="3" max="3" width="18.85546875" customWidth="1"/>
@@ -16942,7 +17645,7 @@
     <col min="13" max="13" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13">
       <c r="B2" t="s">
         <v>858</v>
       </c>
@@ -16971,7 +17674,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:13">
       <c r="B3" t="s">
         <v>859</v>
       </c>
@@ -17003,7 +17706,7 @@
         <v>2.718</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:13">
       <c r="B4" t="s">
         <v>860</v>
       </c>
@@ -17022,7 +17725,7 @@
         <v>34.954999999999998</v>
       </c>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:13">
       <c r="B5" t="s">
         <v>861</v>
       </c>
@@ -17043,7 +17746,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:13">
       <c r="B6" t="s">
         <v>862</v>
       </c>
@@ -17074,7 +17777,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:13">
       <c r="B7" t="s">
         <v>18</v>
       </c>
@@ -17097,7 +17800,7 @@
         <v>4.2839999999999998</v>
       </c>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:13">
       <c r="K9" t="s">
         <v>872</v>
       </c>
@@ -17108,7 +17811,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:13">
       <c r="K10">
         <v>1.51</v>
       </c>
@@ -17120,7 +17823,7 @@
         <v>1.359</v>
       </c>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:13">
       <c r="K12" t="s">
         <v>873</v>
       </c>
@@ -17131,7 +17834,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:13">
       <c r="K13">
         <v>2.1</v>
       </c>
@@ -17151,15 +17854,15 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:D18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:4">
       <c r="B3" t="s">
         <v>343</v>
       </c>
@@ -17167,7 +17870,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:4">
       <c r="B4" t="s">
         <v>445</v>
       </c>
@@ -17175,7 +17878,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:4">
       <c r="B5" t="s">
         <v>446</v>
       </c>
@@ -17183,7 +17886,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4">
       <c r="B6" t="s">
         <v>447</v>
       </c>
@@ -17191,7 +17894,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:4">
       <c r="B7" t="s">
         <v>449</v>
       </c>
@@ -17199,7 +17902,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:4">
       <c r="B8" t="s">
         <v>450</v>
       </c>
@@ -17207,7 +17910,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4">
       <c r="B9" t="s">
         <v>451</v>
       </c>
@@ -17215,7 +17918,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:4">
       <c r="B10" t="s">
         <v>452</v>
       </c>
@@ -17223,7 +17926,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:4">
       <c r="B11" t="s">
         <v>453</v>
       </c>
@@ -17231,7 +17934,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:4">
       <c r="B12" t="s">
         <v>454</v>
       </c>
@@ -17239,7 +17942,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:4">
       <c r="B13" t="s">
         <v>455</v>
       </c>
@@ -17247,7 +17950,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:4">
       <c r="B14" t="s">
         <v>456</v>
       </c>
@@ -17255,7 +17958,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:4">
       <c r="B15" t="s">
         <v>457</v>
       </c>
@@ -17263,7 +17966,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:4">
       <c r="B16" s="35" t="s">
         <v>18</v>
       </c>
@@ -17275,108 +17978,9 @@
         <v>448</v>
       </c>
     </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:3">
       <c r="C18" s="11">
         <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C3:L15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="3" width="21.28515625" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" customWidth="1"/>
-    <col min="9" max="9" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C3" s="11" t="s">
-        <v>458</v>
-      </c>
-      <c r="D3" t="s">
-        <v>460</v>
-      </c>
-      <c r="E3" t="s">
-        <v>459</v>
-      </c>
-      <c r="G3">
-        <v>11</v>
-      </c>
-      <c r="I3">
-        <f>200 *100*6000</f>
-        <v>120000000</v>
-      </c>
-      <c r="J3" t="s">
-        <v>463</v>
-      </c>
-      <c r="K3">
-        <v>0.12</v>
-      </c>
-      <c r="L3" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="4" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="G4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="G5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="G6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="G7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="G8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="G9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="F10" t="s">
-        <v>461</v>
-      </c>
-      <c r="G10">
-        <f>SUM(G3:G9)</f>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="G14">
-        <v>55</v>
-      </c>
-      <c r="H14">
-        <f>G14*K3</f>
-        <v>6.6</v>
-      </c>
-      <c r="I14" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="15" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="G15" s="23" t="s">
-        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -17387,8 +17991,107 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="C3:L15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="3" width="21.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:12">
+      <c r="C3" s="11" t="s">
+        <v>458</v>
+      </c>
+      <c r="D3" t="s">
+        <v>460</v>
+      </c>
+      <c r="E3" t="s">
+        <v>459</v>
+      </c>
+      <c r="G3">
+        <v>11</v>
+      </c>
+      <c r="I3">
+        <f>200 *100*6000</f>
+        <v>120000000</v>
+      </c>
+      <c r="J3" t="s">
+        <v>463</v>
+      </c>
+      <c r="K3">
+        <v>0.12</v>
+      </c>
+      <c r="L3" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4" spans="3:12">
+      <c r="G4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="3:12">
+      <c r="G5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="3:12">
+      <c r="G6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="3:12">
+      <c r="G7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="3:12">
+      <c r="G8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="3:12">
+      <c r="G9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="3:12">
+      <c r="F10" t="s">
+        <v>461</v>
+      </c>
+      <c r="G10">
+        <f>SUM(G3:G9)</f>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="3:12">
+      <c r="G14">
+        <v>55</v>
+      </c>
+      <c r="H14">
+        <f>G14*K3</f>
+        <v>6.6</v>
+      </c>
+      <c r="I14" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="15" spans="3:12">
+      <c r="G15" s="23" t="s">
+        <v>462</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A3:F28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
     <col min="2" max="2" width="40.7109375" customWidth="1"/>
@@ -17398,12 +18101,12 @@
     <col min="6" max="6" width="104.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="21">
       <c r="B3" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -17423,7 +18126,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>1</v>
       </c>
@@ -17444,7 +18147,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>2</v>
       </c>
@@ -17465,7 +18168,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>3</v>
       </c>
@@ -17486,7 +18189,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>4</v>
       </c>
@@ -17507,7 +18210,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>5</v>
       </c>
@@ -17528,7 +18231,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>6</v>
       </c>
@@ -17547,7 +18250,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>7</v>
       </c>
@@ -17563,7 +18266,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>8</v>
       </c>
@@ -17576,7 +18279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>9</v>
       </c>
@@ -17589,7 +18292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>10</v>
       </c>
@@ -17602,7 +18305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>11</v>
       </c>
@@ -17615,7 +18318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>12</v>
       </c>
@@ -17628,7 +18331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>13</v>
       </c>
@@ -17641,7 +18344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6">
       <c r="A18">
         <v>14</v>
       </c>
@@ -17654,7 +18357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>15</v>
       </c>
@@ -17667,7 +18370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6">
       <c r="A20">
         <v>16</v>
       </c>
@@ -17683,7 +18386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>17</v>
       </c>
@@ -17699,7 +18402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6">
       <c r="A22">
         <v>18</v>
       </c>
@@ -17712,7 +18415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6">
       <c r="A23">
         <v>19</v>
       </c>
@@ -17725,7 +18428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6">
       <c r="A24">
         <v>20</v>
       </c>
@@ -17738,7 +18441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6">
       <c r="A25">
         <v>21</v>
       </c>
@@ -17751,21 +18454,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6">
       <c r="D26" s="3"/>
       <c r="E26" s="3">
         <f>Таблица2[[#This Row],[Цена  (м3 или штук)]]*Таблица2[[#This Row],[Количество (М3/шт)]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6">
       <c r="D27" s="3"/>
       <c r="E27" s="3">
         <f>Таблица2[[#This Row],[Цена  (м3 или штук)]]*Таблица2[[#This Row],[Количество (М3/шт)]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6">
       <c r="A28" s="4" t="s">
         <v>18</v>
       </c>
@@ -17790,10 +18493,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:D9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="35" customWidth="1"/>
@@ -17804,12 +18507,12 @@
     <col min="7" max="7" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:4">
       <c r="B1" s="35" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:4">
       <c r="B2" t="s">
         <v>343</v>
       </c>
@@ -17820,7 +18523,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:4">
       <c r="B3" t="s">
         <v>352</v>
       </c>
@@ -17831,7 +18534,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:4">
       <c r="B4" t="s">
         <v>355</v>
       </c>
@@ -17842,7 +18545,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:4">
       <c r="B5" t="s">
         <v>356</v>
       </c>
@@ -17853,7 +18556,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4">
       <c r="B6" t="s">
         <v>353</v>
       </c>
@@ -17861,7 +18564,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:4">
       <c r="B7" t="s">
         <v>354</v>
       </c>
@@ -17869,7 +18572,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:4">
       <c r="B8" s="11" t="s">
         <v>357</v>
       </c>
@@ -17882,7 +18585,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4">
       <c r="B9" t="s">
         <v>359</v>
       </c>
@@ -17902,351 +18605,4 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="23.42578125" customWidth="1"/>
-    <col min="2" max="2" width="20.140625" customWidth="1"/>
-    <col min="3" max="3" width="75" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" customWidth="1"/>
-    <col min="5" max="5" width="28" customWidth="1"/>
-    <col min="6" max="6" width="20.28515625" customWidth="1"/>
-    <col min="7" max="7" width="59.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>309</v>
-      </c>
-      <c r="C1" s="11"/>
-      <c r="E1" s="11" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="11" t="s">
-        <v>266</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>267</v>
-      </c>
-      <c r="B3" t="s">
-        <v>268</v>
-      </c>
-      <c r="C3" t="s">
-        <v>269</v>
-      </c>
-      <c r="E3" t="s">
-        <v>267</v>
-      </c>
-      <c r="F3" t="s">
-        <v>268</v>
-      </c>
-      <c r="G3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>308</v>
-      </c>
-      <c r="B4" s="23">
-        <v>300</v>
-      </c>
-      <c r="C4" t="s">
-        <v>270</v>
-      </c>
-      <c r="E4" t="s">
-        <v>308</v>
-      </c>
-      <c r="F4" s="23">
-        <v>375</v>
-      </c>
-      <c r="G4" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>318</v>
-      </c>
-      <c r="B5" s="23">
-        <v>1500</v>
-      </c>
-      <c r="C5" t="s">
-        <v>322</v>
-      </c>
-      <c r="E5" t="s">
-        <v>312</v>
-      </c>
-      <c r="F5" s="23">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>319</v>
-      </c>
-      <c r="B6" s="23">
-        <v>2125</v>
-      </c>
-      <c r="C6" t="s">
-        <v>324</v>
-      </c>
-      <c r="E6" t="s">
-        <v>313</v>
-      </c>
-      <c r="F6" s="23">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>320</v>
-      </c>
-      <c r="B7" s="23">
-        <v>3100</v>
-      </c>
-      <c r="C7" t="s">
-        <v>323</v>
-      </c>
-      <c r="E7" t="s">
-        <v>314</v>
-      </c>
-      <c r="F7" s="23">
-        <v>3100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>321</v>
-      </c>
-      <c r="B8" s="23">
-        <v>4525</v>
-      </c>
-      <c r="C8" t="s">
-        <v>325</v>
-      </c>
-      <c r="E8" t="s">
-        <v>315</v>
-      </c>
-      <c r="F8" s="23">
-        <v>4450</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>308</v>
-      </c>
-      <c r="B9" s="23">
-        <v>300</v>
-      </c>
-      <c r="E9" t="s">
-        <v>316</v>
-      </c>
-      <c r="F9" s="23">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
-        <v>317</v>
-      </c>
-      <c r="B10" s="24">
-        <f>SUM(B4:B9)</f>
-        <v>11850</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>317</v>
-      </c>
-      <c r="F10" s="24">
-        <f>SUM(F4:F9)</f>
-        <v>11850</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F11" s="23"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C12" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="F12" s="23"/>
-      <c r="G12" s="11" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F13" s="23"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="11" t="s">
-        <v>327</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>267</v>
-      </c>
-      <c r="B15" t="s">
-        <v>268</v>
-      </c>
-      <c r="C15" t="s">
-        <v>269</v>
-      </c>
-      <c r="E15" t="s">
-        <v>267</v>
-      </c>
-      <c r="F15" t="s">
-        <v>268</v>
-      </c>
-      <c r="G15" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>308</v>
-      </c>
-      <c r="B16" s="23">
-        <v>300</v>
-      </c>
-      <c r="C16" t="s">
-        <v>270</v>
-      </c>
-      <c r="E16" t="s">
-        <v>308</v>
-      </c>
-      <c r="F16" s="23">
-        <v>375</v>
-      </c>
-      <c r="G16" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
-        <v>328</v>
-      </c>
-      <c r="B17" s="23">
-        <v>3175</v>
-      </c>
-      <c r="C17" t="s">
-        <v>337</v>
-      </c>
-      <c r="E17" s="25" t="s">
-        <v>332</v>
-      </c>
-      <c r="F17" s="23">
-        <v>3100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="25" t="s">
-        <v>329</v>
-      </c>
-      <c r="B18" s="23">
-        <v>1700</v>
-      </c>
-      <c r="E18" s="25" t="s">
-        <v>333</v>
-      </c>
-      <c r="F18" s="23">
-        <v>1700</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="25" t="s">
-        <v>330</v>
-      </c>
-      <c r="B19" s="23">
-        <v>1625</v>
-      </c>
-      <c r="C19" t="s">
-        <v>338</v>
-      </c>
-      <c r="E19" s="25" t="s">
-        <v>334</v>
-      </c>
-      <c r="F19" s="23">
-        <v>1700</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="25" t="s">
-        <v>331</v>
-      </c>
-      <c r="B20" s="23">
-        <v>5900</v>
-      </c>
-      <c r="C20" t="s">
-        <v>339</v>
-      </c>
-      <c r="E20" s="25" t="s">
-        <v>335</v>
-      </c>
-      <c r="F20" s="23">
-        <v>5750</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>308</v>
-      </c>
-      <c r="B21" s="23">
-        <v>300</v>
-      </c>
-      <c r="C21" t="s">
-        <v>270</v>
-      </c>
-      <c r="E21" t="s">
-        <v>316</v>
-      </c>
-      <c r="F21" s="23">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
-        <v>317</v>
-      </c>
-      <c r="B22" s="24">
-        <f>SUM(B16:B21)</f>
-        <v>13000</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>317</v>
-      </c>
-      <c r="F22" s="24">
-        <f>SUM(F16:F21)</f>
-        <v>13000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C25" s="26" t="s">
-        <v>341</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <tableParts count="4">
-    <tablePart r:id="rId2"/>
-    <tablePart r:id="rId3"/>
-    <tablePart r:id="rId4"/>
-    <tablePart r:id="rId5"/>
-  </tableParts>
-</worksheet>
 </file>
--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zip\develop\my_home\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Building\my_home\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25320" windowHeight="8145" firstSheet="2" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25320" windowHeight="8145" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Расчёт колличества бетона " sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
     <sheet name="дерево заказ на 18 апр 2026" sheetId="15" r:id="rId15"/>
     <sheet name="расчёт кол-ва профилей оконных" sheetId="17" r:id="rId16"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -444,7 +444,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="964">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1580" uniqueCount="971">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3869,15 +3869,36 @@
   <si>
     <t>Кабель Партнер-Электро ВВГпнг(A)-LS 3x1.5 100 м ГОСТ цвет черный</t>
   </si>
+  <si>
+    <t>ИП Савельев Электроцентр</t>
+  </si>
+  <si>
+    <t>Кабель ВВГ-пнг(А)-LS 3*1,5 100 метров</t>
+  </si>
+  <si>
+    <t>Кабель ВВГ-пнг(А)-LS 3*2,5 100 метров</t>
+  </si>
+  <si>
+    <t>площадка под стяжку усиленная для прямого монтажа черная 50 шт, промрукав</t>
+  </si>
+  <si>
+    <t>коробка распред 85\85\42 серая 5 шт</t>
+  </si>
+  <si>
+    <t>коробка распред 80\80\40 черн 5 шт</t>
+  </si>
+  <si>
+    <t>хомут 4,0 * 150 черн нейлон морозостойкое упак 100шт</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
-    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
   </numFmts>
   <fonts count="38">
     <font>
@@ -4225,17 +4246,17 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="9" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4249,9 +4270,9 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4289,11 +4310,11 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4338,9 +4359,9 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -4353,6 +4374,143 @@
     <cellStyle name="Процентный" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="41">
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -4423,147 +4581,10 @@
       </font>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -4841,9 +4862,9 @@
   <tableColumns count="5">
     <tableColumn id="1" name="№ п/п"/>
     <tableColumn id="2" name="Наименование "/>
-    <tableColumn id="3" name="Цена (руб)" totalsRowFunction="sum" dataDxfId="40" totalsRowDxfId="11"/>
+    <tableColumn id="3" name="Цена (руб)" totalsRowFunction="sum" dataDxfId="40" totalsRowDxfId="1"/>
     <tableColumn id="4" name="Примечание"/>
-    <tableColumn id="5" name="дата" dataDxfId="39" totalsRowDxfId="10"/>
+    <tableColumn id="5" name="дата" dataDxfId="39" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4890,7 +4911,7 @@
   <autoFilter ref="B4:D15"/>
   <tableColumns count="3">
     <tableColumn id="1" name="назначение"/>
-    <tableColumn id="2" name="количество розеток (шт)" dataDxfId="34"/>
+    <tableColumn id="2" name="количество розеток (шт)" dataDxfId="30"/>
     <tableColumn id="3" name="примечание"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4902,7 +4923,7 @@
   <autoFilter ref="B19:D23"/>
   <tableColumns count="3">
     <tableColumn id="1" name="назначение"/>
-    <tableColumn id="2" name="количество (шт)" dataDxfId="33"/>
+    <tableColumn id="2" name="количество (шт)" dataDxfId="29"/>
     <tableColumn id="3" name="примечание"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4914,7 +4935,7 @@
   <autoFilter ref="B28:D32"/>
   <tableColumns count="3">
     <tableColumn id="1" name="назначение"/>
-    <tableColumn id="2" name="количество (шт)" dataDxfId="32"/>
+    <tableColumn id="2" name="количество (шт)" dataDxfId="28"/>
     <tableColumn id="3" name="примечание"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4926,7 +4947,7 @@
   <autoFilter ref="B36:D40"/>
   <tableColumns count="3">
     <tableColumn id="1" name="назначение"/>
-    <tableColumn id="2" name="количество (шт)" dataDxfId="31"/>
+    <tableColumn id="2" name="количество (шт)" dataDxfId="27"/>
     <tableColumn id="3" name="примечание"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4938,7 +4959,7 @@
   <autoFilter ref="B44:D48"/>
   <tableColumns count="3">
     <tableColumn id="1" name="назначение"/>
-    <tableColumn id="2" name="количество (шт)" dataDxfId="30"/>
+    <tableColumn id="2" name="количество (шт)" dataDxfId="26"/>
     <tableColumn id="3" name="примечание"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4950,7 +4971,7 @@
   <autoFilter ref="B52:D55"/>
   <tableColumns count="3">
     <tableColumn id="1" name="назначение"/>
-    <tableColumn id="2" name="количество (шт)" dataDxfId="29"/>
+    <tableColumn id="2" name="количество (шт)" dataDxfId="25"/>
     <tableColumn id="3" name="примечание"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4962,7 +4983,7 @@
   <autoFilter ref="B59:D68"/>
   <tableColumns count="3">
     <tableColumn id="1" name="назначение"/>
-    <tableColumn id="2" name="количество (шт)" dataDxfId="28"/>
+    <tableColumn id="2" name="количество (шт)" dataDxfId="24"/>
     <tableColumn id="3" name="примечание"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4974,9 +4995,9 @@
   <autoFilter ref="I3:L7"/>
   <tableColumns count="4">
     <tableColumn id="1" name="№"/>
-    <tableColumn id="2" name="наименование" dataDxfId="3"/>
+    <tableColumn id="2" name="наименование" dataDxfId="38"/>
     <tableColumn id="3" name="количество"/>
-    <tableColumn id="4" name="цена" dataDxfId="2" dataCellStyle="Денежный"/>
+    <tableColumn id="4" name="цена" dataDxfId="37" dataCellStyle="Денежный"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4987,7 +5008,7 @@
   <autoFilter ref="B69:D72"/>
   <tableColumns count="3">
     <tableColumn id="1" name="назначение"/>
-    <tableColumn id="2" name="количество (шт)" dataDxfId="27"/>
+    <tableColumn id="2" name="количество (шт)" dataDxfId="23"/>
     <tableColumn id="3" name="примечание"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4999,7 +5020,7 @@
   <autoFilter ref="B4:C17"/>
   <tableColumns count="2">
     <tableColumn id="1" name="Комплектующие\Магазины"/>
-    <tableColumn id="2" name=" Цена в Бауцентр (руб)" dataDxfId="26"/>
+    <tableColumn id="2" name=" Цена в Бауцентр (руб)" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5010,13 +5031,13 @@
   <autoFilter ref="E4:L17"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Комплектующие\Магазины"/>
-    <tableColumn id="2" name=" Legrand" dataDxfId="25"/>
-    <tableColumn id="6" name="Dekraft" dataDxfId="24"/>
-    <tableColumn id="7" name="EKF" dataDxfId="23"/>
-    <tableColumn id="8" name="TDM electric" dataDxfId="22"/>
-    <tableColumn id="9" name="IEK" dataDxfId="21"/>
-    <tableColumn id="10" name="Спец 800вт" dataDxfId="20"/>
-    <tableColumn id="11" name="Столбец1" dataDxfId="19"/>
+    <tableColumn id="2" name=" Legrand" dataDxfId="21"/>
+    <tableColumn id="6" name="Dekraft" dataDxfId="20"/>
+    <tableColumn id="7" name="EKF" dataDxfId="19"/>
+    <tableColumn id="8" name="TDM electric" dataDxfId="18"/>
+    <tableColumn id="9" name="IEK" dataDxfId="17"/>
+    <tableColumn id="10" name="Спец 800вт" dataDxfId="16"/>
+    <tableColumn id="11" name="Столбец1" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5027,13 +5048,13 @@
   <autoFilter ref="E22:L35"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Комплектующие\Магазины"/>
-    <tableColumn id="2" name=" Legrand" dataDxfId="18"/>
-    <tableColumn id="6" name="Dekraft" dataDxfId="17"/>
-    <tableColumn id="7" name="EKF" dataDxfId="16"/>
-    <tableColumn id="8" name="TDM electric" dataDxfId="15"/>
-    <tableColumn id="9" name="IEK" dataDxfId="14"/>
-    <tableColumn id="10" name="Спец 800вт" dataDxfId="13"/>
-    <tableColumn id="11" name="Etimat" dataDxfId="12"/>
+    <tableColumn id="2" name=" Legrand" dataDxfId="14"/>
+    <tableColumn id="6" name="Dekraft" dataDxfId="13"/>
+    <tableColumn id="7" name="EKF" dataDxfId="12"/>
+    <tableColumn id="8" name="TDM electric" dataDxfId="11"/>
+    <tableColumn id="9" name="IEK" dataDxfId="10"/>
+    <tableColumn id="10" name="Спец 800вт" dataDxfId="9"/>
+    <tableColumn id="11" name="Etimat" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5070,9 +5091,9 @@
   <autoFilter ref="I10:L14"/>
   <tableColumns count="4">
     <tableColumn id="1" name="№"/>
-    <tableColumn id="2" name="наименование" dataDxfId="1"/>
+    <tableColumn id="2" name="наименование" dataDxfId="36"/>
     <tableColumn id="3" name="количество"/>
-    <tableColumn id="4" name="цена" dataDxfId="0" dataCellStyle="Денежный"/>
+    <tableColumn id="4" name="цена" dataDxfId="35" dataCellStyle="Денежный"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5085,10 +5106,10 @@
     <tableColumn id="1" name="сторона дома"/>
     <tableColumn id="2" name="ширина (м)"/>
     <tableColumn id="3" name="высота (м)"/>
-    <tableColumn id="4" name="площадь проёмов (м2)" dataDxfId="38">
+    <tableColumn id="4" name="площадь проёмов (м2)" dataDxfId="34">
       <calculatedColumnFormula>M3*2+M7</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" name="площадь утепления (м2)" dataDxfId="37">
+    <tableColumn id="5" name="площадь утепления (м2)" dataDxfId="33">
       <calculatedColumnFormula>Таблица24[[#This Row],[ширина (м)]]*Таблица24[[#This Row],[высота (м)]]-Таблица24[[#This Row],[площадь проёмов (м2)]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" name="примечание"/>
@@ -5101,15 +5122,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Таблица2" displayName="Таблица2" ref="A4:F28" totalsRowCount="1">
   <autoFilter ref="A4:F27"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="№ п/п" totalsRowLabel="Итого:" totalsRowDxfId="9"/>
-    <tableColumn id="2" name="Тип" totalsRowDxfId="8"/>
-    <tableColumn id="3" name="Количество (М3/шт)" totalsRowDxfId="7"/>
-    <tableColumn id="4" name="Цена  (м3 или штук)" dataDxfId="36" totalsRowDxfId="6"/>
-    <tableColumn id="5" name="Сумма" totalsRowFunction="custom" dataDxfId="35" totalsRowDxfId="5">
+    <tableColumn id="1" name="№ п/п" totalsRowLabel="Итого:" totalsRowDxfId="7"/>
+    <tableColumn id="2" name="Тип" totalsRowDxfId="6"/>
+    <tableColumn id="3" name="Количество (М3/шт)" totalsRowDxfId="5"/>
+    <tableColumn id="4" name="Цена  (м3 или штук)" dataDxfId="32" totalsRowDxfId="4"/>
+    <tableColumn id="5" name="Сумма" totalsRowFunction="custom" dataDxfId="31" totalsRowDxfId="3">
       <calculatedColumnFormula>Таблица2[[#This Row],[Цена  (м3 или штук)]]*Таблица2[[#This Row],[Количество (М3/шт)]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(E5:E27)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" name="Примечание" totalsRowDxfId="4"/>
+    <tableColumn id="6" name="Примечание" totalsRowDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -17233,28 +17254,88 @@
       </c>
     </row>
     <row r="562" spans="3:6">
-      <c r="D562" s="7"/>
-      <c r="F562" s="9"/>
+      <c r="C562" t="s">
+        <v>965</v>
+      </c>
+      <c r="D562" s="7">
+        <v>7290</v>
+      </c>
+      <c r="E562" t="s">
+        <v>964</v>
+      </c>
+      <c r="F562" s="9">
+        <v>46272</v>
+      </c>
     </row>
     <row r="563" spans="3:6">
-      <c r="D563" s="7"/>
-      <c r="F563" s="9"/>
+      <c r="C563" t="s">
+        <v>966</v>
+      </c>
+      <c r="D563" s="7">
+        <v>11190</v>
+      </c>
+      <c r="E563" t="s">
+        <v>964</v>
+      </c>
+      <c r="F563" s="9">
+        <v>46272</v>
+      </c>
     </row>
     <row r="564" spans="3:6">
-      <c r="D564" s="7"/>
-      <c r="F564" s="9"/>
+      <c r="C564" t="s">
+        <v>967</v>
+      </c>
+      <c r="D564" s="7">
+        <v>237.65</v>
+      </c>
+      <c r="E564" t="s">
+        <v>964</v>
+      </c>
+      <c r="F564" s="9">
+        <v>46272</v>
+      </c>
     </row>
     <row r="565" spans="3:6">
-      <c r="D565" s="7"/>
-      <c r="F565" s="9"/>
+      <c r="C565" t="s">
+        <v>968</v>
+      </c>
+      <c r="D565" s="7">
+        <v>785.7</v>
+      </c>
+      <c r="E565" t="s">
+        <v>964</v>
+      </c>
+      <c r="F565" s="9">
+        <v>46272</v>
+      </c>
     </row>
     <row r="566" spans="3:6">
-      <c r="D566" s="7"/>
-      <c r="F566" s="9"/>
+      <c r="C566" t="s">
+        <v>969</v>
+      </c>
+      <c r="D566" s="7">
+        <v>669.3</v>
+      </c>
+      <c r="E566" t="s">
+        <v>964</v>
+      </c>
+      <c r="F566" s="9">
+        <v>46272</v>
+      </c>
     </row>
     <row r="567" spans="3:6">
-      <c r="D567" s="7"/>
-      <c r="F567" s="9"/>
+      <c r="C567" t="s">
+        <v>970</v>
+      </c>
+      <c r="D567" s="7">
+        <v>110.58</v>
+      </c>
+      <c r="E567" t="s">
+        <v>964</v>
+      </c>
+      <c r="F567" s="9">
+        <v>46272</v>
+      </c>
     </row>
     <row r="568" spans="3:6">
       <c r="D568" s="7"/>
@@ -17267,7 +17348,7 @@
     <row r="570" spans="3:6">
       <c r="D570" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>6362509.9900000012</v>
+        <v>6382793.2200000016</v>
       </c>
       <c r="F570" s="9"/>
     </row>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -444,7 +444,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1580" uniqueCount="971">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="975">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3889,6 +3889,18 @@
   </si>
   <si>
     <t>хомут 4,0 * 150 черн нейлон морозостойкое упак 100шт</t>
+  </si>
+  <si>
+    <t>труба гофр ПВХ 20 мм серая с зондом IEK 100 метров</t>
+  </si>
+  <si>
+    <t>труба металопластиковая pex-al-pex 16x2.0 valtec 200 метров -бухта</t>
+  </si>
+  <si>
+    <t>колодка клеммная 12 пар (2,5-6,0 мм2) 10А черная iek</t>
+  </si>
+  <si>
+    <t>крепление для ппр труб 16 (10шт упак) 2 упак</t>
   </si>
 </sst>
 </file>
@@ -4857,8 +4869,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F570" totalsRowCount="1">
-  <autoFilter ref="B5:F569"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F582" totalsRowCount="1">
+  <autoFilter ref="B5:F581"/>
   <tableColumns count="5">
     <tableColumn id="1" name="№ п/п"/>
     <tableColumn id="2" name="Наименование "/>
@@ -7799,7 +7811,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:I570"/>
+  <dimension ref="B3:I582"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="94.7109375" customWidth="1"/>
@@ -17338,19 +17350,107 @@
       </c>
     </row>
     <row r="568" spans="3:6">
-      <c r="D568" s="7"/>
-      <c r="F568" s="9"/>
+      <c r="C568" t="s">
+        <v>971</v>
+      </c>
+      <c r="D568" s="7">
+        <v>2786</v>
+      </c>
+      <c r="E568" t="s">
+        <v>964</v>
+      </c>
+      <c r="F568" s="9">
+        <v>46274</v>
+      </c>
     </row>
     <row r="569" spans="3:6">
-      <c r="D569" s="7"/>
-      <c r="F569" s="9"/>
+      <c r="C569" t="s">
+        <v>972</v>
+      </c>
+      <c r="D569" s="7">
+        <v>25800</v>
+      </c>
+      <c r="E569" t="s">
+        <v>885</v>
+      </c>
+      <c r="F569" s="9">
+        <v>46274</v>
+      </c>
     </row>
     <row r="570" spans="3:6">
+      <c r="C570" t="s">
+        <v>973</v>
+      </c>
       <c r="D570" s="7">
+        <v>75</v>
+      </c>
+      <c r="E570" t="s">
+        <v>885</v>
+      </c>
+      <c r="F570" s="9">
+        <v>46274</v>
+      </c>
+    </row>
+    <row r="571" spans="3:6">
+      <c r="C571" t="s">
+        <v>974</v>
+      </c>
+      <c r="D571" s="7">
+        <v>78</v>
+      </c>
+      <c r="E571" t="s">
+        <v>885</v>
+      </c>
+      <c r="F571" s="9">
+        <v>46274</v>
+      </c>
+    </row>
+    <row r="572" spans="3:6">
+      <c r="D572" s="7"/>
+      <c r="F572" s="9"/>
+    </row>
+    <row r="573" spans="3:6">
+      <c r="D573" s="7"/>
+      <c r="F573" s="9"/>
+    </row>
+    <row r="574" spans="3:6">
+      <c r="D574" s="7"/>
+      <c r="F574" s="9"/>
+    </row>
+    <row r="575" spans="3:6">
+      <c r="D575" s="7"/>
+      <c r="F575" s="9"/>
+    </row>
+    <row r="576" spans="3:6">
+      <c r="D576" s="7"/>
+      <c r="F576" s="9"/>
+    </row>
+    <row r="577" spans="4:6">
+      <c r="D577" s="7"/>
+      <c r="F577" s="9"/>
+    </row>
+    <row r="578" spans="4:6">
+      <c r="D578" s="7"/>
+      <c r="F578" s="9"/>
+    </row>
+    <row r="579" spans="4:6">
+      <c r="D579" s="7"/>
+      <c r="F579" s="9"/>
+    </row>
+    <row r="580" spans="4:6">
+      <c r="D580" s="7"/>
+      <c r="F580" s="9"/>
+    </row>
+    <row r="581" spans="4:6">
+      <c r="D581" s="7"/>
+      <c r="F581" s="9"/>
+    </row>
+    <row r="582" spans="4:6">
+      <c r="D582" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>6382793.2200000016</v>
-      </c>
-      <c r="F570" s="9"/>
+        <v>6411532.2200000016</v>
+      </c>
+      <c r="F582" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>
